--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="389">
   <si>
     <t>ZP01</t>
   </si>
@@ -418,7 +418,205 @@
     <t>1100175780</t>
   </si>
   <si>
-    <t>100003408</t>
+    <t>100003410</t>
+  </si>
+  <si>
+    <t>980000022800</t>
+  </si>
+  <si>
+    <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100177770</t>
+  </si>
+  <si>
+    <t>100003412</t>
+  </si>
+  <si>
+    <t>1300000176</t>
+  </si>
+  <si>
+    <t>100003414</t>
+  </si>
+  <si>
+    <t>980000045400</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1100177640</t>
+  </si>
+  <si>
+    <t>100003418</t>
+  </si>
+  <si>
+    <t>1100162420</t>
+  </si>
+  <si>
+    <t>100003423</t>
+  </si>
+  <si>
+    <t>1100178840</t>
+  </si>
+  <si>
+    <t>100003425</t>
+  </si>
+  <si>
+    <t>980000028700</t>
+  </si>
+  <si>
+    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100179510</t>
+  </si>
+  <si>
+    <t>100003436</t>
+  </si>
+  <si>
+    <t>980000036400</t>
+  </si>
+  <si>
+    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
+  </si>
+  <si>
+    <t>4200000001</t>
+  </si>
+  <si>
+    <t>100003437</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>100003438</t>
+  </si>
+  <si>
+    <t>100003439</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100180870</t>
+  </si>
+  <si>
+    <t>100003440</t>
+  </si>
+  <si>
+    <t>100003445</t>
+  </si>
+  <si>
+    <t>1100181240</t>
+  </si>
+  <si>
+    <t>100003446</t>
+  </si>
+  <si>
+    <t>980000022400</t>
+  </si>
+  <si>
+    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100181710</t>
+  </si>
+  <si>
+    <t>100003447</t>
+  </si>
+  <si>
+    <t>1100181640</t>
+  </si>
+  <si>
+    <t>100003448</t>
+  </si>
+  <si>
+    <t>980000017700</t>
+  </si>
+  <si>
+    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100182230</t>
+  </si>
+  <si>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100182240</t>
+  </si>
+  <si>
+    <t>100003450</t>
+  </si>
+  <si>
+    <t>980000018002</t>
+  </si>
+  <si>
+    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100181610</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>980000019200</t>
+  </si>
+  <si>
+    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182450</t>
+  </si>
+  <si>
+    <t>100003453</t>
+  </si>
+  <si>
+    <t>1100182220</t>
+  </si>
+  <si>
+    <t>100003459</t>
+  </si>
+  <si>
+    <t>1100180730</t>
+  </si>
+  <si>
+    <t>100003460</t>
+  </si>
+  <si>
+    <t>980000019400</t>
+  </si>
+  <si>
+    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100175760</t>
+  </si>
+  <si>
+    <t>100003462</t>
+  </si>
+  <si>
+    <t>1100183170</t>
+  </si>
+  <si>
+    <t>100003463</t>
+  </si>
+  <si>
+    <t>100003464</t>
   </si>
   <si>
     <t>980000043500</t>
@@ -427,10 +625,106 @@
     <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
   </si>
   <si>
-    <t>1100177860</t>
-  </si>
-  <si>
-    <t>100003409</t>
+    <t>1100177340</t>
+  </si>
+  <si>
+    <t>100003465</t>
+  </si>
+  <si>
+    <t>980000013700</t>
+  </si>
+  <si>
+    <t>S-Plus 8_X=800, Y=520, Z=550</t>
+  </si>
+  <si>
+    <t>1100177930</t>
+  </si>
+  <si>
+    <t>100003466</t>
+  </si>
+  <si>
+    <t>980000041200</t>
+  </si>
+  <si>
+    <t>S8_X=700, Y=420, Z=510</t>
+  </si>
+  <si>
+    <t>1100181200</t>
+  </si>
+  <si>
+    <t>100003467</t>
+  </si>
+  <si>
+    <t>100003468</t>
+  </si>
+  <si>
+    <t>1100182880</t>
+  </si>
+  <si>
+    <t>100003469</t>
+  </si>
+  <si>
+    <t>1100179090</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1100182820</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>1100172880</t>
+  </si>
+  <si>
+    <t>100003472</t>
+  </si>
+  <si>
+    <t>980000030801</t>
+  </si>
+  <si>
+    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100177910</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>1300000180</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>980000027800</t>
+  </si>
+  <si>
+    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>1100183180</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>1100184110</t>
+  </si>
+  <si>
+    <t>100003478</t>
   </si>
   <si>
     <t>980000000800</t>
@@ -439,324 +733,6 @@
     <t>PRO-1000_X=1000, Y=600, Z=630</t>
   </si>
   <si>
-    <t>1100167080</t>
-  </si>
-  <si>
-    <t>100003410</t>
-  </si>
-  <si>
-    <t>980000022800</t>
-  </si>
-  <si>
-    <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100177770</t>
-  </si>
-  <si>
-    <t>100003412</t>
-  </si>
-  <si>
-    <t>1300000176</t>
-  </si>
-  <si>
-    <t>100003414</t>
-  </si>
-  <si>
-    <t>980000045400</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100177640</t>
-  </si>
-  <si>
-    <t>100003418</t>
-  </si>
-  <si>
-    <t>1100162420</t>
-  </si>
-  <si>
-    <t>100003423</t>
-  </si>
-  <si>
-    <t>1100178840</t>
-  </si>
-  <si>
-    <t>100003425</t>
-  </si>
-  <si>
-    <t>980000028700</t>
-  </si>
-  <si>
-    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100179510</t>
-  </si>
-  <si>
-    <t>100003436</t>
-  </si>
-  <si>
-    <t>980000036400</t>
-  </si>
-  <si>
-    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
-  </si>
-  <si>
-    <t>4200000001</t>
-  </si>
-  <si>
-    <t>100003437</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>100003438</t>
-  </si>
-  <si>
-    <t>100003439</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100180870</t>
-  </si>
-  <si>
-    <t>100003440</t>
-  </si>
-  <si>
-    <t>100003441</t>
-  </si>
-  <si>
-    <t>1100181370</t>
-  </si>
-  <si>
-    <t>100003445</t>
-  </si>
-  <si>
-    <t>1100181240</t>
-  </si>
-  <si>
-    <t>100003446</t>
-  </si>
-  <si>
-    <t>980000022400</t>
-  </si>
-  <si>
-    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100181710</t>
-  </si>
-  <si>
-    <t>100003447</t>
-  </si>
-  <si>
-    <t>1100181640</t>
-  </si>
-  <si>
-    <t>100003448</t>
-  </si>
-  <si>
-    <t>980000017700</t>
-  </si>
-  <si>
-    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100182230</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100182240</t>
-  </si>
-  <si>
-    <t>100003450</t>
-  </si>
-  <si>
-    <t>980000018002</t>
-  </si>
-  <si>
-    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100181610</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>980000019200</t>
-  </si>
-  <si>
-    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182450</t>
-  </si>
-  <si>
-    <t>100003453</t>
-  </si>
-  <si>
-    <t>1100182220</t>
-  </si>
-  <si>
-    <t>100003457</t>
-  </si>
-  <si>
-    <t>1100182020</t>
-  </si>
-  <si>
-    <t>100003459</t>
-  </si>
-  <si>
-    <t>1100180730</t>
-  </si>
-  <si>
-    <t>100003460</t>
-  </si>
-  <si>
-    <t>980000019400</t>
-  </si>
-  <si>
-    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100175760</t>
-  </si>
-  <si>
-    <t>100003462</t>
-  </si>
-  <si>
-    <t>1100183170</t>
-  </si>
-  <si>
-    <t>100003463</t>
-  </si>
-  <si>
-    <t>100003464</t>
-  </si>
-  <si>
-    <t>1100177340</t>
-  </si>
-  <si>
-    <t>100003465</t>
-  </si>
-  <si>
-    <t>980000013700</t>
-  </si>
-  <si>
-    <t>S-Plus 8_X=800, Y=520, Z=550</t>
-  </si>
-  <si>
-    <t>1100177930</t>
-  </si>
-  <si>
-    <t>100003466</t>
-  </si>
-  <si>
-    <t>980000041200</t>
-  </si>
-  <si>
-    <t>S8_X=700, Y=420, Z=510</t>
-  </si>
-  <si>
-    <t>1100181200</t>
-  </si>
-  <si>
-    <t>100003467</t>
-  </si>
-  <si>
-    <t>100003468</t>
-  </si>
-  <si>
-    <t>1100182880</t>
-  </si>
-  <si>
-    <t>100003469</t>
-  </si>
-  <si>
-    <t>1100179090</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1100182820</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>1100172880</t>
-  </si>
-  <si>
-    <t>100003472</t>
-  </si>
-  <si>
-    <t>980000030801</t>
-  </si>
-  <si>
-    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100177910</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>1300000180</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>980000027800</t>
-  </si>
-  <si>
-    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>1100183180</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>1100184110</t>
-  </si>
-  <si>
-    <t>100003478</t>
-  </si>
-  <si>
     <t>1100180510</t>
   </si>
   <si>
@@ -769,6 +745,9 @@
     <t>100003480</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
     <t>1100184470</t>
   </si>
   <si>
@@ -793,9 +772,6 @@
     <t>100003484</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
     <t>1100181160</t>
   </si>
   <si>
@@ -919,90 +895,90 @@
     <t>100003502</t>
   </si>
   <si>
+    <t>1100183140</t>
+  </si>
+  <si>
+    <t>100003503</t>
+  </si>
+  <si>
+    <t>1100184480</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003506</t>
+  </si>
+  <si>
+    <t>1100184300</t>
+  </si>
+  <si>
+    <t>100003507</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003509</t>
+  </si>
+  <si>
+    <t>1100188510</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
+  </si>
+  <si>
+    <t>1100182140</t>
+  </si>
+  <si>
+    <t>100003512</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
     <t>REL  MSPT PRC  RMWB SETC</t>
   </si>
   <si>
-    <t>1100183140</t>
-  </si>
-  <si>
-    <t>100003503</t>
-  </si>
-  <si>
-    <t>1100184480</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003506</t>
-  </si>
-  <si>
-    <t>1100184300</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
-    <t>1100182140</t>
-  </si>
-  <si>
-    <t>100003512</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
     <t>1100188460</t>
   </si>
   <si>
@@ -1129,24 +1105,6 @@
     <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
   </si>
   <si>
-    <t>630000334</t>
-  </si>
-  <si>
-    <t>080200446902</t>
-  </si>
-  <si>
-    <t>5A65E機頭DA15K,032370_BT40,CAWDI</t>
-  </si>
-  <si>
-    <t>630000335</t>
-  </si>
-  <si>
-    <t>080100152306</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
-  </si>
-  <si>
     <t>630000336</t>
   </si>
   <si>
@@ -1154,6 +1112,24 @@
   </si>
   <si>
     <t>D8K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>630000337</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
+  </si>
+  <si>
+    <t>630000338</t>
+  </si>
+  <si>
+    <t>080200254502</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1306,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1329,52 +1305,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2303,7 +2279,7 @@
         <v>45853</v>
       </c>
       <c r="I20" s="3">
-        <v>45947</v>
+        <v>46056</v>
       </c>
       <c r="J20" t="s">
         <v>37</v>
@@ -2606,7 +2582,7 @@
         <v>46135</v>
       </c>
       <c r="J26" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
@@ -3053,7 +3029,7 @@
         <v>45980</v>
       </c>
       <c r="I35" s="3">
-        <v>46098</v>
+        <v>46084</v>
       </c>
       <c r="J35" t="s">
         <v>26</v>
@@ -3147,22 +3123,22 @@
         <v>137</v>
       </c>
       <c r="G37" s="3">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="H37" s="3">
-        <v>45972</v>
+        <v>46017</v>
       </c>
       <c r="I37" s="3">
-        <v>46078</v>
+        <v>46132</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3191,19 +3167,19 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="G38" s="3">
         <v>45943</v>
       </c>
       <c r="H38" s="3">
-        <v>45953</v>
+        <v>46041</v>
       </c>
       <c r="I38" s="3">
-        <v>46002</v>
+        <v>46083</v>
       </c>
       <c r="J38" t="s">
         <v>37</v>
@@ -3221,7 +3197,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3232,46 +3208,46 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" t="s">
         <v>143</v>
       </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="G39" s="3">
+        <v>45944</v>
+      </c>
+      <c r="H39" s="3">
+        <v>45986</v>
+      </c>
+      <c r="I39" s="3">
+        <v>46066</v>
+      </c>
+      <c r="J39" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="3">
+        <v>45944</v>
+      </c>
+      <c r="M39" t="s">
+        <v>6</v>
+      </c>
+      <c r="N39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O39" t="s">
         <v>144</v>
-      </c>
-      <c r="F39" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46017</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46128</v>
-      </c>
-      <c r="J39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K39" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" s="3">
-        <v>45943</v>
-      </c>
-      <c r="M39" t="s">
-        <v>6</v>
-      </c>
-      <c r="N39" t="s">
-        <v>7</v>
-      </c>
-      <c r="O39" t="s">
-        <v>146</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3282,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3291,28 +3267,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G40" s="3">
-        <v>45943</v>
+        <v>45950</v>
       </c>
       <c r="H40" s="3">
-        <v>46076</v>
+        <v>45957</v>
       </c>
       <c r="I40" s="3">
-        <v>46098</v>
+        <v>46136</v>
       </c>
       <c r="J40" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>45943</v>
+        <v>45946</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3321,7 +3297,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3332,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3341,28 +3317,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="G41" s="3">
-        <v>45944</v>
+        <v>45951</v>
       </c>
       <c r="H41" s="3">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="I41" s="3">
-        <v>46066</v>
+        <v>46052</v>
       </c>
       <c r="J41" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>45944</v>
+        <v>45951</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3371,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3382,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3391,28 +3367,28 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="G42" s="3">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="H42" s="3">
-        <v>45957</v>
+        <v>45987</v>
       </c>
       <c r="I42" s="3">
-        <v>46136</v>
+        <v>46066</v>
       </c>
       <c r="J42" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>45946</v>
+        <v>45951</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3421,7 +3397,7 @@
         <v>7</v>
       </c>
       <c r="O42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3432,28 +3408,28 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>154</v>
+      </c>
+      <c r="F43" t="s">
         <v>155</v>
       </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
       <c r="G43" s="3">
-        <v>45951</v>
+        <v>45966</v>
       </c>
       <c r="H43" s="3">
-        <v>46006</v>
+        <v>46064</v>
       </c>
       <c r="I43" s="3">
-        <v>46052</v>
+        <v>46099</v>
       </c>
       <c r="J43" t="s">
         <v>37</v>
@@ -3462,7 +3438,7 @@
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>45951</v>
+        <v>45966</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3497,13 +3473,13 @@
         <v>159</v>
       </c>
       <c r="G44" s="3">
-        <v>45951</v>
+        <v>45966</v>
       </c>
       <c r="H44" s="3">
-        <v>45987</v>
+        <v>46049</v>
       </c>
       <c r="I44" s="3">
-        <v>46066</v>
+        <v>46085</v>
       </c>
       <c r="J44" t="s">
         <v>37</v>
@@ -3512,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>45951</v>
+        <v>45966</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3521,7 +3497,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3532,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3541,10 +3517,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="G45" s="3">
         <v>45966</v>
@@ -3553,7 +3529,7 @@
         <v>46064</v>
       </c>
       <c r="I45" s="3">
-        <v>46099</v>
+        <v>46139</v>
       </c>
       <c r="J45" t="s">
         <v>37</v>
@@ -3571,7 +3547,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3582,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3591,28 +3567,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F46" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G46" s="3">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="H46" s="3">
-        <v>46049</v>
+        <v>46002</v>
       </c>
       <c r="I46" s="3">
-        <v>46085</v>
+        <v>46042</v>
       </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3632,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3641,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="G47" s="3">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="H47" s="3">
-        <v>46064</v>
+        <v>46006</v>
       </c>
       <c r="I47" s="3">
-        <v>46139</v>
+        <v>46044</v>
       </c>
       <c r="J47" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3682,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3691,28 +3667,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G48" s="3">
-        <v>45967</v>
+        <v>45972</v>
       </c>
       <c r="H48" s="3">
-        <v>46002</v>
+        <v>46065</v>
       </c>
       <c r="I48" s="3">
-        <v>46042</v>
+        <v>46099</v>
       </c>
       <c r="J48" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>45967</v>
+        <v>45972</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3721,7 +3697,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3732,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3741,37 +3717,37 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" t="s">
         <v>170</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" s="3">
+        <v>45978</v>
+      </c>
+      <c r="H49" s="3">
+        <v>46042</v>
+      </c>
+      <c r="I49" s="3">
+        <v>46163</v>
+      </c>
+      <c r="J49" t="s">
+        <v>37</v>
+      </c>
+      <c r="K49" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3">
+        <v>45978</v>
+      </c>
+      <c r="M49" t="s">
+        <v>6</v>
+      </c>
+      <c r="N49" t="s">
+        <v>7</v>
+      </c>
+      <c r="O49" t="s">
         <v>171</v>
-      </c>
-      <c r="G49" s="3">
-        <v>45967</v>
-      </c>
-      <c r="H49" s="3">
-        <v>46006</v>
-      </c>
-      <c r="I49" s="3">
-        <v>46044</v>
-      </c>
-      <c r="J49" t="s">
-        <v>26</v>
-      </c>
-      <c r="K49" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>45967</v>
-      </c>
-      <c r="M49" t="s">
-        <v>6</v>
-      </c>
-      <c r="N49" t="s">
-        <v>7</v>
-      </c>
-      <c r="O49" t="s">
-        <v>172</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3782,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3791,19 +3767,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="F50" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="G50" s="3">
-        <v>45971</v>
+        <v>45978</v>
       </c>
       <c r="H50" s="3">
-        <v>46006</v>
+        <v>46013</v>
       </c>
       <c r="I50" s="3">
-        <v>46055</v>
+        <v>46064</v>
       </c>
       <c r="J50" t="s">
         <v>37</v>
@@ -3812,7 +3788,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>45971</v>
+        <v>45978</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3821,7 +3797,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3832,37 +3808,37 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F51" t="s">
         <v>176</v>
       </c>
-      <c r="C51" s="2">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
-        <v>162</v>
-      </c>
-      <c r="F51" t="s">
-        <v>163</v>
-      </c>
       <c r="G51" s="3">
-        <v>45972</v>
+        <v>45979</v>
       </c>
       <c r="H51" s="3">
-        <v>46065</v>
+        <v>46031</v>
       </c>
       <c r="I51" s="3">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="J51" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>45972</v>
+        <v>45979</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3891,37 +3867,37 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="3">
+        <v>45979</v>
+      </c>
+      <c r="H52" s="3">
+        <v>46105</v>
+      </c>
+      <c r="I52" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J52" t="s">
         <v>179</v>
       </c>
-      <c r="F52" t="s">
+      <c r="K52" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
+        <v>45979</v>
+      </c>
+      <c r="M52" t="s">
+        <v>6</v>
+      </c>
+      <c r="N52" t="s">
+        <v>7</v>
+      </c>
+      <c r="O52" t="s">
         <v>180</v>
-      </c>
-      <c r="G52" s="3">
-        <v>45978</v>
-      </c>
-      <c r="H52" s="3">
-        <v>46042</v>
-      </c>
-      <c r="I52" s="3">
-        <v>46163</v>
-      </c>
-      <c r="J52" t="s">
-        <v>37</v>
-      </c>
-      <c r="K52" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
-        <v>45978</v>
-      </c>
-      <c r="M52" t="s">
-        <v>6</v>
-      </c>
-      <c r="N52" t="s">
-        <v>7</v>
-      </c>
-      <c r="O52" t="s">
-        <v>181</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -3932,37 +3908,37 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>170</v>
-      </c>
       <c r="F53" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G53" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H53" s="3">
-        <v>46013</v>
+        <v>46031</v>
       </c>
       <c r="I53" s="3">
-        <v>46064</v>
+        <v>46086</v>
       </c>
       <c r="J53" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3971,7 +3947,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -3982,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3991,22 +3967,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G54" s="3">
         <v>45979</v>
       </c>
       <c r="H54" s="3">
-        <v>46031</v>
+        <v>46083</v>
       </c>
       <c r="I54" s="3">
-        <v>46083</v>
+        <v>46147</v>
       </c>
       <c r="J54" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -4021,7 +3997,7 @@
         <v>7</v>
       </c>
       <c r="O54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P54" t="s">
         <v>9</v>
@@ -4032,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -4041,22 +4017,22 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="G55" s="3">
         <v>45979</v>
       </c>
       <c r="H55" s="3">
-        <v>46105</v>
+        <v>46035</v>
       </c>
       <c r="I55" s="3">
-        <v>46147</v>
+        <v>46119</v>
       </c>
       <c r="J55" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
@@ -4091,37 +4067,37 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
+        <v>186</v>
+      </c>
+      <c r="F56" t="s">
+        <v>187</v>
+      </c>
+      <c r="G56" s="3">
+        <v>45986</v>
+      </c>
+      <c r="H56" s="3">
+        <v>46017</v>
+      </c>
+      <c r="I56" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J56" t="s">
+        <v>37</v>
+      </c>
+      <c r="K56" t="s">
+        <v>5</v>
+      </c>
+      <c r="L56" s="3">
+        <v>45986</v>
+      </c>
+      <c r="M56" t="s">
+        <v>6</v>
+      </c>
+      <c r="N56" t="s">
+        <v>7</v>
+      </c>
+      <c r="O56" t="s">
         <v>192</v>
-      </c>
-      <c r="F56" t="s">
-        <v>193</v>
-      </c>
-      <c r="G56" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H56" s="3">
-        <v>46031</v>
-      </c>
-      <c r="I56" s="3">
-        <v>46078</v>
-      </c>
-      <c r="J56" t="s">
-        <v>26</v>
-      </c>
-      <c r="K56" t="s">
-        <v>5</v>
-      </c>
-      <c r="L56" s="3">
-        <v>45979</v>
-      </c>
-      <c r="M56" t="s">
-        <v>6</v>
-      </c>
-      <c r="N56" t="s">
-        <v>7</v>
-      </c>
-      <c r="O56" t="s">
-        <v>194</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4132,46 +4108,46 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" t="s">
         <v>195</v>
       </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="G57" s="3">
+        <v>45987</v>
+      </c>
+      <c r="H57" s="3">
+        <v>46121</v>
+      </c>
+      <c r="I57" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J57" t="s">
         <v>196</v>
       </c>
-      <c r="F57" t="s">
+      <c r="K57" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
+        <v>45986</v>
+      </c>
+      <c r="M57" t="s">
+        <v>6</v>
+      </c>
+      <c r="N57" t="s">
+        <v>7</v>
+      </c>
+      <c r="O57" t="s">
         <v>197</v>
-      </c>
-      <c r="G57" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H57" s="3">
-        <v>46083</v>
-      </c>
-      <c r="I57" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J57" t="s">
-        <v>189</v>
-      </c>
-      <c r="K57" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
-        <v>45979</v>
-      </c>
-      <c r="M57" t="s">
-        <v>6</v>
-      </c>
-      <c r="N57" t="s">
-        <v>7</v>
-      </c>
-      <c r="O57" t="s">
-        <v>198</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4182,46 +4158,46 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>154</v>
+      </c>
+      <c r="F58" t="s">
+        <v>155</v>
+      </c>
+      <c r="G58" s="3">
+        <v>45987</v>
+      </c>
+      <c r="H58" s="3">
+        <v>46029</v>
+      </c>
+      <c r="I58" s="3">
+        <v>46058</v>
+      </c>
+      <c r="J58" t="s">
+        <v>37</v>
+      </c>
+      <c r="K58" t="s">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
+        <v>45987</v>
+      </c>
+      <c r="M58" t="s">
+        <v>6</v>
+      </c>
+      <c r="N58" t="s">
+        <v>7</v>
+      </c>
+      <c r="O58" t="s">
         <v>199</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>158</v>
-      </c>
-      <c r="F58" t="s">
-        <v>159</v>
-      </c>
-      <c r="G58" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H58" s="3">
-        <v>46035</v>
-      </c>
-      <c r="I58" s="3">
-        <v>46119</v>
-      </c>
-      <c r="J58" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>45979</v>
-      </c>
-      <c r="M58" t="s">
-        <v>6</v>
-      </c>
-      <c r="N58" t="s">
-        <v>7</v>
-      </c>
-      <c r="O58" t="s">
-        <v>200</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4232,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4241,19 +4217,19 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="G59" s="3">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="H59" s="3">
-        <v>45999</v>
+        <v>46029</v>
       </c>
       <c r="I59" s="3">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="J59" t="s">
         <v>37</v>
@@ -4262,7 +4238,7 @@
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4271,7 +4247,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4282,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
+        <v>201</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" t="s">
         <v>203</v>
       </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
-        <v>196</v>
-      </c>
-      <c r="F60" t="s">
-        <v>197</v>
-      </c>
       <c r="G60" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="H60" s="3">
-        <v>46017</v>
+        <v>46001</v>
       </c>
       <c r="I60" s="3">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="J60" t="s">
         <v>37</v>
@@ -4312,7 +4288,7 @@
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>45986</v>
+        <v>45992</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4347,31 +4323,31 @@
         <v>207</v>
       </c>
       <c r="G61" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H61" s="3">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="I61" s="3">
-        <v>46183</v>
+        <v>46139</v>
       </c>
       <c r="J61" t="s">
+        <v>196</v>
+      </c>
+      <c r="K61" t="s">
+        <v>5</v>
+      </c>
+      <c r="L61" s="3">
+        <v>45993</v>
+      </c>
+      <c r="M61" t="s">
+        <v>6</v>
+      </c>
+      <c r="N61" t="s">
+        <v>7</v>
+      </c>
+      <c r="O61" t="s">
         <v>208</v>
-      </c>
-      <c r="K61" t="s">
-        <v>5</v>
-      </c>
-      <c r="L61" s="3">
-        <v>45986</v>
-      </c>
-      <c r="M61" t="s">
-        <v>6</v>
-      </c>
-      <c r="N61" t="s">
-        <v>7</v>
-      </c>
-      <c r="O61" t="s">
-        <v>209</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4382,28 +4358,28 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
         <v>210</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>162</v>
-      </c>
       <c r="F62" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="G62" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H62" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="I62" s="3">
-        <v>46058</v>
+        <v>46076</v>
       </c>
       <c r="J62" t="s">
         <v>37</v>
@@ -4412,7 +4388,7 @@
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4421,7 +4397,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4432,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4441,19 +4417,19 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="F63" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="G63" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H63" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="I63" s="3">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="J63" t="s">
         <v>37</v>
@@ -4462,7 +4438,7 @@
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4471,7 +4447,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4482,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4491,19 +4467,19 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="G64" s="3">
         <v>45993</v>
       </c>
       <c r="H64" s="3">
-        <v>46001</v>
+        <v>46041</v>
       </c>
       <c r="I64" s="3">
-        <v>46085</v>
+        <v>46127</v>
       </c>
       <c r="J64" t="s">
         <v>37</v>
@@ -4512,7 +4488,7 @@
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4521,7 +4497,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4532,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4541,37 +4517,37 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>216</v>
+        <v>116</v>
       </c>
       <c r="F65" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="3">
+        <v>45994</v>
+      </c>
+      <c r="H65" s="3">
+        <v>46125</v>
+      </c>
+      <c r="I65" s="3">
+        <v>46213</v>
+      </c>
+      <c r="J65" t="s">
+        <v>96</v>
+      </c>
+      <c r="K65" t="s">
+        <v>5</v>
+      </c>
+      <c r="L65" s="3">
+        <v>45994</v>
+      </c>
+      <c r="M65" t="s">
+        <v>6</v>
+      </c>
+      <c r="N65" t="s">
+        <v>7</v>
+      </c>
+      <c r="O65" t="s">
         <v>217</v>
-      </c>
-      <c r="G65" s="3">
-        <v>45993</v>
-      </c>
-      <c r="H65" s="3">
-        <v>46114</v>
-      </c>
-      <c r="I65" s="3">
-        <v>46139</v>
-      </c>
-      <c r="J65" t="s">
-        <v>208</v>
-      </c>
-      <c r="K65" t="s">
-        <v>5</v>
-      </c>
-      <c r="L65" s="3">
-        <v>45993</v>
-      </c>
-      <c r="M65" t="s">
-        <v>6</v>
-      </c>
-      <c r="N65" t="s">
-        <v>7</v>
-      </c>
-      <c r="O65" t="s">
-        <v>218</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4582,46 +4558,46 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" t="s">
+        <v>176</v>
+      </c>
+      <c r="G66" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H66" s="3">
+        <v>46094</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46139</v>
+      </c>
+      <c r="J66" t="s">
+        <v>96</v>
+      </c>
+      <c r="K66" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
+        <v>45995</v>
+      </c>
+      <c r="M66" t="s">
+        <v>6</v>
+      </c>
+      <c r="N66" t="s">
+        <v>7</v>
+      </c>
+      <c r="O66" t="s">
         <v>219</v>
-      </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>220</v>
-      </c>
-      <c r="F66" t="s">
-        <v>221</v>
-      </c>
-      <c r="G66" s="3">
-        <v>45993</v>
-      </c>
-      <c r="H66" s="3">
-        <v>46030</v>
-      </c>
-      <c r="I66" s="3">
-        <v>46062</v>
-      </c>
-      <c r="J66" t="s">
-        <v>37</v>
-      </c>
-      <c r="K66" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
-        <v>45993</v>
-      </c>
-      <c r="M66" t="s">
-        <v>6</v>
-      </c>
-      <c r="N66" t="s">
-        <v>7</v>
-      </c>
-      <c r="O66" t="s">
-        <v>222</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4632,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4641,37 +4617,37 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="F67" t="s">
+        <v>183</v>
+      </c>
+      <c r="G67" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H67" s="3">
+        <v>46100</v>
+      </c>
+      <c r="I67" s="3">
+        <v>46139</v>
+      </c>
+      <c r="J67" t="s">
+        <v>96</v>
+      </c>
+      <c r="K67" t="s">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3">
+        <v>45995</v>
+      </c>
+      <c r="M67" t="s">
+        <v>6</v>
+      </c>
+      <c r="N67" t="s">
+        <v>7</v>
+      </c>
+      <c r="O67" t="s">
         <v>221</v>
-      </c>
-      <c r="G67" s="3">
-        <v>45993</v>
-      </c>
-      <c r="H67" s="3">
-        <v>46030</v>
-      </c>
-      <c r="I67" s="3">
-        <v>46063</v>
-      </c>
-      <c r="J67" t="s">
-        <v>37</v>
-      </c>
-      <c r="K67" t="s">
-        <v>5</v>
-      </c>
-      <c r="L67" s="3">
-        <v>45993</v>
-      </c>
-      <c r="M67" t="s">
-        <v>6</v>
-      </c>
-      <c r="N67" t="s">
-        <v>7</v>
-      </c>
-      <c r="O67" t="s">
-        <v>222</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4682,37 +4658,37 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
+        <v>222</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>223</v>
+      </c>
+      <c r="F68" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="2">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>64</v>
-      </c>
-      <c r="F68" t="s">
-        <v>65</v>
-      </c>
       <c r="G68" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H68" s="3">
-        <v>46041</v>
+        <v>46119</v>
       </c>
       <c r="I68" s="3">
-        <v>46127</v>
+        <v>46199</v>
       </c>
       <c r="J68" t="s">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4721,7 +4697,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4732,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4741,28 +4717,28 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="F69" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="G69" s="3">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="H69" s="3">
-        <v>46125</v>
+        <v>46107</v>
       </c>
       <c r="I69" s="3">
-        <v>46213</v>
+        <v>46139</v>
       </c>
       <c r="J69" t="s">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4771,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4782,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4791,28 +4767,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="F70" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="G70" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H70" s="3">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="I70" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="J70" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4821,7 +4797,7 @@
         <v>7</v>
       </c>
       <c r="O70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -4832,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4841,19 +4817,19 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="F71" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="G71" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H71" s="3">
-        <v>46100</v>
+        <v>46114</v>
       </c>
       <c r="I71" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="J71" t="s">
         <v>96</v>
@@ -4862,7 +4838,7 @@
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4871,7 +4847,7 @@
         <v>7</v>
       </c>
       <c r="O71" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P71" t="s">
         <v>9</v>
@@ -4882,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4891,28 +4867,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F72" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G72" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="H72" s="3">
-        <v>46119</v>
+        <v>46010</v>
       </c>
       <c r="I72" s="3">
-        <v>46199</v>
+        <v>46045</v>
       </c>
       <c r="J72" t="s">
-        <v>235</v>
+        <v>37</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4921,7 +4897,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -4932,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4941,28 +4917,28 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="G73" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H73" s="3">
-        <v>46107</v>
+        <v>46008</v>
       </c>
       <c r="I73" s="3">
-        <v>46139</v>
+        <v>46045</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>37</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4971,7 +4947,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -4982,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4991,28 +4967,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="F74" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="G74" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H74" s="3">
-        <v>46108</v>
+        <v>46051</v>
       </c>
       <c r="I74" s="3">
-        <v>46140</v>
+        <v>46119</v>
       </c>
       <c r="J74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -5021,7 +4997,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5032,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5041,28 +5017,28 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F75" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G75" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H75" s="3">
-        <v>46114</v>
+        <v>46051</v>
       </c>
       <c r="I75" s="3">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="J75" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -5071,7 +5047,7 @@
         <v>7</v>
       </c>
       <c r="O75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P75" t="s">
         <v>9</v>
@@ -5082,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5091,28 +5067,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="F76" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="G76" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H76" s="3">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="I76" s="3">
-        <v>46045</v>
+        <v>46169</v>
       </c>
       <c r="J76" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -5121,7 +5097,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5132,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5141,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F77" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="G77" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H77" s="3">
-        <v>46008</v>
+        <v>46090</v>
       </c>
       <c r="I77" s="3">
-        <v>46045</v>
+        <v>46175</v>
       </c>
       <c r="J77" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5171,7 +5147,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5182,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5191,28 +5167,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G78" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H78" s="3">
-        <v>46051</v>
+        <v>46041</v>
       </c>
       <c r="I78" s="3">
         <v>46119</v>
       </c>
       <c r="J78" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5221,7 +5197,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5232,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5241,28 +5217,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="G79" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="H79" s="3">
-        <v>46051</v>
+        <v>46062</v>
       </c>
       <c r="I79" s="3">
-        <v>46146</v>
+        <v>46094</v>
       </c>
       <c r="J79" t="s">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5271,7 +5247,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5282,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5291,28 +5267,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="G80" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="H80" s="3">
-        <v>46084</v>
+        <v>46063</v>
       </c>
       <c r="I80" s="3">
-        <v>46169</v>
+        <v>46094</v>
       </c>
       <c r="J80" t="s">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5321,7 +5297,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5332,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5341,28 +5317,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G81" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="H81" s="3">
-        <v>46090</v>
+        <v>46134</v>
       </c>
       <c r="I81" s="3">
-        <v>46175</v>
+        <v>46155</v>
       </c>
       <c r="J81" t="s">
-        <v>96</v>
+        <v>259</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5371,7 +5347,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5382,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5391,28 +5367,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="F82" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="G82" s="3">
-        <v>46007</v>
+        <v>46020</v>
       </c>
       <c r="H82" s="3">
-        <v>46041</v>
+        <v>46028</v>
       </c>
       <c r="I82" s="3">
-        <v>46119</v>
+        <v>46078</v>
       </c>
       <c r="J82" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5421,7 +5397,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5432,37 +5408,37 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
+        <v>265</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
         <v>262</v>
       </c>
-      <c r="C83" s="2">
-        <v>1</v>
-      </c>
-      <c r="D83" s="2">
-        <v>0</v>
-      </c>
-      <c r="E83" t="s">
-        <v>166</v>
-      </c>
       <c r="F83" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="G83" s="3">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="H83" s="3">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="I83" s="3">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="J83" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5471,7 +5447,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5482,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5491,28 +5467,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G84" s="3">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="H84" s="3">
-        <v>46063</v>
+        <v>46092</v>
       </c>
       <c r="I84" s="3">
-        <v>46094</v>
+        <v>46119</v>
       </c>
       <c r="J84" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5521,7 +5497,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5532,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5547,31 +5523,31 @@
         <v>17</v>
       </c>
       <c r="G85" s="3">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="H85" s="3">
-        <v>46134</v>
+        <v>46031</v>
       </c>
       <c r="I85" s="3">
-        <v>46155</v>
+        <v>46056</v>
       </c>
       <c r="J85" t="s">
+        <v>269</v>
+      </c>
+      <c r="K85" t="s">
+        <v>5</v>
+      </c>
+      <c r="L85" s="3">
+        <v>46021</v>
+      </c>
+      <c r="M85" t="s">
+        <v>6</v>
+      </c>
+      <c r="N85" t="s">
+        <v>7</v>
+      </c>
+      <c r="O85" t="s">
         <v>267</v>
-      </c>
-      <c r="K85" t="s">
-        <v>5</v>
-      </c>
-      <c r="L85" s="3">
-        <v>46014</v>
-      </c>
-      <c r="M85" t="s">
-        <v>6</v>
-      </c>
-      <c r="N85" t="s">
-        <v>7</v>
-      </c>
-      <c r="O85" t="s">
-        <v>268</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5582,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5591,37 +5567,37 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="F86" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="3">
+        <v>46021</v>
+      </c>
+      <c r="H86" s="3">
+        <v>46091</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J86" t="s">
+        <v>244</v>
+      </c>
+      <c r="K86" t="s">
+        <v>5</v>
+      </c>
+      <c r="L86" s="3">
+        <v>46021</v>
+      </c>
+      <c r="M86" t="s">
+        <v>6</v>
+      </c>
+      <c r="N86" t="s">
+        <v>7</v>
+      </c>
+      <c r="O86" t="s">
         <v>271</v>
-      </c>
-      <c r="G86" s="3">
-        <v>46020</v>
-      </c>
-      <c r="H86" s="3">
-        <v>46028</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46076</v>
-      </c>
-      <c r="J86" t="s">
-        <v>260</v>
-      </c>
-      <c r="K86" t="s">
-        <v>5</v>
-      </c>
-      <c r="L86" s="3">
-        <v>46015</v>
-      </c>
-      <c r="M86" t="s">
-        <v>6</v>
-      </c>
-      <c r="N86" t="s">
-        <v>7</v>
-      </c>
-      <c r="O86" t="s">
-        <v>272</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5632,37 +5608,37 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
+        <v>272</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>238</v>
+      </c>
+      <c r="F87" t="s">
+        <v>239</v>
+      </c>
+      <c r="G87" s="3">
+        <v>46027</v>
+      </c>
+      <c r="H87" s="3">
+        <v>46028</v>
+      </c>
+      <c r="I87" s="3">
+        <v>46055</v>
+      </c>
+      <c r="J87" t="s">
         <v>273</v>
       </c>
-      <c r="C87" s="2">
-        <v>1</v>
-      </c>
-      <c r="D87" s="2">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
-        <v>270</v>
-      </c>
-      <c r="F87" t="s">
-        <v>271</v>
-      </c>
-      <c r="G87" s="3">
-        <v>46020</v>
-      </c>
-      <c r="H87" s="3">
-        <v>46031</v>
-      </c>
-      <c r="I87" s="3">
-        <v>46084</v>
-      </c>
-      <c r="J87" t="s">
-        <v>260</v>
-      </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5671,7 +5647,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5682,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5691,28 +5667,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="F88" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="G88" s="3">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H88" s="3">
-        <v>46092</v>
+        <v>46042</v>
       </c>
       <c r="I88" s="3">
-        <v>46119</v>
+        <v>46108</v>
       </c>
       <c r="J88" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5721,7 +5697,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5732,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5741,28 +5717,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F89" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="G89" s="3">
-        <v>46021</v>
+        <v>46027</v>
       </c>
       <c r="H89" s="3">
-        <v>46031</v>
+        <v>46126</v>
       </c>
       <c r="I89" s="3">
-        <v>46056</v>
+        <v>46188</v>
       </c>
       <c r="J89" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5771,7 +5747,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5782,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5791,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F90" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G90" s="3">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="H90" s="3">
-        <v>46091</v>
+        <v>46030</v>
       </c>
       <c r="I90" s="3">
-        <v>46119</v>
+        <v>46056</v>
       </c>
       <c r="J90" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5821,7 +5797,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5832,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5841,29 +5817,29 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="F91" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="G91" s="3">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H91" s="3">
+        <v>46049</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46091</v>
+      </c>
+      <c r="J91" t="s">
+        <v>244</v>
+      </c>
+      <c r="K91" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>46028</v>
       </c>
-      <c r="I91" s="3">
-        <v>46055</v>
-      </c>
-      <c r="J91" t="s">
-        <v>281</v>
-      </c>
-      <c r="K91" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
-        <v>46022</v>
-      </c>
       <c r="M91" t="s">
         <v>6</v>
       </c>
@@ -5871,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -5882,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5891,28 +5867,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G92" s="3">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="H92" s="3">
-        <v>46042</v>
+        <v>46031</v>
       </c>
       <c r="I92" s="3">
-        <v>46108</v>
+        <v>46079</v>
       </c>
       <c r="J92" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5921,7 +5897,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -5932,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5941,28 +5917,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F93" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G93" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="H93" s="3">
-        <v>46126</v>
+        <v>46043</v>
       </c>
       <c r="I93" s="3">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="J93" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5971,7 +5947,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -5982,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -5991,28 +5967,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F94" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G94" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H94" s="3">
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="I94" s="3">
-        <v>46056</v>
+        <v>46079</v>
       </c>
       <c r="J94" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -6032,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6041,28 +6017,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="F95" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="G95" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H95" s="3">
-        <v>46049</v>
+        <v>46077</v>
       </c>
       <c r="I95" s="3">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="J95" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6071,7 +6047,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6082,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6091,37 +6067,37 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="F96" t="s">
+        <v>176</v>
+      </c>
+      <c r="G96" s="3">
+        <v>46031</v>
+      </c>
+      <c r="H96" s="3">
+        <v>46062</v>
+      </c>
+      <c r="I96" s="3">
+        <v>46111</v>
+      </c>
+      <c r="J96" t="s">
+        <v>273</v>
+      </c>
+      <c r="K96" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
+        <v>46031</v>
+      </c>
+      <c r="M96" t="s">
+        <v>6</v>
+      </c>
+      <c r="N96" t="s">
+        <v>7</v>
+      </c>
+      <c r="O96" t="s">
         <v>296</v>
-      </c>
-      <c r="G96" s="3">
-        <v>46028</v>
-      </c>
-      <c r="H96" s="3">
-        <v>46031</v>
-      </c>
-      <c r="I96" s="3">
-        <v>46079</v>
-      </c>
-      <c r="J96" t="s">
-        <v>260</v>
-      </c>
-      <c r="K96" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
-        <v>46028</v>
-      </c>
-      <c r="M96" t="s">
-        <v>6</v>
-      </c>
-      <c r="N96" t="s">
-        <v>7</v>
-      </c>
-      <c r="O96" t="s">
-        <v>297</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6132,37 +6108,37 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
+        <v>297</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0</v>
+      </c>
+      <c r="E97" t="s">
         <v>298</v>
       </c>
-      <c r="C97" s="2">
-        <v>1</v>
-      </c>
-      <c r="D97" s="2">
-        <v>0</v>
-      </c>
-      <c r="E97" t="s">
-        <v>48</v>
-      </c>
       <c r="F97" t="s">
-        <v>49</v>
+        <v>299</v>
       </c>
       <c r="G97" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="H97" s="3">
-        <v>46043</v>
+        <v>46058</v>
       </c>
       <c r="I97" s="3">
-        <v>46086</v>
+        <v>46160</v>
       </c>
       <c r="J97" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6171,7 +6147,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6182,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6191,28 +6167,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>48</v>
+        <v>302</v>
       </c>
       <c r="F98" t="s">
-        <v>49</v>
+        <v>303</v>
       </c>
       <c r="G98" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="H98" s="3">
-        <v>46037</v>
+        <v>46091</v>
       </c>
       <c r="I98" s="3">
-        <v>46079</v>
+        <v>46198</v>
       </c>
       <c r="J98" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6221,7 +6197,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6232,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6241,28 +6217,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="F99" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="G99" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="H99" s="3">
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="I99" s="3">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="J99" t="s">
-        <v>302</v>
+        <v>196</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6271,7 +6247,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6282,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6291,28 +6267,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="F100" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="G100" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="H100" s="3">
-        <v>46062</v>
+        <v>46129</v>
       </c>
       <c r="I100" s="3">
-        <v>46111</v>
+        <v>46167</v>
       </c>
       <c r="J100" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6321,7 +6297,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6332,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6341,28 +6317,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>307</v>
+        <v>175</v>
       </c>
       <c r="F101" t="s">
+        <v>176</v>
+      </c>
+      <c r="G101" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H101" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I101" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J101" t="s">
         <v>308</v>
       </c>
-      <c r="G101" s="3">
-        <v>46031</v>
-      </c>
-      <c r="H101" s="3">
-        <v>46058</v>
-      </c>
-      <c r="I101" s="3">
-        <v>46160</v>
-      </c>
-      <c r="J101" t="s">
-        <v>260</v>
-      </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6371,7 +6347,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6382,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6391,28 +6367,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="F102" t="s">
-        <v>312</v>
+        <v>176</v>
       </c>
       <c r="G102" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="H102" s="3">
         <v>46091</v>
       </c>
       <c r="I102" s="3">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="J102" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6441,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
+        <v>169</v>
+      </c>
+      <c r="F103" t="s">
         <v>170</v>
       </c>
-      <c r="F103" t="s">
-        <v>171</v>
-      </c>
       <c r="G103" s="3">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="H103" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="I103" s="3">
-        <v>46106</v>
+        <v>46183</v>
       </c>
       <c r="J103" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6497,31 +6473,31 @@
         <v>151</v>
       </c>
       <c r="G104" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H104" s="3">
-        <v>46129</v>
+        <v>46090</v>
       </c>
       <c r="I104" s="3">
-        <v>46167</v>
+        <v>46154</v>
       </c>
       <c r="J104" t="s">
+        <v>259</v>
+      </c>
+      <c r="K104" t="s">
+        <v>5</v>
+      </c>
+      <c r="L104" s="3">
+        <v>46044</v>
+      </c>
+      <c r="M104" t="s">
+        <v>6</v>
+      </c>
+      <c r="N104" t="s">
+        <v>7</v>
+      </c>
+      <c r="O104" t="s">
         <v>317</v>
-      </c>
-      <c r="K104" t="s">
-        <v>5</v>
-      </c>
-      <c r="L104" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M104" t="s">
-        <v>6</v>
-      </c>
-      <c r="N104" t="s">
-        <v>7</v>
-      </c>
-      <c r="O104" t="s">
-        <v>318</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6532,31 +6508,31 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
+        <v>318</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
         <v>319</v>
       </c>
-      <c r="C105" s="2">
-        <v>1</v>
-      </c>
-      <c r="D105" s="2">
-        <v>0</v>
-      </c>
-      <c r="E105" t="s">
-        <v>185</v>
-      </c>
       <c r="F105" t="s">
-        <v>186</v>
+        <v>320</v>
       </c>
       <c r="G105" s="3">
         <v>46044</v>
       </c>
       <c r="H105" s="3">
-        <v>46148</v>
+        <v>46063</v>
       </c>
       <c r="I105" s="3">
-        <v>46183</v>
+        <v>46105</v>
       </c>
       <c r="J105" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
@@ -6571,7 +6547,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6582,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6591,22 +6567,22 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>185</v>
+        <v>324</v>
       </c>
       <c r="F106" t="s">
-        <v>186</v>
+        <v>325</v>
       </c>
       <c r="G106" s="3">
         <v>46044</v>
       </c>
       <c r="H106" s="3">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="I106" s="3">
-        <v>46128</v>
+        <v>46154</v>
       </c>
       <c r="J106" t="s">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
@@ -6621,7 +6597,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6632,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6641,28 +6617,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>179</v>
+        <v>328</v>
       </c>
       <c r="F107" t="s">
-        <v>180</v>
+        <v>329</v>
       </c>
       <c r="G107" s="3">
         <v>46048</v>
       </c>
       <c r="H107" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="I107" s="3">
-        <v>46183</v>
+        <v>46154</v>
       </c>
       <c r="J107" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6671,7 +6647,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6682,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6691,28 +6667,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F108" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G108" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H108" s="3">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="I108" s="3">
-        <v>46154</v>
+        <v>46128</v>
       </c>
       <c r="J108" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6721,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6732,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6741,28 +6717,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F109" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G109" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="H109" s="3">
-        <v>46063</v>
+        <v>46090</v>
       </c>
       <c r="I109" s="3">
-        <v>46105</v>
+        <v>46142</v>
       </c>
       <c r="J109" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6771,7 +6747,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6782,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6791,28 +6767,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>332</v>
+        <v>162</v>
       </c>
       <c r="F110" t="s">
-        <v>333</v>
+        <v>163</v>
       </c>
       <c r="G110" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H110" s="3">
-        <v>46085</v>
+        <v>46052</v>
       </c>
       <c r="I110" s="3">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="J110" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6821,7 +6797,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6832,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6841,28 +6817,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>336</v>
+        <v>162</v>
       </c>
       <c r="F111" t="s">
-        <v>337</v>
+        <v>163</v>
       </c>
       <c r="G111" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H111" s="3">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="I111" s="3">
-        <v>46154</v>
+        <v>46111</v>
       </c>
       <c r="J111" t="s">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6871,7 +6847,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -6882,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6891,28 +6867,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="F112" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="G112" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H112" s="3">
-        <v>46091</v>
+        <v>46052</v>
       </c>
       <c r="I112" s="3">
-        <v>46128</v>
+        <v>46079</v>
       </c>
       <c r="J112" t="s">
-        <v>317</v>
+        <v>244</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6921,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -6932,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6941,28 +6917,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F113" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="G113" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H113" s="3">
-        <v>46090</v>
+        <v>46051</v>
       </c>
       <c r="I113" s="3">
-        <v>46142</v>
+        <v>46111</v>
       </c>
       <c r="J113" t="s">
-        <v>267</v>
+        <v>196</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6979,10 +6955,10 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="B114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -6991,37 +6967,37 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>170</v>
+        <v>347</v>
       </c>
       <c r="F114" t="s">
-        <v>171</v>
+        <v>348</v>
       </c>
       <c r="G114" s="3">
-        <v>46050</v>
+        <v>46028</v>
       </c>
       <c r="H114" s="3">
-        <v>46086</v>
+        <v>46028</v>
       </c>
       <c r="I114" s="3">
-        <v>46106</v>
+        <v>46037</v>
       </c>
       <c r="J114" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="K114" t="s">
-        <v>5</v>
+        <v>349</v>
       </c>
       <c r="L114" s="3">
-        <v>46050</v>
+        <v>46028</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
       </c>
       <c r="N114" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="O114" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7029,10 +7005,10 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" t="s">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7041,37 +7017,37 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>170</v>
+        <v>353</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>354</v>
       </c>
       <c r="G115" s="3">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="H115" s="3">
-        <v>46091</v>
+        <v>46044</v>
       </c>
       <c r="I115" s="3">
-        <v>46111</v>
+        <v>46066</v>
       </c>
       <c r="J115" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="K115" t="s">
-        <v>5</v>
+        <v>349</v>
       </c>
       <c r="L115" s="3">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
       </c>
       <c r="N115" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="O115" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7079,49 +7055,49 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" t="s">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="B116" t="s">
+        <v>355</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" t="s">
+        <v>356</v>
+      </c>
+      <c r="F116" t="s">
+        <v>357</v>
+      </c>
+      <c r="G116" s="3">
+        <v>46042</v>
+      </c>
+      <c r="H116" s="3">
+        <v>46042</v>
+      </c>
+      <c r="I116" s="3">
+        <v>46043</v>
+      </c>
+      <c r="J116" t="s">
+        <v>269</v>
+      </c>
+      <c r="K116" t="s">
         <v>349</v>
       </c>
-      <c r="C116" s="2">
-        <v>1</v>
-      </c>
-      <c r="D116" s="2">
-        <v>0</v>
-      </c>
-      <c r="E116" t="s">
-        <v>170</v>
-      </c>
-      <c r="F116" t="s">
-        <v>171</v>
-      </c>
-      <c r="G116" s="3">
-        <v>46050</v>
-      </c>
-      <c r="H116" s="3">
-        <v>46058</v>
-      </c>
-      <c r="I116" s="3">
-        <v>46086</v>
-      </c>
-      <c r="J116" t="s">
-        <v>281</v>
-      </c>
-      <c r="K116" t="s">
-        <v>5</v>
-      </c>
       <c r="L116" s="3">
-        <v>46050</v>
+        <v>46042</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
       </c>
       <c r="N116" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="O116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7129,10 +7105,10 @@
     </row>
     <row r="117" spans="1:16">
       <c r="A117" t="s">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="B117" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7141,37 +7117,37 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="F117" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="G117" s="3">
-        <v>46050</v>
+        <v>46043</v>
       </c>
       <c r="H117" s="3">
         <v>46051</v>
       </c>
       <c r="I117" s="3">
-        <v>46111</v>
+        <v>46057</v>
       </c>
       <c r="J117" t="s">
-        <v>302</v>
+        <v>228</v>
       </c>
       <c r="K117" t="s">
-        <v>5</v>
+        <v>349</v>
       </c>
       <c r="L117" s="3">
-        <v>46050</v>
+        <v>46043</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
       </c>
       <c r="N117" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="O117" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7179,10 +7155,10 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B118" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7191,37 +7167,37 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F118" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G118" s="3">
-        <v>46028</v>
+        <v>46052</v>
       </c>
       <c r="H118" s="3">
-        <v>46028</v>
+        <v>46059</v>
       </c>
       <c r="I118" s="3">
-        <v>46037</v>
+        <v>46062</v>
       </c>
       <c r="J118" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="K118" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L118" s="3">
-        <v>46028</v>
+        <v>46052</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
       </c>
       <c r="N118" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="O118" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7229,10 +7205,10 @@
     </row>
     <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B119" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7241,37 +7217,37 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F119" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G119" s="3">
-        <v>46035</v>
+        <v>46052</v>
       </c>
       <c r="H119" s="3">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="I119" s="3">
-        <v>46066</v>
+        <v>46058</v>
       </c>
       <c r="J119" t="s">
-        <v>286</v>
+        <v>228</v>
       </c>
       <c r="K119" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L119" s="3">
-        <v>46035</v>
+        <v>46052</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
       </c>
       <c r="N119" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="O119" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7279,10 +7255,10 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7291,37 +7267,37 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F120" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G120" s="3">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="H120" s="3">
-        <v>46042</v>
+        <v>46058</v>
       </c>
       <c r="I120" s="3">
-        <v>46043</v>
+        <v>46083</v>
       </c>
       <c r="J120" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="K120" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L120" s="3">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
       </c>
       <c r="N120" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="O120" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7329,10 +7305,10 @@
     </row>
     <row r="121" spans="1:16">
       <c r="A121" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B121" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7341,239 +7317,39 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F121" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G121" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="H121" s="3">
-        <v>46051</v>
+        <v>46064</v>
       </c>
       <c r="I121" s="3">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="J121" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="K121" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L121" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
       </c>
       <c r="N121" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="O121" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="P121" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16">
-      <c r="A122" t="s">
-        <v>353</v>
-      </c>
-      <c r="B122" t="s">
-        <v>369</v>
-      </c>
-      <c r="C122" s="2">
-        <v>1</v>
-      </c>
-      <c r="D122" s="2">
-        <v>0</v>
-      </c>
-      <c r="E122" t="s">
-        <v>370</v>
-      </c>
-      <c r="F122" t="s">
-        <v>371</v>
-      </c>
-      <c r="G122" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H122" s="3">
-        <v>46059</v>
-      </c>
-      <c r="I122" s="3">
-        <v>46062</v>
-      </c>
-      <c r="J122" t="s">
-        <v>238</v>
-      </c>
-      <c r="K122" t="s">
-        <v>357</v>
-      </c>
-      <c r="L122" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M122" t="s">
-        <v>6</v>
-      </c>
-      <c r="N122" t="s">
-        <v>358</v>
-      </c>
-      <c r="O122" t="s">
-        <v>359</v>
-      </c>
-      <c r="P122" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16">
-      <c r="A123" t="s">
-        <v>353</v>
-      </c>
-      <c r="B123" t="s">
-        <v>372</v>
-      </c>
-      <c r="C123" s="2">
-        <v>1</v>
-      </c>
-      <c r="D123" s="2">
-        <v>0</v>
-      </c>
-      <c r="E123" t="s">
-        <v>373</v>
-      </c>
-      <c r="F123" t="s">
-        <v>374</v>
-      </c>
-      <c r="G123" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H123" s="3">
-        <v>46064</v>
-      </c>
-      <c r="I123" s="3">
-        <v>46066</v>
-      </c>
-      <c r="J123" t="s">
-        <v>238</v>
-      </c>
-      <c r="K123" t="s">
-        <v>357</v>
-      </c>
-      <c r="L123" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M123" t="s">
-        <v>6</v>
-      </c>
-      <c r="N123" t="s">
-        <v>358</v>
-      </c>
-      <c r="O123" t="s">
-        <v>359</v>
-      </c>
-      <c r="P123" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16">
-      <c r="A124" t="s">
-        <v>353</v>
-      </c>
-      <c r="B124" t="s">
-        <v>375</v>
-      </c>
-      <c r="C124" s="2">
-        <v>1</v>
-      </c>
-      <c r="D124" s="2">
-        <v>0</v>
-      </c>
-      <c r="E124" t="s">
-        <v>376</v>
-      </c>
-      <c r="F124" t="s">
-        <v>377</v>
-      </c>
-      <c r="G124" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H124" s="3">
-        <v>46057</v>
-      </c>
-      <c r="I124" s="3">
-        <v>46062</v>
-      </c>
-      <c r="J124" t="s">
-        <v>238</v>
-      </c>
-      <c r="K124" t="s">
-        <v>357</v>
-      </c>
-      <c r="L124" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M124" t="s">
-        <v>6</v>
-      </c>
-      <c r="N124" t="s">
-        <v>358</v>
-      </c>
-      <c r="O124" t="s">
-        <v>359</v>
-      </c>
-      <c r="P124" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16">
-      <c r="A125" t="s">
-        <v>353</v>
-      </c>
-      <c r="B125" t="s">
-        <v>378</v>
-      </c>
-      <c r="C125" s="2">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
-        <v>379</v>
-      </c>
-      <c r="F125" t="s">
-        <v>380</v>
-      </c>
-      <c r="G125" s="3">
-        <v>46052</v>
-      </c>
-      <c r="H125" s="3">
-        <v>46052</v>
-      </c>
-      <c r="I125" s="3">
-        <v>46058</v>
-      </c>
-      <c r="J125" t="s">
-        <v>238</v>
-      </c>
-      <c r="K125" t="s">
-        <v>357</v>
-      </c>
-      <c r="L125" s="3">
-        <v>46052</v>
-      </c>
-      <c r="M125" t="s">
-        <v>6</v>
-      </c>
-      <c r="N125" t="s">
-        <v>358</v>
-      </c>
-      <c r="O125" t="s">
-        <v>359</v>
-      </c>
-      <c r="P125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="437">
   <si>
     <t>ZP01</t>
   </si>
@@ -178,7 +178,145 @@
     <t>1100181630</t>
   </si>
   <si>
-    <t>100003264</t>
+    <t>100003291</t>
+  </si>
+  <si>
+    <t>980000000900</t>
+  </si>
+  <si>
+    <t>MVP-10_X=1050, Y=530, Z=630</t>
+  </si>
+  <si>
+    <t>1100189200</t>
+  </si>
+  <si>
+    <t>100003296</t>
+  </si>
+  <si>
+    <t>980000045000</t>
+  </si>
+  <si>
+    <t>TGV-106_X=1000, Y=600, Z=510</t>
+  </si>
+  <si>
+    <t>1100180440</t>
+  </si>
+  <si>
+    <t>100003306</t>
+  </si>
+  <si>
+    <t>980000045500</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #50_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1300000171</t>
+  </si>
+  <si>
+    <t>100003314</t>
+  </si>
+  <si>
+    <t>980000029800</t>
+  </si>
+  <si>
+    <t>HSA-828EAY_X=8M, Y=3.6M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100163530</t>
+  </si>
+  <si>
+    <t>100003315</t>
+  </si>
+  <si>
+    <t>980000045900</t>
+  </si>
+  <si>
+    <t>LG-1370 NEO_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1300000173</t>
+  </si>
+  <si>
+    <t>100003316</t>
+  </si>
+  <si>
+    <t>980000046000</t>
+  </si>
+  <si>
+    <t>LG-1570 NEO_X=1500, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100190750</t>
+  </si>
+  <si>
+    <t>100003318</t>
+  </si>
+  <si>
+    <t>1100186240</t>
+  </si>
+  <si>
+    <t>100003323</t>
+  </si>
+  <si>
+    <t>1100185500</t>
+  </si>
+  <si>
+    <t>100003324</t>
+  </si>
+  <si>
+    <t>980000024501</t>
+  </si>
+  <si>
+    <t>HSM-560_X=560, Y=430, Z=450</t>
+  </si>
+  <si>
+    <t>1300000177</t>
+  </si>
+  <si>
+    <t>100003345</t>
+  </si>
+  <si>
+    <t>980000016300</t>
+  </si>
+  <si>
+    <t>HCMC-1370_X=1300, Y=700, Z=660</t>
+  </si>
+  <si>
+    <t>1100169870</t>
+  </si>
+  <si>
+    <t>100003346</t>
+  </si>
+  <si>
+    <t>100003360</t>
+  </si>
+  <si>
+    <t>980000036900</t>
+  </si>
+  <si>
+    <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
+  </si>
+  <si>
+    <t>1100170790</t>
+  </si>
+  <si>
+    <t>100003370</t>
+  </si>
+  <si>
+    <t>980000029700</t>
+  </si>
+  <si>
+    <t>HSA-728EAY_X=7M, Y=3.6M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100167320</t>
+  </si>
+  <si>
+    <t>100003373</t>
   </si>
   <si>
     <t>980000041900</t>
@@ -187,256 +325,544 @@
     <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
   </si>
   <si>
-    <t>1100172060</t>
-  </si>
-  <si>
-    <t>100003291</t>
-  </si>
-  <si>
-    <t>980000000900</t>
-  </si>
-  <si>
-    <t>MVP-10_X=1050, Y=530, Z=630</t>
-  </si>
-  <si>
-    <t>1100189200</t>
-  </si>
-  <si>
-    <t>100003296</t>
-  </si>
-  <si>
-    <t>980000045000</t>
-  </si>
-  <si>
-    <t>TGV-106_X=1000, Y=600, Z=510</t>
-  </si>
-  <si>
-    <t>1100180440</t>
-  </si>
-  <si>
-    <t>100003306</t>
-  </si>
-  <si>
-    <t>980000045500</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #50_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100187880</t>
-  </si>
-  <si>
-    <t>100003314</t>
-  </si>
-  <si>
-    <t>980000029800</t>
-  </si>
-  <si>
-    <t>HSA-828EAY_X=8M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100163530</t>
-  </si>
-  <si>
-    <t>100003315</t>
-  </si>
-  <si>
-    <t>980000045900</t>
-  </si>
-  <si>
-    <t>LG-1370 NEO_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1300000173</t>
-  </si>
-  <si>
-    <t>100003316</t>
-  </si>
-  <si>
-    <t>980000046000</t>
-  </si>
-  <si>
-    <t>LG-1570 NEO_X=1500, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1300000174</t>
-  </si>
-  <si>
-    <t>100003318</t>
-  </si>
-  <si>
-    <t>1300000175</t>
-  </si>
-  <si>
-    <t>100003323</t>
-  </si>
-  <si>
-    <t>1100185500</t>
-  </si>
-  <si>
-    <t>100003324</t>
-  </si>
-  <si>
-    <t>980000024501</t>
-  </si>
-  <si>
-    <t>HSM-560_X=560, Y=430, Z=450</t>
-  </si>
-  <si>
-    <t>1300000177</t>
-  </si>
-  <si>
-    <t>100003344</t>
-  </si>
-  <si>
-    <t>980000016300</t>
-  </si>
-  <si>
-    <t>HCMC-1370_X=1300, Y=700, Z=660</t>
-  </si>
-  <si>
-    <t>1100169840</t>
-  </si>
-  <si>
-    <t>100003345</t>
+    <t>1100172660</t>
+  </si>
+  <si>
+    <t>100003393</t>
+  </si>
+  <si>
+    <t>980000012800</t>
+  </si>
+  <si>
+    <t>PBM-115A_X=2000, Y=1600, Z=1500</t>
+  </si>
+  <si>
+    <t>1100163730</t>
+  </si>
+  <si>
+    <t>100003400</t>
+  </si>
+  <si>
+    <t>980000036100</t>
+  </si>
+  <si>
+    <t>5BC-429_X=4M,Y=2.9M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100172120</t>
+  </si>
+  <si>
+    <t>100003401</t>
+  </si>
+  <si>
+    <t>980000022200</t>
+  </si>
+  <si>
+    <t>HSA-423EA_X=4M, Y=2.3M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100168090</t>
+  </si>
+  <si>
+    <t>100003406</t>
+  </si>
+  <si>
+    <t>980000032401</t>
+  </si>
+  <si>
+    <t>HSA-320,#50_X3M,Y2M ,Z0.78/1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100176970</t>
+  </si>
+  <si>
+    <t>100003407</t>
+  </si>
+  <si>
+    <t>980000018700</t>
+  </si>
+  <si>
+    <t>HSA-527_X=5000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100175780</t>
+  </si>
+  <si>
+    <t>100003410</t>
+  </si>
+  <si>
+    <t>980000022800</t>
+  </si>
+  <si>
+    <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100177770</t>
+  </si>
+  <si>
+    <t>100003412</t>
+  </si>
+  <si>
+    <t>1300000176</t>
+  </si>
+  <si>
+    <t>100003418</t>
+  </si>
+  <si>
+    <t>1100162420</t>
+  </si>
+  <si>
+    <t>100003423</t>
+  </si>
+  <si>
+    <t>1100178840</t>
+  </si>
+  <si>
+    <t>100003425</t>
+  </si>
+  <si>
+    <t>980000028700</t>
+  </si>
+  <si>
+    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100179510</t>
+  </si>
+  <si>
+    <t>100003436</t>
+  </si>
+  <si>
+    <t>980000036400</t>
+  </si>
+  <si>
+    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
+  </si>
+  <si>
+    <t>4200000001</t>
+  </si>
+  <si>
+    <t>100003437</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>100003438</t>
+  </si>
+  <si>
+    <t>100003445</t>
+  </si>
+  <si>
+    <t>1100181240</t>
+  </si>
+  <si>
+    <t>100003446</t>
+  </si>
+  <si>
+    <t>980000022400</t>
+  </si>
+  <si>
+    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100181710</t>
+  </si>
+  <si>
+    <t>100003448</t>
+  </si>
+  <si>
+    <t>980000017700</t>
+  </si>
+  <si>
+    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100182230</t>
+  </si>
+  <si>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100182240</t>
+  </si>
+  <si>
+    <t>100003450</t>
+  </si>
+  <si>
+    <t>980000018002</t>
+  </si>
+  <si>
+    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100181610</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>980000019200</t>
+  </si>
+  <si>
+    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182450</t>
+  </si>
+  <si>
+    <t>100003453</t>
+  </si>
+  <si>
+    <t>1100182220</t>
+  </si>
+  <si>
+    <t>100003459</t>
+  </si>
+  <si>
+    <t>1100180730</t>
+  </si>
+  <si>
+    <t>100003460</t>
+  </si>
+  <si>
+    <t>980000019400</t>
+  </si>
+  <si>
+    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
   </si>
   <si>
     <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
   </si>
   <si>
-    <t>1100169870</t>
-  </si>
-  <si>
-    <t>100003346</t>
-  </si>
-  <si>
-    <t>100003347</t>
-  </si>
-  <si>
-    <t>100003360</t>
-  </si>
-  <si>
-    <t>980000036900</t>
-  </si>
-  <si>
-    <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
-  </si>
-  <si>
-    <t>1100170790</t>
-  </si>
-  <si>
-    <t>100003370</t>
-  </si>
-  <si>
-    <t>980000029700</t>
-  </si>
-  <si>
-    <t>HSA-728EAY_X=7M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100167320</t>
-  </si>
-  <si>
-    <t>100003373</t>
-  </si>
-  <si>
-    <t>1100172660</t>
-  </si>
-  <si>
-    <t>100003393</t>
-  </si>
-  <si>
-    <t>980000012800</t>
-  </si>
-  <si>
-    <t>PBM-115A_X=2000, Y=1600, Z=1500</t>
-  </si>
-  <si>
-    <t>1100163730</t>
-  </si>
-  <si>
-    <t>100003400</t>
-  </si>
-  <si>
-    <t>980000036100</t>
-  </si>
-  <si>
-    <t>5BC-429_X=4M,Y=2.9M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100172120</t>
-  </si>
-  <si>
-    <t>100003401</t>
-  </si>
-  <si>
-    <t>980000022200</t>
-  </si>
-  <si>
-    <t>HSA-423EA_X=4M, Y=2.3M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100168090</t>
-  </si>
-  <si>
-    <t>100003402</t>
-  </si>
-  <si>
-    <t>980000032501</t>
-  </si>
-  <si>
-    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100144480</t>
-  </si>
-  <si>
-    <t>100003406</t>
-  </si>
-  <si>
-    <t>980000032401</t>
-  </si>
-  <si>
-    <t>HSA-320,#50_X3M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100176970</t>
-  </si>
-  <si>
-    <t>100003407</t>
-  </si>
-  <si>
-    <t>980000018700</t>
-  </si>
-  <si>
-    <t>HSA-527_X=5000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>1100175780</t>
-  </si>
-  <si>
-    <t>100003410</t>
-  </si>
-  <si>
-    <t>980000022800</t>
-  </si>
-  <si>
-    <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100177770</t>
-  </si>
-  <si>
-    <t>100003412</t>
-  </si>
-  <si>
-    <t>1300000176</t>
-  </si>
-  <si>
-    <t>100003414</t>
+    <t>1100175760</t>
+  </si>
+  <si>
+    <t>100003462</t>
+  </si>
+  <si>
+    <t>1100183170</t>
+  </si>
+  <si>
+    <t>100003463</t>
+  </si>
+  <si>
+    <t>100003464</t>
+  </si>
+  <si>
+    <t>980000043500</t>
+  </si>
+  <si>
+    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
+  </si>
+  <si>
+    <t>1100177340</t>
+  </si>
+  <si>
+    <t>100003465</t>
+  </si>
+  <si>
+    <t>980000013700</t>
+  </si>
+  <si>
+    <t>S-Plus 8_X=800, Y=520, Z=550</t>
+  </si>
+  <si>
+    <t>1100177930</t>
+  </si>
+  <si>
+    <t>100003466</t>
+  </si>
+  <si>
+    <t>980000041200</t>
+  </si>
+  <si>
+    <t>S8_X=700, Y=420, Z=510</t>
+  </si>
+  <si>
+    <t>1100181200</t>
+  </si>
+  <si>
+    <t>100003467</t>
+  </si>
+  <si>
+    <t>100003468</t>
+  </si>
+  <si>
+    <t>1100182880</t>
+  </si>
+  <si>
+    <t>100003469</t>
+  </si>
+  <si>
+    <t>1100179090</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1100182820</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>1100172880</t>
+  </si>
+  <si>
+    <t>100003472</t>
+  </si>
+  <si>
+    <t>980000030801</t>
+  </si>
+  <si>
+    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100177910</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1300000180</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>980000027800</t>
+  </si>
+  <si>
+    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100183180</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>1100184110</t>
+  </si>
+  <si>
+    <t>100003478</t>
+  </si>
+  <si>
+    <t>980000000800</t>
+  </si>
+  <si>
+    <t>PRO-1000_X=1000, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100180510</t>
+  </si>
+  <si>
+    <t>100003480</t>
+  </si>
+  <si>
+    <t>1100184470</t>
+  </si>
+  <si>
+    <t>100003481</t>
+  </si>
+  <si>
+    <t>1100184950</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
+    <t>1100185590</t>
+  </si>
+  <si>
+    <t>100003483</t>
+  </si>
+  <si>
+    <t>1100185600</t>
+  </si>
+  <si>
+    <t>100003484</t>
+  </si>
+  <si>
+    <t>1100181160</t>
+  </si>
+  <si>
+    <t>100003485</t>
+  </si>
+  <si>
+    <t>1100177650</t>
+  </si>
+  <si>
+    <t>100003486</t>
+  </si>
+  <si>
+    <t>1100184890</t>
+  </si>
+  <si>
+    <t>100003488</t>
+  </si>
+  <si>
+    <t>1100185870</t>
+  </si>
+  <si>
+    <t>100003489</t>
+  </si>
+  <si>
+    <t>980000047800</t>
+  </si>
+  <si>
+    <t>LG-2100,#40_X=2050, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100186480</t>
+  </si>
+  <si>
+    <t>100003490</t>
+  </si>
+  <si>
+    <t>100003491</t>
+  </si>
+  <si>
+    <t>1100186570</t>
+  </si>
+  <si>
+    <t>100003492</t>
+  </si>
+  <si>
+    <t>100003493</t>
+  </si>
+  <si>
+    <t>1100186580</t>
+  </si>
+  <si>
+    <t>100003494</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100186710</t>
+  </si>
+  <si>
+    <t>100003495</t>
+  </si>
+  <si>
+    <t>980000021500</t>
+  </si>
+  <si>
+    <t>HSA-528_X=5000,Y=2800,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100186690</t>
+  </si>
+  <si>
+    <t>100003496</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>1300000181</t>
+  </si>
+  <si>
+    <t>100003497</t>
+  </si>
+  <si>
+    <t>1100187100</t>
+  </si>
+  <si>
+    <t>100003498</t>
+  </si>
+  <si>
+    <t>1100187060</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
+    <t>980000048000</t>
+  </si>
+  <si>
+    <t>SMC-7_X=700, Y=400, Z=300</t>
+  </si>
+  <si>
+    <t>1300000182</t>
+  </si>
+  <si>
+    <t>100003500</t>
+  </si>
+  <si>
+    <t>1100183110</t>
+  </si>
+  <si>
+    <t>100003501</t>
+  </si>
+  <si>
+    <t>100003502</t>
+  </si>
+  <si>
+    <t>1100183140</t>
+  </si>
+  <si>
+    <t>100003503</t>
+  </si>
+  <si>
+    <t>1100184480</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003506</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100184300</t>
+  </si>
+  <si>
+    <t>100003507</t>
   </si>
   <si>
     <t>980000045400</t>
@@ -445,640 +871,391 @@
     <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
   </si>
   <si>
-    <t>1100177640</t>
-  </si>
-  <si>
-    <t>100003418</t>
-  </si>
-  <si>
-    <t>1100162420</t>
-  </si>
-  <si>
-    <t>100003423</t>
-  </si>
-  <si>
-    <t>1100178840</t>
-  </si>
-  <si>
-    <t>100003425</t>
-  </si>
-  <si>
-    <t>980000028700</t>
-  </si>
-  <si>
-    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100179510</t>
-  </si>
-  <si>
-    <t>100003436</t>
-  </si>
-  <si>
-    <t>980000036400</t>
-  </si>
-  <si>
-    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
-  </si>
-  <si>
-    <t>4200000001</t>
-  </si>
-  <si>
-    <t>100003437</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>100003438</t>
-  </si>
-  <si>
-    <t>100003439</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100180870</t>
-  </si>
-  <si>
-    <t>100003440</t>
-  </si>
-  <si>
-    <t>100003445</t>
-  </si>
-  <si>
-    <t>1100181240</t>
-  </si>
-  <si>
-    <t>100003446</t>
-  </si>
-  <si>
-    <t>980000022400</t>
-  </si>
-  <si>
-    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100181710</t>
-  </si>
-  <si>
-    <t>100003447</t>
-  </si>
-  <si>
-    <t>1100181640</t>
-  </si>
-  <si>
-    <t>100003448</t>
-  </si>
-  <si>
-    <t>980000017700</t>
-  </si>
-  <si>
-    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100182230</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100182240</t>
-  </si>
-  <si>
-    <t>100003450</t>
-  </si>
-  <si>
-    <t>980000018002</t>
-  </si>
-  <si>
-    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100181610</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>980000019200</t>
-  </si>
-  <si>
-    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182450</t>
-  </si>
-  <si>
-    <t>100003453</t>
-  </si>
-  <si>
-    <t>1100182220</t>
-  </si>
-  <si>
-    <t>100003459</t>
-  </si>
-  <si>
-    <t>1100180730</t>
-  </si>
-  <si>
-    <t>100003460</t>
-  </si>
-  <si>
-    <t>980000019400</t>
-  </si>
-  <si>
-    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003509</t>
   </si>
   <si>
     <t>REL  MSPT PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>1100175760</t>
-  </si>
-  <si>
-    <t>100003462</t>
-  </si>
-  <si>
-    <t>1100183170</t>
-  </si>
-  <si>
-    <t>100003463</t>
-  </si>
-  <si>
-    <t>100003464</t>
-  </si>
-  <si>
-    <t>980000043500</t>
-  </si>
-  <si>
-    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
-  </si>
-  <si>
-    <t>1100177340</t>
-  </si>
-  <si>
-    <t>100003465</t>
-  </si>
-  <si>
-    <t>980000013700</t>
-  </si>
-  <si>
-    <t>S-Plus 8_X=800, Y=520, Z=550</t>
-  </si>
-  <si>
-    <t>1100177930</t>
-  </si>
-  <si>
-    <t>100003466</t>
-  </si>
-  <si>
-    <t>980000041200</t>
-  </si>
-  <si>
-    <t>S8_X=700, Y=420, Z=510</t>
-  </si>
-  <si>
-    <t>1100181200</t>
-  </si>
-  <si>
-    <t>100003467</t>
-  </si>
-  <si>
-    <t>100003468</t>
-  </si>
-  <si>
-    <t>1100182880</t>
-  </si>
-  <si>
-    <t>100003469</t>
-  </si>
-  <si>
-    <t>1100179090</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1100182820</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>1100172880</t>
-  </si>
-  <si>
-    <t>100003472</t>
-  </si>
-  <si>
-    <t>980000030801</t>
-  </si>
-  <si>
-    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100177910</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>1300000180</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>980000027800</t>
-  </si>
-  <si>
-    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>1100183180</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>1100184110</t>
-  </si>
-  <si>
-    <t>100003478</t>
-  </si>
-  <si>
-    <t>980000000800</t>
-  </si>
-  <si>
-    <t>PRO-1000_X=1000, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100180510</t>
-  </si>
-  <si>
-    <t>100003479</t>
-  </si>
-  <si>
-    <t>1100184460</t>
-  </si>
-  <si>
-    <t>100003480</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100184470</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>1100184950</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>1100185590</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1100185600</t>
-  </si>
-  <si>
-    <t>100003484</t>
-  </si>
-  <si>
-    <t>1100181160</t>
-  </si>
-  <si>
-    <t>100003485</t>
-  </si>
-  <si>
-    <t>1100177650</t>
-  </si>
-  <si>
-    <t>100003486</t>
-  </si>
-  <si>
-    <t>1100184890</t>
-  </si>
-  <si>
-    <t>100003488</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>1100185870</t>
-  </si>
-  <si>
-    <t>100003489</t>
-  </si>
-  <si>
-    <t>980000047800</t>
-  </si>
-  <si>
-    <t>LG-2100,#40_X=2050, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100186480</t>
-  </si>
-  <si>
-    <t>100003490</t>
-  </si>
-  <si>
-    <t>100003491</t>
-  </si>
-  <si>
-    <t>1100186570</t>
-  </si>
-  <si>
-    <t>100003492</t>
+    <t>1100188510</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
+  </si>
+  <si>
+    <t>1100182140</t>
+  </si>
+  <si>
+    <t>100003512</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100188460</t>
+  </si>
+  <si>
+    <t>100003513</t>
+  </si>
+  <si>
+    <t>980000028600</t>
+  </si>
+  <si>
+    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182130</t>
+  </si>
+  <si>
+    <t>100003514</t>
+  </si>
+  <si>
+    <t>980000017001</t>
+  </si>
+  <si>
+    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182120</t>
+  </si>
+  <si>
+    <t>100003515</t>
+  </si>
+  <si>
+    <t>1100185540</t>
+  </si>
+  <si>
+    <t>100003516</t>
+  </si>
+  <si>
+    <t>980000017201</t>
+  </si>
+  <si>
+    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182570</t>
+  </si>
+  <si>
+    <t>100003517</t>
+  </si>
+  <si>
+    <t>1100186720</t>
+  </si>
+  <si>
+    <t>100003518</t>
+  </si>
+  <si>
+    <t>1100188530</t>
+  </si>
+  <si>
+    <t>100003519</t>
+  </si>
+  <si>
+    <t>1100188540</t>
+  </si>
+  <si>
+    <t>100003520</t>
+  </si>
+  <si>
+    <t>1100186590</t>
+  </si>
+  <si>
+    <t>100003521</t>
+  </si>
+  <si>
+    <t>980000000100</t>
+  </si>
+  <si>
+    <t>MVP-8_X=860, Y=530, Z=630</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100180520</t>
+  </si>
+  <si>
+    <t>100003522</t>
+  </si>
+  <si>
+    <t>1100187480</t>
+  </si>
+  <si>
+    <t>100003523</t>
+  </si>
+  <si>
+    <t>1100182050</t>
+  </si>
+  <si>
+    <t>100003524</t>
+  </si>
+  <si>
+    <t>1100182060</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>980000044600</t>
+  </si>
+  <si>
+    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100190220</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1100190240</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>980000005501</t>
+  </si>
+  <si>
+    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100186230</t>
+  </si>
+  <si>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003530</t>
+  </si>
+  <si>
+    <t>1100190880</t>
+  </si>
+  <si>
+    <t>100003531</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003538</t>
+  </si>
+  <si>
+    <t>1100190050</t>
+  </si>
+  <si>
+    <t>100003539</t>
+  </si>
+  <si>
+    <t>100003540</t>
+  </si>
+  <si>
+    <t>100003541</t>
+  </si>
+  <si>
+    <t>1100185360</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
+  </si>
+  <si>
+    <t>CRTD MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100186250</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>100003551</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>ZP09</t>
+  </si>
+  <si>
+    <t>630000329</t>
+  </si>
+  <si>
+    <t>080300029000</t>
+  </si>
+  <si>
+    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
+  </si>
+  <si>
+    <t>PENNY</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>630000332</t>
+  </si>
+  <si>
+    <t>080100145201</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M65,0045</t>
+  </si>
+  <si>
+    <t>630000333</t>
+  </si>
+  <si>
+    <t>080200530600</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
+  </si>
+  <si>
+    <t>630000336</t>
+  </si>
+  <si>
+    <t>080100016701</t>
+  </si>
+  <si>
+    <t>D8K 主軸,010801_BT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>630000337</t>
+  </si>
+  <si>
+    <t>080300018208</t>
+  </si>
+  <si>
+    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
   </si>
   <si>
     <t>REL  PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>100003493</t>
-  </si>
-  <si>
-    <t>1100186580</t>
-  </si>
-  <si>
-    <t>100003494</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100186710</t>
-  </si>
-  <si>
-    <t>100003495</t>
-  </si>
-  <si>
-    <t>980000021500</t>
-  </si>
-  <si>
-    <t>HSA-528_X=5000,Y=2800,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100186690</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1300000181</t>
-  </si>
-  <si>
-    <t>100003497</t>
-  </si>
-  <si>
-    <t>1100187100</t>
-  </si>
-  <si>
-    <t>100003498</t>
-  </si>
-  <si>
-    <t>1100187060</t>
-  </si>
-  <si>
-    <t>100003499</t>
-  </si>
-  <si>
-    <t>980000048000</t>
-  </si>
-  <si>
-    <t>SMC-7_X=700, Y=400, Z=300</t>
-  </si>
-  <si>
-    <t>1300000182</t>
-  </si>
-  <si>
-    <t>100003500</t>
-  </si>
-  <si>
-    <t>1100183110</t>
-  </si>
-  <si>
-    <t>100003501</t>
-  </si>
-  <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1100183140</t>
-  </si>
-  <si>
-    <t>100003503</t>
-  </si>
-  <si>
-    <t>1100184480</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003506</t>
-  </si>
-  <si>
-    <t>1100184300</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
-    <t>1100182140</t>
-  </si>
-  <si>
-    <t>100003512</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100188460</t>
-  </si>
-  <si>
-    <t>100003513</t>
-  </si>
-  <si>
-    <t>980000028600</t>
-  </si>
-  <si>
-    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182130</t>
-  </si>
-  <si>
-    <t>100003514</t>
-  </si>
-  <si>
-    <t>980000017001</t>
-  </si>
-  <si>
-    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182120</t>
-  </si>
-  <si>
-    <t>100003515</t>
-  </si>
-  <si>
-    <t>1100185540</t>
-  </si>
-  <si>
-    <t>100003516</t>
-  </si>
-  <si>
-    <t>980000017201</t>
-  </si>
-  <si>
-    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182570</t>
-  </si>
-  <si>
-    <t>100003517</t>
-  </si>
-  <si>
-    <t>1100186720</t>
-  </si>
-  <si>
-    <t>100003518</t>
-  </si>
-  <si>
-    <t>1100188530</t>
-  </si>
-  <si>
-    <t>100003519</t>
-  </si>
-  <si>
-    <t>1100188540</t>
-  </si>
-  <si>
-    <t>100003520</t>
-  </si>
-  <si>
-    <t>1100186590</t>
-  </si>
-  <si>
-    <t>ZP09</t>
-  </si>
-  <si>
-    <t>630000326</t>
-  </si>
-  <si>
-    <t>080200014702</t>
-  </si>
-  <si>
-    <t>EA機頭G6K,011164_Z1200,55A18,0</t>
-  </si>
-  <si>
-    <t>PENNY</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>080300029000</t>
-  </si>
-  <si>
-    <t>HF-AU,032731_1°-BT50-45°-4K-C-F,溫降案</t>
-  </si>
-  <si>
-    <t>630000331</t>
+    <t>630000338</t>
+  </si>
+  <si>
+    <t>080200254502</t>
+  </si>
+  <si>
+    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
+  </si>
+  <si>
+    <t>630000340</t>
+  </si>
+  <si>
+    <t>080100018301</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>630000341</t>
   </si>
   <si>
     <t>080200332002</t>
@@ -1087,49 +1264,16 @@
     <t>PBM115機頭G4K,011381_BT50,FO2C45</t>
   </si>
   <si>
-    <t>630000332</t>
-  </si>
-  <si>
-    <t>080100145201</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M65,0045</t>
-  </si>
-  <si>
-    <t>630000333</t>
-  </si>
-  <si>
-    <t>080200530600</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,48F18,0</t>
-  </si>
-  <si>
-    <t>630000336</t>
-  </si>
-  <si>
-    <t>080100016701</t>
-  </si>
-  <si>
-    <t>D8K 主軸,010801_BT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>630000337</t>
-  </si>
-  <si>
-    <t>080300018208</t>
-  </si>
-  <si>
-    <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
-  </si>
-  <si>
-    <t>630000338</t>
-  </si>
-  <si>
-    <t>080200254502</t>
-  </si>
-  <si>
-    <t>5A65E機頭D15K,032370_BT40,CAWDI</t>
+    <t>630000342</t>
+  </si>
+  <si>
+    <t>080100156608</t>
+  </si>
+  <si>
+    <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC SETC</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1282,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P121"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1305,52 +1449,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>376</v>
+        <v>424</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>380</v>
+        <v>428</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1629,7 +1773,7 @@
         <v>45580</v>
       </c>
       <c r="I7" s="3">
-        <v>46062</v>
+        <v>46077</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -1829,7 +1973,7 @@
         <v>45624</v>
       </c>
       <c r="I11" s="3">
-        <v>45959</v>
+        <v>46066</v>
       </c>
       <c r="J11" t="s">
         <v>37</v>
@@ -1973,13 +2117,13 @@
         <v>57</v>
       </c>
       <c r="G14" s="3">
-        <v>45762</v>
+        <v>45784</v>
       </c>
       <c r="H14" s="3">
-        <v>45796</v>
+        <v>45827</v>
       </c>
       <c r="I14" s="3">
-        <v>46062</v>
+        <v>46056</v>
       </c>
       <c r="J14" t="s">
         <v>37</v>
@@ -1988,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="L14" s="3">
-        <v>45761</v>
+        <v>45782</v>
       </c>
       <c r="M14" t="s">
         <v>6</v>
@@ -2023,13 +2167,13 @@
         <v>61</v>
       </c>
       <c r="G15" s="3">
-        <v>45784</v>
+        <v>45793</v>
       </c>
       <c r="H15" s="3">
         <v>45827</v>
       </c>
       <c r="I15" s="3">
-        <v>46056</v>
+        <v>46090</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
@@ -2038,7 +2182,7 @@
         <v>5</v>
       </c>
       <c r="L15" s="3">
-        <v>45782</v>
+        <v>45789</v>
       </c>
       <c r="M15" t="s">
         <v>6</v>
@@ -2073,13 +2217,13 @@
         <v>65</v>
       </c>
       <c r="G16" s="3">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="H16" s="3">
-        <v>45827</v>
+        <v>45799</v>
       </c>
       <c r="I16" s="3">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="J16" t="s">
         <v>37</v>
@@ -2088,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="3">
-        <v>45789</v>
+        <v>45797</v>
       </c>
       <c r="M16" t="s">
         <v>6</v>
@@ -2123,22 +2267,22 @@
         <v>69</v>
       </c>
       <c r="G17" s="3">
-        <v>45798</v>
+        <v>45804</v>
       </c>
       <c r="H17" s="3">
-        <v>45799</v>
+        <v>45923</v>
       </c>
       <c r="I17" s="3">
-        <v>46044</v>
+        <v>46013</v>
       </c>
       <c r="J17" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="3">
-        <v>45797</v>
+        <v>45804</v>
       </c>
       <c r="M17" t="s">
         <v>6</v>
@@ -2173,22 +2317,22 @@
         <v>73</v>
       </c>
       <c r="G18" s="3">
-        <v>45804</v>
+        <v>45810</v>
       </c>
       <c r="H18" s="3">
-        <v>45923</v>
+        <v>45848</v>
       </c>
       <c r="I18" s="3">
-        <v>46013</v>
+        <v>46076</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3">
-        <v>45804</v>
+        <v>45806</v>
       </c>
       <c r="M18" t="s">
         <v>6</v>
@@ -2226,10 +2370,10 @@
         <v>45810</v>
       </c>
       <c r="H19" s="3">
-        <v>45848</v>
+        <v>45853</v>
       </c>
       <c r="I19" s="3">
-        <v>46003</v>
+        <v>46090</v>
       </c>
       <c r="J19" t="s">
         <v>37</v>
@@ -2267,37 +2411,37 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="3">
+        <v>45811</v>
+      </c>
+      <c r="H20" s="3">
+        <v>45945</v>
+      </c>
+      <c r="I20" s="3">
+        <v>46078</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
+        <v>45811</v>
+      </c>
+      <c r="M20" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" t="s">
+        <v>7</v>
+      </c>
+      <c r="O20" t="s">
         <v>80</v>
-      </c>
-      <c r="F20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" s="3">
-        <v>45810</v>
-      </c>
-      <c r="H20" s="3">
-        <v>45853</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46056</v>
-      </c>
-      <c r="J20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K20" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
-        <v>45806</v>
-      </c>
-      <c r="M20" t="s">
-        <v>6</v>
-      </c>
-      <c r="N20" t="s">
-        <v>7</v>
-      </c>
-      <c r="O20" t="s">
-        <v>82</v>
       </c>
       <c r="P20" t="s">
         <v>9</v>
@@ -2308,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2317,28 +2461,28 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G21" s="3">
-        <v>45811</v>
+        <v>45813</v>
       </c>
       <c r="H21" s="3">
-        <v>45945</v>
+        <v>45814</v>
       </c>
       <c r="I21" s="3">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="J21" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2347,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="O21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P21" t="s">
         <v>9</v>
@@ -2358,28 +2502,28 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" t="s">
         <v>85</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
       </c>
       <c r="G22" s="3">
         <v>45813</v>
       </c>
       <c r="H22" s="3">
-        <v>45814</v>
+        <v>45827</v>
       </c>
       <c r="I22" s="3">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="J22" t="s">
         <v>37</v>
@@ -2423,13 +2567,13 @@
         <v>89</v>
       </c>
       <c r="G23" s="3">
-        <v>45813</v>
+        <v>45835</v>
       </c>
       <c r="H23" s="3">
-        <v>45827</v>
+        <v>46098</v>
       </c>
       <c r="I23" s="3">
-        <v>46049</v>
+        <v>46135</v>
       </c>
       <c r="J23" t="s">
         <v>37</v>
@@ -2438,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45812</v>
+        <v>45835</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2467,19 +2611,19 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G24" s="3">
         <v>45835</v>
       </c>
       <c r="H24" s="3">
-        <v>45853</v>
+        <v>46098</v>
       </c>
       <c r="I24" s="3">
-        <v>46048</v>
+        <v>46135</v>
       </c>
       <c r="J24" t="s">
         <v>37</v>
@@ -2497,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="O24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P24" t="s">
         <v>9</v>
@@ -2508,46 +2652,46 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="3">
+        <v>45848</v>
+      </c>
+      <c r="H25" s="3">
+        <v>46001</v>
+      </c>
+      <c r="I25" s="3">
+        <v>46149</v>
+      </c>
+      <c r="J25" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="3">
-        <v>45835</v>
-      </c>
-      <c r="H25" s="3">
-        <v>46098</v>
-      </c>
-      <c r="I25" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
+        <v>5</v>
+      </c>
+      <c r="L25" s="3">
+        <v>45848</v>
+      </c>
+      <c r="M25" t="s">
+        <v>6</v>
+      </c>
+      <c r="N25" t="s">
+        <v>7</v>
+      </c>
+      <c r="O25" t="s">
         <v>96</v>
-      </c>
-      <c r="K25" t="s">
-        <v>5</v>
-      </c>
-      <c r="L25" s="3">
-        <v>45835</v>
-      </c>
-      <c r="M25" t="s">
-        <v>6</v>
-      </c>
-      <c r="N25" t="s">
-        <v>7</v>
-      </c>
-      <c r="O25" t="s">
-        <v>97</v>
       </c>
       <c r="P25" t="s">
         <v>9</v>
@@ -2558,28 +2702,28 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>92</v>
-      </c>
       <c r="F26" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G26" s="3">
-        <v>45835</v>
+        <v>45861</v>
       </c>
       <c r="H26" s="3">
-        <v>46098</v>
+        <v>45946</v>
       </c>
       <c r="I26" s="3">
-        <v>46135</v>
+        <v>46107</v>
       </c>
       <c r="J26" t="s">
         <v>37</v>
@@ -2588,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>45835</v>
+        <v>45861</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2597,7 +2741,7 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P26" t="s">
         <v>9</v>
@@ -2608,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2617,19 +2761,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G27" s="3">
-        <v>45835</v>
+        <v>45870</v>
       </c>
       <c r="H27" s="3">
-        <v>45847</v>
+        <v>45950</v>
       </c>
       <c r="I27" s="3">
-        <v>46041</v>
+        <v>46064</v>
       </c>
       <c r="J27" t="s">
         <v>37</v>
@@ -2638,7 +2782,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45835</v>
+        <v>45870</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2647,7 +2791,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2658,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2667,28 +2811,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G28" s="3">
-        <v>45848</v>
+        <v>45887</v>
       </c>
       <c r="H28" s="3">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="I28" s="3">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>45848</v>
+        <v>45887</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2697,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="O28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="P28" t="s">
         <v>9</v>
@@ -2708,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2717,28 +2861,28 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G29" s="3">
-        <v>45861</v>
+        <v>45901</v>
       </c>
       <c r="H29" s="3">
-        <v>45946</v>
+        <v>46045</v>
       </c>
       <c r="I29" s="3">
-        <v>46087</v>
+        <v>46163</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>45861</v>
+        <v>45901</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2747,7 +2891,7 @@
         <v>7</v>
       </c>
       <c r="O29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="P29" t="s">
         <v>9</v>
@@ -2758,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2767,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="G30" s="3">
-        <v>45870</v>
+        <v>45911</v>
       </c>
       <c r="H30" s="3">
-        <v>45950</v>
+        <v>45930</v>
       </c>
       <c r="I30" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="J30" t="s">
         <v>37</v>
@@ -2788,7 +2932,7 @@
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>45870</v>
+        <v>45911</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2797,7 +2941,7 @@
         <v>7</v>
       </c>
       <c r="O30" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="P30" t="s">
         <v>9</v>
@@ -2808,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2817,19 +2961,19 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G31" s="3">
-        <v>45887</v>
+        <v>45923</v>
       </c>
       <c r="H31" s="3">
-        <v>45999</v>
+        <v>45980</v>
       </c>
       <c r="I31" s="3">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="J31" t="s">
         <v>26</v>
@@ -2838,7 +2982,7 @@
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>45887</v>
+        <v>45923</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2847,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="O31" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="P31" t="s">
         <v>9</v>
@@ -2858,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2867,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G32" s="3">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="H32" s="3">
-        <v>46045</v>
+        <v>45999</v>
       </c>
       <c r="I32" s="3">
-        <v>46141</v>
+        <v>46094</v>
       </c>
       <c r="J32" t="s">
         <v>37</v>
@@ -2888,7 +3032,7 @@
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -2897,7 +3041,7 @@
         <v>7</v>
       </c>
       <c r="O32" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="P32" t="s">
         <v>9</v>
@@ -2908,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -2917,19 +3061,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G33" s="3">
-        <v>45911</v>
+        <v>45943</v>
       </c>
       <c r="H33" s="3">
-        <v>45930</v>
+        <v>46017</v>
       </c>
       <c r="I33" s="3">
-        <v>46065</v>
+        <v>46132</v>
       </c>
       <c r="J33" t="s">
         <v>37</v>
@@ -2938,7 +3082,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>45911</v>
+        <v>45943</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -2947,7 +3091,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="P33" t="s">
         <v>9</v>
@@ -2958,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -2967,19 +3111,19 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G34" s="3">
-        <v>45918</v>
+        <v>45943</v>
       </c>
       <c r="H34" s="3">
-        <v>45965</v>
+        <v>46041</v>
       </c>
       <c r="I34" s="3">
-        <v>46042</v>
+        <v>46085</v>
       </c>
       <c r="J34" t="s">
         <v>37</v>
@@ -2988,7 +3132,7 @@
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>45917</v>
+        <v>45943</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -2997,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P34" t="s">
         <v>9</v>
@@ -3008,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -3017,19 +3161,19 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="G35" s="3">
-        <v>45923</v>
+        <v>45950</v>
       </c>
       <c r="H35" s="3">
-        <v>45980</v>
+        <v>45957</v>
       </c>
       <c r="I35" s="3">
-        <v>46084</v>
+        <v>46141</v>
       </c>
       <c r="J35" t="s">
         <v>26</v>
@@ -3038,7 +3182,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>45923</v>
+        <v>45946</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -3047,7 +3191,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3058,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3067,19 +3211,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="F36" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="G36" s="3">
-        <v>45931</v>
+        <v>45951</v>
       </c>
       <c r="H36" s="3">
-        <v>45999</v>
+        <v>46006</v>
       </c>
       <c r="I36" s="3">
-        <v>46094</v>
+        <v>46065</v>
       </c>
       <c r="J36" t="s">
         <v>37</v>
@@ -3088,7 +3232,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>45931</v>
+        <v>45951</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -3123,13 +3267,13 @@
         <v>137</v>
       </c>
       <c r="G37" s="3">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="H37" s="3">
-        <v>46017</v>
+        <v>45987</v>
       </c>
       <c r="I37" s="3">
-        <v>46132</v>
+        <v>46066</v>
       </c>
       <c r="J37" t="s">
         <v>37</v>
@@ -3138,7 +3282,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3167,19 +3311,19 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="G38" s="3">
-        <v>45943</v>
+        <v>45966</v>
       </c>
       <c r="H38" s="3">
-        <v>46041</v>
+        <v>46050</v>
       </c>
       <c r="I38" s="3">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="J38" t="s">
         <v>37</v>
@@ -3188,7 +3332,7 @@
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>45943</v>
+        <v>45966</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -3197,7 +3341,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3208,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3217,37 +3361,37 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="3">
+        <v>45966</v>
+      </c>
+      <c r="H39" s="3">
+        <v>46049</v>
+      </c>
+      <c r="I39" s="3">
+        <v>46085</v>
+      </c>
+      <c r="J39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="3">
+        <v>45966</v>
+      </c>
+      <c r="M39" t="s">
+        <v>6</v>
+      </c>
+      <c r="N39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O39" t="s">
         <v>142</v>
-      </c>
-      <c r="F39" t="s">
-        <v>143</v>
-      </c>
-      <c r="G39" s="3">
-        <v>45944</v>
-      </c>
-      <c r="H39" s="3">
-        <v>45986</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46066</v>
-      </c>
-      <c r="J39" t="s">
-        <v>26</v>
-      </c>
-      <c r="K39" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" s="3">
-        <v>45944</v>
-      </c>
-      <c r="M39" t="s">
-        <v>6</v>
-      </c>
-      <c r="N39" t="s">
-        <v>7</v>
-      </c>
-      <c r="O39" t="s">
-        <v>144</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3258,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3267,28 +3411,28 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G40" s="3">
-        <v>45950</v>
+        <v>45966</v>
       </c>
       <c r="H40" s="3">
-        <v>45957</v>
+        <v>46051</v>
       </c>
       <c r="I40" s="3">
-        <v>46136</v>
+        <v>46133</v>
       </c>
       <c r="J40" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>45946</v>
+        <v>45966</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3297,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3317,19 +3461,19 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="G41" s="3">
-        <v>45951</v>
+        <v>45972</v>
       </c>
       <c r="H41" s="3">
-        <v>46006</v>
+        <v>46051</v>
       </c>
       <c r="I41" s="3">
-        <v>46052</v>
+        <v>46087</v>
       </c>
       <c r="J41" t="s">
         <v>37</v>
@@ -3338,7 +3482,7 @@
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>45951</v>
+        <v>45972</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3373,13 +3517,13 @@
         <v>151</v>
       </c>
       <c r="G42" s="3">
-        <v>45951</v>
+        <v>45978</v>
       </c>
       <c r="H42" s="3">
-        <v>45987</v>
+        <v>46042</v>
       </c>
       <c r="I42" s="3">
-        <v>46066</v>
+        <v>46163</v>
       </c>
       <c r="J42" t="s">
         <v>37</v>
@@ -3388,7 +3532,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>45951</v>
+        <v>45978</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3423,22 +3567,22 @@
         <v>155</v>
       </c>
       <c r="G43" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H43" s="3">
-        <v>46064</v>
+        <v>46031</v>
       </c>
       <c r="I43" s="3">
-        <v>46099</v>
+        <v>46085</v>
       </c>
       <c r="J43" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3467,37 +3611,37 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" t="s">
+        <v>155</v>
+      </c>
+      <c r="G44" s="3">
+        <v>45979</v>
+      </c>
+      <c r="H44" s="3">
+        <v>46105</v>
+      </c>
+      <c r="I44" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J44" t="s">
         <v>158</v>
       </c>
-      <c r="F44" t="s">
+      <c r="K44" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
+        <v>45979</v>
+      </c>
+      <c r="M44" t="s">
+        <v>6</v>
+      </c>
+      <c r="N44" t="s">
+        <v>7</v>
+      </c>
+      <c r="O44" t="s">
         <v>159</v>
-      </c>
-      <c r="G44" s="3">
-        <v>45966</v>
-      </c>
-      <c r="H44" s="3">
-        <v>46049</v>
-      </c>
-      <c r="I44" s="3">
-        <v>46085</v>
-      </c>
-      <c r="J44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K44" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3">
-        <v>45966</v>
-      </c>
-      <c r="M44" t="s">
-        <v>6</v>
-      </c>
-      <c r="N44" t="s">
-        <v>7</v>
-      </c>
-      <c r="O44" t="s">
-        <v>156</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3517,28 +3661,28 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="G45" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H45" s="3">
-        <v>46064</v>
+        <v>46031</v>
       </c>
       <c r="I45" s="3">
-        <v>46139</v>
+        <v>46097</v>
       </c>
       <c r="J45" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3547,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3558,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3567,19 +3711,19 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F46" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G46" s="3">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="H46" s="3">
-        <v>46002</v>
+        <v>46083</v>
       </c>
       <c r="I46" s="3">
-        <v>46042</v>
+        <v>46147</v>
       </c>
       <c r="J46" t="s">
         <v>26</v>
@@ -3588,7 +3732,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3597,7 +3741,7 @@
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3608,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3617,19 +3761,19 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F47" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="G47" s="3">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="H47" s="3">
-        <v>46006</v>
+        <v>46035</v>
       </c>
       <c r="I47" s="3">
-        <v>46044</v>
+        <v>46119</v>
       </c>
       <c r="J47" t="s">
         <v>26</v>
@@ -3638,7 +3782,7 @@
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3647,7 +3791,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3658,28 +3802,28 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>165</v>
+      </c>
+      <c r="F48" t="s">
         <v>166</v>
       </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>154</v>
-      </c>
-      <c r="F48" t="s">
-        <v>155</v>
-      </c>
       <c r="G48" s="3">
-        <v>45972</v>
+        <v>45986</v>
       </c>
       <c r="H48" s="3">
-        <v>46065</v>
+        <v>46017</v>
       </c>
       <c r="I48" s="3">
-        <v>46099</v>
+        <v>46087</v>
       </c>
       <c r="J48" t="s">
         <v>37</v>
@@ -3688,7 +3832,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>45972</v>
+        <v>45986</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3697,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3708,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3717,28 +3861,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F49" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G49" s="3">
-        <v>45978</v>
+        <v>45987</v>
       </c>
       <c r="H49" s="3">
-        <v>46042</v>
+        <v>46121</v>
       </c>
       <c r="I49" s="3">
-        <v>46163</v>
+        <v>46183</v>
       </c>
       <c r="J49" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3747,7 +3891,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3758,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3767,19 +3911,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="F50" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G50" s="3">
-        <v>45978</v>
+        <v>45987</v>
       </c>
       <c r="H50" s="3">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="I50" s="3">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="J50" t="s">
         <v>37</v>
@@ -3788,7 +3932,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>45978</v>
+        <v>45987</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3797,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3808,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3817,28 +3961,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F51" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="G51" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="H51" s="3">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="I51" s="3">
-        <v>46083</v>
+        <v>46056</v>
       </c>
       <c r="J51" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3847,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -3858,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3867,28 +4011,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F52" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G52" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H52" s="3">
-        <v>46105</v>
+        <v>46001</v>
       </c>
       <c r="I52" s="3">
-        <v>46147</v>
+        <v>46085</v>
       </c>
       <c r="J52" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -3897,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -3908,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -3917,28 +4061,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G53" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H53" s="3">
-        <v>46031</v>
+        <v>46114</v>
       </c>
       <c r="I53" s="3">
-        <v>46086</v>
+        <v>46139</v>
       </c>
       <c r="J53" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -3947,7 +4091,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -3958,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -3967,28 +4111,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F54" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G54" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H54" s="3">
-        <v>46083</v>
+        <v>46030</v>
       </c>
       <c r="I54" s="3">
-        <v>46147</v>
+        <v>46079</v>
       </c>
       <c r="J54" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -3997,7 +4141,7 @@
         <v>7</v>
       </c>
       <c r="O54" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P54" t="s">
         <v>9</v>
@@ -4008,37 +4152,37 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
         <v>189</v>
       </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-      <c r="E55" t="s">
-        <v>150</v>
-      </c>
       <c r="F55" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="G55" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H55" s="3">
-        <v>46035</v>
+        <v>46030</v>
       </c>
       <c r="I55" s="3">
-        <v>46119</v>
+        <v>46078</v>
       </c>
       <c r="J55" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -4047,7 +4191,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4058,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -4067,19 +4211,19 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="G56" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="H56" s="3">
-        <v>46017</v>
+        <v>46041</v>
       </c>
       <c r="I56" s="3">
-        <v>46094</v>
+        <v>46127</v>
       </c>
       <c r="J56" t="s">
         <v>37</v>
@@ -4088,7 +4232,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4097,7 +4241,7 @@
         <v>7</v>
       </c>
       <c r="O56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4108,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4117,37 +4261,37 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="F57" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="G57" s="3">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="H57" s="3">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="I57" s="3">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="J57" t="s">
+        <v>175</v>
+      </c>
+      <c r="K57" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
+        <v>45994</v>
+      </c>
+      <c r="M57" t="s">
+        <v>6</v>
+      </c>
+      <c r="N57" t="s">
+        <v>7</v>
+      </c>
+      <c r="O57" t="s">
         <v>196</v>
-      </c>
-      <c r="K57" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
-        <v>45986</v>
-      </c>
-      <c r="M57" t="s">
-        <v>6</v>
-      </c>
-      <c r="N57" t="s">
-        <v>7</v>
-      </c>
-      <c r="O57" t="s">
-        <v>197</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4158,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -4173,22 +4317,22 @@
         <v>155</v>
       </c>
       <c r="G58" s="3">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="H58" s="3">
-        <v>46029</v>
+        <v>46094</v>
       </c>
       <c r="I58" s="3">
-        <v>46058</v>
+        <v>46139</v>
       </c>
       <c r="J58" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4197,7 +4341,7 @@
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4208,46 +4352,46 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>161</v>
+      </c>
+      <c r="F59" t="s">
+        <v>162</v>
+      </c>
+      <c r="G59" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H59" s="3">
+        <v>46100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>46139</v>
+      </c>
+      <c r="J59" t="s">
+        <v>175</v>
+      </c>
+      <c r="K59" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
+        <v>45995</v>
+      </c>
+      <c r="M59" t="s">
+        <v>6</v>
+      </c>
+      <c r="N59" t="s">
+        <v>7</v>
+      </c>
+      <c r="O59" t="s">
         <v>200</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
-        <v>154</v>
-      </c>
-      <c r="F59" t="s">
-        <v>155</v>
-      </c>
-      <c r="G59" s="3">
-        <v>45987</v>
-      </c>
-      <c r="H59" s="3">
-        <v>46029</v>
-      </c>
-      <c r="I59" s="3">
-        <v>46056</v>
-      </c>
-      <c r="J59" t="s">
-        <v>37</v>
-      </c>
-      <c r="K59" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
-        <v>45987</v>
-      </c>
-      <c r="M59" t="s">
-        <v>6</v>
-      </c>
-      <c r="N59" t="s">
-        <v>7</v>
-      </c>
-      <c r="O59" t="s">
-        <v>199</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4273,22 +4417,22 @@
         <v>203</v>
       </c>
       <c r="G60" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H60" s="3">
-        <v>46001</v>
+        <v>46119</v>
       </c>
       <c r="I60" s="3">
-        <v>46085</v>
+        <v>46199</v>
       </c>
       <c r="J60" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4297,7 +4441,7 @@
         <v>7</v>
       </c>
       <c r="O60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P60" t="s">
         <v>9</v>
@@ -4308,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4317,28 +4461,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>206</v>
+        <v>56</v>
       </c>
       <c r="F61" t="s">
-        <v>207</v>
+        <v>57</v>
       </c>
       <c r="G61" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="H61" s="3">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="I61" s="3">
         <v>46139</v>
       </c>
       <c r="J61" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4373,22 +4517,22 @@
         <v>211</v>
       </c>
       <c r="G62" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="H62" s="3">
-        <v>46030</v>
+        <v>46108</v>
       </c>
       <c r="I62" s="3">
-        <v>46076</v>
+        <v>46140</v>
       </c>
       <c r="J62" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4397,7 +4541,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4408,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4417,28 +4561,28 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>210</v>
+        <v>72</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="G63" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="H63" s="3">
-        <v>46030</v>
+        <v>46114</v>
       </c>
       <c r="I63" s="3">
-        <v>46066</v>
+        <v>46140</v>
       </c>
       <c r="J63" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4447,7 +4591,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4458,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4467,19 +4611,19 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>64</v>
+        <v>217</v>
       </c>
       <c r="F64" t="s">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="G64" s="3">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="H64" s="3">
-        <v>46041</v>
+        <v>46010</v>
       </c>
       <c r="I64" s="3">
-        <v>46127</v>
+        <v>46045</v>
       </c>
       <c r="J64" t="s">
         <v>37</v>
@@ -4488,7 +4632,7 @@
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4497,7 +4641,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4508,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4517,28 +4661,28 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="G65" s="3">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="H65" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I65" s="3">
         <v>46125</v>
       </c>
-      <c r="I65" s="3">
-        <v>46213</v>
-      </c>
       <c r="J65" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4547,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4558,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4567,28 +4711,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="F66" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="G66" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="H66" s="3">
-        <v>46094</v>
+        <v>46041</v>
       </c>
       <c r="I66" s="3">
-        <v>46139</v>
+        <v>46149</v>
       </c>
       <c r="J66" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4597,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4608,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4617,28 +4761,28 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="F67" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="G67" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="H67" s="3">
-        <v>46100</v>
+        <v>46084</v>
       </c>
       <c r="I67" s="3">
-        <v>46139</v>
+        <v>46169</v>
       </c>
       <c r="J67" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4647,7 +4791,7 @@
         <v>7</v>
       </c>
       <c r="O67" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4658,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4667,28 +4811,28 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="F68" t="s">
-        <v>224</v>
+        <v>53</v>
       </c>
       <c r="G68" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="H68" s="3">
-        <v>46119</v>
+        <v>46090</v>
       </c>
       <c r="I68" s="3">
-        <v>46199</v>
+        <v>46175</v>
       </c>
       <c r="J68" t="s">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4697,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4708,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4717,28 +4861,28 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="G69" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H69" s="3">
-        <v>46107</v>
+        <v>46041</v>
       </c>
       <c r="I69" s="3">
-        <v>46139</v>
+        <v>46122</v>
       </c>
       <c r="J69" t="s">
-        <v>228</v>
+        <v>37</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4767,37 +4911,37 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
+        <v>144</v>
+      </c>
+      <c r="F70" t="s">
+        <v>145</v>
+      </c>
+      <c r="G70" s="3">
+        <v>46013</v>
+      </c>
+      <c r="H70" s="3">
+        <v>46037</v>
+      </c>
+      <c r="I70" s="3">
+        <v>46084</v>
+      </c>
+      <c r="J70" t="s">
+        <v>37</v>
+      </c>
+      <c r="K70" t="s">
+        <v>5</v>
+      </c>
+      <c r="L70" s="3">
+        <v>46013</v>
+      </c>
+      <c r="M70" t="s">
+        <v>6</v>
+      </c>
+      <c r="N70" t="s">
+        <v>7</v>
+      </c>
+      <c r="O70" t="s">
         <v>231</v>
-      </c>
-      <c r="F70" t="s">
-        <v>232</v>
-      </c>
-      <c r="G70" s="3">
-        <v>46000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>46108</v>
-      </c>
-      <c r="I70" s="3">
-        <v>46140</v>
-      </c>
-      <c r="J70" t="s">
-        <v>233</v>
-      </c>
-      <c r="K70" t="s">
-        <v>5</v>
-      </c>
-      <c r="L70" s="3">
-        <v>46000</v>
-      </c>
-      <c r="M70" t="s">
-        <v>6</v>
-      </c>
-      <c r="N70" t="s">
-        <v>7</v>
-      </c>
-      <c r="O70" t="s">
-        <v>234</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -4808,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4823,22 +4967,22 @@
         <v>77</v>
       </c>
       <c r="G71" s="3">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="H71" s="3">
-        <v>46114</v>
+        <v>46063</v>
       </c>
       <c r="I71" s="3">
-        <v>46140</v>
+        <v>46094</v>
       </c>
       <c r="J71" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -4847,7 +4991,7 @@
         <v>7</v>
       </c>
       <c r="O71" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P71" t="s">
         <v>9</v>
@@ -4858,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4867,28 +5011,28 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>238</v>
+        <v>16</v>
       </c>
       <c r="F72" t="s">
-        <v>239</v>
+        <v>17</v>
       </c>
       <c r="G72" s="3">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="H72" s="3">
-        <v>46010</v>
+        <v>46134</v>
       </c>
       <c r="I72" s="3">
-        <v>46045</v>
+        <v>46155</v>
       </c>
       <c r="J72" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="M72" t="s">
         <v>6</v>
@@ -4897,7 +5041,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -4908,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -4917,19 +5061,19 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="F73" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="G73" s="3">
-        <v>46002</v>
+        <v>46020</v>
       </c>
       <c r="H73" s="3">
-        <v>46008</v>
+        <v>46028</v>
       </c>
       <c r="I73" s="3">
-        <v>46045</v>
+        <v>46084</v>
       </c>
       <c r="J73" t="s">
         <v>37</v>
@@ -4938,7 +5082,7 @@
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46002</v>
+        <v>46015</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -4947,7 +5091,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -4958,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -4967,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="F74" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="G74" s="3">
-        <v>46002</v>
+        <v>46020</v>
       </c>
       <c r="H74" s="3">
-        <v>46051</v>
+        <v>46031</v>
       </c>
       <c r="I74" s="3">
-        <v>46119</v>
+        <v>46083</v>
       </c>
       <c r="J74" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46002</v>
+        <v>46015</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -4997,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5008,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5017,19 +5161,19 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G75" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="H75" s="3">
-        <v>46051</v>
+        <v>46036</v>
       </c>
       <c r="I75" s="3">
-        <v>46146</v>
+        <v>46090</v>
       </c>
       <c r="J75" t="s">
         <v>37</v>
@@ -5038,7 +5182,7 @@
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -5047,7 +5191,7 @@
         <v>7</v>
       </c>
       <c r="O75" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="P75" t="s">
         <v>9</v>
@@ -5058,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5067,28 +5211,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G76" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="H76" s="3">
-        <v>46084</v>
+        <v>46031</v>
       </c>
       <c r="I76" s="3">
-        <v>46169</v>
+        <v>46086</v>
       </c>
       <c r="J76" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -5097,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5108,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5117,28 +5261,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G77" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="H77" s="3">
-        <v>46090</v>
+        <v>46037</v>
       </c>
       <c r="I77" s="3">
-        <v>46175</v>
+        <v>46086</v>
       </c>
       <c r="J77" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5147,7 +5291,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5158,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5167,28 +5311,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F78" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G78" s="3">
-        <v>46007</v>
+        <v>46027</v>
       </c>
       <c r="H78" s="3">
-        <v>46041</v>
+        <v>46028</v>
       </c>
       <c r="I78" s="3">
-        <v>46119</v>
+        <v>46055</v>
       </c>
       <c r="J78" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5197,7 +5341,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5208,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5217,28 +5361,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="F79" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="G79" s="3">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="H79" s="3">
-        <v>46062</v>
+        <v>46056</v>
       </c>
       <c r="I79" s="3">
-        <v>46094</v>
+        <v>46134</v>
       </c>
       <c r="J79" t="s">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5247,7 +5391,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5258,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5267,28 +5411,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="F80" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G80" s="3">
-        <v>46013</v>
+        <v>46027</v>
       </c>
       <c r="H80" s="3">
-        <v>46063</v>
+        <v>46126</v>
       </c>
       <c r="I80" s="3">
-        <v>46094</v>
+        <v>46188</v>
       </c>
       <c r="J80" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5297,7 +5441,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5308,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5317,28 +5461,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F81" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G81" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="H81" s="3">
-        <v>46134</v>
+        <v>46030</v>
       </c>
       <c r="I81" s="3">
-        <v>46155</v>
+        <v>46066</v>
       </c>
       <c r="J81" t="s">
-        <v>259</v>
+        <v>37</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5347,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5358,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5367,29 +5511,29 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="F82" t="s">
-        <v>263</v>
+        <v>49</v>
       </c>
       <c r="G82" s="3">
-        <v>46020</v>
+        <v>46028</v>
       </c>
       <c r="H82" s="3">
+        <v>46048</v>
+      </c>
+      <c r="I82" s="3">
+        <v>46087</v>
+      </c>
+      <c r="J82" t="s">
+        <v>37</v>
+      </c>
+      <c r="K82" t="s">
+        <v>5</v>
+      </c>
+      <c r="L82" s="3">
         <v>46028</v>
       </c>
-      <c r="I82" s="3">
-        <v>46078</v>
-      </c>
-      <c r="J82" t="s">
-        <v>244</v>
-      </c>
-      <c r="K82" t="s">
-        <v>5</v>
-      </c>
-      <c r="L82" s="3">
-        <v>46015</v>
-      </c>
       <c r="M82" t="s">
         <v>6</v>
       </c>
@@ -5397,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5408,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5417,28 +5561,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
+        <v>261</v>
+      </c>
+      <c r="F83" t="s">
         <v>262</v>
       </c>
-      <c r="F83" t="s">
-        <v>263</v>
-      </c>
       <c r="G83" s="3">
-        <v>46020</v>
+        <v>46028</v>
       </c>
       <c r="H83" s="3">
         <v>46031</v>
       </c>
       <c r="I83" s="3">
-        <v>46091</v>
+        <v>46087</v>
       </c>
       <c r="J83" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46015</v>
+        <v>46028</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5447,7 +5591,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5458,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5467,28 +5611,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G84" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="H84" s="3">
-        <v>46092</v>
+        <v>46042</v>
       </c>
       <c r="I84" s="3">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="J84" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5497,7 +5641,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5508,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5517,28 +5661,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G85" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="H85" s="3">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="I85" s="3">
-        <v>46056</v>
+        <v>46085</v>
       </c>
       <c r="J85" t="s">
-        <v>269</v>
+        <v>37</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5547,7 +5691,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5558,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5567,28 +5711,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="F86" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="G86" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="H86" s="3">
-        <v>46091</v>
+        <v>46057</v>
       </c>
       <c r="I86" s="3">
-        <v>46119</v>
+        <v>46111</v>
       </c>
       <c r="J86" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5597,7 +5741,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5608,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5617,28 +5761,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="F87" t="s">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="G87" s="3">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="H87" s="3">
-        <v>46028</v>
+        <v>46055</v>
       </c>
       <c r="I87" s="3">
-        <v>46055</v>
+        <v>46112</v>
       </c>
       <c r="J87" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5647,7 +5791,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5658,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5667,28 +5811,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F88" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G88" s="3">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="H88" s="3">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="I88" s="3">
-        <v>46108</v>
+        <v>46170</v>
       </c>
       <c r="J88" t="s">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5697,7 +5841,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5708,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5717,28 +5861,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>276</v>
       </c>
       <c r="F89" t="s">
-        <v>45</v>
+        <v>277</v>
       </c>
       <c r="G89" s="3">
-        <v>46027</v>
+        <v>46041</v>
       </c>
       <c r="H89" s="3">
-        <v>46126</v>
+        <v>46091</v>
       </c>
       <c r="I89" s="3">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="J89" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46022</v>
+        <v>46041</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5747,7 +5891,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5758,46 +5902,46 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
+        <v>280</v>
+      </c>
+      <c r="F90" t="s">
+        <v>281</v>
+      </c>
+      <c r="G90" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H90" s="3">
+        <v>46084</v>
+      </c>
+      <c r="I90" s="3">
+        <v>46106</v>
+      </c>
+      <c r="J90" t="s">
+        <v>37</v>
+      </c>
+      <c r="K90" t="s">
+        <v>5</v>
+      </c>
+      <c r="L90" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M90" t="s">
+        <v>6</v>
+      </c>
+      <c r="N90" t="s">
+        <v>7</v>
+      </c>
+      <c r="O90" t="s">
         <v>282</v>
-      </c>
-      <c r="C90" s="2">
-        <v>1</v>
-      </c>
-      <c r="D90" s="2">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
-        <v>60</v>
-      </c>
-      <c r="F90" t="s">
-        <v>61</v>
-      </c>
-      <c r="G90" s="3">
-        <v>46028</v>
-      </c>
-      <c r="H90" s="3">
-        <v>46030</v>
-      </c>
-      <c r="I90" s="3">
-        <v>46056</v>
-      </c>
-      <c r="J90" t="s">
-        <v>244</v>
-      </c>
-      <c r="K90" t="s">
-        <v>5</v>
-      </c>
-      <c r="L90" s="3">
-        <v>46028</v>
-      </c>
-      <c r="M90" t="s">
-        <v>6</v>
-      </c>
-      <c r="N90" t="s">
-        <v>7</v>
-      </c>
-      <c r="O90" t="s">
-        <v>283</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5808,37 +5952,37 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
+        <v>283</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
         <v>284</v>
       </c>
-      <c r="C91" s="2">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
-        <v>48</v>
-      </c>
       <c r="F91" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="G91" s="3">
-        <v>46028</v>
+        <v>46043</v>
       </c>
       <c r="H91" s="3">
-        <v>46049</v>
+        <v>46129</v>
       </c>
       <c r="I91" s="3">
-        <v>46091</v>
+        <v>46167</v>
       </c>
       <c r="J91" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46028</v>
+        <v>46043</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5847,7 +5991,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -5858,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5867,28 +6011,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>287</v>
+        <v>154</v>
       </c>
       <c r="F92" t="s">
-        <v>288</v>
+        <v>155</v>
       </c>
       <c r="G92" s="3">
-        <v>46028</v>
+        <v>46044</v>
       </c>
       <c r="H92" s="3">
-        <v>46031</v>
+        <v>46148</v>
       </c>
       <c r="I92" s="3">
-        <v>46079</v>
+        <v>46183</v>
       </c>
       <c r="J92" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46028</v>
+        <v>46044</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -5897,7 +6041,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -5908,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -5917,28 +6061,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="F93" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="G93" s="3">
-        <v>46029</v>
+        <v>46044</v>
       </c>
       <c r="H93" s="3">
-        <v>46043</v>
+        <v>46091</v>
       </c>
       <c r="I93" s="3">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="J93" t="s">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46029</v>
+        <v>46044</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -5947,7 +6091,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -5958,37 +6102,37 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
+        <v>294</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94" t="s">
+        <v>150</v>
+      </c>
+      <c r="F94" t="s">
+        <v>151</v>
+      </c>
+      <c r="G94" s="3">
+        <v>46048</v>
+      </c>
+      <c r="H94" s="3">
+        <v>46091</v>
+      </c>
+      <c r="I94" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J94" t="s">
         <v>292</v>
       </c>
-      <c r="C94" s="2">
-        <v>1</v>
-      </c>
-      <c r="D94" s="2">
-        <v>0</v>
-      </c>
-      <c r="E94" t="s">
-        <v>48</v>
-      </c>
-      <c r="F94" t="s">
-        <v>49</v>
-      </c>
-      <c r="G94" s="3">
-        <v>46029</v>
-      </c>
-      <c r="H94" s="3">
-        <v>46037</v>
-      </c>
-      <c r="I94" s="3">
-        <v>46079</v>
-      </c>
-      <c r="J94" t="s">
-        <v>244</v>
-      </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46029</v>
+        <v>46044</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -5997,7 +6141,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6008,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6017,28 +6161,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="F95" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="G95" s="3">
-        <v>46029</v>
+        <v>46044</v>
       </c>
       <c r="H95" s="3">
-        <v>46077</v>
+        <v>46090</v>
       </c>
       <c r="I95" s="3">
-        <v>46112</v>
+        <v>46154</v>
       </c>
       <c r="J95" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46029</v>
+        <v>46044</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6047,7 +6191,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6058,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6067,28 +6211,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>175</v>
+        <v>299</v>
       </c>
       <c r="F96" t="s">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="G96" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="H96" s="3">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="I96" s="3">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="J96" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6097,7 +6241,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6108,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6117,28 +6261,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F97" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G97" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="H97" s="3">
-        <v>46058</v>
+        <v>46085</v>
       </c>
       <c r="I97" s="3">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="J97" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6147,7 +6291,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6158,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6167,28 +6311,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F98" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G98" s="3">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="H98" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="I98" s="3">
-        <v>46198</v>
+        <v>46154</v>
       </c>
       <c r="J98" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6197,7 +6341,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6208,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6217,28 +6361,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F99" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G99" s="3">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="H99" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="I99" s="3">
-        <v>46106</v>
+        <v>46128</v>
       </c>
       <c r="J99" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6247,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6258,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6267,28 +6411,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>142</v>
+        <v>313</v>
       </c>
       <c r="F100" t="s">
-        <v>143</v>
+        <v>314</v>
       </c>
       <c r="G100" s="3">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="H100" s="3">
-        <v>46129</v>
+        <v>46090</v>
       </c>
       <c r="I100" s="3">
-        <v>46167</v>
+        <v>46142</v>
       </c>
       <c r="J100" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6297,7 +6441,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6308,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6317,28 +6461,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="F101" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="G101" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H101" s="3">
-        <v>46148</v>
+        <v>46052</v>
       </c>
       <c r="I101" s="3">
-        <v>46183</v>
+        <v>46085</v>
       </c>
       <c r="J101" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6347,7 +6491,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6358,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6367,28 +6511,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="F102" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="G102" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H102" s="3">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="I102" s="3">
-        <v>46128</v>
+        <v>46111</v>
       </c>
       <c r="J102" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6397,7 +6541,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6408,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6417,28 +6561,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="F103" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="G103" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H103" s="3">
-        <v>46091</v>
+        <v>46052</v>
       </c>
       <c r="I103" s="3">
-        <v>46183</v>
+        <v>46086</v>
       </c>
       <c r="J103" t="s">
-        <v>259</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6447,7 +6591,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6458,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6467,28 +6611,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="F104" t="s">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="G104" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H104" s="3">
-        <v>46090</v>
+        <v>46051</v>
       </c>
       <c r="I104" s="3">
-        <v>46154</v>
+        <v>46111</v>
       </c>
       <c r="J104" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6497,7 +6641,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6508,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6517,28 +6661,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F105" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G105" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H105" s="3">
-        <v>46063</v>
+        <v>46100</v>
       </c>
       <c r="I105" s="3">
-        <v>46105</v>
+        <v>46127</v>
       </c>
       <c r="J105" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6547,7 +6691,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6558,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6567,28 +6711,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F106" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G106" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="H106" s="3">
-        <v>46085</v>
+        <v>46099</v>
       </c>
       <c r="I106" s="3">
-        <v>46154</v>
+        <v>46127</v>
       </c>
       <c r="J106" t="s">
-        <v>228</v>
+        <v>327</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46044</v>
+        <v>46057</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6597,7 +6741,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6608,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6617,28 +6761,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>328</v>
+        <v>140</v>
       </c>
       <c r="F107" t="s">
-        <v>329</v>
+        <v>141</v>
       </c>
       <c r="G107" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="H107" s="3">
-        <v>46093</v>
+        <v>46104</v>
       </c>
       <c r="I107" s="3">
-        <v>46154</v>
+        <v>46133</v>
       </c>
       <c r="J107" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6647,7 +6791,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6658,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6667,28 +6811,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F108" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="G108" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="H108" s="3">
-        <v>46091</v>
+        <v>46106</v>
       </c>
       <c r="I108" s="3">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="J108" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6697,7 +6841,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6708,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6717,28 +6861,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F109" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G109" s="3">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="H109" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="I109" s="3">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="J109" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6747,7 +6891,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6758,37 +6902,37 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
+        <v>339</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>336</v>
+      </c>
+      <c r="F110" t="s">
         <v>337</v>
       </c>
-      <c r="C110" s="2">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
-        <v>162</v>
-      </c>
-      <c r="F110" t="s">
-        <v>163</v>
-      </c>
       <c r="G110" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="H110" s="3">
-        <v>46052</v>
+        <v>46160</v>
       </c>
       <c r="I110" s="3">
-        <v>46079</v>
+        <v>46209</v>
       </c>
       <c r="J110" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6797,7 +6941,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6808,7 +6952,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6817,28 +6961,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="F111" t="s">
-        <v>163</v>
+        <v>343</v>
       </c>
       <c r="G111" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H111" s="3">
         <v>46091</v>
       </c>
       <c r="I111" s="3">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="J111" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6847,7 +6991,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -6858,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6867,28 +7011,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="F112" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="G112" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H112" s="3">
-        <v>46052</v>
+        <v>46182</v>
       </c>
       <c r="I112" s="3">
-        <v>46079</v>
+        <v>46218</v>
       </c>
       <c r="J112" t="s">
-        <v>244</v>
+        <v>346</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -6897,7 +7041,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -6908,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -6917,28 +7061,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>334</v>
+        <v>88</v>
       </c>
       <c r="F113" t="s">
-        <v>335</v>
+        <v>89</v>
       </c>
       <c r="G113" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H113" s="3">
-        <v>46051</v>
+        <v>46182</v>
       </c>
       <c r="I113" s="3">
-        <v>46111</v>
+        <v>46218</v>
       </c>
       <c r="J113" t="s">
-        <v>196</v>
+        <v>346</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -6947,7 +7091,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -6955,49 +7099,49 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
+        <v>349</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
+        <v>88</v>
+      </c>
+      <c r="F114" t="s">
+        <v>89</v>
+      </c>
+      <c r="G114" s="3">
+        <v>46064</v>
+      </c>
+      <c r="H114" s="3">
+        <v>46246</v>
+      </c>
+      <c r="I114" s="3">
+        <v>46281</v>
+      </c>
+      <c r="J114" t="s">
         <v>346</v>
       </c>
-      <c r="C114" s="2">
-        <v>1</v>
-      </c>
-      <c r="D114" s="2">
-        <v>0</v>
-      </c>
-      <c r="E114" t="s">
-        <v>347</v>
-      </c>
-      <c r="F114" t="s">
-        <v>348</v>
-      </c>
-      <c r="G114" s="3">
-        <v>46028</v>
-      </c>
-      <c r="H114" s="3">
-        <v>46028</v>
-      </c>
-      <c r="I114" s="3">
-        <v>46037</v>
-      </c>
-      <c r="J114" t="s">
-        <v>269</v>
-      </c>
       <c r="K114" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46028</v>
+        <v>46064</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
       </c>
       <c r="N114" t="s">
+        <v>7</v>
+      </c>
+      <c r="O114" t="s">
         <v>350</v>
-      </c>
-      <c r="O114" t="s">
-        <v>351</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7005,10 +7149,10 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7017,37 +7161,37 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>353</v>
+        <v>88</v>
       </c>
       <c r="F115" t="s">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="G115" s="3">
-        <v>46035</v>
+        <v>46064</v>
       </c>
       <c r="H115" s="3">
-        <v>46044</v>
+        <v>46246</v>
       </c>
       <c r="I115" s="3">
-        <v>46066</v>
+        <v>46281</v>
       </c>
       <c r="J115" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="K115" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46035</v>
+        <v>46064</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
       </c>
       <c r="N115" t="s">
+        <v>7</v>
+      </c>
+      <c r="O115" t="s">
         <v>350</v>
-      </c>
-      <c r="O115" t="s">
-        <v>351</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7055,10 +7199,10 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7067,37 +7211,37 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>356</v>
+        <v>88</v>
       </c>
       <c r="F116" t="s">
-        <v>357</v>
+        <v>89</v>
       </c>
       <c r="G116" s="3">
-        <v>46042</v>
+        <v>46064</v>
       </c>
       <c r="H116" s="3">
-        <v>46042</v>
+        <v>46308</v>
       </c>
       <c r="I116" s="3">
-        <v>46043</v>
+        <v>46344</v>
       </c>
       <c r="J116" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="K116" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46042</v>
+        <v>46064</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
       </c>
       <c r="N116" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7105,10 +7249,10 @@
     </row>
     <row r="117" spans="1:16">
       <c r="A117" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7117,37 +7261,37 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>359</v>
+        <v>88</v>
       </c>
       <c r="F117" t="s">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="G117" s="3">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="H117" s="3">
-        <v>46051</v>
+        <v>46308</v>
       </c>
       <c r="I117" s="3">
-        <v>46057</v>
+        <v>46344</v>
       </c>
       <c r="J117" t="s">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="K117" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
       </c>
       <c r="N117" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7155,10 +7299,10 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7167,37 +7311,37 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>362</v>
+        <v>154</v>
       </c>
       <c r="F118" t="s">
-        <v>363</v>
+        <v>155</v>
       </c>
       <c r="G118" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H118" s="3">
-        <v>46059</v>
+        <v>46150</v>
       </c>
       <c r="I118" s="3">
-        <v>46062</v>
+        <v>46189</v>
       </c>
       <c r="J118" t="s">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="K118" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
       </c>
       <c r="N118" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7205,10 +7349,10 @@
     </row>
     <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7217,37 +7361,37 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>365</v>
+        <v>154</v>
       </c>
       <c r="F119" t="s">
-        <v>366</v>
+        <v>155</v>
       </c>
       <c r="G119" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H119" s="3">
-        <v>46052</v>
+        <v>46178</v>
       </c>
       <c r="I119" s="3">
-        <v>46058</v>
+        <v>46218</v>
       </c>
       <c r="J119" t="s">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="K119" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
       </c>
       <c r="N119" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7255,10 +7399,10 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7267,37 +7411,37 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>368</v>
+        <v>154</v>
       </c>
       <c r="F120" t="s">
-        <v>369</v>
+        <v>155</v>
       </c>
       <c r="G120" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="H120" s="3">
-        <v>46058</v>
+        <v>46244</v>
       </c>
       <c r="I120" s="3">
-        <v>46083</v>
+        <v>46281</v>
       </c>
       <c r="J120" t="s">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="K120" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
       </c>
       <c r="N120" t="s">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7305,51 +7449,1243 @@
     </row>
     <row r="121" spans="1:16">
       <c r="A121" t="s">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
+        <v>361</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
+        <v>154</v>
+      </c>
+      <c r="F121" t="s">
+        <v>155</v>
+      </c>
+      <c r="G121" s="3">
+        <v>46064</v>
+      </c>
+      <c r="H121" s="3">
+        <v>46303</v>
+      </c>
+      <c r="I121" s="3">
+        <v>46344</v>
+      </c>
+      <c r="J121" t="s">
+        <v>346</v>
+      </c>
+      <c r="K121" t="s">
+        <v>5</v>
+      </c>
+      <c r="L121" s="3">
+        <v>46064</v>
+      </c>
+      <c r="M121" t="s">
+        <v>6</v>
+      </c>
+      <c r="N121" t="s">
+        <v>7</v>
+      </c>
+      <c r="O121" t="s">
+        <v>362</v>
+      </c>
+      <c r="P121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>363</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
+        <v>325</v>
+      </c>
+      <c r="F122" t="s">
+        <v>326</v>
+      </c>
+      <c r="G122" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H122" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I122" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J122" t="s">
+        <v>289</v>
+      </c>
+      <c r="K122" t="s">
+        <v>5</v>
+      </c>
+      <c r="L122" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M122" t="s">
+        <v>6</v>
+      </c>
+      <c r="N122" t="s">
+        <v>7</v>
+      </c>
+      <c r="O122" t="s">
+        <v>364</v>
+      </c>
+      <c r="P122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" t="s">
+        <v>365</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>325</v>
+      </c>
+      <c r="F123" t="s">
+        <v>326</v>
+      </c>
+      <c r="G123" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H123" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I123" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J123" t="s">
+        <v>289</v>
+      </c>
+      <c r="K123" t="s">
+        <v>5</v>
+      </c>
+      <c r="L123" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M123" t="s">
+        <v>6</v>
+      </c>
+      <c r="N123" t="s">
+        <v>7</v>
+      </c>
+      <c r="O123" t="s">
+        <v>364</v>
+      </c>
+      <c r="P123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>366</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
+        <v>325</v>
+      </c>
+      <c r="F124" t="s">
+        <v>326</v>
+      </c>
+      <c r="G124" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H124" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I124" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J124" t="s">
+        <v>289</v>
+      </c>
+      <c r="K124" t="s">
+        <v>5</v>
+      </c>
+      <c r="L124" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M124" t="s">
+        <v>6</v>
+      </c>
+      <c r="N124" t="s">
+        <v>7</v>
+      </c>
+      <c r="O124" t="s">
+        <v>364</v>
+      </c>
+      <c r="P124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" t="s">
+        <v>367</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
+        <v>210</v>
+      </c>
+      <c r="F125" t="s">
+        <v>211</v>
+      </c>
+      <c r="G125" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H125" s="3">
+        <v>46107</v>
+      </c>
+      <c r="I125" s="3">
+        <v>46133</v>
+      </c>
+      <c r="J125" t="s">
+        <v>286</v>
+      </c>
+      <c r="K125" t="s">
+        <v>5</v>
+      </c>
+      <c r="L125" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M125" t="s">
+        <v>6</v>
+      </c>
+      <c r="N125" t="s">
+        <v>7</v>
+      </c>
+      <c r="O125" t="s">
+        <v>368</v>
+      </c>
+      <c r="P125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" t="s">
+        <v>369</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
         <v>370</v>
       </c>
-      <c r="C121" s="2">
-        <v>1</v>
-      </c>
-      <c r="D121" s="2">
-        <v>0</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="F126" t="s">
         <v>371</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G126" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H126" s="3">
+        <v>46079</v>
+      </c>
+      <c r="I126" s="3">
+        <v>46134</v>
+      </c>
+      <c r="J126" t="s">
+        <v>212</v>
+      </c>
+      <c r="K126" t="s">
+        <v>5</v>
+      </c>
+      <c r="L126" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M126" t="s">
+        <v>6</v>
+      </c>
+      <c r="N126" t="s">
+        <v>7</v>
+      </c>
+      <c r="O126" t="s">
         <v>372</v>
       </c>
-      <c r="G121" s="3">
+      <c r="P126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" t="s">
+        <v>373</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
+        <v>370</v>
+      </c>
+      <c r="F127" t="s">
+        <v>371</v>
+      </c>
+      <c r="G127" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H127" s="3">
+        <v>46167</v>
+      </c>
+      <c r="I127" s="3">
+        <v>46218</v>
+      </c>
+      <c r="J127" t="s">
+        <v>286</v>
+      </c>
+      <c r="K127" t="s">
+        <v>5</v>
+      </c>
+      <c r="L127" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M127" t="s">
+        <v>6</v>
+      </c>
+      <c r="N127" t="s">
+        <v>7</v>
+      </c>
+      <c r="O127" t="s">
+        <v>374</v>
+      </c>
+      <c r="P127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" t="s">
+        <v>375</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>370</v>
+      </c>
+      <c r="F128" t="s">
+        <v>371</v>
+      </c>
+      <c r="G128" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H128" s="3">
+        <v>46167</v>
+      </c>
+      <c r="I128" s="3">
+        <v>46218</v>
+      </c>
+      <c r="J128" t="s">
+        <v>286</v>
+      </c>
+      <c r="K128" t="s">
+        <v>5</v>
+      </c>
+      <c r="L128" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M128" t="s">
+        <v>6</v>
+      </c>
+      <c r="N128" t="s">
+        <v>7</v>
+      </c>
+      <c r="O128" t="s">
+        <v>374</v>
+      </c>
+      <c r="P128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" t="s">
+        <v>376</v>
+      </c>
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" t="s">
+        <v>370</v>
+      </c>
+      <c r="F129" t="s">
+        <v>371</v>
+      </c>
+      <c r="G129" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H129" s="3">
+        <v>46217</v>
+      </c>
+      <c r="I129" s="3">
+        <v>46267</v>
+      </c>
+      <c r="J129" t="s">
+        <v>286</v>
+      </c>
+      <c r="K129" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M129" t="s">
+        <v>6</v>
+      </c>
+      <c r="N129" t="s">
+        <v>7</v>
+      </c>
+      <c r="O129" t="s">
+        <v>377</v>
+      </c>
+      <c r="P129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s">
+        <v>378</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" t="s">
+        <v>370</v>
+      </c>
+      <c r="F130" t="s">
+        <v>371</v>
+      </c>
+      <c r="G130" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H130" s="3">
+        <v>46217</v>
+      </c>
+      <c r="I130" s="3">
+        <v>46267</v>
+      </c>
+      <c r="J130" t="s">
+        <v>286</v>
+      </c>
+      <c r="K130" t="s">
+        <v>5</v>
+      </c>
+      <c r="L130" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M130" t="s">
+        <v>6</v>
+      </c>
+      <c r="N130" t="s">
+        <v>7</v>
+      </c>
+      <c r="O130" t="s">
+        <v>377</v>
+      </c>
+      <c r="P130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s">
+        <v>379</v>
+      </c>
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" t="s">
+        <v>370</v>
+      </c>
+      <c r="F131" t="s">
+        <v>371</v>
+      </c>
+      <c r="G131" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H131" s="3">
+        <v>46254</v>
+      </c>
+      <c r="I131" s="3">
+        <v>46309</v>
+      </c>
+      <c r="J131" t="s">
+        <v>286</v>
+      </c>
+      <c r="K131" t="s">
+        <v>5</v>
+      </c>
+      <c r="L131" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M131" t="s">
+        <v>6</v>
+      </c>
+      <c r="N131" t="s">
+        <v>7</v>
+      </c>
+      <c r="O131" t="s">
+        <v>380</v>
+      </c>
+      <c r="P131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" t="s">
+        <v>381</v>
+      </c>
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" t="s">
+        <v>370</v>
+      </c>
+      <c r="F132" t="s">
+        <v>371</v>
+      </c>
+      <c r="G132" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H132" s="3">
+        <v>46254</v>
+      </c>
+      <c r="I132" s="3">
+        <v>46309</v>
+      </c>
+      <c r="J132" t="s">
+        <v>286</v>
+      </c>
+      <c r="K132" t="s">
+        <v>5</v>
+      </c>
+      <c r="L132" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M132" t="s">
+        <v>6</v>
+      </c>
+      <c r="N132" t="s">
+        <v>7</v>
+      </c>
+      <c r="O132" t="s">
+        <v>380</v>
+      </c>
+      <c r="P132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
+        <v>382</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133" t="s">
+        <v>48</v>
+      </c>
+      <c r="F133" t="s">
+        <v>49</v>
+      </c>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I133" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J133" t="s">
+        <v>383</v>
+      </c>
+      <c r="K133" t="s">
+        <v>5</v>
+      </c>
+      <c r="L133" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M133" t="s">
+        <v>6</v>
+      </c>
+      <c r="N133" t="s">
+        <v>7</v>
+      </c>
+      <c r="O133" t="s">
+        <v>384</v>
+      </c>
+      <c r="P133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>385</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
+        <v>48</v>
+      </c>
+      <c r="F134" t="s">
+        <v>49</v>
+      </c>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I134" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J134" t="s">
+        <v>383</v>
+      </c>
+      <c r="K134" t="s">
+        <v>5</v>
+      </c>
+      <c r="L134" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M134" t="s">
+        <v>6</v>
+      </c>
+      <c r="N134" t="s">
+        <v>7</v>
+      </c>
+      <c r="O134" t="s">
+        <v>384</v>
+      </c>
+      <c r="P134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" t="s">
+        <v>386</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>48</v>
+      </c>
+      <c r="F135" t="s">
+        <v>49</v>
+      </c>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I135" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J135" t="s">
+        <v>383</v>
+      </c>
+      <c r="K135" t="s">
+        <v>5</v>
+      </c>
+      <c r="L135" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M135" t="s">
+        <v>6</v>
+      </c>
+      <c r="N135" t="s">
+        <v>7</v>
+      </c>
+      <c r="O135" t="s">
+        <v>384</v>
+      </c>
+      <c r="P135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" t="s">
+        <v>0</v>
+      </c>
+      <c r="B136" t="s">
+        <v>387</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s">
+        <v>48</v>
+      </c>
+      <c r="F136" t="s">
+        <v>49</v>
+      </c>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I136" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J136" t="s">
+        <v>383</v>
+      </c>
+      <c r="K136" t="s">
+        <v>5</v>
+      </c>
+      <c r="L136" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M136" t="s">
+        <v>6</v>
+      </c>
+      <c r="N136" t="s">
+        <v>7</v>
+      </c>
+      <c r="O136" t="s">
+        <v>384</v>
+      </c>
+      <c r="P136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" t="s">
+        <v>388</v>
+      </c>
+      <c r="B137" t="s">
+        <v>389</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>390</v>
+      </c>
+      <c r="F137" t="s">
+        <v>391</v>
+      </c>
+      <c r="G137" s="3">
+        <v>46035</v>
+      </c>
+      <c r="H137" s="3">
         <v>46052</v>
       </c>
-      <c r="H121" s="3">
+      <c r="I137" s="3">
+        <v>46076</v>
+      </c>
+      <c r="J137" t="s">
+        <v>26</v>
+      </c>
+      <c r="K137" t="s">
+        <v>392</v>
+      </c>
+      <c r="L137" s="3">
+        <v>46035</v>
+      </c>
+      <c r="M137" t="s">
+        <v>6</v>
+      </c>
+      <c r="N137" t="s">
+        <v>393</v>
+      </c>
+      <c r="O137" t="s">
+        <v>394</v>
+      </c>
+      <c r="P137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" t="s">
+        <v>395</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0</v>
+      </c>
+      <c r="E138" t="s">
+        <v>396</v>
+      </c>
+      <c r="F138" t="s">
+        <v>397</v>
+      </c>
+      <c r="G138" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H138" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I138" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J138" t="s">
+        <v>254</v>
+      </c>
+      <c r="K138" t="s">
+        <v>392</v>
+      </c>
+      <c r="L138" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M138" t="s">
+        <v>6</v>
+      </c>
+      <c r="N138" t="s">
+        <v>393</v>
+      </c>
+      <c r="O138" t="s">
+        <v>394</v>
+      </c>
+      <c r="P138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" t="s">
+        <v>388</v>
+      </c>
+      <c r="B139" t="s">
+        <v>398</v>
+      </c>
+      <c r="C139" s="2">
+        <v>1</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0</v>
+      </c>
+      <c r="E139" t="s">
+        <v>399</v>
+      </c>
+      <c r="F139" t="s">
+        <v>400</v>
+      </c>
+      <c r="G139" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H139" s="3">
+        <v>46059</v>
+      </c>
+      <c r="I139" s="3">
+        <v>46062</v>
+      </c>
+      <c r="J139" t="s">
+        <v>207</v>
+      </c>
+      <c r="K139" t="s">
+        <v>392</v>
+      </c>
+      <c r="L139" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M139" t="s">
+        <v>6</v>
+      </c>
+      <c r="N139" t="s">
+        <v>393</v>
+      </c>
+      <c r="O139" t="s">
+        <v>394</v>
+      </c>
+      <c r="P139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" t="s">
+        <v>388</v>
+      </c>
+      <c r="B140" t="s">
+        <v>401</v>
+      </c>
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0</v>
+      </c>
+      <c r="E140" t="s">
+        <v>402</v>
+      </c>
+      <c r="F140" t="s">
+        <v>403</v>
+      </c>
+      <c r="G140" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H140" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I140" s="3">
+        <v>46058</v>
+      </c>
+      <c r="J140" t="s">
+        <v>254</v>
+      </c>
+      <c r="K140" t="s">
+        <v>392</v>
+      </c>
+      <c r="L140" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M140" t="s">
+        <v>6</v>
+      </c>
+      <c r="N140" t="s">
+        <v>393</v>
+      </c>
+      <c r="O140" t="s">
+        <v>394</v>
+      </c>
+      <c r="P140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" t="s">
+        <v>388</v>
+      </c>
+      <c r="B141" t="s">
+        <v>404</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>405</v>
+      </c>
+      <c r="F141" t="s">
+        <v>406</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46077</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J141" t="s">
+        <v>407</v>
+      </c>
+      <c r="K141" t="s">
+        <v>392</v>
+      </c>
+      <c r="L141" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N141" t="s">
+        <v>393</v>
+      </c>
+      <c r="O141" t="s">
+        <v>394</v>
+      </c>
+      <c r="P141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>388</v>
+      </c>
+      <c r="B142" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
+        <v>409</v>
+      </c>
+      <c r="F142" t="s">
+        <v>410</v>
+      </c>
+      <c r="G142" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H142" s="3">
         <v>46064</v>
       </c>
-      <c r="I121" s="3">
+      <c r="I142" s="3">
         <v>46066</v>
       </c>
-      <c r="J121" t="s">
-        <v>228</v>
-      </c>
-      <c r="K121" t="s">
-        <v>349</v>
-      </c>
-      <c r="L121" s="3">
+      <c r="J142" t="s">
+        <v>407</v>
+      </c>
+      <c r="K142" t="s">
+        <v>392</v>
+      </c>
+      <c r="L142" s="3">
         <v>46052</v>
       </c>
-      <c r="M121" t="s">
-        <v>6</v>
-      </c>
-      <c r="N121" t="s">
-        <v>350</v>
-      </c>
-      <c r="O121" t="s">
-        <v>351</v>
-      </c>
-      <c r="P121" t="s">
+      <c r="M142" t="s">
+        <v>6</v>
+      </c>
+      <c r="N142" t="s">
+        <v>393</v>
+      </c>
+      <c r="O142" t="s">
+        <v>394</v>
+      </c>
+      <c r="P142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>388</v>
+      </c>
+      <c r="B143" t="s">
+        <v>411</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>412</v>
+      </c>
+      <c r="F143" t="s">
+        <v>413</v>
+      </c>
+      <c r="G143" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J143" t="s">
+        <v>254</v>
+      </c>
+      <c r="K143" t="s">
+        <v>392</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
+        <v>393</v>
+      </c>
+      <c r="O143" t="s">
+        <v>394</v>
+      </c>
+      <c r="P143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>388</v>
+      </c>
+      <c r="B144" t="s">
+        <v>414</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>0</v>
+      </c>
+      <c r="E144" t="s">
+        <v>415</v>
+      </c>
+      <c r="F144" t="s">
+        <v>416</v>
+      </c>
+      <c r="G144" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H144" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I144" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J144" t="s">
+        <v>207</v>
+      </c>
+      <c r="K144" t="s">
+        <v>392</v>
+      </c>
+      <c r="L144" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M144" t="s">
+        <v>6</v>
+      </c>
+      <c r="N144" t="s">
+        <v>393</v>
+      </c>
+      <c r="O144" t="s">
+        <v>394</v>
+      </c>
+      <c r="P144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>388</v>
+      </c>
+      <c r="B145" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
+        <v>418</v>
+      </c>
+      <c r="F145" t="s">
+        <v>419</v>
+      </c>
+      <c r="G145" s="3">
+        <v>46077</v>
+      </c>
+      <c r="H145" s="3">
+        <v>46078</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46084</v>
+      </c>
+      <c r="J145" t="s">
+        <v>420</v>
+      </c>
+      <c r="K145" t="s">
+        <v>392</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46077</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>393</v>
+      </c>
+      <c r="O145" t="s">
+        <v>394</v>
+      </c>
+      <c r="P145" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="445">
   <si>
     <t>ZP01</t>
   </si>
@@ -754,9 +754,6 @@
     <t>100003494</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
     <t>1100186710</t>
   </si>
   <si>
@@ -781,12 +778,6 @@
     <t>1300000181</t>
   </si>
   <si>
-    <t>100003497</t>
-  </si>
-  <si>
-    <t>1100187100</t>
-  </si>
-  <si>
     <t>100003498</t>
   </si>
   <si>
@@ -1003,6 +994,9 @@
     <t>100003522</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
     <t>1100187480</t>
   </si>
   <si>
@@ -1162,9 +1156,6 @@
     <t>100003549</t>
   </si>
   <si>
-    <t>CRTD MSPT PRC  SETC</t>
-  </si>
-  <si>
     <t>1100186250</t>
   </si>
   <si>
@@ -1177,6 +1168,42 @@
     <t>100003552</t>
   </si>
   <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>980000018800</t>
+  </si>
+  <si>
+    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100171080</t>
+  </si>
+  <si>
+    <t>100003554</t>
+  </si>
+  <si>
+    <t>980000001000</t>
+  </si>
+  <si>
+    <t>LG-800_X=800, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100191660</t>
+  </si>
+  <si>
+    <t>100003555</t>
+  </si>
+  <si>
+    <t>1100191670</t>
+  </si>
+  <si>
+    <t>100003556</t>
+  </si>
+  <si>
+    <t>1100191680</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -1225,6 +1252,9 @@
     <t>D8K 主軸,010801_BT50,M50E,C045</t>
   </si>
   <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
     <t>630000337</t>
   </si>
   <si>
@@ -1234,9 +1264,6 @@
     <t>自動頭HF-A90,031944_1°-BT50-45°-4K-C</t>
   </si>
   <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
     <t>630000338</t>
   </si>
   <si>
@@ -1271,9 +1298,6 @@
   </si>
   <si>
     <t>DA15K 主軸,021857_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC SETC</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1426,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1449,52 +1473,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1773,7 +1797,7 @@
         <v>45580</v>
       </c>
       <c r="I7" s="3">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="J7" t="s">
         <v>26</v>
@@ -1973,7 +1997,7 @@
         <v>45624</v>
       </c>
       <c r="I11" s="3">
-        <v>46066</v>
+        <v>46084</v>
       </c>
       <c r="J11" t="s">
         <v>37</v>
@@ -2173,7 +2197,7 @@
         <v>45827</v>
       </c>
       <c r="I15" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="J15" t="s">
         <v>37</v>
@@ -2423,7 +2447,7 @@
         <v>45945</v>
       </c>
       <c r="I20" s="3">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2873,7 +2897,7 @@
         <v>46045</v>
       </c>
       <c r="I29" s="3">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="J29" t="s">
         <v>37</v>
@@ -3123,7 +3147,7 @@
         <v>46041</v>
       </c>
       <c r="I34" s="3">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="J34" t="s">
         <v>37</v>
@@ -3323,7 +3347,7 @@
         <v>46050</v>
       </c>
       <c r="I38" s="3">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="J38" t="s">
         <v>37</v>
@@ -3523,7 +3547,7 @@
         <v>46042</v>
       </c>
       <c r="I42" s="3">
-        <v>46163</v>
+        <v>46178</v>
       </c>
       <c r="J42" t="s">
         <v>37</v>
@@ -3573,7 +3597,7 @@
         <v>46031</v>
       </c>
       <c r="I43" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="J43" t="s">
         <v>26</v>
@@ -3673,7 +3697,7 @@
         <v>46031</v>
       </c>
       <c r="I45" s="3">
-        <v>46097</v>
+        <v>46091</v>
       </c>
       <c r="J45" t="s">
         <v>26</v>
@@ -4970,10 +4994,10 @@
         <v>46013</v>
       </c>
       <c r="H71" s="3">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="I71" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="J71" t="s">
         <v>37</v>
@@ -5326,7 +5350,7 @@
         <v>46055</v>
       </c>
       <c r="J78" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -5341,7 +5365,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5352,19 +5376,19 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
         <v>249</v>
       </c>
-      <c r="C79" s="2">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>250</v>
-      </c>
-      <c r="F79" t="s">
-        <v>251</v>
       </c>
       <c r="G79" s="3">
         <v>46022</v>
@@ -5373,7 +5397,7 @@
         <v>46056</v>
       </c>
       <c r="I79" s="3">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="J79" t="s">
         <v>26</v>
@@ -5391,7 +5415,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5402,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5426,7 +5450,7 @@
         <v>46188</v>
       </c>
       <c r="J80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
@@ -5441,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5452,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5461,19 +5485,19 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F81" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G81" s="3">
         <v>46028</v>
       </c>
       <c r="H81" s="3">
-        <v>46030</v>
+        <v>46048</v>
       </c>
       <c r="I81" s="3">
-        <v>46066</v>
+        <v>46087</v>
       </c>
       <c r="J81" t="s">
         <v>37</v>
@@ -5491,7 +5515,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5502,28 +5526,28 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
+        <v>257</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
         <v>258</v>
       </c>
-      <c r="C82" s="2">
-        <v>1</v>
-      </c>
-      <c r="D82" s="2">
-        <v>0</v>
-      </c>
-      <c r="E82" t="s">
-        <v>48</v>
-      </c>
       <c r="F82" t="s">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="G82" s="3">
         <v>46028</v>
       </c>
       <c r="H82" s="3">
-        <v>46048</v>
+        <v>46031</v>
       </c>
       <c r="I82" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="J82" t="s">
         <v>37</v>
@@ -5541,7 +5565,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5552,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5561,16 +5585,16 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>261</v>
+        <v>48</v>
       </c>
       <c r="F83" t="s">
-        <v>262</v>
+        <v>49</v>
       </c>
       <c r="G83" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H83" s="3">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="I83" s="3">
         <v>46087</v>
@@ -5582,7 +5606,7 @@
         <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5591,7 +5615,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5602,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5620,10 +5644,10 @@
         <v>46029</v>
       </c>
       <c r="H84" s="3">
-        <v>46042</v>
+        <v>46037</v>
       </c>
       <c r="I84" s="3">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="J84" t="s">
         <v>37</v>
@@ -5641,7 +5665,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5652,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5661,19 +5685,19 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="F85" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="G85" s="3">
         <v>46029</v>
       </c>
       <c r="H85" s="3">
-        <v>46037</v>
+        <v>46057</v>
       </c>
       <c r="I85" s="3">
-        <v>46085</v>
+        <v>46107</v>
       </c>
       <c r="J85" t="s">
         <v>37</v>
@@ -5702,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5711,19 +5735,19 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F86" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G86" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="H86" s="3">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="I86" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="J86" t="s">
         <v>37</v>
@@ -5732,7 +5756,7 @@
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5741,7 +5765,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5752,28 +5776,28 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
+        <v>268</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
         <v>269</v>
       </c>
-      <c r="C87" s="2">
-        <v>1</v>
-      </c>
-      <c r="D87" s="2">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
-        <v>154</v>
-      </c>
       <c r="F87" t="s">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="G87" s="3">
         <v>46031</v>
       </c>
       <c r="H87" s="3">
-        <v>46055</v>
+        <v>46050</v>
       </c>
       <c r="I87" s="3">
-        <v>46112</v>
+        <v>46170</v>
       </c>
       <c r="J87" t="s">
         <v>37</v>
@@ -5791,7 +5815,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5802,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5811,28 +5835,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G88" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="H88" s="3">
-        <v>46050</v>
+        <v>46091</v>
       </c>
       <c r="I88" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J88" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46031</v>
+        <v>46041</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5841,7 +5865,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5852,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5861,28 +5885,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G89" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="H89" s="3">
-        <v>46091</v>
+        <v>46076</v>
       </c>
       <c r="I89" s="3">
-        <v>46198</v>
+        <v>46100</v>
       </c>
       <c r="J89" t="s">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5891,7 +5915,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5902,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5911,22 +5935,22 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F90" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G90" s="3">
         <v>46043</v>
       </c>
       <c r="H90" s="3">
-        <v>46084</v>
+        <v>46129</v>
       </c>
       <c r="I90" s="3">
-        <v>46106</v>
+        <v>46167</v>
       </c>
       <c r="J90" t="s">
-        <v>37</v>
+        <v>283</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
@@ -5941,7 +5965,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5952,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5961,19 +5985,19 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>284</v>
+        <v>154</v>
       </c>
       <c r="F91" t="s">
-        <v>285</v>
+        <v>155</v>
       </c>
       <c r="G91" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H91" s="3">
-        <v>46129</v>
+        <v>46148</v>
       </c>
       <c r="I91" s="3">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="J91" t="s">
         <v>286</v>
@@ -5982,7 +6006,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -6020,10 +6044,10 @@
         <v>46044</v>
       </c>
       <c r="H92" s="3">
-        <v>46148</v>
+        <v>46091</v>
       </c>
       <c r="I92" s="3">
-        <v>46183</v>
+        <v>46128</v>
       </c>
       <c r="J92" t="s">
         <v>289</v>
@@ -6061,22 +6085,22 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F93" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G93" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H93" s="3">
         <v>46091</v>
       </c>
       <c r="I93" s="3">
-        <v>46128</v>
+        <v>46183</v>
       </c>
       <c r="J93" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
@@ -6091,7 +6115,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6102,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6111,22 +6135,22 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F94" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G94" s="3">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="H94" s="3">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="I94" s="3">
-        <v>46183</v>
+        <v>46154</v>
       </c>
       <c r="J94" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
@@ -6141,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6152,31 +6176,31 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" t="s">
         <v>296</v>
       </c>
-      <c r="C95" s="2">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0</v>
-      </c>
-      <c r="E95" t="s">
-        <v>136</v>
-      </c>
       <c r="F95" t="s">
-        <v>137</v>
+        <v>297</v>
       </c>
       <c r="G95" s="3">
         <v>46044</v>
       </c>
       <c r="H95" s="3">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="I95" s="3">
-        <v>46154</v>
+        <v>46107</v>
       </c>
       <c r="J95" t="s">
-        <v>292</v>
+        <v>37</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
@@ -6191,7 +6215,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6202,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6211,22 +6235,22 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G96" s="3">
         <v>46044</v>
       </c>
       <c r="H96" s="3">
-        <v>46065</v>
+        <v>46085</v>
       </c>
       <c r="I96" s="3">
-        <v>46107</v>
+        <v>46154</v>
       </c>
       <c r="J96" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
@@ -6241,7 +6265,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6252,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6261,28 +6285,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G97" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H97" s="3">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="I97" s="3">
         <v>46154</v>
       </c>
       <c r="J97" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6291,7 +6315,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6302,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6311,22 +6335,22 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="F98" t="s">
-        <v>308</v>
+        <v>155</v>
       </c>
       <c r="G98" s="3">
         <v>46048</v>
       </c>
       <c r="H98" s="3">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="I98" s="3">
-        <v>46154</v>
+        <v>46128</v>
       </c>
       <c r="J98" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
@@ -6341,7 +6365,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6352,37 +6376,37 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
+        <v>309</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
         <v>310</v>
       </c>
-      <c r="C99" s="2">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
-        <v>154</v>
-      </c>
       <c r="F99" t="s">
-        <v>155</v>
+        <v>311</v>
       </c>
       <c r="G99" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="H99" s="3">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="I99" s="3">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="J99" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6391,7 +6415,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6402,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6411,37 +6435,37 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="F100" t="s">
+        <v>278</v>
+      </c>
+      <c r="G100" s="3">
+        <v>46050</v>
+      </c>
+      <c r="H100" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I100" s="3">
+        <v>46085</v>
+      </c>
+      <c r="J100" t="s">
+        <v>37</v>
+      </c>
+      <c r="K100" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>46050</v>
+      </c>
+      <c r="M100" t="s">
+        <v>6</v>
+      </c>
+      <c r="N100" t="s">
+        <v>7</v>
+      </c>
+      <c r="O100" t="s">
         <v>314</v>
-      </c>
-      <c r="G100" s="3">
-        <v>46049</v>
-      </c>
-      <c r="H100" s="3">
-        <v>46090</v>
-      </c>
-      <c r="I100" s="3">
-        <v>46142</v>
-      </c>
-      <c r="J100" t="s">
-        <v>292</v>
-      </c>
-      <c r="K100" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>46049</v>
-      </c>
-      <c r="M100" t="s">
-        <v>6</v>
-      </c>
-      <c r="N100" t="s">
-        <v>7</v>
-      </c>
-      <c r="O100" t="s">
-        <v>315</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6452,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6461,19 +6485,19 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F101" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G101" s="3">
         <v>46050</v>
       </c>
       <c r="H101" s="3">
-        <v>46052</v>
+        <v>46090</v>
       </c>
       <c r="I101" s="3">
-        <v>46085</v>
+        <v>46111</v>
       </c>
       <c r="J101" t="s">
         <v>37</v>
@@ -6491,7 +6515,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6502,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6511,19 +6535,19 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F102" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G102" s="3">
         <v>46050</v>
       </c>
       <c r="H102" s="3">
-        <v>46090</v>
+        <v>46052</v>
       </c>
       <c r="I102" s="3">
-        <v>46111</v>
+        <v>46086</v>
       </c>
       <c r="J102" t="s">
         <v>37</v>
@@ -6541,7 +6565,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6552,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6561,19 +6585,19 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="F103" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="G103" s="3">
         <v>46050</v>
       </c>
       <c r="H103" s="3">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="I103" s="3">
-        <v>46086</v>
+        <v>46111</v>
       </c>
       <c r="J103" t="s">
         <v>37</v>
@@ -6591,7 +6615,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6602,37 +6626,37 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
+        <v>321</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
         <v>322</v>
       </c>
-      <c r="C104" s="2">
-        <v>1</v>
-      </c>
-      <c r="D104" s="2">
-        <v>0</v>
-      </c>
-      <c r="E104" t="s">
-        <v>313</v>
-      </c>
       <c r="F104" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="G104" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="H104" s="3">
-        <v>46051</v>
+        <v>46100</v>
       </c>
       <c r="I104" s="3">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="J104" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6641,7 +6665,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6652,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6661,16 +6685,16 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F105" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G105" s="3">
         <v>46057</v>
       </c>
       <c r="H105" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="I105" s="3">
         <v>46127</v>
@@ -6711,28 +6735,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>325</v>
+        <v>140</v>
       </c>
       <c r="F106" t="s">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="G106" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="H106" s="3">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="I106" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="J106" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6770,13 +6794,13 @@
         <v>46062</v>
       </c>
       <c r="H107" s="3">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="I107" s="3">
         <v>46133</v>
       </c>
       <c r="J107" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
@@ -6811,19 +6835,19 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>140</v>
+        <v>334</v>
       </c>
       <c r="F108" t="s">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="G108" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H108" s="3">
-        <v>46106</v>
+        <v>46094</v>
       </c>
       <c r="I108" s="3">
-        <v>46133</v>
+        <v>46147</v>
       </c>
       <c r="J108" t="s">
         <v>289</v>
@@ -6832,7 +6856,7 @@
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6841,7 +6865,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6852,31 +6876,31 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
+        <v>337</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
+        <v>334</v>
+      </c>
+      <c r="F109" t="s">
         <v>335</v>
-      </c>
-      <c r="C109" s="2">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
-        <v>336</v>
-      </c>
-      <c r="F109" t="s">
-        <v>337</v>
       </c>
       <c r="G109" s="3">
         <v>46063</v>
       </c>
       <c r="H109" s="3">
-        <v>46094</v>
+        <v>46160</v>
       </c>
       <c r="I109" s="3">
-        <v>46147</v>
+        <v>46209</v>
       </c>
       <c r="J109" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
@@ -6911,28 +6935,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F110" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G110" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H110" s="3">
-        <v>46160</v>
+        <v>46091</v>
       </c>
       <c r="I110" s="3">
-        <v>46209</v>
+        <v>46119</v>
       </c>
       <c r="J110" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6941,7 +6965,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6952,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6961,22 +6985,22 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>342</v>
+        <v>88</v>
       </c>
       <c r="F111" t="s">
-        <v>343</v>
+        <v>89</v>
       </c>
       <c r="G111" s="3">
         <v>46064</v>
       </c>
       <c r="H111" s="3">
-        <v>46091</v>
+        <v>46182</v>
       </c>
       <c r="I111" s="3">
-        <v>46119</v>
+        <v>46218</v>
       </c>
       <c r="J111" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
@@ -6991,7 +7015,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -7002,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7026,7 +7050,7 @@
         <v>46218</v>
       </c>
       <c r="J112" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
@@ -7041,7 +7065,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7052,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7070,13 +7094,13 @@
         <v>46064</v>
       </c>
       <c r="H113" s="3">
-        <v>46182</v>
+        <v>46246</v>
       </c>
       <c r="I113" s="3">
-        <v>46218</v>
+        <v>46281</v>
       </c>
       <c r="J113" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -7091,7 +7115,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7126,7 +7150,7 @@
         <v>46281</v>
       </c>
       <c r="J114" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -7141,7 +7165,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7152,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7170,13 +7194,13 @@
         <v>46064</v>
       </c>
       <c r="H115" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I115" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J115" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -7191,7 +7215,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7226,7 +7250,7 @@
         <v>46344</v>
       </c>
       <c r="J116" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
@@ -7241,7 +7265,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7252,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7261,22 +7285,22 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="F117" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="G117" s="3">
         <v>46064</v>
       </c>
       <c r="H117" s="3">
-        <v>46308</v>
+        <v>46150</v>
       </c>
       <c r="I117" s="3">
-        <v>46344</v>
+        <v>46189</v>
       </c>
       <c r="J117" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -7291,7 +7315,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7320,13 +7344,13 @@
         <v>46064</v>
       </c>
       <c r="H118" s="3">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="I118" s="3">
-        <v>46189</v>
+        <v>46218</v>
       </c>
       <c r="J118" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
@@ -7370,13 +7394,13 @@
         <v>46064</v>
       </c>
       <c r="H119" s="3">
-        <v>46178</v>
+        <v>46244</v>
       </c>
       <c r="I119" s="3">
-        <v>46218</v>
+        <v>46281</v>
       </c>
       <c r="J119" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
@@ -7420,13 +7444,13 @@
         <v>46064</v>
       </c>
       <c r="H120" s="3">
-        <v>46244</v>
+        <v>46303</v>
       </c>
       <c r="I120" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
@@ -7461,28 +7485,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>154</v>
+        <v>322</v>
       </c>
       <c r="F121" t="s">
-        <v>155</v>
+        <v>323</v>
       </c>
       <c r="G121" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H121" s="3">
-        <v>46303</v>
+        <v>46092</v>
       </c>
       <c r="I121" s="3">
-        <v>46344</v>
+        <v>46119</v>
       </c>
       <c r="J121" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7511,10 +7535,10 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F122" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G122" s="3">
         <v>46076</v>
@@ -7526,7 +7550,7 @@
         <v>46119</v>
       </c>
       <c r="J122" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
@@ -7541,7 +7565,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7552,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7561,10 +7585,10 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F123" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G123" s="3">
         <v>46076</v>
@@ -7576,7 +7600,7 @@
         <v>46119</v>
       </c>
       <c r="J123" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
@@ -7591,7 +7615,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7602,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7611,19 +7635,19 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="F124" t="s">
-        <v>326</v>
+        <v>211</v>
       </c>
       <c r="G124" s="3">
         <v>46076</v>
       </c>
       <c r="H124" s="3">
-        <v>46092</v>
+        <v>46107</v>
       </c>
       <c r="I124" s="3">
-        <v>46119</v>
+        <v>46133</v>
       </c>
       <c r="J124" t="s">
         <v>289</v>
@@ -7641,7 +7665,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7661,22 +7685,22 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>210</v>
+        <v>368</v>
       </c>
       <c r="F125" t="s">
-        <v>211</v>
+        <v>369</v>
       </c>
       <c r="G125" s="3">
         <v>46076</v>
       </c>
       <c r="H125" s="3">
-        <v>46107</v>
+        <v>46077</v>
       </c>
       <c r="I125" s="3">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="J125" t="s">
-        <v>286</v>
+        <v>212</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
@@ -7691,7 +7715,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7702,31 +7726,31 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
+        <v>371</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>368</v>
+      </c>
+      <c r="F126" t="s">
         <v>369</v>
-      </c>
-      <c r="C126" s="2">
-        <v>1</v>
-      </c>
-      <c r="D126" s="2">
-        <v>0</v>
-      </c>
-      <c r="E126" t="s">
-        <v>370</v>
-      </c>
-      <c r="F126" t="s">
-        <v>371</v>
       </c>
       <c r="G126" s="3">
         <v>46076</v>
       </c>
       <c r="H126" s="3">
-        <v>46079</v>
+        <v>46167</v>
       </c>
       <c r="I126" s="3">
-        <v>46134</v>
+        <v>46218</v>
       </c>
       <c r="J126" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
@@ -7761,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F127" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G127" s="3">
         <v>46076</v>
@@ -7776,7 +7800,7 @@
         <v>46218</v>
       </c>
       <c r="J127" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
@@ -7791,7 +7815,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7802,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7811,22 +7835,22 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F128" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G128" s="3">
         <v>46076</v>
       </c>
       <c r="H128" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I128" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J128" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
@@ -7841,7 +7865,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7861,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F129" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G129" s="3">
         <v>46076</v>
@@ -7876,7 +7900,7 @@
         <v>46267</v>
       </c>
       <c r="J129" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
@@ -7891,7 +7915,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7902,7 +7926,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7911,22 +7935,22 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F130" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G130" s="3">
         <v>46076</v>
       </c>
       <c r="H130" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I130" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J130" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
@@ -7941,7 +7965,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7961,10 +7985,10 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F131" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G131" s="3">
         <v>46076</v>
@@ -7976,7 +8000,7 @@
         <v>46309</v>
       </c>
       <c r="J131" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
@@ -7991,7 +8015,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -8002,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -8011,19 +8035,19 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>370</v>
+        <v>48</v>
       </c>
       <c r="F132" t="s">
-        <v>371</v>
+        <v>49</v>
       </c>
       <c r="G132" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H132" s="3">
-        <v>46254</v>
+        <v>46114</v>
       </c>
       <c r="I132" s="3">
-        <v>46309</v>
+        <v>46154</v>
       </c>
       <c r="J132" t="s">
         <v>286</v>
@@ -8041,7 +8065,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8066,7 +8090,9 @@
       <c r="F133" t="s">
         <v>49</v>
       </c>
-      <c r="G133" s="3"/>
+      <c r="G133" s="3">
+        <v>46083</v>
+      </c>
       <c r="H133" s="3">
         <v>46114</v>
       </c>
@@ -8074,7 +8100,7 @@
         <v>46154</v>
       </c>
       <c r="J133" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
@@ -8089,7 +8115,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8100,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8114,7 +8140,9 @@
       <c r="F134" t="s">
         <v>49</v>
       </c>
-      <c r="G134" s="3"/>
+      <c r="G134" s="3">
+        <v>46083</v>
+      </c>
       <c r="H134" s="3">
         <v>46114</v>
       </c>
@@ -8122,7 +8150,7 @@
         <v>46154</v>
       </c>
       <c r="J134" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
@@ -8137,7 +8165,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8148,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8162,7 +8190,9 @@
       <c r="F135" t="s">
         <v>49</v>
       </c>
-      <c r="G135" s="3"/>
+      <c r="G135" s="3">
+        <v>46083</v>
+      </c>
       <c r="H135" s="3">
         <v>46114</v>
       </c>
@@ -8170,7 +8200,7 @@
         <v>46154</v>
       </c>
       <c r="J135" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
@@ -8185,7 +8215,7 @@
         <v>7</v>
       </c>
       <c r="O135" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8196,35 +8226,37 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
+        <v>385</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s">
+        <v>386</v>
+      </c>
+      <c r="F136" t="s">
         <v>387</v>
       </c>
-      <c r="C136" s="2">
-        <v>1</v>
-      </c>
-      <c r="D136" s="2">
-        <v>0</v>
-      </c>
-      <c r="E136" t="s">
-        <v>48</v>
-      </c>
-      <c r="F136" t="s">
-        <v>49</v>
-      </c>
-      <c r="G136" s="3"/>
+      <c r="G136" s="3">
+        <v>46079</v>
+      </c>
       <c r="H136" s="3">
-        <v>46114</v>
+        <v>46163</v>
       </c>
       <c r="I136" s="3">
-        <v>46154</v>
+        <v>46238</v>
       </c>
       <c r="J136" t="s">
-        <v>383</v>
+        <v>283</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8233,7 +8265,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8241,7 +8273,7 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
         <v>389</v>
@@ -8259,31 +8291,31 @@
         <v>391</v>
       </c>
       <c r="G137" s="3">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="H137" s="3">
-        <v>46052</v>
+        <v>46087</v>
       </c>
       <c r="I137" s="3">
-        <v>46076</v>
+        <v>46106</v>
       </c>
       <c r="J137" t="s">
-        <v>26</v>
+        <v>286</v>
       </c>
       <c r="K137" t="s">
+        <v>5</v>
+      </c>
+      <c r="L137" s="3">
+        <v>46079</v>
+      </c>
+      <c r="M137" t="s">
+        <v>6</v>
+      </c>
+      <c r="N137" t="s">
+        <v>7</v>
+      </c>
+      <c r="O137" t="s">
         <v>392</v>
-      </c>
-      <c r="L137" s="3">
-        <v>46035</v>
-      </c>
-      <c r="M137" t="s">
-        <v>6</v>
-      </c>
-      <c r="N137" t="s">
-        <v>393</v>
-      </c>
-      <c r="O137" t="s">
-        <v>394</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8291,10 +8323,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8303,34 +8335,34 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="F138" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="G138" s="3">
-        <v>46043</v>
+        <v>46079</v>
       </c>
       <c r="H138" s="3">
-        <v>46051</v>
+        <v>46087</v>
       </c>
       <c r="I138" s="3">
-        <v>46057</v>
+        <v>46106</v>
       </c>
       <c r="J138" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="K138" t="s">
-        <v>392</v>
+        <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46043</v>
+        <v>46079</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
       </c>
       <c r="N138" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="O138" t="s">
         <v>394</v>
@@ -8341,10 +8373,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8353,37 +8385,37 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="F139" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="G139" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="H139" s="3">
-        <v>46059</v>
+        <v>46087</v>
       </c>
       <c r="I139" s="3">
-        <v>46062</v>
+        <v>46106</v>
       </c>
       <c r="J139" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
       <c r="K139" t="s">
-        <v>392</v>
+        <v>5</v>
       </c>
       <c r="L139" s="3">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
       </c>
       <c r="N139" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="O139" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8391,10 +8423,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B140" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8403,37 +8435,37 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F140" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G140" s="3">
-        <v>46052</v>
+        <v>46035</v>
       </c>
       <c r="H140" s="3">
         <v>46052</v>
       </c>
       <c r="I140" s="3">
-        <v>46058</v>
+        <v>46076</v>
       </c>
       <c r="J140" t="s">
-        <v>254</v>
+        <v>26</v>
       </c>
       <c r="K140" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L140" s="3">
-        <v>46052</v>
+        <v>46035</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
       </c>
       <c r="N140" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O140" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8441,7 +8473,7 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B141" t="s">
         <v>404</v>
@@ -8459,31 +8491,31 @@
         <v>406</v>
       </c>
       <c r="G141" s="3">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="H141" s="3">
-        <v>46077</v>
+        <v>46051</v>
       </c>
       <c r="I141" s="3">
-        <v>46094</v>
+        <v>46057</v>
       </c>
       <c r="J141" t="s">
-        <v>407</v>
+        <v>253</v>
       </c>
       <c r="K141" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L141" s="3">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O141" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P141" t="s">
         <v>9</v>
@@ -8491,37 +8523,37 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B142" t="s">
+        <v>407</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="2">
-        <v>1</v>
-      </c>
-      <c r="D142" s="2">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>409</v>
-      </c>
-      <c r="F142" t="s">
-        <v>410</v>
       </c>
       <c r="G142" s="3">
         <v>46052</v>
       </c>
       <c r="H142" s="3">
-        <v>46064</v>
+        <v>46059</v>
       </c>
       <c r="I142" s="3">
-        <v>46066</v>
+        <v>46062</v>
       </c>
       <c r="J142" t="s">
-        <v>407</v>
+        <v>207</v>
       </c>
       <c r="K142" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L142" s="3">
         <v>46052</v>
@@ -8530,10 +8562,10 @@
         <v>6</v>
       </c>
       <c r="N142" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O142" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8541,49 +8573,49 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B143" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
         <v>411</v>
       </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>412</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46052</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46058</v>
+      </c>
+      <c r="J143" t="s">
         <v>413</v>
       </c>
-      <c r="G143" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H143" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J143" t="s">
-        <v>254</v>
-      </c>
       <c r="K143" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L143" s="3">
-        <v>46057</v>
+        <v>46052</v>
       </c>
       <c r="M143" t="s">
         <v>6</v>
       </c>
       <c r="N143" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O143" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P143" t="s">
         <v>9</v>
@@ -8591,7 +8623,7 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B144" t="s">
         <v>414</v>
@@ -8609,31 +8641,31 @@
         <v>416</v>
       </c>
       <c r="G144" s="3">
-        <v>46076</v>
+        <v>46052</v>
       </c>
       <c r="H144" s="3">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="I144" s="3">
-        <v>46119</v>
+        <v>46094</v>
       </c>
       <c r="J144" t="s">
-        <v>207</v>
+        <v>413</v>
       </c>
       <c r="K144" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L144" s="3">
-        <v>46076</v>
+        <v>46052</v>
       </c>
       <c r="M144" t="s">
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O144" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8641,7 +8673,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B145" t="s">
         <v>417</v>
@@ -8659,33 +8691,183 @@
         <v>419</v>
       </c>
       <c r="G145" s="3">
+        <v>46052</v>
+      </c>
+      <c r="H145" s="3">
+        <v>46064</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46066</v>
+      </c>
+      <c r="J145" t="s">
+        <v>413</v>
+      </c>
+      <c r="K145" t="s">
+        <v>401</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46052</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>402</v>
+      </c>
+      <c r="O145" t="s">
+        <v>403</v>
+      </c>
+      <c r="P145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>397</v>
+      </c>
+      <c r="B146" t="s">
+        <v>420</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>421</v>
+      </c>
+      <c r="F146" t="s">
+        <v>422</v>
+      </c>
+      <c r="G146" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H146" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I146" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J146" t="s">
+        <v>253</v>
+      </c>
+      <c r="K146" t="s">
+        <v>401</v>
+      </c>
+      <c r="L146" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M146" t="s">
+        <v>6</v>
+      </c>
+      <c r="N146" t="s">
+        <v>402</v>
+      </c>
+      <c r="O146" t="s">
+        <v>403</v>
+      </c>
+      <c r="P146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>397</v>
+      </c>
+      <c r="B147" t="s">
+        <v>423</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>424</v>
+      </c>
+      <c r="F147" t="s">
+        <v>425</v>
+      </c>
+      <c r="G147" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H147" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I147" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J147" t="s">
+        <v>207</v>
+      </c>
+      <c r="K147" t="s">
+        <v>401</v>
+      </c>
+      <c r="L147" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M147" t="s">
+        <v>6</v>
+      </c>
+      <c r="N147" t="s">
+        <v>402</v>
+      </c>
+      <c r="O147" t="s">
+        <v>403</v>
+      </c>
+      <c r="P147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" t="s">
+        <v>397</v>
+      </c>
+      <c r="B148" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148" t="s">
+        <v>427</v>
+      </c>
+      <c r="F148" t="s">
+        <v>428</v>
+      </c>
+      <c r="G148" s="3">
         <v>46077</v>
       </c>
-      <c r="H145" s="3">
+      <c r="H148" s="3">
         <v>46078</v>
       </c>
-      <c r="I145" s="3">
+      <c r="I148" s="3">
         <v>46084</v>
       </c>
-      <c r="J145" t="s">
-        <v>420</v>
-      </c>
-      <c r="K145" t="s">
-        <v>392</v>
-      </c>
-      <c r="L145" s="3">
+      <c r="J148" t="s">
+        <v>413</v>
+      </c>
+      <c r="K148" t="s">
+        <v>401</v>
+      </c>
+      <c r="L148" s="3">
         <v>46077</v>
       </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>393</v>
-      </c>
-      <c r="O145" t="s">
-        <v>394</v>
-      </c>
-      <c r="P145" t="s">
+      <c r="M148" t="s">
+        <v>6</v>
+      </c>
+      <c r="N148" t="s">
+        <v>402</v>
+      </c>
+      <c r="O148" t="s">
+        <v>403</v>
+      </c>
+      <c r="P148" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="441">
   <si>
     <t>ZP01</t>
   </si>
@@ -205,7 +205,7 @@
     <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
+    <t>REL  MSPT PCNF PRC  CSER MANC MSCP RESA*</t>
   </si>
   <si>
     <t>1100170790</t>
@@ -232,6 +232,9 @@
     <t>5BC-429_X=4M,Y=2.9M,Z=1.0/1.2/1.4M</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF PRC  CSER MANC RESA RMWB*</t>
+  </si>
+  <si>
     <t>1100172120</t>
   </si>
   <si>
@@ -244,9 +247,6 @@
     <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF PRC  CSER MANC RESA RMWB*</t>
-  </si>
-  <si>
     <t>1100177770</t>
   </si>
   <si>
@@ -262,15 +262,6 @@
     <t>1300000176</t>
   </si>
   <si>
-    <t>100003418</t>
-  </si>
-  <si>
-    <t>REL  PCNF DLV  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100162420</t>
-  </si>
-  <si>
     <t>100003438</t>
   </si>
   <si>
@@ -313,7 +304,247 @@
     <t>1100182450</t>
   </si>
   <si>
-    <t>100003453</t>
+    <t>100003460</t>
+  </si>
+  <si>
+    <t>980000019400</t>
+  </si>
+  <si>
+    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100175760</t>
+  </si>
+  <si>
+    <t>100003465</t>
+  </si>
+  <si>
+    <t>980000013700</t>
+  </si>
+  <si>
+    <t>S-Plus 8_X=800, Y=520, Z=550</t>
+  </si>
+  <si>
+    <t>1100177930</t>
+  </si>
+  <si>
+    <t>100003468</t>
+  </si>
+  <si>
+    <t>980000045000</t>
+  </si>
+  <si>
+    <t>TGV-106_X=1000, Y=600, Z=510</t>
+  </si>
+  <si>
+    <t>1100182880</t>
+  </si>
+  <si>
+    <t>100003469</t>
+  </si>
+  <si>
+    <t>1100179090</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1100182820</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>980000018002</t>
+  </si>
+  <si>
+    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100172880</t>
+  </si>
+  <si>
+    <t>100003472</t>
+  </si>
+  <si>
+    <t>980000030801</t>
+  </si>
+  <si>
+    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
+  </si>
+  <si>
+    <t>1100177910</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>1300000180</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>980000027800</t>
+  </si>
+  <si>
+    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100183180</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>1100184110</t>
+  </si>
+  <si>
+    <t>100003478</t>
+  </si>
+  <si>
+    <t>980000000800</t>
+  </si>
+  <si>
+    <t>PRO-1000_X=1000, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100180510</t>
+  </si>
+  <si>
+    <t>100003481</t>
+  </si>
+  <si>
+    <t>1100184950</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
+    <t>1100185590</t>
+  </si>
+  <si>
+    <t>100003483</t>
+  </si>
+  <si>
+    <t>1100185600</t>
+  </si>
+  <si>
+    <t>100003484</t>
+  </si>
+  <si>
+    <t>980000043500</t>
+  </si>
+  <si>
+    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
+  </si>
+  <si>
+    <t>1100181160</t>
+  </si>
+  <si>
+    <t>100003488</t>
+  </si>
+  <si>
+    <t>1100185870</t>
+  </si>
+  <si>
+    <t>100003496</t>
+  </si>
+  <si>
+    <t>1300000181</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
+    <t>980000048000</t>
+  </si>
+  <si>
+    <t>SMC-7_X=700, Y=400, Z=300</t>
+  </si>
+  <si>
+    <t>1100193980</t>
+  </si>
+  <si>
+    <t>100003500</t>
+  </si>
+  <si>
+    <t>980000017600</t>
+  </si>
+  <si>
+    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100183110</t>
+  </si>
+  <si>
+    <t>100003501</t>
+  </si>
+  <si>
+    <t>100003502</t>
+  </si>
+  <si>
+    <t>1100183140</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003507</t>
+  </si>
+  <si>
+    <t>980000045400</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003509</t>
+  </si>
+  <si>
+    <t>1100188510</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
   </si>
   <si>
     <t>980000028700</t>
@@ -322,252 +553,6 @@
     <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
   </si>
   <si>
-    <t>1100182220</t>
-  </si>
-  <si>
-    <t>100003460</t>
-  </si>
-  <si>
-    <t>980000019400</t>
-  </si>
-  <si>
-    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100175760</t>
-  </si>
-  <si>
-    <t>100003465</t>
-  </si>
-  <si>
-    <t>980000013700</t>
-  </si>
-  <si>
-    <t>S-Plus 8_X=800, Y=520, Z=550</t>
-  </si>
-  <si>
-    <t>1100177930</t>
-  </si>
-  <si>
-    <t>100003468</t>
-  </si>
-  <si>
-    <t>980000045000</t>
-  </si>
-  <si>
-    <t>TGV-106_X=1000, Y=600, Z=510</t>
-  </si>
-  <si>
-    <t>1100182880</t>
-  </si>
-  <si>
-    <t>100003469</t>
-  </si>
-  <si>
-    <t>1100179090</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1100182820</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>980000018002</t>
-  </si>
-  <si>
-    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100172880</t>
-  </si>
-  <si>
-    <t>100003472</t>
-  </si>
-  <si>
-    <t>980000030801</t>
-  </si>
-  <si>
-    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
-  </si>
-  <si>
-    <t>1100177910</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>1300000180</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>980000027800</t>
-  </si>
-  <si>
-    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>1100183180</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>1100184110</t>
-  </si>
-  <si>
-    <t>100003478</t>
-  </si>
-  <si>
-    <t>980000000800</t>
-  </si>
-  <si>
-    <t>PRO-1000_X=1000, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100180510</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>1100184950</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>1100185590</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1100185600</t>
-  </si>
-  <si>
-    <t>100003484</t>
-  </si>
-  <si>
-    <t>980000043500</t>
-  </si>
-  <si>
-    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
-  </si>
-  <si>
-    <t>1100181160</t>
-  </si>
-  <si>
-    <t>100003488</t>
-  </si>
-  <si>
-    <t>1100185870</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1300000181</t>
-  </si>
-  <si>
-    <t>100003499</t>
-  </si>
-  <si>
-    <t>980000048000</t>
-  </si>
-  <si>
-    <t>SMC-7_X=700, Y=400, Z=300</t>
-  </si>
-  <si>
-    <t>1100193980</t>
-  </si>
-  <si>
-    <t>100003500</t>
-  </si>
-  <si>
-    <t>980000017600</t>
-  </si>
-  <si>
-    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100183110</t>
-  </si>
-  <si>
-    <t>100003501</t>
-  </si>
-  <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1100183140</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>980000045400</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
     <t>1100182140</t>
   </si>
   <si>
@@ -580,6 +565,9 @@
     <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
+  </si>
+  <si>
     <t>1100188460</t>
   </si>
   <si>
@@ -1213,6 +1201,21 @@
     <t>1100197580</t>
   </si>
   <si>
+    <t>100003622</t>
+  </si>
+  <si>
+    <t>1100197240</t>
+  </si>
+  <si>
+    <t>100003623</t>
+  </si>
+  <si>
+    <t>1100191070</t>
+  </si>
+  <si>
+    <t>100003624</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -1243,55 +1246,46 @@
     <t>D6K 主軸,010801_BBT50,M50E,C045</t>
   </si>
   <si>
-    <t>630000348</t>
-  </si>
-  <si>
-    <t>080200570900</t>
-  </si>
-  <si>
-    <t>SMC-5機頭D24K,031793_#40,28F15,0</t>
+    <t>630000349</t>
+  </si>
+  <si>
+    <t>080200563200</t>
+  </si>
+  <si>
+    <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>630000351</t>
+  </si>
+  <si>
+    <t>080100076704</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
+  </si>
+  <si>
+    <t>630000354</t>
+  </si>
+  <si>
+    <t>080200017902</t>
+  </si>
+  <si>
+    <t>EA機頭G8K,011262_Z1200,55A22,C</t>
   </si>
   <si>
     <t>REL  PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>630000349</t>
-  </si>
-  <si>
-    <t>080200563200</t>
-  </si>
-  <si>
-    <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>630000351</t>
-  </si>
-  <si>
-    <t>080100076704</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
-  </si>
-  <si>
-    <t>630000352</t>
-  </si>
-  <si>
-    <t>080100059604</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021361_BT40,5GT,0W45</t>
-  </si>
-  <si>
-    <t>630000354</t>
-  </si>
-  <si>
-    <t>080200017902</t>
-  </si>
-  <si>
-    <t>EA機頭G8K,011262_Z1200,55A22,C</t>
+    <t>630000355</t>
+  </si>
+  <si>
+    <t>080100145601</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M50E,0045</t>
   </si>
   <si>
     <t>訂單類型</t>
@@ -1467,52 +1461,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2141,7 +2135,7 @@
         <v>46056</v>
       </c>
       <c r="I14" s="3">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -2191,7 +2185,7 @@
         <v>46055</v>
       </c>
       <c r="I15" s="3">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -2344,7 +2338,7 @@
         <v>46183</v>
       </c>
       <c r="J18" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2359,7 +2353,7 @@
         <v>7</v>
       </c>
       <c r="O18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P18" t="s">
         <v>9</v>
@@ -2370,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2379,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="3">
         <v>45943</v>
@@ -2394,7 +2388,7 @@
         <v>46135</v>
       </c>
       <c r="J19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -2476,40 +2470,40 @@
         <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3">
-        <v>45950</v>
+        <v>45966</v>
       </c>
       <c r="H21" s="3">
-        <v>45957</v>
+        <v>46051</v>
       </c>
       <c r="I21" s="3">
-        <v>46135</v>
+        <v>46153</v>
       </c>
       <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
+        <v>45966</v>
+      </c>
+      <c r="M21" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O21" t="s">
         <v>84</v>
-      </c>
-      <c r="K21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
-        <v>45946</v>
-      </c>
-      <c r="M21" t="s">
-        <v>6</v>
-      </c>
-      <c r="N21" t="s">
-        <v>7</v>
-      </c>
-      <c r="O21" t="s">
-        <v>85</v>
       </c>
       <c r="P21" t="s">
         <v>9</v>
@@ -2520,28 +2514,28 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="G22" s="3">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="H22" s="3">
-        <v>46051</v>
+        <v>46042</v>
       </c>
       <c r="I22" s="3">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -2550,7 +2544,7 @@
         <v>5</v>
       </c>
       <c r="L22" s="3">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2559,7 +2553,7 @@
         <v>7</v>
       </c>
       <c r="O22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P22" t="s">
         <v>9</v>
@@ -2570,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2579,28 +2573,28 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H23" s="3">
-        <v>46042</v>
+        <v>46099</v>
       </c>
       <c r="I23" s="3">
-        <v>46147</v>
+        <v>46156</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2609,7 +2603,7 @@
         <v>7</v>
       </c>
       <c r="O23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P23" t="s">
         <v>9</v>
@@ -2620,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2629,19 +2623,19 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G24" s="3">
         <v>45979</v>
       </c>
       <c r="H24" s="3">
-        <v>46099</v>
+        <v>46065</v>
       </c>
       <c r="I24" s="3">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="J24" t="s">
         <v>13</v>
@@ -2659,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="O24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" t="s">
         <v>9</v>
@@ -2670,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2679,28 +2673,28 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G25" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="H25" s="3">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="I25" s="3">
-        <v>46153</v>
+        <v>46191</v>
       </c>
       <c r="J25" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2709,7 +2703,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" t="s">
         <v>9</v>
@@ -2720,37 +2714,37 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G26" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="H26" s="3">
-        <v>46036</v>
+        <v>46076</v>
       </c>
       <c r="I26" s="3">
-        <v>46139</v>
+        <v>46129</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>45979</v>
+        <v>45993</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2759,7 +2753,7 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" t="s">
         <v>9</v>
@@ -2770,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2779,19 +2773,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G27" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H27" s="3">
-        <v>46125</v>
+        <v>46041</v>
       </c>
       <c r="I27" s="3">
-        <v>46191</v>
+        <v>46142</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -2800,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2809,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2820,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2829,37 +2823,37 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="3">
+        <v>45994</v>
+      </c>
+      <c r="H28" s="3">
+        <v>46125</v>
+      </c>
+      <c r="I28" s="3">
+        <v>46216</v>
+      </c>
+      <c r="J28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s">
+        <v>5</v>
+      </c>
+      <c r="L28" s="3">
+        <v>45994</v>
+      </c>
+      <c r="M28" t="s">
+        <v>6</v>
+      </c>
+      <c r="N28" t="s">
+        <v>7</v>
+      </c>
+      <c r="O28" t="s">
         <v>110</v>
-      </c>
-      <c r="G28" s="3">
-        <v>45993</v>
-      </c>
-      <c r="H28" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I28" s="3">
-        <v>46129</v>
-      </c>
-      <c r="J28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K28" t="s">
-        <v>5</v>
-      </c>
-      <c r="L28" s="3">
-        <v>45993</v>
-      </c>
-      <c r="M28" t="s">
-        <v>6</v>
-      </c>
-      <c r="N28" t="s">
-        <v>7</v>
-      </c>
-      <c r="O28" t="s">
-        <v>111</v>
       </c>
       <c r="P28" t="s">
         <v>9</v>
@@ -2870,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2879,19 +2873,19 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="G29" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H29" s="3">
-        <v>46041</v>
+        <v>46101</v>
       </c>
       <c r="I29" s="3">
-        <v>46142</v>
+        <v>46154</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -2900,7 +2894,7 @@
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2909,7 +2903,7 @@
         <v>7</v>
       </c>
       <c r="O29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P29" t="s">
         <v>9</v>
@@ -2920,46 +2914,46 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="3">
+        <v>45995</v>
+      </c>
+      <c r="H30" s="3">
+        <v>46094</v>
+      </c>
+      <c r="I30" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" t="s">
+        <v>5</v>
+      </c>
+      <c r="L30" s="3">
+        <v>45995</v>
+      </c>
+      <c r="M30" t="s">
+        <v>6</v>
+      </c>
+      <c r="N30" t="s">
+        <v>7</v>
+      </c>
+      <c r="O30" t="s">
         <v>116</v>
-      </c>
-      <c r="C30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="3">
-        <v>45994</v>
-      </c>
-      <c r="H30" s="3">
-        <v>46125</v>
-      </c>
-      <c r="I30" s="3">
-        <v>46216</v>
-      </c>
-      <c r="J30" t="s">
-        <v>77</v>
-      </c>
-      <c r="K30" t="s">
-        <v>5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>45994</v>
-      </c>
-      <c r="M30" t="s">
-        <v>6</v>
-      </c>
-      <c r="N30" t="s">
-        <v>7</v>
-      </c>
-      <c r="O30" t="s">
-        <v>117</v>
       </c>
       <c r="P30" t="s">
         <v>9</v>
@@ -2970,28 +2964,28 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>93</v>
-      </c>
       <c r="F31" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="G31" s="3">
         <v>45995</v>
       </c>
       <c r="H31" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="I31" s="3">
-        <v>46154</v>
+        <v>46202</v>
       </c>
       <c r="J31" t="s">
         <v>22</v>
@@ -3009,7 +3003,7 @@
         <v>7</v>
       </c>
       <c r="O31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" t="s">
         <v>9</v>
@@ -3020,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -3029,37 +3023,37 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>46087</v>
+      </c>
+      <c r="I32" s="3">
+        <v>46122</v>
+      </c>
+      <c r="J32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M32" t="s">
+        <v>6</v>
+      </c>
+      <c r="N32" t="s">
+        <v>7</v>
+      </c>
+      <c r="O32" t="s">
         <v>122</v>
-      </c>
-      <c r="G32" s="3">
-        <v>45995</v>
-      </c>
-      <c r="H32" s="3">
-        <v>46094</v>
-      </c>
-      <c r="I32" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J32" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
-        <v>45995</v>
-      </c>
-      <c r="M32" t="s">
-        <v>6</v>
-      </c>
-      <c r="N32" t="s">
-        <v>7</v>
-      </c>
-      <c r="O32" t="s">
-        <v>123</v>
       </c>
       <c r="P32" t="s">
         <v>9</v>
@@ -3070,28 +3064,28 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
         <v>124</v>
       </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>125</v>
       </c>
-      <c r="F33" t="s">
-        <v>126</v>
-      </c>
       <c r="G33" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H33" s="3">
-        <v>46105</v>
+        <v>46050</v>
       </c>
       <c r="I33" s="3">
-        <v>46202</v>
+        <v>46148</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
@@ -3100,7 +3094,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -3109,7 +3103,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P33" t="s">
         <v>9</v>
@@ -3120,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -3129,22 +3123,22 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G34" s="3">
         <v>46000</v>
       </c>
       <c r="H34" s="3">
-        <v>46087</v>
+        <v>46104</v>
       </c>
       <c r="I34" s="3">
-        <v>46122</v>
+        <v>46147</v>
       </c>
       <c r="J34" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -3159,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P34" t="s">
         <v>9</v>
@@ -3170,28 +3164,28 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="2">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>131</v>
       </c>
-      <c r="F35" t="s">
-        <v>132</v>
-      </c>
       <c r="G35" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H35" s="3">
-        <v>46050</v>
+        <v>46010</v>
       </c>
       <c r="I35" s="3">
-        <v>46148</v>
+        <v>46045</v>
       </c>
       <c r="J35" t="s">
         <v>22</v>
@@ -3200,7 +3194,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -3209,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3220,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3229,19 +3223,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G36" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H36" s="3">
-        <v>46104</v>
+        <v>46041</v>
       </c>
       <c r="I36" s="3">
-        <v>46142</v>
+        <v>46160</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
@@ -3250,7 +3244,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -3259,7 +3253,7 @@
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -3270,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3279,19 +3273,19 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="G37" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H37" s="3">
-        <v>46010</v>
+        <v>46090</v>
       </c>
       <c r="I37" s="3">
-        <v>46045</v>
+        <v>46171</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -3300,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3309,7 +3303,7 @@
         <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -3320,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3338,10 +3332,10 @@
         <v>46007</v>
       </c>
       <c r="H38" s="3">
-        <v>46041</v>
+        <v>46093</v>
       </c>
       <c r="I38" s="3">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="J38" t="s">
         <v>22</v>
@@ -3359,7 +3353,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3370,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -3379,19 +3373,19 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="G39" s="3">
         <v>46007</v>
       </c>
       <c r="H39" s="3">
-        <v>46090</v>
+        <v>46041</v>
       </c>
       <c r="I39" s="3">
-        <v>46171</v>
+        <v>46139</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
@@ -3409,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="O39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3420,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3429,19 +3423,19 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G40" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="H40" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="I40" s="3">
-        <v>46185</v>
+        <v>46147</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -3450,7 +3444,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3459,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3470,46 +3464,46 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="3">
+        <v>46027</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46126</v>
+      </c>
+      <c r="I41" s="3">
+        <v>46188</v>
+      </c>
+      <c r="J41" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
+        <v>46022</v>
+      </c>
+      <c r="M41" t="s">
+        <v>6</v>
+      </c>
+      <c r="N41" t="s">
+        <v>7</v>
+      </c>
+      <c r="O41" t="s">
         <v>146</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>147</v>
-      </c>
-      <c r="F41" t="s">
-        <v>148</v>
-      </c>
-      <c r="G41" s="3">
-        <v>46007</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46041</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46139</v>
-      </c>
-      <c r="J41" t="s">
-        <v>22</v>
-      </c>
-      <c r="K41" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
-        <v>46007</v>
-      </c>
-      <c r="M41" t="s">
-        <v>6</v>
-      </c>
-      <c r="N41" t="s">
-        <v>7</v>
-      </c>
-      <c r="O41" t="s">
-        <v>149</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3520,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3529,19 +3523,19 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="G42" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="H42" s="3">
-        <v>46134</v>
+        <v>46031</v>
       </c>
       <c r="I42" s="3">
-        <v>46155</v>
+        <v>46141</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -3550,7 +3544,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3559,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="O42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3570,37 +3564,37 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>25</v>
-      </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="G43" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="H43" s="3">
-        <v>46126</v>
+        <v>46042</v>
       </c>
       <c r="I43" s="3">
-        <v>46188</v>
+        <v>46087</v>
       </c>
       <c r="J43" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3609,7 +3603,7 @@
         <v>7</v>
       </c>
       <c r="O43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P43" t="s">
         <v>9</v>
@@ -3620,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3629,19 +3623,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G44" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H44" s="3">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="I44" s="3">
-        <v>46135</v>
+        <v>46085</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -3650,7 +3644,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3659,7 +3653,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3670,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3679,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="G45" s="3">
         <v>46029</v>
       </c>
       <c r="H45" s="3">
-        <v>46042</v>
+        <v>46057</v>
       </c>
       <c r="I45" s="3">
-        <v>46087</v>
+        <v>46136</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -3709,7 +3703,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3720,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3735,13 +3729,13 @@
         <v>160</v>
       </c>
       <c r="G46" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="H46" s="3">
-        <v>46037</v>
+        <v>46050</v>
       </c>
       <c r="I46" s="3">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -3750,7 +3744,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3770,28 +3764,28 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
         <v>163</v>
       </c>
-      <c r="C47" s="2">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>121</v>
-      </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="G47" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="H47" s="3">
-        <v>46057</v>
+        <v>46090</v>
       </c>
       <c r="I47" s="3">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -3800,7 +3794,7 @@
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3809,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3820,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3829,16 +3823,16 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G48" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="H48" s="3">
-        <v>46050</v>
+        <v>46129</v>
       </c>
       <c r="I48" s="3">
         <v>46167</v>
@@ -3850,7 +3844,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3859,7 +3853,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3870,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3879,28 +3873,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
+        <v>91</v>
+      </c>
+      <c r="G49" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H49" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I49" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J49" t="s">
         <v>171</v>
       </c>
-      <c r="G49" s="3">
-        <v>46041</v>
-      </c>
-      <c r="H49" s="3">
-        <v>46090</v>
-      </c>
-      <c r="I49" s="3">
-        <v>46211</v>
-      </c>
-      <c r="J49" t="s">
-        <v>22</v>
-      </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3929,19 +3923,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>174</v>
+        <v>90</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="G50" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H50" s="3">
-        <v>46129</v>
+        <v>46090</v>
       </c>
       <c r="I50" s="3">
-        <v>46167</v>
+        <v>46136</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -3950,7 +3944,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3959,7 +3953,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3970,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3979,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F51" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G51" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H51" s="3">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="I51" s="3">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="J51" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -4009,7 +4003,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -4020,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -4029,19 +4023,19 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="F52" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="G52" s="3">
         <v>46044</v>
       </c>
       <c r="H52" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I52" s="3">
-        <v>46136</v>
+        <v>46156</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -4059,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -4070,31 +4064,31 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>89</v>
-      </c>
       <c r="F53" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="G53" s="3">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="H53" s="3">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="I53" s="3">
-        <v>46195</v>
+        <v>46133</v>
       </c>
       <c r="J53" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
@@ -4109,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -4120,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -4129,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="F54" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="G54" s="3">
         <v>46044</v>
       </c>
       <c r="H54" s="3">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="I54" s="3">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="J54" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -4159,7 +4153,7 @@
         <v>7</v>
       </c>
       <c r="O54" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="P54" t="s">
         <v>9</v>
@@ -4170,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -4179,19 +4173,19 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F55" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G55" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H55" s="3">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="I55" s="3">
-        <v>46133</v>
+        <v>46174</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -4200,7 +4194,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -4209,7 +4203,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4220,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -4229,28 +4223,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="F56" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="G56" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H56" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="I56" s="3">
-        <v>46153</v>
+        <v>46134</v>
       </c>
       <c r="J56" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4259,7 +4253,7 @@
         <v>7</v>
       </c>
       <c r="O56" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4270,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4279,19 +4273,19 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F57" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G57" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="H57" s="3">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="I57" s="3">
-        <v>46174</v>
+        <v>46161</v>
       </c>
       <c r="J57" t="s">
         <v>22</v>
@@ -4300,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4309,7 +4303,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4320,28 +4314,28 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>200</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>197</v>
+      </c>
+      <c r="F58" t="s">
         <v>198</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>93</v>
-      </c>
-      <c r="F58" t="s">
-        <v>94</v>
-      </c>
       <c r="G58" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H58" s="3">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="I58" s="3">
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="J58" t="s">
         <v>22</v>
@@ -4350,7 +4344,7 @@
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4359,7 +4353,7 @@
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4370,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4379,19 +4373,19 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G59" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="H59" s="3">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="I59" s="3">
-        <v>46161</v>
+        <v>46134</v>
       </c>
       <c r="J59" t="s">
         <v>22</v>
@@ -4400,7 +4394,7 @@
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4409,7 +4403,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4420,28 +4414,28 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60" t="s">
         <v>204</v>
       </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
-        <v>201</v>
-      </c>
-      <c r="F60" t="s">
-        <v>202</v>
-      </c>
       <c r="G60" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="H60" s="3">
         <v>46083</v>
       </c>
       <c r="I60" s="3">
-        <v>46154</v>
+        <v>46136</v>
       </c>
       <c r="J60" t="s">
         <v>22</v>
@@ -4450,7 +4444,7 @@
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4459,7 +4453,7 @@
         <v>7</v>
       </c>
       <c r="O60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P60" t="s">
         <v>9</v>
@@ -4470,37 +4464,37 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
       </c>
       <c r="D61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G61" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="H61" s="3">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="I61" s="3">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="J61" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4509,7 +4503,7 @@
         <v>7</v>
       </c>
       <c r="O61" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4520,37 +4514,37 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>209</v>
+      </c>
+      <c r="F62" t="s">
         <v>210</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>207</v>
-      </c>
-      <c r="F62" t="s">
-        <v>208</v>
-      </c>
       <c r="G62" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="H62" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="I62" s="3">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="J62" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4559,7 +4553,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4570,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4579,19 +4573,19 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F63" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G63" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H63" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="I63" s="3">
-        <v>46135</v>
+        <v>46170</v>
       </c>
       <c r="J63" t="s">
         <v>22</v>
@@ -4600,7 +4594,7 @@
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4609,7 +4603,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4620,28 +4614,28 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>215</v>
+      </c>
+      <c r="F64" t="s">
         <v>216</v>
       </c>
-      <c r="C64" s="2">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
-        <v>213</v>
-      </c>
-      <c r="F64" t="s">
-        <v>214</v>
-      </c>
       <c r="G64" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H64" s="3">
-        <v>46086</v>
+        <v>46134</v>
       </c>
       <c r="I64" s="3">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="J64" t="s">
         <v>22</v>
@@ -4650,7 +4644,7 @@
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4659,7 +4653,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4670,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4679,19 +4673,19 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G65" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H65" s="3">
-        <v>46091</v>
+        <v>46079</v>
       </c>
       <c r="I65" s="3">
-        <v>46170</v>
+        <v>46140</v>
       </c>
       <c r="J65" t="s">
         <v>22</v>
@@ -4700,7 +4694,7 @@
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4709,7 +4703,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4720,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4729,28 +4723,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F66" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
       <c r="G66" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H66" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="I66" s="3">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="J66" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4759,7 +4753,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4770,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4779,22 +4773,22 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="F67" t="s">
-        <v>226</v>
+        <v>58</v>
       </c>
       <c r="G67" s="3">
         <v>46064</v>
       </c>
       <c r="H67" s="3">
-        <v>46079</v>
+        <v>46140</v>
       </c>
       <c r="I67" s="3">
-        <v>46140</v>
+        <v>46176</v>
       </c>
       <c r="J67" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4809,7 +4803,7 @@
         <v>7</v>
       </c>
       <c r="O67" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4820,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4838,13 +4832,13 @@
         <v>46064</v>
       </c>
       <c r="H68" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I68" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4888,13 +4882,13 @@
         <v>46064</v>
       </c>
       <c r="H69" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I69" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J69" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4920,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4938,13 +4932,13 @@
         <v>46064</v>
       </c>
       <c r="H70" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I70" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J70" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4988,13 +4982,13 @@
         <v>46064</v>
       </c>
       <c r="H71" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I71" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J71" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -5020,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -5029,22 +5023,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="G72" s="3">
         <v>46064</v>
       </c>
       <c r="H72" s="3">
-        <v>46308</v>
+        <v>46150</v>
       </c>
       <c r="I72" s="3">
-        <v>46344</v>
+        <v>46189</v>
       </c>
       <c r="J72" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -5059,7 +5053,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5070,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -5079,22 +5073,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="F73" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="G73" s="3">
         <v>46064</v>
       </c>
       <c r="H73" s="3">
-        <v>46308</v>
+        <v>46178</v>
       </c>
       <c r="I73" s="3">
-        <v>46344</v>
+        <v>46218</v>
       </c>
       <c r="J73" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -5109,7 +5103,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5120,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -5129,22 +5123,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F74" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G74" s="3">
         <v>46064</v>
       </c>
       <c r="H74" s="3">
-        <v>46150</v>
+        <v>46244</v>
       </c>
       <c r="I74" s="3">
-        <v>46189</v>
+        <v>46281</v>
       </c>
       <c r="J74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -5159,7 +5153,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5170,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5179,22 +5173,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F75" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G75" s="3">
         <v>46064</v>
       </c>
       <c r="H75" s="3">
-        <v>46178</v>
+        <v>46303</v>
       </c>
       <c r="I75" s="3">
-        <v>46218</v>
+        <v>46344</v>
       </c>
       <c r="J75" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -5229,28 +5223,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F76" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="G76" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H76" s="3">
-        <v>46244</v>
+        <v>46090</v>
       </c>
       <c r="I76" s="3">
-        <v>46281</v>
+        <v>46140</v>
       </c>
       <c r="J76" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -5279,28 +5273,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>93</v>
+        <v>247</v>
       </c>
       <c r="F77" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="G77" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H77" s="3">
-        <v>46303</v>
+        <v>46077</v>
       </c>
       <c r="I77" s="3">
-        <v>46344</v>
+        <v>46142</v>
       </c>
       <c r="J77" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5309,7 +5303,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5320,31 +5314,31 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0</v>
+      </c>
+      <c r="E78" t="s">
+        <v>247</v>
+      </c>
+      <c r="F78" t="s">
         <v>248</v>
-      </c>
-      <c r="C78" s="2">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2">
-        <v>0</v>
-      </c>
-      <c r="E78" t="s">
-        <v>131</v>
-      </c>
-      <c r="F78" t="s">
-        <v>132</v>
       </c>
       <c r="G78" s="3">
         <v>46076</v>
       </c>
       <c r="H78" s="3">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="I78" s="3">
-        <v>46140</v>
+        <v>46218</v>
       </c>
       <c r="J78" t="s">
-        <v>22</v>
+        <v>251</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -5359,7 +5353,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5370,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5379,22 +5373,22 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F79" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G79" s="3">
         <v>46076</v>
       </c>
       <c r="H79" s="3">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="I79" s="3">
-        <v>46142</v>
+        <v>46218</v>
       </c>
       <c r="J79" t="s">
-        <v>22</v>
+        <v>251</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
@@ -5409,7 +5403,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5429,22 +5423,22 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F80" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G80" s="3">
         <v>46076</v>
       </c>
       <c r="H80" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I80" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J80" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
@@ -5459,7 +5453,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5470,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5479,22 +5473,22 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F81" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G81" s="3">
         <v>46076</v>
       </c>
       <c r="H81" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I81" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J81" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
@@ -5509,7 +5503,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5529,22 +5523,22 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F82" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G82" s="3">
         <v>46076</v>
       </c>
       <c r="H82" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I82" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J82" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -5579,22 +5573,22 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G83" s="3">
         <v>46076</v>
       </c>
       <c r="H83" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I83" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J83" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
@@ -5620,31 +5614,31 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
+        <v>152</v>
+      </c>
+      <c r="F84" t="s">
+        <v>153</v>
+      </c>
+      <c r="G84" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H84" s="3">
+        <v>46114</v>
+      </c>
+      <c r="I84" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J84" t="s">
         <v>262</v>
-      </c>
-      <c r="C84" s="2">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2">
-        <v>0</v>
-      </c>
-      <c r="E84" t="s">
-        <v>251</v>
-      </c>
-      <c r="F84" t="s">
-        <v>252</v>
-      </c>
-      <c r="G84" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H84" s="3">
-        <v>46254</v>
-      </c>
-      <c r="I84" s="3">
-        <v>46309</v>
-      </c>
-      <c r="J84" t="s">
-        <v>261</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
@@ -5679,22 +5673,22 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="F85" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="G85" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H85" s="3">
-        <v>46254</v>
+        <v>46108</v>
       </c>
       <c r="I85" s="3">
-        <v>46309</v>
+        <v>46156</v>
       </c>
       <c r="J85" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
@@ -5729,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F86" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G86" s="3">
         <v>46083</v>
@@ -5744,7 +5738,7 @@
         <v>46154</v>
       </c>
       <c r="J86" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
@@ -5759,7 +5753,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5770,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5779,22 +5773,22 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F87" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G87" s="3">
         <v>46083</v>
       </c>
       <c r="H87" s="3">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="I87" s="3">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="J87" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
@@ -5809,7 +5803,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5820,37 +5814,37 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>268</v>
+      </c>
+      <c r="F88" t="s">
         <v>269</v>
       </c>
-      <c r="C88" s="2">
-        <v>1</v>
-      </c>
-      <c r="D88" s="2">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
-        <v>159</v>
-      </c>
-      <c r="F88" t="s">
-        <v>160</v>
-      </c>
       <c r="G88" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="H88" s="3">
-        <v>46114</v>
+        <v>46163</v>
       </c>
       <c r="I88" s="3">
-        <v>46154</v>
+        <v>46238</v>
       </c>
       <c r="J88" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5859,7 +5853,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5870,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5879,28 +5873,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>159</v>
+        <v>273</v>
       </c>
       <c r="F89" t="s">
-        <v>160</v>
+        <v>274</v>
       </c>
       <c r="G89" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H89" s="3">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="I89" s="3">
-        <v>46154</v>
+        <v>46196</v>
       </c>
       <c r="J89" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5909,7 +5903,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5920,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5929,28 +5923,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>272</v>
+        <v>86</v>
       </c>
       <c r="F90" t="s">
-        <v>273</v>
+        <v>87</v>
       </c>
       <c r="G90" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="H90" s="3">
-        <v>46163</v>
+        <v>46128</v>
       </c>
       <c r="I90" s="3">
-        <v>46238</v>
+        <v>46217</v>
       </c>
       <c r="J90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5959,7 +5953,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5970,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5979,22 +5973,22 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F91" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G91" s="3">
         <v>46086</v>
       </c>
       <c r="H91" s="3">
-        <v>46128</v>
+        <v>46219</v>
       </c>
       <c r="I91" s="3">
-        <v>46196</v>
+        <v>46279</v>
       </c>
       <c r="J91" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
@@ -6009,7 +6003,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -6020,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -6029,25 +6023,25 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="F92" t="s">
-        <v>90</v>
+        <v>285</v>
       </c>
       <c r="G92" s="3">
         <v>46086</v>
       </c>
       <c r="H92" s="3">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="I92" s="3">
-        <v>46217</v>
+        <v>46203</v>
       </c>
       <c r="J92" t="s">
-        <v>279</v>
+        <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="L92" s="3">
         <v>46086</v>
@@ -6059,7 +6053,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6070,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6079,25 +6073,25 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F93" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G93" s="3">
         <v>46086</v>
       </c>
       <c r="H93" s="3">
-        <v>46219</v>
+        <v>46210</v>
       </c>
       <c r="I93" s="3">
-        <v>46279</v>
+        <v>46324</v>
       </c>
       <c r="J93" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="L93" s="3">
         <v>46086</v>
@@ -6109,7 +6103,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6120,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6129,28 +6123,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F94" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G94" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H94" s="3">
-        <v>46121</v>
+        <v>46178</v>
       </c>
       <c r="I94" s="3">
-        <v>46203</v>
+        <v>46233</v>
       </c>
       <c r="J94" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="K94" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -6159,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6170,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6179,28 +6173,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>293</v>
+        <v>45</v>
       </c>
       <c r="F95" t="s">
-        <v>294</v>
+        <v>46</v>
       </c>
       <c r="G95" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H95" s="3">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="I95" s="3">
-        <v>46324</v>
+        <v>46234</v>
       </c>
       <c r="J95" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="K95" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6209,7 +6203,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6220,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6229,28 +6223,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F96" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G96" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H96" s="3">
-        <v>46178</v>
+        <v>46092</v>
       </c>
       <c r="I96" s="3">
-        <v>46233</v>
+        <v>46163</v>
       </c>
       <c r="J96" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6259,7 +6253,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6270,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6279,28 +6273,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F97" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G97" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H97" s="3">
-        <v>46212</v>
+        <v>46100</v>
       </c>
       <c r="I97" s="3">
-        <v>46234</v>
+        <v>46146</v>
       </c>
       <c r="J97" t="s">
-        <v>302</v>
+        <v>22</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6309,7 +6303,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6320,7 +6314,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6329,37 +6323,37 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
+        <v>80</v>
+      </c>
+      <c r="F98" t="s">
+        <v>81</v>
+      </c>
+      <c r="G98" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H98" s="3">
+        <v>46106</v>
+      </c>
+      <c r="I98" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J98" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" t="s">
+        <v>5</v>
+      </c>
+      <c r="L98" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M98" t="s">
+        <v>6</v>
+      </c>
+      <c r="N98" t="s">
+        <v>7</v>
+      </c>
+      <c r="O98" t="s">
         <v>305</v>
-      </c>
-      <c r="F98" t="s">
-        <v>306</v>
-      </c>
-      <c r="G98" s="3">
-        <v>46092</v>
-      </c>
-      <c r="H98" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I98" s="3">
-        <v>46163</v>
-      </c>
-      <c r="J98" t="s">
-        <v>274</v>
-      </c>
-      <c r="K98" t="s">
-        <v>5</v>
-      </c>
-      <c r="L98" s="3">
-        <v>46092</v>
-      </c>
-      <c r="M98" t="s">
-        <v>6</v>
-      </c>
-      <c r="N98" t="s">
-        <v>7</v>
-      </c>
-      <c r="O98" t="s">
-        <v>307</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6370,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6388,10 +6382,10 @@
         <v>46094</v>
       </c>
       <c r="H99" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="I99" s="3">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -6409,7 +6403,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6420,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6438,13 +6432,13 @@
         <v>46094</v>
       </c>
       <c r="H100" s="3">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="I100" s="3">
-        <v>46146</v>
+        <v>46169</v>
       </c>
       <c r="J100" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
@@ -6470,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6488,13 +6482,13 @@
         <v>46094</v>
       </c>
       <c r="H101" s="3">
-        <v>46101</v>
+        <v>46133</v>
       </c>
       <c r="I101" s="3">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="J101" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
@@ -6520,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6541,7 +6535,7 @@
         <v>46133</v>
       </c>
       <c r="I102" s="3">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="J102" t="s">
         <v>13</v>
@@ -6559,7 +6553,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6570,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6588,10 +6582,10 @@
         <v>46094</v>
       </c>
       <c r="H103" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I103" s="3">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="J103" t="s">
         <v>13</v>
@@ -6620,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6638,10 +6632,10 @@
         <v>46094</v>
       </c>
       <c r="H104" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I104" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="J104" t="s">
         <v>13</v>
@@ -6670,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6709,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6720,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6738,13 +6732,13 @@
         <v>46094</v>
       </c>
       <c r="H106" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I106" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J106" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
@@ -6759,7 +6753,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6770,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6788,13 +6782,13 @@
         <v>46094</v>
       </c>
       <c r="H107" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I107" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J107" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
@@ -6809,7 +6803,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6820,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6844,7 +6838,7 @@
         <v>46198</v>
       </c>
       <c r="J108" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
@@ -6859,7 +6853,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6870,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6879,37 +6873,37 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="F109" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="G109" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H109" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I109" s="3">
+        <v>46181</v>
+      </c>
+      <c r="J109" t="s">
+        <v>270</v>
+      </c>
+      <c r="K109" t="s">
+        <v>5</v>
+      </c>
+      <c r="L109" s="3">
         <v>46094</v>
       </c>
-      <c r="H109" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I109" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J109" t="s">
+      <c r="M109" t="s">
+        <v>6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>7</v>
+      </c>
+      <c r="O109" t="s">
         <v>321</v>
-      </c>
-      <c r="K109" t="s">
-        <v>5</v>
-      </c>
-      <c r="L109" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M109" t="s">
-        <v>6</v>
-      </c>
-      <c r="N109" t="s">
-        <v>7</v>
-      </c>
-      <c r="O109" t="s">
-        <v>317</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6920,46 +6914,46 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
+        <v>322</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" t="s">
+        <v>42</v>
+      </c>
+      <c r="G110" s="3">
+        <v>46105</v>
+      </c>
+      <c r="H110" s="3">
+        <v>46224</v>
+      </c>
+      <c r="I110" s="3">
+        <v>46246</v>
+      </c>
+      <c r="J110" t="s">
+        <v>298</v>
+      </c>
+      <c r="K110" t="s">
+        <v>5</v>
+      </c>
+      <c r="L110" s="3">
+        <v>46105</v>
+      </c>
+      <c r="M110" t="s">
+        <v>6</v>
+      </c>
+      <c r="N110" t="s">
+        <v>7</v>
+      </c>
+      <c r="O110" t="s">
         <v>323</v>
-      </c>
-      <c r="C110" s="2">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
-        <v>80</v>
-      </c>
-      <c r="F110" t="s">
-        <v>81</v>
-      </c>
-      <c r="G110" s="3">
-        <v>46094</v>
-      </c>
-      <c r="H110" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I110" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J110" t="s">
-        <v>321</v>
-      </c>
-      <c r="K110" t="s">
-        <v>5</v>
-      </c>
-      <c r="L110" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M110" t="s">
-        <v>6</v>
-      </c>
-      <c r="N110" t="s">
-        <v>7</v>
-      </c>
-      <c r="O110" t="s">
-        <v>317</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6979,28 +6973,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="F111" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="G111" s="3">
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="H111" s="3">
-        <v>46149</v>
+        <v>46232</v>
       </c>
       <c r="I111" s="3">
-        <v>46181</v>
+        <v>46253</v>
       </c>
       <c r="J111" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="K111" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="L111" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -7009,7 +7003,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -7020,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7029,28 +7023,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="F112" t="s">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="G112" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H112" s="3">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="I112" s="3">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="J112" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K112" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="L112" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -7059,7 +7053,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7070,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7079,25 +7073,25 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="F113" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="G113" s="3">
         <v>46106</v>
       </c>
       <c r="H113" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="I113" s="3">
         <v>46253</v>
       </c>
       <c r="J113" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K113" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L113" s="3">
         <v>46106</v>
@@ -7109,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7120,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7129,28 +7123,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="F114" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="G114" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="H114" s="3">
-        <v>46217</v>
+        <v>46135</v>
       </c>
       <c r="I114" s="3">
-        <v>46251</v>
+        <v>46156</v>
       </c>
       <c r="J114" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="K114" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="L114" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -7159,7 +7153,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7170,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7179,28 +7173,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="F115" t="s">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="G115" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H115" s="3">
-        <v>46227</v>
+        <v>46171</v>
       </c>
       <c r="I115" s="3">
-        <v>46253</v>
+        <v>46190</v>
       </c>
       <c r="J115" t="s">
-        <v>336</v>
+        <v>171</v>
       </c>
       <c r="K115" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -7229,28 +7223,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="F116" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="G116" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H116" s="3">
-        <v>46135</v>
+        <v>46171</v>
       </c>
       <c r="I116" s="3">
-        <v>46156</v>
+        <v>46190</v>
       </c>
       <c r="J116" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="K116" t="s">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -7259,7 +7253,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7270,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7294,7 +7288,7 @@
         <v>46190</v>
       </c>
       <c r="J117" t="s">
-        <v>178</v>
+        <v>332</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -7309,7 +7303,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7320,7 +7314,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7338,13 +7332,13 @@
         <v>46113</v>
       </c>
       <c r="H118" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I118" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J118" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
@@ -7370,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7388,13 +7382,13 @@
         <v>46113</v>
       </c>
       <c r="H119" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I119" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J119" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
@@ -7420,31 +7414,31 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
+        <v>343</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
         <v>344</v>
       </c>
-      <c r="C120" s="2">
-        <v>1</v>
-      </c>
-      <c r="D120" s="2">
-        <v>0</v>
-      </c>
-      <c r="E120" t="s">
-        <v>80</v>
-      </c>
       <c r="F120" t="s">
-        <v>81</v>
+        <v>345</v>
       </c>
       <c r="G120" s="3">
         <v>46113</v>
       </c>
       <c r="H120" s="3">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="I120" s="3">
-        <v>46254</v>
+        <v>46266</v>
       </c>
       <c r="J120" t="s">
-        <v>336</v>
+        <v>171</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
@@ -7459,7 +7453,7 @@
         <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7470,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7479,22 +7473,22 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F121" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G121" s="3">
         <v>46113</v>
       </c>
       <c r="H121" s="3">
-        <v>46237</v>
+        <v>46170</v>
       </c>
       <c r="I121" s="3">
-        <v>46254</v>
+        <v>46196</v>
       </c>
       <c r="J121" t="s">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
@@ -7509,7 +7503,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7520,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7529,28 +7523,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="F122" t="s">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="G122" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H122" s="3">
-        <v>46231</v>
+        <v>46154</v>
       </c>
       <c r="I122" s="3">
-        <v>46266</v>
+        <v>46183</v>
       </c>
       <c r="J122" t="s">
-        <v>178</v>
+        <v>298</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7579,28 +7573,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F123" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G123" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H123" s="3">
-        <v>46170</v>
+        <v>46154</v>
       </c>
       <c r="I123" s="3">
-        <v>46196</v>
+        <v>46183</v>
       </c>
       <c r="J123" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7609,7 +7603,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7620,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7629,22 +7623,22 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F124" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="G124" s="3">
         <v>46114</v>
       </c>
       <c r="H124" s="3">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="I124" s="3">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="J124" t="s">
-        <v>302</v>
+        <v>171</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
@@ -7659,7 +7653,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7670,37 +7664,37 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
         <v>355</v>
       </c>
-      <c r="C125" s="2">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
-        <v>80</v>
-      </c>
       <c r="F125" t="s">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="G125" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H125" s="3">
-        <v>46154</v>
+        <v>46135</v>
       </c>
       <c r="I125" s="3">
-        <v>46183</v>
+        <v>46161</v>
       </c>
       <c r="J125" t="s">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7709,7 +7703,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7720,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7735,7 +7729,7 @@
         <v>50</v>
       </c>
       <c r="G126" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H126" s="3">
         <v>46161</v>
@@ -7744,13 +7738,13 @@
         <v>46182</v>
       </c>
       <c r="J126" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7759,7 +7753,7 @@
         <v>7</v>
       </c>
       <c r="O126" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P126" t="s">
         <v>9</v>
@@ -7770,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7779,28 +7773,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>359</v>
+        <v>130</v>
       </c>
       <c r="F127" t="s">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="G127" s="3">
         <v>46122</v>
       </c>
       <c r="H127" s="3">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="I127" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="J127" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7829,28 +7823,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>49</v>
+        <v>364</v>
       </c>
       <c r="F128" t="s">
-        <v>50</v>
+        <v>365</v>
       </c>
       <c r="G128" s="3">
         <v>46122</v>
       </c>
       <c r="H128" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="I128" s="3">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="J128" t="s">
-        <v>178</v>
+        <v>270</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7859,7 +7853,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7870,31 +7864,31 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
+        <v>367</v>
+      </c>
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" t="s">
+        <v>364</v>
+      </c>
+      <c r="F129" t="s">
         <v>365</v>
-      </c>
-      <c r="C129" s="2">
-        <v>1</v>
-      </c>
-      <c r="D129" s="2">
-        <v>0</v>
-      </c>
-      <c r="E129" t="s">
-        <v>137</v>
-      </c>
-      <c r="F129" t="s">
-        <v>138</v>
       </c>
       <c r="G129" s="3">
         <v>46122</v>
       </c>
       <c r="H129" s="3">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="I129" s="3">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J129" t="s">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
@@ -7920,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7929,22 +7923,22 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>368</v>
+        <v>221</v>
       </c>
       <c r="F130" t="s">
-        <v>369</v>
+        <v>222</v>
       </c>
       <c r="G130" s="3">
         <v>46122</v>
       </c>
       <c r="H130" s="3">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="I130" s="3">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="J130" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
@@ -7959,7 +7953,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7970,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7979,22 +7973,22 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>368</v>
+        <v>209</v>
       </c>
       <c r="F131" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="G131" s="3">
         <v>46122</v>
       </c>
       <c r="H131" s="3">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="I131" s="3">
-        <v>46189</v>
+        <v>46168</v>
       </c>
       <c r="J131" t="s">
-        <v>178</v>
+        <v>275</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
@@ -8009,7 +8003,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -8029,28 +8023,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F132" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G132" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H132" s="3">
-        <v>46157</v>
+        <v>46142</v>
       </c>
       <c r="I132" s="3">
-        <v>46188</v>
+        <v>46168</v>
       </c>
       <c r="J132" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8079,28 +8073,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>213</v>
+        <v>375</v>
       </c>
       <c r="F133" t="s">
-        <v>214</v>
+        <v>376</v>
       </c>
       <c r="G133" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H133" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="I133" s="3">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="J133" t="s">
-        <v>279</v>
+        <v>171</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8109,7 +8103,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8120,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8129,28 +8123,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>213</v>
+        <v>364</v>
       </c>
       <c r="F134" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="G134" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="H134" s="3">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="I134" s="3">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="J134" t="s">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -8159,7 +8153,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8170,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8179,28 +8173,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F135" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G135" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H135" s="3">
-        <v>46161</v>
+        <v>46127</v>
       </c>
       <c r="I135" s="3">
-        <v>46210</v>
+        <v>46146</v>
       </c>
       <c r="J135" t="s">
-        <v>178</v>
+        <v>275</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -8209,7 +8203,7 @@
         <v>7</v>
       </c>
       <c r="O135" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8220,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8229,28 +8223,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>368</v>
+        <v>330</v>
       </c>
       <c r="F136" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G136" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="H136" s="3">
-        <v>46146</v>
+        <v>46182</v>
       </c>
       <c r="I136" s="3">
-        <v>46170</v>
+        <v>46210</v>
       </c>
       <c r="J136" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8259,7 +8253,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8270,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8279,28 +8273,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="F137" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="G137" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="H137" s="3">
-        <v>46127</v>
+        <v>46174</v>
       </c>
       <c r="I137" s="3">
-        <v>46146</v>
+        <v>46195</v>
       </c>
       <c r="J137" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8329,28 +8323,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="F138" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="G138" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H138" s="3">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="I138" s="3">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="J138" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="K138" t="s">
         <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8379,10 +8373,10 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F139" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G139" s="3">
         <v>46133</v>
@@ -8394,7 +8388,7 @@
         <v>46195</v>
       </c>
       <c r="J139" t="s">
-        <v>336</v>
+        <v>171</v>
       </c>
       <c r="K139" t="s">
         <v>5</v>
@@ -8429,28 +8423,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>368</v>
+        <v>152</v>
       </c>
       <c r="F140" t="s">
-        <v>369</v>
+        <v>153</v>
       </c>
       <c r="G140" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H140" s="3">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="I140" s="3">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="J140" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8479,28 +8473,28 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>368</v>
+        <v>330</v>
       </c>
       <c r="F141" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="G141" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="H141" s="3">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="I141" s="3">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="J141" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K141" t="s">
         <v>5</v>
       </c>
       <c r="L141" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
@@ -8529,28 +8523,28 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="F142" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="G142" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="H142" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="I142" s="3">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="J142" t="s">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="K142" t="s">
         <v>5</v>
       </c>
       <c r="L142" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="M142" t="s">
         <v>6</v>
@@ -8579,28 +8573,28 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>334</v>
+        <v>140</v>
       </c>
       <c r="F143" t="s">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="G143" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H143" s="3">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="I143" s="3">
-        <v>46198</v>
+        <v>46245</v>
       </c>
       <c r="J143" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="K143" t="s">
         <v>5</v>
       </c>
       <c r="L143" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M143" t="s">
         <v>6</v>
@@ -8617,11 +8611,11 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" t="s">
         <v>400</v>
       </c>
-      <c r="B144" t="s">
-        <v>401</v>
-      </c>
       <c r="C144" s="2">
         <v>1</v>
       </c>
@@ -8629,37 +8623,37 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>402</v>
+        <v>140</v>
       </c>
       <c r="F144" t="s">
-        <v>403</v>
+        <v>141</v>
       </c>
       <c r="G144" s="3">
-        <v>46043</v>
+        <v>46140</v>
       </c>
       <c r="H144" s="3">
-        <v>46051</v>
+        <v>46191</v>
       </c>
       <c r="I144" s="3">
-        <v>46057</v>
+        <v>46245</v>
       </c>
       <c r="J144" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="K144" t="s">
-        <v>404</v>
+        <v>5</v>
       </c>
       <c r="L144" s="3">
-        <v>46043</v>
+        <v>46140</v>
       </c>
       <c r="M144" t="s">
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>405</v>
+        <v>7</v>
       </c>
       <c r="O144" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8667,49 +8661,49 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B145" t="s">
+        <v>402</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
+        <v>403</v>
+      </c>
+      <c r="F145" t="s">
+        <v>404</v>
+      </c>
+      <c r="G145" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H145" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J145" t="s">
+        <v>317</v>
+      </c>
+      <c r="K145" t="s">
+        <v>405</v>
+      </c>
+      <c r="L145" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
+        <v>406</v>
+      </c>
+      <c r="O145" t="s">
         <v>407</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
-        <v>408</v>
-      </c>
-      <c r="F145" t="s">
-        <v>409</v>
-      </c>
-      <c r="G145" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H145" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I145" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J145" t="s">
-        <v>13</v>
-      </c>
-      <c r="K145" t="s">
-        <v>404</v>
-      </c>
-      <c r="L145" s="3">
-        <v>46057</v>
-      </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>405</v>
-      </c>
-      <c r="O145" t="s">
-        <v>406</v>
       </c>
       <c r="P145" t="s">
         <v>9</v>
@@ -8717,49 +8711,49 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B146" t="s">
+        <v>408</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>409</v>
+      </c>
+      <c r="F146" t="s">
         <v>410</v>
       </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>411</v>
-      </c>
-      <c r="F146" t="s">
-        <v>412</v>
-      </c>
       <c r="G146" s="3">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H146" s="3">
-        <v>46121</v>
+        <v>46076</v>
       </c>
       <c r="I146" s="3">
-        <v>46122</v>
+        <v>46083</v>
       </c>
       <c r="J146" t="s">
-        <v>413</v>
+        <v>13</v>
       </c>
       <c r="K146" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L146" s="3">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="M146" t="s">
         <v>6</v>
       </c>
       <c r="N146" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O146" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P146" t="s">
         <v>9</v>
@@ -8767,10 +8761,10 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B147" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C147" s="2">
         <v>1</v>
@@ -8779,10 +8773,10 @@
         <v>0</v>
       </c>
       <c r="E147" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F147" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G147" s="3">
         <v>46114</v>
@@ -8794,10 +8788,10 @@
         <v>46148</v>
       </c>
       <c r="J147" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K147" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L147" s="3">
         <v>46114</v>
@@ -8806,10 +8800,10 @@
         <v>6</v>
       </c>
       <c r="N147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O147" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P147" t="s">
         <v>9</v>
@@ -8817,10 +8811,10 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B148" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C148" s="2">
         <v>1</v>
@@ -8829,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F148" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G148" s="3">
         <v>46122</v>
@@ -8844,10 +8838,10 @@
         <v>46148</v>
       </c>
       <c r="J148" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K148" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L148" s="3">
         <v>46122</v>
@@ -8856,10 +8850,10 @@
         <v>6</v>
       </c>
       <c r="N148" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P148" t="s">
         <v>9</v>
@@ -8867,49 +8861,49 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B149" t="s">
+        <v>418</v>
+      </c>
+      <c r="C149" s="2">
+        <v>1</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0</v>
+      </c>
+      <c r="E149" t="s">
+        <v>419</v>
+      </c>
+      <c r="F149" t="s">
+        <v>420</v>
+      </c>
+      <c r="G149" s="3">
+        <v>46135</v>
+      </c>
+      <c r="H149" s="3">
+        <v>46135</v>
+      </c>
+      <c r="I149" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J149" t="s">
         <v>421</v>
       </c>
-      <c r="C149" s="2">
-        <v>1</v>
-      </c>
-      <c r="D149" s="2">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
-        <v>422</v>
-      </c>
-      <c r="F149" t="s">
-        <v>423</v>
-      </c>
-      <c r="G149" s="3">
-        <v>46127</v>
-      </c>
-      <c r="H149" s="3">
-        <v>46132</v>
-      </c>
-      <c r="I149" s="3">
-        <v>46136</v>
-      </c>
-      <c r="J149" t="s">
-        <v>413</v>
-      </c>
       <c r="K149" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L149" s="3">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="M149" t="s">
         <v>6</v>
       </c>
       <c r="N149" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O149" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P149" t="s">
         <v>9</v>
@@ -8917,49 +8911,49 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B150" t="s">
+        <v>422</v>
+      </c>
+      <c r="C150" s="2">
+        <v>1</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" t="s">
+        <v>423</v>
+      </c>
+      <c r="F150" t="s">
         <v>424</v>
       </c>
-      <c r="C150" s="2">
-        <v>1</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>425</v>
-      </c>
-      <c r="F150" t="s">
-        <v>426</v>
-      </c>
       <c r="G150" s="3">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="H150" s="3">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="I150" s="3">
         <v>46147</v>
       </c>
       <c r="J150" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="K150" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L150" s="3">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="M150" t="s">
         <v>6</v>
       </c>
       <c r="N150" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O150" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P150" t="s">
         <v>9</v>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="437">
   <si>
     <t>ZP01</t>
   </si>
@@ -277,6 +277,9 @@
     <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
+  </si>
+  <si>
     <t>1100181710</t>
   </si>
   <si>
@@ -565,9 +568,6 @@
     <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
-  </si>
-  <si>
     <t>1100188460</t>
   </si>
   <si>
@@ -637,493 +637,481 @@
     <t>1100187480</t>
   </si>
   <si>
-    <t>100003523</t>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>980000044600</t>
+  </si>
+  <si>
+    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100190220</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1100190240</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>980000005501</t>
+  </si>
+  <si>
+    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100186230</t>
+  </si>
+  <si>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003530</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190880</t>
+  </si>
+  <si>
+    <t>100003531</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003541</t>
+  </si>
+  <si>
+    <t>1100185360</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100186250</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>100003551</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>980000018800</t>
+  </si>
+  <si>
+    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100171080</t>
+  </si>
+  <si>
+    <t>100003558</t>
+  </si>
+  <si>
+    <t>980000018600</t>
+  </si>
+  <si>
+    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185560</t>
+  </si>
+  <si>
+    <t>100003559</t>
+  </si>
+  <si>
+    <t>1100190960</t>
+  </si>
+  <si>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>980000023300</t>
+  </si>
+  <si>
+    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
+  </si>
+  <si>
+    <t>1100189660</t>
+  </si>
+  <si>
+    <t>100003561</t>
+  </si>
+  <si>
+    <t>980000027600</t>
+  </si>
+  <si>
+    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>1100189730</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>980000037701</t>
+  </si>
+  <si>
+    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100191710</t>
+  </si>
+  <si>
+    <t>100003563</t>
+  </si>
+  <si>
+    <t>980000032501</t>
+  </si>
+  <si>
+    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100184050</t>
+  </si>
+  <si>
+    <t>100003564</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100192160</t>
+  </si>
+  <si>
+    <t>100003568</t>
+  </si>
+  <si>
+    <t>980000041900</t>
+  </si>
+  <si>
+    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
+  </si>
+  <si>
+    <t>1300000184</t>
+  </si>
+  <si>
+    <t>100003569</t>
+  </si>
+  <si>
+    <t>1100192900</t>
+  </si>
+  <si>
+    <t>100003570</t>
+  </si>
+  <si>
+    <t>100003571</t>
+  </si>
+  <si>
+    <t>100003572</t>
+  </si>
+  <si>
+    <t>1100192930</t>
+  </si>
+  <si>
+    <t>100003573</t>
+  </si>
+  <si>
+    <t>100003574</t>
+  </si>
+  <si>
+    <t>100003575</t>
+  </si>
+  <si>
+    <t>1100192830</t>
+  </si>
+  <si>
+    <t>100003576</t>
+  </si>
+  <si>
+    <t>100003577</t>
+  </si>
+  <si>
+    <t>100003578</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003579</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>100003585</t>
+  </si>
+  <si>
+    <t>1100178040</t>
+  </si>
+  <si>
+    <t>100003587</t>
+  </si>
+  <si>
+    <t>1100193830</t>
+  </si>
+  <si>
+    <t>100003590</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100193820</t>
+  </si>
+  <si>
+    <t>100003592</t>
+  </si>
+  <si>
+    <t>1100178390</t>
+  </si>
+  <si>
+    <t>100003593</t>
+  </si>
+  <si>
+    <t>980000022901</t>
+  </si>
+  <si>
+    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100193130</t>
+  </si>
+  <si>
+    <t>100003594</t>
+  </si>
+  <si>
+    <t>1100194400</t>
+  </si>
+  <si>
+    <t>100003595</t>
+  </si>
+  <si>
+    <t>1100193850</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>100003597</t>
+  </si>
+  <si>
+    <t>100003598</t>
+  </si>
+  <si>
+    <t>1100193860</t>
+  </si>
+  <si>
+    <t>100003599</t>
+  </si>
+  <si>
+    <t>100003600</t>
+  </si>
+  <si>
+    <t>980000045100</t>
+  </si>
+  <si>
+    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100191950</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>1100183290</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>1100194940</t>
+  </si>
+  <si>
+    <t>100003603</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>1100194930</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100194670</t>
+  </si>
+  <si>
+    <t>100003606</t>
+  </si>
+  <si>
+    <t>1100195420</t>
+  </si>
+  <si>
+    <t>100003607</t>
+  </si>
+  <si>
+    <t>1100195960</t>
+  </si>
+  <si>
+    <t>100003608</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100195080</t>
+  </si>
+  <si>
+    <t>100003609</t>
+  </si>
+  <si>
+    <t>100003610</t>
+  </si>
+  <si>
+    <t>1100187490</t>
+  </si>
+  <si>
+    <t>100003611</t>
   </si>
   <si>
     <t>980000036400</t>
   </si>
   <si>
     <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
-  </si>
-  <si>
-    <t>1100182050</t>
-  </si>
-  <si>
-    <t>100003524</t>
-  </si>
-  <si>
-    <t>1100182060</t>
-  </si>
-  <si>
-    <t>100003525</t>
-  </si>
-  <si>
-    <t>980000044600</t>
-  </si>
-  <si>
-    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100190220</t>
-  </si>
-  <si>
-    <t>100003526</t>
-  </si>
-  <si>
-    <t>1100190240</t>
-  </si>
-  <si>
-    <t>100003527</t>
-  </si>
-  <si>
-    <t>980000005501</t>
-  </si>
-  <si>
-    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100186230</t>
-  </si>
-  <si>
-    <t>100003528</t>
-  </si>
-  <si>
-    <t>1100190870</t>
-  </si>
-  <si>
-    <t>100003529</t>
-  </si>
-  <si>
-    <t>100003530</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190880</t>
-  </si>
-  <si>
-    <t>100003531</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>100003532</t>
-  </si>
-  <si>
-    <t>1100190890</t>
-  </si>
-  <si>
-    <t>100003533</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>1100190900</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190910</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1100190920</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1100190930</t>
-  </si>
-  <si>
-    <t>100003541</t>
-  </si>
-  <si>
-    <t>1100185360</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>980000048100</t>
-  </si>
-  <si>
-    <t>5A-350XL_X=650, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100191210</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100191250</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1100191260</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1100191270</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>100003549</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100186250</t>
-  </si>
-  <si>
-    <t>100003550</t>
-  </si>
-  <si>
-    <t>100003551</t>
-  </si>
-  <si>
-    <t>100003552</t>
-  </si>
-  <si>
-    <t>100003553</t>
-  </si>
-  <si>
-    <t>980000018800</t>
-  </si>
-  <si>
-    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100171080</t>
-  </si>
-  <si>
-    <t>100003558</t>
-  </si>
-  <si>
-    <t>980000018600</t>
-  </si>
-  <si>
-    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185560</t>
-  </si>
-  <si>
-    <t>100003559</t>
-  </si>
-  <si>
-    <t>1100190960</t>
-  </si>
-  <si>
-    <t>100003560</t>
-  </si>
-  <si>
-    <t>980000023300</t>
-  </si>
-  <si>
-    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
-  </si>
-  <si>
-    <t>1100189660</t>
-  </si>
-  <si>
-    <t>100003561</t>
-  </si>
-  <si>
-    <t>980000027600</t>
-  </si>
-  <si>
-    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>1100189730</t>
-  </si>
-  <si>
-    <t>100003562</t>
-  </si>
-  <si>
-    <t>980000037701</t>
-  </si>
-  <si>
-    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100191710</t>
-  </si>
-  <si>
-    <t>100003563</t>
-  </si>
-  <si>
-    <t>980000032501</t>
-  </si>
-  <si>
-    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100184050</t>
-  </si>
-  <si>
-    <t>100003564</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100192160</t>
-  </si>
-  <si>
-    <t>100003568</t>
-  </si>
-  <si>
-    <t>980000041900</t>
-  </si>
-  <si>
-    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
-  </si>
-  <si>
-    <t>1300000184</t>
-  </si>
-  <si>
-    <t>100003569</t>
-  </si>
-  <si>
-    <t>1100192900</t>
-  </si>
-  <si>
-    <t>100003570</t>
-  </si>
-  <si>
-    <t>100003571</t>
-  </si>
-  <si>
-    <t>100003572</t>
-  </si>
-  <si>
-    <t>1100192930</t>
-  </si>
-  <si>
-    <t>100003573</t>
-  </si>
-  <si>
-    <t>100003574</t>
-  </si>
-  <si>
-    <t>100003575</t>
-  </si>
-  <si>
-    <t>1100192830</t>
-  </si>
-  <si>
-    <t>100003576</t>
-  </si>
-  <si>
-    <t>100003577</t>
-  </si>
-  <si>
-    <t>100003578</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003579</t>
-  </si>
-  <si>
-    <t>100003580</t>
-  </si>
-  <si>
-    <t>100003585</t>
-  </si>
-  <si>
-    <t>1100178040</t>
-  </si>
-  <si>
-    <t>100003587</t>
-  </si>
-  <si>
-    <t>1100193830</t>
-  </si>
-  <si>
-    <t>100003590</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100193820</t>
-  </si>
-  <si>
-    <t>100003592</t>
-  </si>
-  <si>
-    <t>1100178390</t>
-  </si>
-  <si>
-    <t>100003593</t>
-  </si>
-  <si>
-    <t>980000022901</t>
-  </si>
-  <si>
-    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100193130</t>
-  </si>
-  <si>
-    <t>100003594</t>
-  </si>
-  <si>
-    <t>1100194400</t>
-  </si>
-  <si>
-    <t>100003595</t>
-  </si>
-  <si>
-    <t>1100193850</t>
-  </si>
-  <si>
-    <t>100003596</t>
-  </si>
-  <si>
-    <t>100003597</t>
-  </si>
-  <si>
-    <t>100003598</t>
-  </si>
-  <si>
-    <t>1100193860</t>
-  </si>
-  <si>
-    <t>100003599</t>
-  </si>
-  <si>
-    <t>100003600</t>
-  </si>
-  <si>
-    <t>980000045100</t>
-  </si>
-  <si>
-    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100191950</t>
-  </si>
-  <si>
-    <t>100003601</t>
-  </si>
-  <si>
-    <t>1100183290</t>
-  </si>
-  <si>
-    <t>100003602</t>
-  </si>
-  <si>
-    <t>1100194940</t>
-  </si>
-  <si>
-    <t>100003603</t>
-  </si>
-  <si>
-    <t>100003604</t>
-  </si>
-  <si>
-    <t>1100194930</t>
-  </si>
-  <si>
-    <t>100003605</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100194670</t>
-  </si>
-  <si>
-    <t>100003606</t>
-  </si>
-  <si>
-    <t>1100195420</t>
-  </si>
-  <si>
-    <t>100003607</t>
-  </si>
-  <si>
-    <t>1100195960</t>
-  </si>
-  <si>
-    <t>100003608</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100195080</t>
-  </si>
-  <si>
-    <t>100003609</t>
-  </si>
-  <si>
-    <t>100003610</t>
-  </si>
-  <si>
-    <t>1100187490</t>
-  </si>
-  <si>
-    <t>100003611</t>
   </si>
   <si>
     <t>1100195950</t>
@@ -1438,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1461,52 +1449,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2520,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>86</v>
@@ -2538,7 +2526,7 @@
         <v>46147</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -2553,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="O22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P22" t="s">
         <v>9</v>
@@ -2564,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2573,10 +2561,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" s="3">
         <v>45979</v>
@@ -2603,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="O23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P23" t="s">
         <v>9</v>
@@ -2614,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -2623,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G24" s="3">
         <v>45979</v>
@@ -2653,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="O24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" t="s">
         <v>9</v>
@@ -2664,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2673,10 +2661,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="3">
         <v>45987</v>
@@ -2703,7 +2691,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" t="s">
         <v>9</v>
@@ -2714,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2723,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" s="3">
         <v>45993</v>
@@ -2753,7 +2741,7 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" t="s">
         <v>9</v>
@@ -2764,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2773,10 +2761,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G27" s="3">
         <v>45993</v>
@@ -2803,7 +2791,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2814,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2853,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="O28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" t="s">
         <v>9</v>
@@ -2864,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2873,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G29" s="3">
         <v>45995</v>
@@ -2903,7 +2891,7 @@
         <v>7</v>
       </c>
       <c r="O29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" t="s">
         <v>9</v>
@@ -2914,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2923,10 +2911,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G30" s="3">
         <v>45995</v>
@@ -2953,7 +2941,7 @@
         <v>7</v>
       </c>
       <c r="O30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P30" t="s">
         <v>9</v>
@@ -2964,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2973,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G31" s="3">
         <v>45995</v>
@@ -3003,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="O31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" t="s">
         <v>9</v>
@@ -3014,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -3053,7 +3041,7 @@
         <v>7</v>
       </c>
       <c r="O32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P32" t="s">
         <v>9</v>
@@ -3064,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -3073,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G33" s="3">
         <v>46000</v>
@@ -3103,7 +3091,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P33" t="s">
         <v>9</v>
@@ -3114,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -3153,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" t="s">
         <v>9</v>
@@ -3164,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -3173,10 +3161,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G35" s="3">
         <v>46002</v>
@@ -3203,7 +3191,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3214,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3253,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -3264,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3303,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -3314,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3353,7 +3341,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3364,19 +3352,19 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G39" s="3">
         <v>46007</v>
@@ -3388,7 +3376,7 @@
         <v>46139</v>
       </c>
       <c r="J39" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -3403,7 +3391,7 @@
         <v>7</v>
       </c>
       <c r="O39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3414,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3453,7 +3441,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3464,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -3503,7 +3491,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3514,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3523,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G42" s="3">
         <v>46028</v>
@@ -3553,7 +3541,7 @@
         <v>7</v>
       </c>
       <c r="O42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3564,19 +3552,19 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G43" s="3">
         <v>46029</v>
@@ -3588,7 +3576,7 @@
         <v>46087</v>
       </c>
       <c r="J43" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -3603,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="O43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" t="s">
         <v>9</v>
@@ -3614,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G44" s="3">
         <v>46029</v>
@@ -3638,7 +3626,7 @@
         <v>46085</v>
       </c>
       <c r="J44" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
@@ -3653,7 +3641,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3664,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3673,10 +3661,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G45" s="3">
         <v>46029</v>
@@ -3703,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3714,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3723,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G46" s="3">
         <v>46031</v>
@@ -3753,7 +3741,7 @@
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3764,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3773,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G47" s="3">
         <v>46041</v>
@@ -3803,7 +3791,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3814,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3823,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G48" s="3">
         <v>46043</v>
@@ -3853,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3864,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3873,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G49" s="3">
         <v>46044</v>
@@ -3888,7 +3876,7 @@
         <v>46183</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -3903,7 +3891,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3914,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3923,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G50" s="3">
         <v>46044</v>
@@ -3953,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3964,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -4003,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -4014,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -4023,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G52" s="3">
         <v>46044</v>
@@ -4053,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -4064,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -4073,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G53" s="3">
         <v>46044</v>
@@ -4088,7 +4076,7 @@
         <v>46133</v>
       </c>
       <c r="J53" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
@@ -4223,10 +4211,10 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F56" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G56" s="3">
         <v>46048</v>
@@ -4285,7 +4273,7 @@
         <v>46086</v>
       </c>
       <c r="I57" s="3">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="J57" t="s">
         <v>22</v>
@@ -4470,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
         <v>209</v>
@@ -4479,22 +4467,22 @@
         <v>210</v>
       </c>
       <c r="G61" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H61" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="I61" s="3">
-        <v>46135</v>
+        <v>46170</v>
       </c>
       <c r="J61" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4520,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
         <v>209</v>
@@ -4529,22 +4517,22 @@
         <v>210</v>
       </c>
       <c r="G62" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H62" s="3">
-        <v>46086</v>
+        <v>46134</v>
       </c>
       <c r="I62" s="3">
-        <v>46127</v>
+        <v>46183</v>
       </c>
       <c r="J62" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4579,13 +4567,13 @@
         <v>216</v>
       </c>
       <c r="G63" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H63" s="3">
-        <v>46091</v>
+        <v>46079</v>
       </c>
       <c r="I63" s="3">
-        <v>46170</v>
+        <v>46140</v>
       </c>
       <c r="J63" t="s">
         <v>22</v>
@@ -4594,7 +4582,7 @@
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M63" t="s">
         <v>6</v>
@@ -4623,28 +4611,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F64" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="G64" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H64" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="I64" s="3">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="J64" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4673,22 +4661,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>57</v>
       </c>
       <c r="F65" t="s">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="G65" s="3">
         <v>46064</v>
       </c>
       <c r="H65" s="3">
-        <v>46079</v>
+        <v>46140</v>
       </c>
       <c r="I65" s="3">
-        <v>46140</v>
+        <v>46176</v>
       </c>
       <c r="J65" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4703,7 +4691,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4714,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4732,13 +4720,13 @@
         <v>46064</v>
       </c>
       <c r="H66" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I66" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J66" t="s">
-        <v>13</v>
+        <v>222</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4753,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4764,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4782,13 +4770,13 @@
         <v>46064</v>
       </c>
       <c r="H67" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I67" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J67" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4803,7 +4791,7 @@
         <v>7</v>
       </c>
       <c r="O67" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4814,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4832,13 +4820,13 @@
         <v>46064</v>
       </c>
       <c r="H68" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I68" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J68" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4853,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4864,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4882,13 +4870,13 @@
         <v>46064</v>
       </c>
       <c r="H69" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I69" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J69" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4903,7 +4891,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4914,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4923,22 +4911,22 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G70" s="3">
         <v>46064</v>
       </c>
       <c r="H70" s="3">
-        <v>46308</v>
+        <v>46150</v>
       </c>
       <c r="I70" s="3">
-        <v>46344</v>
+        <v>46189</v>
       </c>
       <c r="J70" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4953,7 +4941,7 @@
         <v>7</v>
       </c>
       <c r="O70" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -4964,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4973,22 +4961,22 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F71" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G71" s="3">
         <v>46064</v>
       </c>
       <c r="H71" s="3">
-        <v>46308</v>
+        <v>46178</v>
       </c>
       <c r="I71" s="3">
-        <v>46344</v>
+        <v>46218</v>
       </c>
       <c r="J71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -5014,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -5023,22 +5011,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F72" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G72" s="3">
         <v>46064</v>
       </c>
       <c r="H72" s="3">
-        <v>46150</v>
+        <v>46244</v>
       </c>
       <c r="I72" s="3">
-        <v>46189</v>
+        <v>46281</v>
       </c>
       <c r="J72" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -5053,7 +5041,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5064,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -5073,22 +5061,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G73" s="3">
         <v>46064</v>
       </c>
       <c r="H73" s="3">
-        <v>46178</v>
+        <v>46303</v>
       </c>
       <c r="I73" s="3">
-        <v>46218</v>
+        <v>46344</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -5103,7 +5091,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5114,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -5123,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="G74" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H74" s="3">
-        <v>46244</v>
+        <v>46090</v>
       </c>
       <c r="I74" s="3">
-        <v>46281</v>
+        <v>46140</v>
       </c>
       <c r="J74" t="s">
-        <v>231</v>
+        <v>22</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -5153,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5164,37 +5152,37 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75" t="s">
         <v>242</v>
       </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>90</v>
-      </c>
-      <c r="F75" t="s">
-        <v>91</v>
-      </c>
       <c r="G75" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H75" s="3">
-        <v>46303</v>
+        <v>46077</v>
       </c>
       <c r="I75" s="3">
-        <v>46344</v>
+        <v>46146</v>
       </c>
       <c r="J75" t="s">
-        <v>231</v>
+        <v>22</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -5223,22 +5211,22 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="G76" s="3">
         <v>46076</v>
       </c>
       <c r="H76" s="3">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="I76" s="3">
-        <v>46140</v>
+        <v>46218</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
+        <v>245</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
@@ -5253,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5264,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5273,22 +5261,22 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G77" s="3">
         <v>46076</v>
       </c>
       <c r="H77" s="3">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="I77" s="3">
-        <v>46142</v>
+        <v>46218</v>
       </c>
       <c r="J77" t="s">
-        <v>22</v>
+        <v>245</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
@@ -5303,7 +5291,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5314,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5323,22 +5311,22 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F78" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G78" s="3">
         <v>46076</v>
       </c>
       <c r="H78" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I78" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J78" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -5353,7 +5341,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5364,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5373,19 +5361,19 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F79" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G79" s="3">
         <v>46076</v>
       </c>
       <c r="H79" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I79" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J79" t="s">
         <v>251</v>
@@ -5403,7 +5391,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5414,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5423,19 +5411,19 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G80" s="3">
         <v>46076</v>
       </c>
       <c r="H80" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I80" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J80" t="s">
         <v>251</v>
@@ -5453,7 +5441,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5464,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5473,22 +5461,22 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G81" s="3">
         <v>46076</v>
       </c>
       <c r="H81" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I81" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J81" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
@@ -5503,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5514,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5523,22 +5511,22 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="F82" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="G82" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H82" s="3">
-        <v>46254</v>
+        <v>46114</v>
       </c>
       <c r="I82" s="3">
-        <v>46309</v>
+        <v>46154</v>
       </c>
       <c r="J82" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -5553,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5564,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5573,22 +5561,22 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="G83" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H83" s="3">
-        <v>46254</v>
+        <v>46108</v>
       </c>
       <c r="I83" s="3">
-        <v>46309</v>
+        <v>46156</v>
       </c>
       <c r="J83" t="s">
-        <v>257</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
@@ -5603,7 +5591,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5614,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5623,10 +5611,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F84" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G84" s="3">
         <v>46083</v>
@@ -5638,7 +5626,7 @@
         <v>46154</v>
       </c>
       <c r="J84" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
@@ -5653,7 +5641,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5664,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5673,22 +5661,22 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F85" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G85" s="3">
         <v>46083</v>
       </c>
       <c r="H85" s="3">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="I85" s="3">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="J85" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
@@ -5703,7 +5691,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5714,46 +5702,46 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
+        <v>261</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0</v>
+      </c>
+      <c r="E86" t="s">
+        <v>262</v>
+      </c>
+      <c r="F86" t="s">
+        <v>263</v>
+      </c>
+      <c r="G86" s="3">
+        <v>46079</v>
+      </c>
+      <c r="H86" s="3">
+        <v>46163</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46238</v>
+      </c>
+      <c r="J86" t="s">
+        <v>264</v>
+      </c>
+      <c r="K86" t="s">
+        <v>5</v>
+      </c>
+      <c r="L86" s="3">
+        <v>46079</v>
+      </c>
+      <c r="M86" t="s">
+        <v>6</v>
+      </c>
+      <c r="N86" t="s">
+        <v>7</v>
+      </c>
+      <c r="O86" t="s">
         <v>265</v>
-      </c>
-      <c r="C86" s="2">
-        <v>1</v>
-      </c>
-      <c r="D86" s="2">
-        <v>0</v>
-      </c>
-      <c r="E86" t="s">
-        <v>152</v>
-      </c>
-      <c r="F86" t="s">
-        <v>153</v>
-      </c>
-      <c r="G86" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H86" s="3">
-        <v>46114</v>
-      </c>
-      <c r="I86" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J86" t="s">
-        <v>262</v>
-      </c>
-      <c r="K86" t="s">
-        <v>5</v>
-      </c>
-      <c r="L86" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M86" t="s">
-        <v>6</v>
-      </c>
-      <c r="N86" t="s">
-        <v>7</v>
-      </c>
-      <c r="O86" t="s">
-        <v>263</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5773,28 +5761,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="F87" t="s">
-        <v>153</v>
+        <v>268</v>
       </c>
       <c r="G87" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H87" s="3">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="I87" s="3">
-        <v>46154</v>
+        <v>46196</v>
       </c>
       <c r="J87" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5803,7 +5791,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5814,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5823,28 +5811,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>268</v>
+        <v>86</v>
       </c>
       <c r="F88" t="s">
+        <v>87</v>
+      </c>
+      <c r="G88" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H88" s="3">
+        <v>46128</v>
+      </c>
+      <c r="I88" s="3">
+        <v>46217</v>
+      </c>
+      <c r="J88" t="s">
         <v>269</v>
       </c>
-      <c r="G88" s="3">
-        <v>46079</v>
-      </c>
-      <c r="H88" s="3">
-        <v>46163</v>
-      </c>
-      <c r="I88" s="3">
-        <v>46238</v>
-      </c>
-      <c r="J88" t="s">
-        <v>270</v>
-      </c>
       <c r="K88" t="s">
         <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5853,7 +5841,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5864,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5873,22 +5861,22 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G89" s="3">
         <v>46086</v>
       </c>
       <c r="H89" s="3">
-        <v>46128</v>
+        <v>46219</v>
       </c>
       <c r="I89" s="3">
-        <v>46196</v>
+        <v>46279</v>
       </c>
       <c r="J89" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
@@ -5923,25 +5911,25 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>86</v>
+        <v>278</v>
       </c>
       <c r="F90" t="s">
-        <v>87</v>
+        <v>279</v>
       </c>
       <c r="G90" s="3">
         <v>46086</v>
       </c>
       <c r="H90" s="3">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="I90" s="3">
-        <v>46217</v>
+        <v>46203</v>
       </c>
       <c r="J90" t="s">
-        <v>275</v>
+        <v>22</v>
       </c>
       <c r="K90" t="s">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="L90" s="3">
         <v>46086</v>
@@ -5953,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5964,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5973,25 +5961,25 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F91" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G91" s="3">
         <v>46086</v>
       </c>
       <c r="H91" s="3">
-        <v>46219</v>
+        <v>46210</v>
       </c>
       <c r="I91" s="3">
-        <v>46279</v>
+        <v>46324</v>
       </c>
       <c r="J91" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K91" t="s">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="L91" s="3">
         <v>46086</v>
@@ -6003,7 +5991,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -6014,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -6023,28 +6011,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G92" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H92" s="3">
-        <v>46121</v>
+        <v>46178</v>
       </c>
       <c r="I92" s="3">
-        <v>46203</v>
+        <v>46233</v>
       </c>
       <c r="J92" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="K92" t="s">
-        <v>286</v>
+        <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -6053,7 +6041,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6064,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6073,28 +6061,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="F93" t="s">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="G93" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H93" s="3">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="I93" s="3">
-        <v>46324</v>
+        <v>46234</v>
       </c>
       <c r="J93" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="K93" t="s">
-        <v>286</v>
+        <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -6103,7 +6091,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6114,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6123,28 +6111,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F94" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G94" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H94" s="3">
-        <v>46178</v>
+        <v>46092</v>
       </c>
       <c r="I94" s="3">
-        <v>46233</v>
+        <v>46163</v>
       </c>
       <c r="J94" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -6153,7 +6141,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6164,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6173,28 +6161,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F95" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G95" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H95" s="3">
-        <v>46212</v>
+        <v>46100</v>
       </c>
       <c r="I95" s="3">
-        <v>46234</v>
+        <v>46146</v>
       </c>
       <c r="J95" t="s">
-        <v>298</v>
+        <v>22</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6223,28 +6211,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="F96" t="s">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="G96" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="H96" s="3">
-        <v>46092</v>
+        <v>46106</v>
       </c>
       <c r="I96" s="3">
-        <v>46163</v>
+        <v>46147</v>
       </c>
       <c r="J96" t="s">
-        <v>270</v>
+        <v>22</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6253,7 +6241,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6264,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6282,10 +6270,10 @@
         <v>46094</v>
       </c>
       <c r="H97" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="I97" s="3">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -6303,7 +6291,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6314,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6332,13 +6320,13 @@
         <v>46094</v>
       </c>
       <c r="H98" s="3">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="I98" s="3">
-        <v>46147</v>
+        <v>46169</v>
       </c>
       <c r="J98" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
@@ -6353,7 +6341,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6364,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6382,13 +6370,13 @@
         <v>46094</v>
       </c>
       <c r="H99" s="3">
-        <v>46101</v>
+        <v>46133</v>
       </c>
       <c r="I99" s="3">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="J99" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
@@ -6403,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6414,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6435,7 +6423,7 @@
         <v>46133</v>
       </c>
       <c r="I100" s="3">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="J100" t="s">
         <v>13</v>
@@ -6453,7 +6441,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6464,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6482,10 +6470,10 @@
         <v>46094</v>
       </c>
       <c r="H101" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I101" s="3">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="J101" t="s">
         <v>13</v>
@@ -6503,7 +6491,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6514,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6532,10 +6520,10 @@
         <v>46094</v>
       </c>
       <c r="H102" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I102" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="J102" t="s">
         <v>13</v>
@@ -6553,7 +6541,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6564,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6603,7 +6591,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6614,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6632,13 +6620,13 @@
         <v>46094</v>
       </c>
       <c r="H104" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I104" s="3">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="J104" t="s">
-        <v>13</v>
+        <v>311</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
@@ -6653,7 +6641,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6664,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6682,13 +6670,13 @@
         <v>46094</v>
       </c>
       <c r="H105" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I105" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J105" t="s">
-        <v>13</v>
+        <v>311</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
@@ -6703,7 +6691,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6714,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6738,7 +6726,7 @@
         <v>46198</v>
       </c>
       <c r="J106" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
@@ -6753,7 +6741,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6764,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6773,29 +6761,29 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="F107" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="G107" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H107" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I107" s="3">
+        <v>46181</v>
+      </c>
+      <c r="J107" t="s">
+        <v>264</v>
+      </c>
+      <c r="K107" t="s">
+        <v>5</v>
+      </c>
+      <c r="L107" s="3">
         <v>46094</v>
       </c>
-      <c r="H107" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I107" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J107" t="s">
-        <v>317</v>
-      </c>
-      <c r="K107" t="s">
-        <v>5</v>
-      </c>
-      <c r="L107" s="3">
-        <v>46093</v>
-      </c>
       <c r="M107" t="s">
         <v>6</v>
       </c>
@@ -6803,7 +6791,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6814,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6823,37 +6811,37 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F108" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G108" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H108" s="3">
-        <v>46167</v>
+        <v>46224</v>
       </c>
       <c r="I108" s="3">
-        <v>46198</v>
+        <v>46246</v>
       </c>
       <c r="J108" t="s">
+        <v>292</v>
+      </c>
+      <c r="K108" t="s">
+        <v>5</v>
+      </c>
+      <c r="L108" s="3">
+        <v>46105</v>
+      </c>
+      <c r="M108" t="s">
+        <v>6</v>
+      </c>
+      <c r="N108" t="s">
+        <v>7</v>
+      </c>
+      <c r="O108" t="s">
         <v>317</v>
-      </c>
-      <c r="K108" t="s">
-        <v>5</v>
-      </c>
-      <c r="L108" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M108" t="s">
-        <v>6</v>
-      </c>
-      <c r="N108" t="s">
-        <v>7</v>
-      </c>
-      <c r="O108" t="s">
-        <v>313</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6864,46 +6852,46 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
+        <v>318</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
+        <v>49</v>
+      </c>
+      <c r="F109" t="s">
+        <v>50</v>
+      </c>
+      <c r="G109" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H109" s="3">
+        <v>46232</v>
+      </c>
+      <c r="I109" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J109" t="s">
+        <v>319</v>
+      </c>
+      <c r="K109" t="s">
+        <v>280</v>
+      </c>
+      <c r="L109" s="3">
+        <v>46106</v>
+      </c>
+      <c r="M109" t="s">
+        <v>6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>7</v>
+      </c>
+      <c r="O109" t="s">
         <v>320</v>
-      </c>
-      <c r="C109" s="2">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
-        <v>182</v>
-      </c>
-      <c r="F109" t="s">
-        <v>183</v>
-      </c>
-      <c r="G109" s="3">
-        <v>46097</v>
-      </c>
-      <c r="H109" s="3">
-        <v>46149</v>
-      </c>
-      <c r="I109" s="3">
-        <v>46181</v>
-      </c>
-      <c r="J109" t="s">
-        <v>270</v>
-      </c>
-      <c r="K109" t="s">
-        <v>5</v>
-      </c>
-      <c r="L109" s="3">
-        <v>46094</v>
-      </c>
-      <c r="M109" t="s">
-        <v>6</v>
-      </c>
-      <c r="N109" t="s">
-        <v>7</v>
-      </c>
-      <c r="O109" t="s">
-        <v>321</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6914,46 +6902,46 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
+        <v>321</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>153</v>
+      </c>
+      <c r="F110" t="s">
+        <v>154</v>
+      </c>
+      <c r="G110" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H110" s="3">
+        <v>46217</v>
+      </c>
+      <c r="I110" s="3">
+        <v>46251</v>
+      </c>
+      <c r="J110" t="s">
+        <v>292</v>
+      </c>
+      <c r="K110" t="s">
+        <v>280</v>
+      </c>
+      <c r="L110" s="3">
+        <v>46106</v>
+      </c>
+      <c r="M110" t="s">
+        <v>6</v>
+      </c>
+      <c r="N110" t="s">
+        <v>7</v>
+      </c>
+      <c r="O110" t="s">
         <v>322</v>
-      </c>
-      <c r="C110" s="2">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2">
-        <v>0</v>
-      </c>
-      <c r="E110" t="s">
-        <v>41</v>
-      </c>
-      <c r="F110" t="s">
-        <v>42</v>
-      </c>
-      <c r="G110" s="3">
-        <v>46105</v>
-      </c>
-      <c r="H110" s="3">
-        <v>46224</v>
-      </c>
-      <c r="I110" s="3">
-        <v>46246</v>
-      </c>
-      <c r="J110" t="s">
-        <v>298</v>
-      </c>
-      <c r="K110" t="s">
-        <v>5</v>
-      </c>
-      <c r="L110" s="3">
-        <v>46105</v>
-      </c>
-      <c r="M110" t="s">
-        <v>6</v>
-      </c>
-      <c r="N110" t="s">
-        <v>7</v>
-      </c>
-      <c r="O110" t="s">
-        <v>323</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6964,34 +6952,34 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
+        <v>323</v>
+      </c>
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
         <v>324</v>
       </c>
-      <c r="C111" s="2">
-        <v>1</v>
-      </c>
-      <c r="D111" s="2">
-        <v>0</v>
-      </c>
-      <c r="E111" t="s">
-        <v>49</v>
-      </c>
       <c r="F111" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="G111" s="3">
         <v>46106</v>
       </c>
       <c r="H111" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="I111" s="3">
         <v>46253</v>
       </c>
       <c r="J111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K111" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L111" s="3">
         <v>46106</v>
@@ -7003,7 +6991,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -7014,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7023,28 +7011,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="F112" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="G112" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="H112" s="3">
-        <v>46217</v>
+        <v>46135</v>
       </c>
       <c r="I112" s="3">
-        <v>46251</v>
+        <v>46156</v>
       </c>
       <c r="J112" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="K112" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L112" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -7053,7 +7041,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7064,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7073,37 +7061,37 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="F113" t="s">
+        <v>81</v>
+      </c>
+      <c r="G113" s="3">
+        <v>46113</v>
+      </c>
+      <c r="H113" s="3">
+        <v>46171</v>
+      </c>
+      <c r="I113" s="3">
+        <v>46190</v>
+      </c>
+      <c r="J113" t="s">
+        <v>172</v>
+      </c>
+      <c r="K113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L113" s="3">
+        <v>46113</v>
+      </c>
+      <c r="M113" t="s">
+        <v>6</v>
+      </c>
+      <c r="N113" t="s">
+        <v>7</v>
+      </c>
+      <c r="O113" t="s">
         <v>331</v>
-      </c>
-      <c r="G113" s="3">
-        <v>46106</v>
-      </c>
-      <c r="H113" s="3">
-        <v>46227</v>
-      </c>
-      <c r="I113" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J113" t="s">
-        <v>332</v>
-      </c>
-      <c r="K113" t="s">
-        <v>286</v>
-      </c>
-      <c r="L113" s="3">
-        <v>46106</v>
-      </c>
-      <c r="M113" t="s">
-        <v>6</v>
-      </c>
-      <c r="N113" t="s">
-        <v>7</v>
-      </c>
-      <c r="O113" t="s">
-        <v>333</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7114,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7123,28 +7111,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="F114" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="G114" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H114" s="3">
-        <v>46135</v>
+        <v>46171</v>
       </c>
       <c r="I114" s="3">
-        <v>46156</v>
+        <v>46190</v>
       </c>
       <c r="J114" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="K114" t="s">
-        <v>286</v>
+        <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -7153,7 +7141,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7164,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7188,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="J115" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -7203,7 +7191,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7214,7 +7202,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7232,13 +7220,13 @@
         <v>46113</v>
       </c>
       <c r="H116" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I116" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J116" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
@@ -7253,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7264,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7282,13 +7270,13 @@
         <v>46113</v>
       </c>
       <c r="H117" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I117" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J117" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -7303,7 +7291,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7314,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7323,22 +7311,22 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="F118" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="G118" s="3">
         <v>46113</v>
       </c>
       <c r="H118" s="3">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="I118" s="3">
-        <v>46254</v>
+        <v>46266</v>
       </c>
       <c r="J118" t="s">
-        <v>332</v>
+        <v>172</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
@@ -7353,7 +7341,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7364,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7373,22 +7361,22 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F119" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G119" s="3">
         <v>46113</v>
       </c>
       <c r="H119" s="3">
-        <v>46237</v>
+        <v>46170</v>
       </c>
       <c r="I119" s="3">
-        <v>46254</v>
+        <v>46196</v>
       </c>
       <c r="J119" t="s">
-        <v>332</v>
+        <v>264</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
@@ -7403,7 +7391,7 @@
         <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7423,37 +7411,37 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
+        <v>80</v>
+      </c>
+      <c r="F120" t="s">
+        <v>81</v>
+      </c>
+      <c r="G120" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H120" s="3">
+        <v>46154</v>
+      </c>
+      <c r="I120" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J120" t="s">
+        <v>292</v>
+      </c>
+      <c r="K120" t="s">
+        <v>5</v>
+      </c>
+      <c r="L120" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M120" t="s">
+        <v>6</v>
+      </c>
+      <c r="N120" t="s">
+        <v>7</v>
+      </c>
+      <c r="O120" t="s">
         <v>344</v>
-      </c>
-      <c r="F120" t="s">
-        <v>345</v>
-      </c>
-      <c r="G120" s="3">
-        <v>46113</v>
-      </c>
-      <c r="H120" s="3">
-        <v>46231</v>
-      </c>
-      <c r="I120" s="3">
-        <v>46266</v>
-      </c>
-      <c r="J120" t="s">
-        <v>171</v>
-      </c>
-      <c r="K120" t="s">
-        <v>5</v>
-      </c>
-      <c r="L120" s="3">
-        <v>46113</v>
-      </c>
-      <c r="M120" t="s">
-        <v>6</v>
-      </c>
-      <c r="N120" t="s">
-        <v>7</v>
-      </c>
-      <c r="O120" t="s">
-        <v>346</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7464,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7473,28 +7461,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F121" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G121" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H121" s="3">
-        <v>46170</v>
+        <v>46154</v>
       </c>
       <c r="I121" s="3">
-        <v>46196</v>
+        <v>46183</v>
       </c>
       <c r="J121" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7503,7 +7491,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7514,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7523,22 +7511,22 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F122" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="G122" s="3">
         <v>46114</v>
       </c>
       <c r="H122" s="3">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="I122" s="3">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="J122" t="s">
-        <v>298</v>
+        <v>172</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
@@ -7553,7 +7541,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7564,37 +7552,37 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
+        <v>348</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>349</v>
+      </c>
+      <c r="F123" t="s">
+        <v>350</v>
+      </c>
+      <c r="G123" s="3">
+        <v>46122</v>
+      </c>
+      <c r="H123" s="3">
+        <v>46135</v>
+      </c>
+      <c r="I123" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J123" t="s">
         <v>351</v>
       </c>
-      <c r="C123" s="2">
-        <v>1</v>
-      </c>
-      <c r="D123" s="2">
-        <v>0</v>
-      </c>
-      <c r="E123" t="s">
-        <v>80</v>
-      </c>
-      <c r="F123" t="s">
-        <v>81</v>
-      </c>
-      <c r="G123" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H123" s="3">
-        <v>46154</v>
-      </c>
-      <c r="I123" s="3">
-        <v>46183</v>
-      </c>
-      <c r="J123" t="s">
-        <v>298</v>
-      </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7603,7 +7591,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7614,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7629,7 +7617,7 @@
         <v>50</v>
       </c>
       <c r="G124" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H124" s="3">
         <v>46161</v>
@@ -7638,13 +7626,13 @@
         <v>46182</v>
       </c>
       <c r="J124" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7653,7 +7641,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7664,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7673,28 +7661,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>355</v>
+        <v>131</v>
       </c>
       <c r="F125" t="s">
-        <v>356</v>
+        <v>132</v>
       </c>
       <c r="G125" s="3">
         <v>46122</v>
       </c>
       <c r="H125" s="3">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="I125" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="J125" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7703,7 +7691,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7714,37 +7702,37 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
+        <v>357</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>358</v>
+      </c>
+      <c r="F126" t="s">
         <v>359</v>
-      </c>
-      <c r="C126" s="2">
-        <v>1</v>
-      </c>
-      <c r="D126" s="2">
-        <v>0</v>
-      </c>
-      <c r="E126" t="s">
-        <v>49</v>
-      </c>
-      <c r="F126" t="s">
-        <v>50</v>
       </c>
       <c r="G126" s="3">
         <v>46122</v>
       </c>
       <c r="H126" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="I126" s="3">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="J126" t="s">
-        <v>171</v>
+        <v>264</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7773,22 +7761,22 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>130</v>
+        <v>358</v>
       </c>
       <c r="F127" t="s">
-        <v>131</v>
+        <v>359</v>
       </c>
       <c r="G127" s="3">
         <v>46122</v>
       </c>
       <c r="H127" s="3">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="I127" s="3">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J127" t="s">
-        <v>357</v>
+        <v>172</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
@@ -7803,7 +7791,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7814,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7823,22 +7811,22 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>364</v>
+        <v>215</v>
       </c>
       <c r="F128" t="s">
-        <v>365</v>
+        <v>216</v>
       </c>
       <c r="G128" s="3">
         <v>46122</v>
       </c>
       <c r="H128" s="3">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="I128" s="3">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="J128" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
@@ -7853,7 +7841,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7864,7 +7852,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7873,22 +7861,22 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F129" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G129" s="3">
         <v>46122</v>
       </c>
       <c r="H129" s="3">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="I129" s="3">
-        <v>46189</v>
+        <v>46168</v>
       </c>
       <c r="J129" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
@@ -7903,7 +7891,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7923,28 +7911,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>221</v>
+        <v>365</v>
       </c>
       <c r="F130" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="G130" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H130" s="3">
-        <v>46156</v>
+        <v>46142</v>
       </c>
       <c r="I130" s="3">
-        <v>46188</v>
+        <v>46168</v>
       </c>
       <c r="J130" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7973,28 +7961,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>209</v>
+        <v>371</v>
       </c>
       <c r="F131" t="s">
-        <v>210</v>
+        <v>372</v>
       </c>
       <c r="G131" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H131" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="I131" s="3">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="J131" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -8003,7 +7991,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -8014,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -8023,28 +8011,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>209</v>
+        <v>358</v>
       </c>
       <c r="F132" t="s">
-        <v>210</v>
+        <v>359</v>
       </c>
       <c r="G132" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="H132" s="3">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="I132" s="3">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="J132" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8053,7 +8041,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8064,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -8073,28 +8061,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F133" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G133" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H133" s="3">
-        <v>46161</v>
+        <v>46127</v>
       </c>
       <c r="I133" s="3">
-        <v>46210</v>
+        <v>46146</v>
       </c>
       <c r="J133" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8103,7 +8091,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8114,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8123,28 +8111,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F134" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="G134" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="H134" s="3">
-        <v>46146</v>
+        <v>46182</v>
       </c>
       <c r="I134" s="3">
-        <v>46170</v>
+        <v>46210</v>
       </c>
       <c r="J134" t="s">
-        <v>357</v>
+        <v>251</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -8153,7 +8141,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8164,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8173,28 +8161,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="F135" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="G135" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="H135" s="3">
-        <v>46127</v>
+        <v>46174</v>
       </c>
       <c r="I135" s="3">
-        <v>46146</v>
+        <v>46195</v>
       </c>
       <c r="J135" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -8223,28 +8211,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="F136" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="G136" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H136" s="3">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="I136" s="3">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="J136" t="s">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8273,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F137" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G137" s="3">
         <v>46133</v>
@@ -8288,7 +8276,7 @@
         <v>46195</v>
       </c>
       <c r="J137" t="s">
-        <v>332</v>
+        <v>172</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
@@ -8323,28 +8311,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>364</v>
+        <v>153</v>
       </c>
       <c r="F138" t="s">
-        <v>365</v>
+        <v>154</v>
       </c>
       <c r="G138" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H138" s="3">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="I138" s="3">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="J138" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K138" t="s">
         <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8373,28 +8361,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F139" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="G139" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="H139" s="3">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="I139" s="3">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="J139" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K139" t="s">
         <v>5</v>
       </c>
       <c r="L139" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8423,28 +8411,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="F140" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="G140" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="H140" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="I140" s="3">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="J140" t="s">
-        <v>357</v>
+        <v>172</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8473,28 +8461,28 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>330</v>
+        <v>141</v>
       </c>
       <c r="F141" t="s">
-        <v>331</v>
+        <v>142</v>
       </c>
       <c r="G141" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H141" s="3">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="I141" s="3">
-        <v>46198</v>
+        <v>46245</v>
       </c>
       <c r="J141" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="K141" t="s">
         <v>5</v>
       </c>
       <c r="L141" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
@@ -8523,22 +8511,22 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="F142" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="G142" s="3">
         <v>46140</v>
       </c>
       <c r="H142" s="3">
-        <v>46142</v>
+        <v>46191</v>
       </c>
       <c r="I142" s="3">
-        <v>46168</v>
+        <v>46245</v>
       </c>
       <c r="J142" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="K142" t="s">
         <v>5</v>
@@ -8553,7 +8541,7 @@
         <v>7</v>
       </c>
       <c r="O142" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8561,7 +8549,7 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="B143" t="s">
         <v>398</v>
@@ -8573,37 +8561,37 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>140</v>
+        <v>399</v>
       </c>
       <c r="F143" t="s">
-        <v>141</v>
+        <v>400</v>
       </c>
       <c r="G143" s="3">
-        <v>46140</v>
+        <v>46043</v>
       </c>
       <c r="H143" s="3">
-        <v>46191</v>
+        <v>46051</v>
       </c>
       <c r="I143" s="3">
-        <v>46245</v>
+        <v>46057</v>
       </c>
       <c r="J143" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="K143" t="s">
-        <v>5</v>
+        <v>401</v>
       </c>
       <c r="L143" s="3">
-        <v>46140</v>
+        <v>46043</v>
       </c>
       <c r="M143" t="s">
         <v>6</v>
       </c>
       <c r="N143" t="s">
-        <v>7</v>
+        <v>402</v>
       </c>
       <c r="O143" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P143" t="s">
         <v>9</v>
@@ -8611,10 +8599,10 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="B144" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
@@ -8623,37 +8611,37 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>140</v>
+        <v>405</v>
       </c>
       <c r="F144" t="s">
-        <v>141</v>
+        <v>406</v>
       </c>
       <c r="G144" s="3">
-        <v>46140</v>
+        <v>46057</v>
       </c>
       <c r="H144" s="3">
-        <v>46191</v>
+        <v>46076</v>
       </c>
       <c r="I144" s="3">
-        <v>46245</v>
+        <v>46083</v>
       </c>
       <c r="J144" t="s">
-        <v>257</v>
+        <v>13</v>
       </c>
       <c r="K144" t="s">
-        <v>5</v>
+        <v>401</v>
       </c>
       <c r="L144" s="3">
-        <v>46140</v>
+        <v>46057</v>
       </c>
       <c r="M144" t="s">
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>7</v>
+        <v>402</v>
       </c>
       <c r="O144" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8661,49 +8649,49 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
+        <v>397</v>
+      </c>
+      <c r="B145" t="s">
+        <v>407</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145" t="s">
+        <v>408</v>
+      </c>
+      <c r="F145" t="s">
+        <v>409</v>
+      </c>
+      <c r="G145" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H145" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I145" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J145" t="s">
+        <v>410</v>
+      </c>
+      <c r="K145" t="s">
         <v>401</v>
       </c>
-      <c r="B145" t="s">
+      <c r="L145" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M145" t="s">
+        <v>6</v>
+      </c>
+      <c r="N145" t="s">
         <v>402</v>
       </c>
-      <c r="C145" s="2">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
+      <c r="O145" t="s">
         <v>403</v>
-      </c>
-      <c r="F145" t="s">
-        <v>404</v>
-      </c>
-      <c r="G145" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H145" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I145" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J145" t="s">
-        <v>317</v>
-      </c>
-      <c r="K145" t="s">
-        <v>405</v>
-      </c>
-      <c r="L145" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>406</v>
-      </c>
-      <c r="O145" t="s">
-        <v>407</v>
       </c>
       <c r="P145" t="s">
         <v>9</v>
@@ -8711,49 +8699,49 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
+        <v>397</v>
+      </c>
+      <c r="B146" t="s">
+        <v>411</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>412</v>
+      </c>
+      <c r="F146" t="s">
+        <v>413</v>
+      </c>
+      <c r="G146" s="3">
+        <v>46122</v>
+      </c>
+      <c r="H146" s="3">
+        <v>46142</v>
+      </c>
+      <c r="I146" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J146" t="s">
+        <v>410</v>
+      </c>
+      <c r="K146" t="s">
         <v>401</v>
       </c>
-      <c r="B146" t="s">
-        <v>408</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>409</v>
-      </c>
-      <c r="F146" t="s">
-        <v>410</v>
-      </c>
-      <c r="G146" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H146" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I146" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J146" t="s">
-        <v>13</v>
-      </c>
-      <c r="K146" t="s">
-        <v>405</v>
-      </c>
       <c r="L146" s="3">
-        <v>46057</v>
+        <v>46122</v>
       </c>
       <c r="M146" t="s">
         <v>6</v>
       </c>
       <c r="N146" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="O146" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="P146" t="s">
         <v>9</v>
@@ -8761,49 +8749,49 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
+        <v>397</v>
+      </c>
+      <c r="B147" t="s">
+        <v>414</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>415</v>
+      </c>
+      <c r="F147" t="s">
+        <v>416</v>
+      </c>
+      <c r="G147" s="3">
+        <v>46135</v>
+      </c>
+      <c r="H147" s="3">
+        <v>46135</v>
+      </c>
+      <c r="I147" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J147" t="s">
+        <v>417</v>
+      </c>
+      <c r="K147" t="s">
         <v>401</v>
       </c>
-      <c r="B147" t="s">
-        <v>411</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>412</v>
-      </c>
-      <c r="F147" t="s">
-        <v>413</v>
-      </c>
-      <c r="G147" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H147" s="3">
-        <v>46148</v>
-      </c>
-      <c r="I147" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J147" t="s">
-        <v>414</v>
-      </c>
-      <c r="K147" t="s">
-        <v>405</v>
-      </c>
       <c r="L147" s="3">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="M147" t="s">
         <v>6</v>
       </c>
       <c r="N147" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="O147" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="P147" t="s">
         <v>9</v>
@@ -8811,151 +8799,51 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
+        <v>397</v>
+      </c>
+      <c r="B148" t="s">
+        <v>418</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148" t="s">
+        <v>419</v>
+      </c>
+      <c r="F148" t="s">
+        <v>420</v>
+      </c>
+      <c r="G148" s="3">
+        <v>46140</v>
+      </c>
+      <c r="H148" s="3">
+        <v>46140</v>
+      </c>
+      <c r="I148" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J148" t="s">
+        <v>311</v>
+      </c>
+      <c r="K148" t="s">
         <v>401</v>
       </c>
-      <c r="B148" t="s">
-        <v>415</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
-        <v>416</v>
-      </c>
-      <c r="F148" t="s">
-        <v>417</v>
-      </c>
-      <c r="G148" s="3">
-        <v>46122</v>
-      </c>
-      <c r="H148" s="3">
-        <v>46142</v>
-      </c>
-      <c r="I148" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J148" t="s">
-        <v>414</v>
-      </c>
-      <c r="K148" t="s">
-        <v>405</v>
-      </c>
       <c r="L148" s="3">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="M148" t="s">
         <v>6</v>
       </c>
       <c r="N148" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="O148" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="P148" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16">
-      <c r="A149" t="s">
-        <v>401</v>
-      </c>
-      <c r="B149" t="s">
-        <v>418</v>
-      </c>
-      <c r="C149" s="2">
-        <v>1</v>
-      </c>
-      <c r="D149" s="2">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
-        <v>419</v>
-      </c>
-      <c r="F149" t="s">
-        <v>420</v>
-      </c>
-      <c r="G149" s="3">
-        <v>46135</v>
-      </c>
-      <c r="H149" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I149" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J149" t="s">
-        <v>421</v>
-      </c>
-      <c r="K149" t="s">
-        <v>405</v>
-      </c>
-      <c r="L149" s="3">
-        <v>46135</v>
-      </c>
-      <c r="M149" t="s">
-        <v>6</v>
-      </c>
-      <c r="N149" t="s">
-        <v>406</v>
-      </c>
-      <c r="O149" t="s">
-        <v>407</v>
-      </c>
-      <c r="P149" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16">
-      <c r="A150" t="s">
-        <v>401</v>
-      </c>
-      <c r="B150" t="s">
-        <v>422</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>423</v>
-      </c>
-      <c r="F150" t="s">
-        <v>424</v>
-      </c>
-      <c r="G150" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H150" s="3">
-        <v>46140</v>
-      </c>
-      <c r="I150" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J150" t="s">
-        <v>317</v>
-      </c>
-      <c r="K150" t="s">
-        <v>405</v>
-      </c>
-      <c r="L150" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M150" t="s">
-        <v>6</v>
-      </c>
-      <c r="N150" t="s">
-        <v>406</v>
-      </c>
-      <c r="O150" t="s">
-        <v>407</v>
-      </c>
-      <c r="P150" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="434">
   <si>
     <t>ZP01</t>
   </si>
@@ -469,316 +469,307 @@
     <t>1100193980</t>
   </si>
   <si>
-    <t>100003500</t>
+    <t>100003502</t>
+  </si>
+  <si>
+    <t>1100183140</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003507</t>
+  </si>
+  <si>
+    <t>980000045400</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003509</t>
+  </si>
+  <si>
+    <t>1100188510</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
+  </si>
+  <si>
+    <t>980000028700</t>
+  </si>
+  <si>
+    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182140</t>
+  </si>
+  <si>
+    <t>100003512</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100188460</t>
+  </si>
+  <si>
+    <t>100003513</t>
+  </si>
+  <si>
+    <t>980000028600</t>
+  </si>
+  <si>
+    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182130</t>
+  </si>
+  <si>
+    <t>100003514</t>
+  </si>
+  <si>
+    <t>980000017001</t>
+  </si>
+  <si>
+    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182120</t>
+  </si>
+  <si>
+    <t>100003515</t>
+  </si>
+  <si>
+    <t>1100185540</t>
+  </si>
+  <si>
+    <t>100003516</t>
+  </si>
+  <si>
+    <t>980000017201</t>
+  </si>
+  <si>
+    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182570</t>
+  </si>
+  <si>
+    <t>100003520</t>
+  </si>
+  <si>
+    <t>1100186590</t>
+  </si>
+  <si>
+    <t>100003521</t>
+  </si>
+  <si>
+    <t>980000000100</t>
+  </si>
+  <si>
+    <t>MVP-8_X=860, Y=530, Z=630</t>
+  </si>
+  <si>
+    <t>1100180520</t>
+  </si>
+  <si>
+    <t>100003522</t>
+  </si>
+  <si>
+    <t>1100187480</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>980000044600</t>
+  </si>
+  <si>
+    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100190220</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1100190240</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>980000005501</t>
+  </si>
+  <si>
+    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100186230</t>
+  </si>
+  <si>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003530</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190880</t>
+  </si>
+  <si>
+    <t>100003531</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003541</t>
+  </si>
+  <si>
+    <t>1100185360</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
   </si>
   <si>
     <t>980000017600</t>
   </si>
   <si>
     <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100183110</t>
-  </si>
-  <si>
-    <t>100003501</t>
-  </si>
-  <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1100183140</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>980000045400</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
-    <t>980000028700</t>
-  </si>
-  <si>
-    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182140</t>
-  </si>
-  <si>
-    <t>100003512</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100188460</t>
-  </si>
-  <si>
-    <t>100003513</t>
-  </si>
-  <si>
-    <t>980000028600</t>
-  </si>
-  <si>
-    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182130</t>
-  </si>
-  <si>
-    <t>100003514</t>
-  </si>
-  <si>
-    <t>980000017001</t>
-  </si>
-  <si>
-    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182120</t>
-  </si>
-  <si>
-    <t>100003515</t>
-  </si>
-  <si>
-    <t>1100185540</t>
-  </si>
-  <si>
-    <t>100003516</t>
-  </si>
-  <si>
-    <t>980000017201</t>
-  </si>
-  <si>
-    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182570</t>
-  </si>
-  <si>
-    <t>100003520</t>
-  </si>
-  <si>
-    <t>1100186590</t>
-  </si>
-  <si>
-    <t>100003521</t>
-  </si>
-  <si>
-    <t>980000000100</t>
-  </si>
-  <si>
-    <t>MVP-8_X=860, Y=530, Z=630</t>
-  </si>
-  <si>
-    <t>1100180520</t>
-  </si>
-  <si>
-    <t>100003522</t>
-  </si>
-  <si>
-    <t>1100187480</t>
-  </si>
-  <si>
-    <t>100003525</t>
-  </si>
-  <si>
-    <t>980000044600</t>
-  </si>
-  <si>
-    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100190220</t>
-  </si>
-  <si>
-    <t>100003526</t>
-  </si>
-  <si>
-    <t>1100190240</t>
-  </si>
-  <si>
-    <t>100003527</t>
-  </si>
-  <si>
-    <t>980000005501</t>
-  </si>
-  <si>
-    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100186230</t>
-  </si>
-  <si>
-    <t>100003528</t>
-  </si>
-  <si>
-    <t>1100190870</t>
-  </si>
-  <si>
-    <t>100003529</t>
-  </si>
-  <si>
-    <t>100003530</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190880</t>
-  </si>
-  <si>
-    <t>100003531</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>100003532</t>
-  </si>
-  <si>
-    <t>1100190890</t>
-  </si>
-  <si>
-    <t>100003533</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>1100190900</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190910</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1100190920</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1100190930</t>
-  </si>
-  <si>
-    <t>100003541</t>
-  </si>
-  <si>
-    <t>1100185360</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>980000048100</t>
-  </si>
-  <si>
-    <t>5A-350XL_X=650, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100191210</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100191250</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1100191260</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1100191270</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>100003549</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
@@ -1426,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1449,52 +1440,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3558,25 +3549,25 @@
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="F43" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="G43" s="3">
         <v>46029</v>
       </c>
       <c r="H43" s="3">
-        <v>46042</v>
+        <v>46057</v>
       </c>
       <c r="I43" s="3">
-        <v>46087</v>
+        <v>46136</v>
       </c>
       <c r="J43" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -3591,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="O43" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P43" t="s">
         <v>9</v>
@@ -3602,37 +3593,37 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>153</v>
-      </c>
-      <c r="F44" t="s">
-        <v>154</v>
-      </c>
       <c r="G44" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="H44" s="3">
-        <v>46037</v>
+        <v>46050</v>
       </c>
       <c r="I44" s="3">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="J44" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K44" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3641,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3652,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3661,19 +3652,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="F45" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="G45" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="H45" s="3">
-        <v>46057</v>
+        <v>46090</v>
       </c>
       <c r="I45" s="3">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -3682,7 +3673,7 @@
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3691,7 +3682,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3702,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3711,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G46" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="H46" s="3">
-        <v>46050</v>
+        <v>46129</v>
       </c>
       <c r="I46" s="3">
         <v>46167</v>
@@ -3732,7 +3723,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="M46" t="s">
         <v>6</v>
@@ -3741,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3752,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3761,28 +3752,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="G47" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="H47" s="3">
-        <v>46090</v>
+        <v>46148</v>
       </c>
       <c r="I47" s="3">
-        <v>46211</v>
+        <v>46183</v>
       </c>
       <c r="J47" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3791,7 +3782,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3802,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3811,19 +3802,19 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="F48" t="s">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="G48" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H48" s="3">
-        <v>46129</v>
+        <v>46090</v>
       </c>
       <c r="I48" s="3">
-        <v>46167</v>
+        <v>46136</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -3832,7 +3823,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3861,22 +3852,22 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G49" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H49" s="3">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="I49" s="3">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -3891,7 +3882,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3902,28 +3893,28 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
         <v>174</v>
       </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
-        <v>91</v>
-      </c>
       <c r="F50" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="G50" s="3">
         <v>46044</v>
       </c>
       <c r="H50" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I50" s="3">
-        <v>46136</v>
+        <v>46156</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -3941,7 +3932,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3952,31 +3943,31 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="G51" s="3">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="H51" s="3">
-        <v>46090</v>
+        <v>46066</v>
       </c>
       <c r="I51" s="3">
-        <v>46195</v>
+        <v>46133</v>
       </c>
       <c r="J51" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
@@ -3991,7 +3982,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -4002,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -4011,22 +4002,22 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G52" s="3">
         <v>46044</v>
       </c>
       <c r="H52" s="3">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="I52" s="3">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="J52" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
@@ -4041,7 +4032,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -4052,37 +4043,37 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G53" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H53" s="3">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="I53" s="3">
-        <v>46133</v>
+        <v>46174</v>
       </c>
       <c r="J53" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -4091,7 +4082,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -4102,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -4111,28 +4102,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="F54" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="G54" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H54" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="I54" s="3">
-        <v>46153</v>
+        <v>46134</v>
       </c>
       <c r="J54" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -4141,7 +4132,7 @@
         <v>7</v>
       </c>
       <c r="O54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" t="s">
         <v>9</v>
@@ -4152,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -4161,19 +4152,19 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G55" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="H55" s="3">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="I55" s="3">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -4182,7 +4173,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -4191,7 +4182,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4202,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -4211,19 +4202,19 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="G56" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H56" s="3">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="I56" s="3">
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="J56" t="s">
         <v>22</v>
@@ -4232,7 +4223,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4241,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="O56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4252,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4261,19 +4252,19 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G57" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="H57" s="3">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="I57" s="3">
-        <v>46164</v>
+        <v>46134</v>
       </c>
       <c r="J57" t="s">
         <v>22</v>
@@ -4282,7 +4273,7 @@
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4291,7 +4282,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4302,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -4311,19 +4302,19 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G58" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="H58" s="3">
         <v>46083</v>
       </c>
       <c r="I58" s="3">
-        <v>46154</v>
+        <v>46136</v>
       </c>
       <c r="J58" t="s">
         <v>22</v>
@@ -4332,7 +4323,7 @@
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4341,7 +4332,7 @@
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4352,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4361,19 +4352,19 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G59" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="H59" s="3">
-        <v>46099</v>
+        <v>46091</v>
       </c>
       <c r="I59" s="3">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="J59" t="s">
         <v>22</v>
@@ -4382,7 +4373,7 @@
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4391,7 +4382,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4402,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4411,19 +4402,19 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G60" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="H60" s="3">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="I60" s="3">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="J60" t="s">
         <v>22</v>
@@ -4432,7 +4423,7 @@
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4441,7 +4432,7 @@
         <v>7</v>
       </c>
       <c r="O60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P60" t="s">
         <v>9</v>
@@ -4452,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4461,19 +4452,19 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G61" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H61" s="3">
-        <v>46091</v>
+        <v>46079</v>
       </c>
       <c r="I61" s="3">
-        <v>46170</v>
+        <v>46140</v>
       </c>
       <c r="J61" t="s">
         <v>22</v>
@@ -4482,7 +4473,7 @@
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4491,7 +4482,7 @@
         <v>7</v>
       </c>
       <c r="O61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4502,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4511,28 +4502,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>209</v>
+        <v>57</v>
       </c>
       <c r="F62" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="G62" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H62" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="I62" s="3">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="J62" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M62" t="s">
         <v>6</v>
@@ -4541,7 +4532,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4552,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4561,22 +4552,22 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F63" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="G63" s="3">
         <v>46064</v>
       </c>
       <c r="H63" s="3">
-        <v>46079</v>
+        <v>46140</v>
       </c>
       <c r="I63" s="3">
-        <v>46140</v>
+        <v>46176</v>
       </c>
       <c r="J63" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
@@ -4591,7 +4582,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4602,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4620,13 +4611,13 @@
         <v>46064</v>
       </c>
       <c r="H64" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I64" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J64" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4641,7 +4632,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4652,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4670,13 +4661,13 @@
         <v>46064</v>
       </c>
       <c r="H65" s="3">
-        <v>46140</v>
+        <v>46246</v>
       </c>
       <c r="I65" s="3">
-        <v>46176</v>
+        <v>46281</v>
       </c>
       <c r="J65" t="s">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4691,7 +4682,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4720,13 +4711,13 @@
         <v>46064</v>
       </c>
       <c r="H66" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I66" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J66" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4741,7 +4732,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4752,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4770,13 +4761,13 @@
         <v>46064</v>
       </c>
       <c r="H67" s="3">
-        <v>46246</v>
+        <v>46308</v>
       </c>
       <c r="I67" s="3">
-        <v>46281</v>
+        <v>46344</v>
       </c>
       <c r="J67" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4791,7 +4782,7 @@
         <v>7</v>
       </c>
       <c r="O67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4802,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4811,22 +4802,22 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F68" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G68" s="3">
         <v>46064</v>
       </c>
       <c r="H68" s="3">
-        <v>46308</v>
+        <v>46150</v>
       </c>
       <c r="I68" s="3">
-        <v>46344</v>
+        <v>46189</v>
       </c>
       <c r="J68" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4841,7 +4832,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4852,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4861,22 +4852,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F69" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G69" s="3">
         <v>46064</v>
       </c>
       <c r="H69" s="3">
-        <v>46308</v>
+        <v>46178</v>
       </c>
       <c r="I69" s="3">
-        <v>46344</v>
+        <v>46218</v>
       </c>
       <c r="J69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4891,7 +4882,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4920,13 +4911,13 @@
         <v>46064</v>
       </c>
       <c r="H70" s="3">
-        <v>46150</v>
+        <v>46244</v>
       </c>
       <c r="I70" s="3">
-        <v>46189</v>
+        <v>46281</v>
       </c>
       <c r="J70" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4970,13 +4961,13 @@
         <v>46064</v>
       </c>
       <c r="H71" s="3">
-        <v>46178</v>
+        <v>46303</v>
       </c>
       <c r="I71" s="3">
-        <v>46218</v>
+        <v>46344</v>
       </c>
       <c r="J71" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
@@ -4991,7 +4982,7 @@
         <v>7</v>
       </c>
       <c r="O71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P71" t="s">
         <v>9</v>
@@ -5002,46 +4993,46 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
+        <v>233</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>125</v>
+      </c>
+      <c r="F72" t="s">
+        <v>126</v>
+      </c>
+      <c r="G72" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H72" s="3">
+        <v>46090</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46140</v>
+      </c>
+      <c r="J72" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M72" t="s">
+        <v>6</v>
+      </c>
+      <c r="N72" t="s">
+        <v>7</v>
+      </c>
+      <c r="O72" t="s">
         <v>234</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>91</v>
-      </c>
-      <c r="F72" t="s">
-        <v>92</v>
-      </c>
-      <c r="G72" s="3">
-        <v>46064</v>
-      </c>
-      <c r="H72" s="3">
-        <v>46244</v>
-      </c>
-      <c r="I72" s="3">
-        <v>46281</v>
-      </c>
-      <c r="J72" t="s">
-        <v>225</v>
-      </c>
-      <c r="K72" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
-        <v>46064</v>
-      </c>
-      <c r="M72" t="s">
-        <v>6</v>
-      </c>
-      <c r="N72" t="s">
-        <v>7</v>
-      </c>
-      <c r="O72" t="s">
-        <v>235</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5052,37 +5043,37 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
+        <v>235</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
         <v>236</v>
       </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
-        <v>91</v>
-      </c>
       <c r="F73" t="s">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c r="G73" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H73" s="3">
-        <v>46303</v>
+        <v>46077</v>
       </c>
       <c r="I73" s="3">
-        <v>46344</v>
+        <v>46146</v>
       </c>
       <c r="J73" t="s">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M73" t="s">
         <v>6</v>
@@ -5091,7 +5082,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5102,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -5111,22 +5102,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="F74" t="s">
-        <v>126</v>
+        <v>237</v>
       </c>
       <c r="G74" s="3">
         <v>46076</v>
       </c>
       <c r="H74" s="3">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="I74" s="3">
-        <v>46140</v>
+        <v>46218</v>
       </c>
       <c r="J74" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -5141,7 +5132,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5152,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5161,22 +5152,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F75" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G75" s="3">
         <v>46076</v>
       </c>
       <c r="H75" s="3">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="I75" s="3">
-        <v>46146</v>
+        <v>46218</v>
       </c>
       <c r="J75" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -5191,7 +5182,7 @@
         <v>7</v>
       </c>
       <c r="O75" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P75" t="s">
         <v>9</v>
@@ -5202,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5211,22 +5202,22 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F76" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G76" s="3">
         <v>46076</v>
       </c>
       <c r="H76" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I76" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J76" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
@@ -5241,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5252,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5261,22 +5252,22 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F77" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G77" s="3">
         <v>46076</v>
       </c>
       <c r="H77" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I77" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
@@ -5291,7 +5282,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5302,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5311,22 +5302,22 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F78" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G78" s="3">
         <v>46076</v>
       </c>
       <c r="H78" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I78" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -5341,7 +5332,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5352,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5361,22 +5352,22 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F79" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G79" s="3">
         <v>46076</v>
       </c>
       <c r="H79" s="3">
-        <v>46217</v>
+        <v>46254</v>
       </c>
       <c r="I79" s="3">
-        <v>46267</v>
+        <v>46309</v>
       </c>
       <c r="J79" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
@@ -5391,7 +5382,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5402,31 +5393,31 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
+        <v>250</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>251</v>
+      </c>
+      <c r="F80" t="s">
         <v>252</v>
       </c>
-      <c r="C80" s="2">
-        <v>1</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
-        <v>241</v>
-      </c>
-      <c r="F80" t="s">
-        <v>242</v>
-      </c>
       <c r="G80" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H80" s="3">
-        <v>46254</v>
+        <v>46114</v>
       </c>
       <c r="I80" s="3">
-        <v>46309</v>
+        <v>46154</v>
       </c>
       <c r="J80" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
@@ -5441,7 +5432,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5452,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5461,22 +5452,22 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F81" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G81" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H81" s="3">
-        <v>46254</v>
+        <v>46108</v>
       </c>
       <c r="I81" s="3">
-        <v>46309</v>
+        <v>46156</v>
       </c>
       <c r="J81" t="s">
-        <v>251</v>
+        <v>22</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
@@ -5491,7 +5482,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5502,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5511,10 +5502,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="F82" t="s">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="G82" s="3">
         <v>46083</v>
@@ -5526,7 +5517,7 @@
         <v>46154</v>
       </c>
       <c r="J82" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -5541,7 +5532,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5552,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5561,22 +5552,22 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="F83" t="s">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="G83" s="3">
         <v>46083</v>
       </c>
       <c r="H83" s="3">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="I83" s="3">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="J83" t="s">
-        <v>22</v>
+        <v>253</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
@@ -5591,7 +5582,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5602,37 +5593,37 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
+        <v>258</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
         <v>259</v>
       </c>
-      <c r="C84" s="2">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2">
-        <v>0</v>
-      </c>
-      <c r="E84" t="s">
-        <v>153</v>
-      </c>
       <c r="F84" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="G84" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="H84" s="3">
-        <v>46114</v>
+        <v>46163</v>
       </c>
       <c r="I84" s="3">
-        <v>46154</v>
+        <v>46238</v>
       </c>
       <c r="J84" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5641,7 +5632,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5652,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5661,28 +5652,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>264</v>
       </c>
       <c r="F85" t="s">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="G85" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H85" s="3">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="I85" s="3">
-        <v>46154</v>
+        <v>46196</v>
       </c>
       <c r="J85" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5691,7 +5682,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5702,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5711,28 +5702,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>86</v>
       </c>
       <c r="F86" t="s">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="G86" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="H86" s="3">
-        <v>46163</v>
+        <v>46128</v>
       </c>
       <c r="I86" s="3">
-        <v>46238</v>
+        <v>46217</v>
       </c>
       <c r="J86" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5741,7 +5732,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5752,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5761,22 +5752,22 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F87" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G87" s="3">
         <v>46086</v>
       </c>
       <c r="H87" s="3">
-        <v>46128</v>
+        <v>46219</v>
       </c>
       <c r="I87" s="3">
-        <v>46196</v>
+        <v>46279</v>
       </c>
       <c r="J87" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
@@ -5791,7 +5782,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5802,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5811,25 +5802,25 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="F88" t="s">
-        <v>87</v>
+        <v>276</v>
       </c>
       <c r="G88" s="3">
         <v>46086</v>
       </c>
       <c r="H88" s="3">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="I88" s="3">
-        <v>46217</v>
+        <v>46203</v>
       </c>
       <c r="J88" t="s">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="K88" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="L88" s="3">
         <v>46086</v>
@@ -5841,7 +5832,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5852,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5861,25 +5852,25 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F89" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G89" s="3">
         <v>46086</v>
       </c>
       <c r="H89" s="3">
-        <v>46219</v>
+        <v>46210</v>
       </c>
       <c r="I89" s="3">
-        <v>46279</v>
+        <v>46324</v>
       </c>
       <c r="J89" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K89" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="L89" s="3">
         <v>46086</v>
@@ -5891,7 +5882,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5902,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5911,28 +5902,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F90" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G90" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H90" s="3">
-        <v>46121</v>
+        <v>46178</v>
       </c>
       <c r="I90" s="3">
-        <v>46203</v>
+        <v>46233</v>
       </c>
       <c r="J90" t="s">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="K90" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c r="L90" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5941,7 +5932,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5952,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5961,28 +5952,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="F91" t="s">
-        <v>284</v>
+        <v>46</v>
       </c>
       <c r="G91" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H91" s="3">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="I91" s="3">
-        <v>46324</v>
+        <v>46234</v>
       </c>
       <c r="J91" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="K91" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5991,7 +5982,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -6002,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -6011,28 +6002,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G92" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="H92" s="3">
-        <v>46178</v>
+        <v>46092</v>
       </c>
       <c r="I92" s="3">
-        <v>46233</v>
+        <v>46163</v>
       </c>
       <c r="J92" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -6041,7 +6032,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6052,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6061,28 +6052,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F93" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G93" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H93" s="3">
-        <v>46212</v>
+        <v>46100</v>
       </c>
       <c r="I93" s="3">
-        <v>46234</v>
+        <v>46146</v>
       </c>
       <c r="J93" t="s">
-        <v>292</v>
+        <v>22</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -6091,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6102,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6111,37 +6102,37 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="F94" t="s">
+        <v>81</v>
+      </c>
+      <c r="G94" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H94" s="3">
+        <v>46106</v>
+      </c>
+      <c r="I94" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J94" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M94" t="s">
+        <v>6</v>
+      </c>
+      <c r="N94" t="s">
+        <v>7</v>
+      </c>
+      <c r="O94" t="s">
         <v>296</v>
-      </c>
-      <c r="G94" s="3">
-        <v>46092</v>
-      </c>
-      <c r="H94" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I94" s="3">
-        <v>46163</v>
-      </c>
-      <c r="J94" t="s">
-        <v>264</v>
-      </c>
-      <c r="K94" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>46092</v>
-      </c>
-      <c r="M94" t="s">
-        <v>6</v>
-      </c>
-      <c r="N94" t="s">
-        <v>7</v>
-      </c>
-      <c r="O94" t="s">
-        <v>297</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6170,10 +6161,10 @@
         <v>46094</v>
       </c>
       <c r="H95" s="3">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="I95" s="3">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
@@ -6191,7 +6182,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6202,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6220,13 +6211,13 @@
         <v>46094</v>
       </c>
       <c r="H96" s="3">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="I96" s="3">
-        <v>46147</v>
+        <v>46169</v>
       </c>
       <c r="J96" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K96" t="s">
         <v>5</v>
@@ -6241,7 +6232,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6270,13 +6261,13 @@
         <v>46094</v>
       </c>
       <c r="H97" s="3">
-        <v>46101</v>
+        <v>46133</v>
       </c>
       <c r="I97" s="3">
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="J97" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
@@ -6291,7 +6282,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6323,7 +6314,7 @@
         <v>46133</v>
       </c>
       <c r="I98" s="3">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="J98" t="s">
         <v>13</v>
@@ -6341,7 +6332,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6352,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6370,10 +6361,10 @@
         <v>46094</v>
       </c>
       <c r="H99" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I99" s="3">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="J99" t="s">
         <v>13</v>
@@ -6391,7 +6382,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6420,10 +6411,10 @@
         <v>46094</v>
       </c>
       <c r="H100" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I100" s="3">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="J100" t="s">
         <v>13</v>
@@ -6441,7 +6432,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6491,7 +6482,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6502,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6520,13 +6511,13 @@
         <v>46094</v>
       </c>
       <c r="H102" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I102" s="3">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="J102" t="s">
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
@@ -6541,7 +6532,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6570,13 +6561,13 @@
         <v>46094</v>
       </c>
       <c r="H103" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I103" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J103" t="s">
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
@@ -6591,7 +6582,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6626,7 +6617,7 @@
         <v>46198</v>
       </c>
       <c r="J104" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
@@ -6641,7 +6632,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6652,46 +6643,46 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
+        <v>178</v>
+      </c>
+      <c r="F105" t="s">
+        <v>179</v>
+      </c>
+      <c r="G105" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H105" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I105" s="3">
+        <v>46181</v>
+      </c>
+      <c r="J105" t="s">
+        <v>261</v>
+      </c>
+      <c r="K105" t="s">
+        <v>5</v>
+      </c>
+      <c r="L105" s="3">
+        <v>46094</v>
+      </c>
+      <c r="M105" t="s">
+        <v>6</v>
+      </c>
+      <c r="N105" t="s">
+        <v>7</v>
+      </c>
+      <c r="O105" t="s">
         <v>312</v>
-      </c>
-      <c r="C105" s="2">
-        <v>1</v>
-      </c>
-      <c r="D105" s="2">
-        <v>0</v>
-      </c>
-      <c r="E105" t="s">
-        <v>80</v>
-      </c>
-      <c r="F105" t="s">
-        <v>81</v>
-      </c>
-      <c r="G105" s="3">
-        <v>46094</v>
-      </c>
-      <c r="H105" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I105" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J105" t="s">
-        <v>311</v>
-      </c>
-      <c r="K105" t="s">
-        <v>5</v>
-      </c>
-      <c r="L105" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M105" t="s">
-        <v>6</v>
-      </c>
-      <c r="N105" t="s">
-        <v>7</v>
-      </c>
-      <c r="O105" t="s">
-        <v>307</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6711,28 +6702,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F106" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G106" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H106" s="3">
-        <v>46167</v>
+        <v>46224</v>
       </c>
       <c r="I106" s="3">
-        <v>46198</v>
+        <v>46246</v>
       </c>
       <c r="J106" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6741,7 +6732,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6752,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6761,28 +6752,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="F107" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="G107" s="3">
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="H107" s="3">
-        <v>46149</v>
+        <v>46232</v>
       </c>
       <c r="I107" s="3">
-        <v>46181</v>
+        <v>46253</v>
       </c>
       <c r="J107" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="K107" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="L107" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6791,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6802,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6811,28 +6802,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>41</v>
+        <v>251</v>
       </c>
       <c r="F108" t="s">
-        <v>42</v>
+        <v>252</v>
       </c>
       <c r="G108" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H108" s="3">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="I108" s="3">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="J108" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K108" t="s">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="L108" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6841,7 +6832,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6852,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6861,25 +6852,25 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>49</v>
+        <v>321</v>
       </c>
       <c r="F109" t="s">
-        <v>50</v>
+        <v>322</v>
       </c>
       <c r="G109" s="3">
         <v>46106</v>
       </c>
       <c r="H109" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="I109" s="3">
         <v>46253</v>
       </c>
       <c r="J109" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="K109" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L109" s="3">
         <v>46106</v>
@@ -6891,7 +6882,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6902,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6911,28 +6902,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="F110" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="G110" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="H110" s="3">
-        <v>46217</v>
+        <v>46135</v>
       </c>
       <c r="I110" s="3">
-        <v>46251</v>
+        <v>46156</v>
       </c>
       <c r="J110" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="K110" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L110" s="3">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6941,7 +6932,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6952,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6961,28 +6952,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="F111" t="s">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="G111" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H111" s="3">
-        <v>46227</v>
+        <v>46171</v>
       </c>
       <c r="I111" s="3">
-        <v>46253</v>
+        <v>46190</v>
       </c>
       <c r="J111" t="s">
-        <v>326</v>
+        <v>167</v>
       </c>
       <c r="K111" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6991,7 +6982,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -7002,46 +6993,46 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
+        <v>329</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" t="s">
+        <v>80</v>
+      </c>
+      <c r="F112" t="s">
+        <v>81</v>
+      </c>
+      <c r="G112" s="3">
+        <v>46113</v>
+      </c>
+      <c r="H112" s="3">
+        <v>46171</v>
+      </c>
+      <c r="I112" s="3">
+        <v>46190</v>
+      </c>
+      <c r="J112" t="s">
+        <v>323</v>
+      </c>
+      <c r="K112" t="s">
+        <v>5</v>
+      </c>
+      <c r="L112" s="3">
+        <v>46113</v>
+      </c>
+      <c r="M112" t="s">
+        <v>6</v>
+      </c>
+      <c r="N112" t="s">
+        <v>7</v>
+      </c>
+      <c r="O112" t="s">
         <v>328</v>
-      </c>
-      <c r="C112" s="2">
-        <v>1</v>
-      </c>
-      <c r="D112" s="2">
-        <v>0</v>
-      </c>
-      <c r="E112" t="s">
-        <v>103</v>
-      </c>
-      <c r="F112" t="s">
-        <v>104</v>
-      </c>
-      <c r="G112" s="3">
-        <v>46107</v>
-      </c>
-      <c r="H112" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I112" s="3">
-        <v>46156</v>
-      </c>
-      <c r="J112" t="s">
-        <v>269</v>
-      </c>
-      <c r="K112" t="s">
-        <v>280</v>
-      </c>
-      <c r="L112" s="3">
-        <v>46107</v>
-      </c>
-      <c r="M112" t="s">
-        <v>6</v>
-      </c>
-      <c r="N112" t="s">
-        <v>7</v>
-      </c>
-      <c r="O112" t="s">
-        <v>329</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7076,7 +7067,7 @@
         <v>46190</v>
       </c>
       <c r="J113" t="s">
-        <v>172</v>
+        <v>323</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -7091,7 +7082,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7102,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7120,13 +7111,13 @@
         <v>46113</v>
       </c>
       <c r="H114" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I114" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J114" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -7141,7 +7132,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7170,13 +7161,13 @@
         <v>46113</v>
       </c>
       <c r="H115" s="3">
-        <v>46171</v>
+        <v>46237</v>
       </c>
       <c r="I115" s="3">
-        <v>46190</v>
+        <v>46254</v>
       </c>
       <c r="J115" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -7191,7 +7182,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7211,22 +7202,22 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="F116" t="s">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="G116" s="3">
         <v>46113</v>
       </c>
       <c r="H116" s="3">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="I116" s="3">
-        <v>46254</v>
+        <v>46266</v>
       </c>
       <c r="J116" t="s">
-        <v>326</v>
+        <v>167</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
@@ -7241,7 +7232,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7252,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7261,22 +7252,22 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F117" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G117" s="3">
         <v>46113</v>
       </c>
       <c r="H117" s="3">
-        <v>46237</v>
+        <v>46170</v>
       </c>
       <c r="I117" s="3">
-        <v>46254</v>
+        <v>46196</v>
       </c>
       <c r="J117" t="s">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
@@ -7291,7 +7282,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7302,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7311,28 +7302,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="F118" t="s">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="G118" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H118" s="3">
-        <v>46231</v>
+        <v>46154</v>
       </c>
       <c r="I118" s="3">
-        <v>46266</v>
+        <v>46183</v>
       </c>
       <c r="J118" t="s">
-        <v>172</v>
+        <v>289</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7341,7 +7332,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7352,46 +7343,46 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
+        <v>342</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
+        <v>80</v>
+      </c>
+      <c r="F119" t="s">
+        <v>81</v>
+      </c>
+      <c r="G119" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H119" s="3">
+        <v>46154</v>
+      </c>
+      <c r="I119" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J119" t="s">
+        <v>289</v>
+      </c>
+      <c r="K119" t="s">
+        <v>5</v>
+      </c>
+      <c r="L119" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M119" t="s">
+        <v>6</v>
+      </c>
+      <c r="N119" t="s">
+        <v>7</v>
+      </c>
+      <c r="O119" t="s">
         <v>341</v>
-      </c>
-      <c r="C119" s="2">
-        <v>1</v>
-      </c>
-      <c r="D119" s="2">
-        <v>0</v>
-      </c>
-      <c r="E119" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" t="s">
-        <v>46</v>
-      </c>
-      <c r="G119" s="3">
-        <v>46113</v>
-      </c>
-      <c r="H119" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I119" s="3">
-        <v>46196</v>
-      </c>
-      <c r="J119" t="s">
-        <v>264</v>
-      </c>
-      <c r="K119" t="s">
-        <v>5</v>
-      </c>
-      <c r="L119" s="3">
-        <v>46113</v>
-      </c>
-      <c r="M119" t="s">
-        <v>6</v>
-      </c>
-      <c r="N119" t="s">
-        <v>7</v>
-      </c>
-      <c r="O119" t="s">
-        <v>342</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7411,22 +7402,22 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F120" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="G120" s="3">
         <v>46114</v>
       </c>
       <c r="H120" s="3">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="I120" s="3">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="J120" t="s">
-        <v>292</v>
+        <v>167</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
@@ -7461,28 +7452,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="F121" t="s">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="G121" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H121" s="3">
-        <v>46154</v>
+        <v>46135</v>
       </c>
       <c r="I121" s="3">
-        <v>46183</v>
+        <v>46161</v>
       </c>
       <c r="J121" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7491,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7502,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7517,7 +7508,7 @@
         <v>50</v>
       </c>
       <c r="G122" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H122" s="3">
         <v>46161</v>
@@ -7526,13 +7517,13 @@
         <v>46182</v>
       </c>
       <c r="J122" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7541,7 +7532,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7552,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7561,28 +7552,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="F123" t="s">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="G123" s="3">
         <v>46122</v>
       </c>
       <c r="H123" s="3">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="I123" s="3">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="J123" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7591,7 +7582,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7602,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7611,28 +7602,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>49</v>
+        <v>355</v>
       </c>
       <c r="F124" t="s">
-        <v>50</v>
+        <v>356</v>
       </c>
       <c r="G124" s="3">
         <v>46122</v>
       </c>
       <c r="H124" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="I124" s="3">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="J124" t="s">
-        <v>172</v>
+        <v>261</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7641,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7652,31 +7643,31 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
+        <v>358</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
         <v>355</v>
       </c>
-      <c r="C125" s="2">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
-        <v>131</v>
-      </c>
       <c r="F125" t="s">
-        <v>132</v>
+        <v>356</v>
       </c>
       <c r="G125" s="3">
         <v>46122</v>
       </c>
       <c r="H125" s="3">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="I125" s="3">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J125" t="s">
-        <v>351</v>
+        <v>167</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
@@ -7691,7 +7682,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7702,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7711,22 +7702,22 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>358</v>
+        <v>210</v>
       </c>
       <c r="F126" t="s">
-        <v>359</v>
+        <v>211</v>
       </c>
       <c r="G126" s="3">
         <v>46122</v>
       </c>
       <c r="H126" s="3">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="I126" s="3">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="J126" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
@@ -7761,22 +7752,22 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F127" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G127" s="3">
         <v>46122</v>
       </c>
       <c r="H127" s="3">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="I127" s="3">
-        <v>46189</v>
+        <v>46168</v>
       </c>
       <c r="J127" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
@@ -7791,7 +7782,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7802,37 +7793,37 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
+        <v>365</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
         <v>362</v>
       </c>
-      <c r="C128" s="2">
-        <v>1</v>
-      </c>
-      <c r="D128" s="2">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
-        <v>215</v>
-      </c>
       <c r="F128" t="s">
-        <v>216</v>
+        <v>363</v>
       </c>
       <c r="G128" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H128" s="3">
-        <v>46156</v>
+        <v>46142</v>
       </c>
       <c r="I128" s="3">
-        <v>46188</v>
+        <v>46168</v>
       </c>
       <c r="J128" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7841,7 +7832,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7852,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7861,28 +7852,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F129" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G129" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H129" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="I129" s="3">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="J129" t="s">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7891,7 +7882,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7902,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7911,28 +7902,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F130" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G130" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="H130" s="3">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="I130" s="3">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="J130" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7941,7 +7932,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7952,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7961,28 +7952,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F131" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G131" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H131" s="3">
-        <v>46161</v>
+        <v>46127</v>
       </c>
       <c r="I131" s="3">
-        <v>46210</v>
+        <v>46146</v>
       </c>
       <c r="J131" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7991,7 +7982,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -8002,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -8011,28 +8002,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="F132" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="G132" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="H132" s="3">
-        <v>46146</v>
+        <v>46182</v>
       </c>
       <c r="I132" s="3">
-        <v>46170</v>
+        <v>46210</v>
       </c>
       <c r="J132" t="s">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8041,7 +8032,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8052,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -8061,28 +8052,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="F133" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="G133" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="H133" s="3">
-        <v>46127</v>
+        <v>46174</v>
       </c>
       <c r="I133" s="3">
-        <v>46146</v>
+        <v>46195</v>
       </c>
       <c r="J133" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8091,7 +8082,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8102,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8111,28 +8102,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="F134" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="G134" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H134" s="3">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="I134" s="3">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="J134" t="s">
-        <v>251</v>
+        <v>323</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -8141,7 +8132,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8152,7 +8143,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8161,10 +8152,10 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F135" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G135" s="3">
         <v>46133</v>
@@ -8176,7 +8167,7 @@
         <v>46195</v>
       </c>
       <c r="J135" t="s">
-        <v>326</v>
+        <v>167</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
@@ -8191,7 +8182,7 @@
         <v>7</v>
       </c>
       <c r="O135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8202,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8211,28 +8202,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>358</v>
+        <v>251</v>
       </c>
       <c r="F136" t="s">
-        <v>359</v>
+        <v>252</v>
       </c>
       <c r="G136" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H136" s="3">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="I136" s="3">
-        <v>46195</v>
+        <v>46171</v>
       </c>
       <c r="J136" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8241,7 +8232,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8252,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8261,28 +8252,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="F137" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="G137" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="H137" s="3">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="I137" s="3">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="J137" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8291,7 +8282,7 @@
         <v>7</v>
       </c>
       <c r="O137" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8302,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8311,28 +8302,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="F138" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="G138" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="H138" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="I138" s="3">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="J138" t="s">
-        <v>351</v>
+        <v>167</v>
       </c>
       <c r="K138" t="s">
         <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8341,7 +8332,7 @@
         <v>7</v>
       </c>
       <c r="O138" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P138" t="s">
         <v>9</v>
@@ -8352,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8361,28 +8352,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="F139" t="s">
-        <v>325</v>
+        <v>142</v>
       </c>
       <c r="G139" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="H139" s="3">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="I139" s="3">
-        <v>46198</v>
+        <v>46245</v>
       </c>
       <c r="J139" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="K139" t="s">
         <v>5</v>
       </c>
       <c r="L139" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8391,7 +8382,7 @@
         <v>7</v>
       </c>
       <c r="O139" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8402,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8411,22 +8402,22 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="F140" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="G140" s="3">
         <v>46140</v>
       </c>
       <c r="H140" s="3">
-        <v>46142</v>
+        <v>46191</v>
       </c>
       <c r="I140" s="3">
-        <v>46168</v>
+        <v>46245</v>
       </c>
       <c r="J140" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
@@ -8441,7 +8432,7 @@
         <v>7</v>
       </c>
       <c r="O140" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8449,10 +8440,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="B141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8461,37 +8452,37 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>141</v>
+        <v>396</v>
       </c>
       <c r="F141" t="s">
-        <v>142</v>
+        <v>397</v>
       </c>
       <c r="G141" s="3">
-        <v>46140</v>
+        <v>46043</v>
       </c>
       <c r="H141" s="3">
-        <v>46191</v>
+        <v>46051</v>
       </c>
       <c r="I141" s="3">
-        <v>46245</v>
+        <v>46057</v>
       </c>
       <c r="J141" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="K141" t="s">
-        <v>5</v>
+        <v>398</v>
       </c>
       <c r="L141" s="3">
-        <v>46140</v>
+        <v>46043</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>7</v>
+        <v>399</v>
       </c>
       <c r="O141" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="P141" t="s">
         <v>9</v>
@@ -8499,10 +8490,10 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="B142" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C142" s="2">
         <v>1</v>
@@ -8511,37 +8502,37 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>141</v>
+        <v>402</v>
       </c>
       <c r="F142" t="s">
-        <v>142</v>
+        <v>403</v>
       </c>
       <c r="G142" s="3">
-        <v>46140</v>
+        <v>46057</v>
       </c>
       <c r="H142" s="3">
-        <v>46191</v>
+        <v>46076</v>
       </c>
       <c r="I142" s="3">
-        <v>46245</v>
+        <v>46083</v>
       </c>
       <c r="J142" t="s">
-        <v>251</v>
+        <v>13</v>
       </c>
       <c r="K142" t="s">
-        <v>5</v>
+        <v>398</v>
       </c>
       <c r="L142" s="3">
-        <v>46140</v>
+        <v>46057</v>
       </c>
       <c r="M142" t="s">
         <v>6</v>
       </c>
       <c r="N142" t="s">
-        <v>7</v>
+        <v>399</v>
       </c>
       <c r="O142" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8549,49 +8540,49 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B143" t="s">
+        <v>404</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>405</v>
+      </c>
+      <c r="F143" t="s">
+        <v>406</v>
+      </c>
+      <c r="G143" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J143" t="s">
+        <v>407</v>
+      </c>
+      <c r="K143" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="L143" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
         <v>399</v>
       </c>
-      <c r="F143" t="s">
+      <c r="O143" t="s">
         <v>400</v>
-      </c>
-      <c r="G143" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H143" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J143" t="s">
-        <v>311</v>
-      </c>
-      <c r="K143" t="s">
-        <v>401</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M143" t="s">
-        <v>6</v>
-      </c>
-      <c r="N143" t="s">
-        <v>402</v>
-      </c>
-      <c r="O143" t="s">
-        <v>403</v>
       </c>
       <c r="P143" t="s">
         <v>9</v>
@@ -8599,10 +8590,10 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B144" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
@@ -8611,37 +8602,37 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G144" s="3">
-        <v>46057</v>
+        <v>46122</v>
       </c>
       <c r="H144" s="3">
-        <v>46076</v>
+        <v>46142</v>
       </c>
       <c r="I144" s="3">
-        <v>46083</v>
+        <v>46148</v>
       </c>
       <c r="J144" t="s">
-        <v>13</v>
+        <v>407</v>
       </c>
       <c r="K144" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="L144" s="3">
-        <v>46057</v>
+        <v>46122</v>
       </c>
       <c r="M144" t="s">
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O144" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8649,10 +8640,10 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C145" s="2">
         <v>1</v>
@@ -8661,37 +8652,37 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F145" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G145" s="3">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="H145" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="I145" s="3">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="J145" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="K145" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="L145" s="3">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="M145" t="s">
         <v>6</v>
       </c>
       <c r="N145" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O145" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="P145" t="s">
         <v>9</v>
@@ -8699,10 +8690,10 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B146" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
@@ -8711,139 +8702,39 @@
         <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F146" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G146" s="3">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="H146" s="3">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="I146" s="3">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="J146" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="K146" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="L146" s="3">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="M146" t="s">
         <v>6</v>
       </c>
       <c r="N146" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O146" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="P146" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16">
-      <c r="A147" t="s">
-        <v>397</v>
-      </c>
-      <c r="B147" t="s">
-        <v>414</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>415</v>
-      </c>
-      <c r="F147" t="s">
-        <v>416</v>
-      </c>
-      <c r="G147" s="3">
-        <v>46135</v>
-      </c>
-      <c r="H147" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I147" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J147" t="s">
-        <v>417</v>
-      </c>
-      <c r="K147" t="s">
-        <v>401</v>
-      </c>
-      <c r="L147" s="3">
-        <v>46135</v>
-      </c>
-      <c r="M147" t="s">
-        <v>6</v>
-      </c>
-      <c r="N147" t="s">
-        <v>402</v>
-      </c>
-      <c r="O147" t="s">
-        <v>403</v>
-      </c>
-      <c r="P147" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16">
-      <c r="A148" t="s">
-        <v>397</v>
-      </c>
-      <c r="B148" t="s">
-        <v>418</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
-        <v>419</v>
-      </c>
-      <c r="F148" t="s">
-        <v>420</v>
-      </c>
-      <c r="G148" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H148" s="3">
-        <v>46140</v>
-      </c>
-      <c r="I148" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J148" t="s">
-        <v>311</v>
-      </c>
-      <c r="K148" t="s">
-        <v>401</v>
-      </c>
-      <c r="L148" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M148" t="s">
-        <v>6</v>
-      </c>
-      <c r="N148" t="s">
-        <v>402</v>
-      </c>
-      <c r="O148" t="s">
-        <v>403</v>
-      </c>
-      <c r="P148" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -2214,7 +2214,7 @@
         <v>46001</v>
       </c>
       <c r="I16" s="3">
-        <v>46129</v>
+        <v>46169</v>
       </c>
       <c r="J16" t="s">
         <v>64</v>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -4099,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
         <v>91</v>
@@ -4117,7 +4117,7 @@
         <v>46134</v>
       </c>
       <c r="J54" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -946,6 +946,9 @@
     <t>100003580</t>
   </si>
   <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
     <t>100003585</t>
   </si>
   <si>
@@ -1232,9 +1235,6 @@
   </si>
   <si>
     <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>630000351</t>
@@ -6617,7 +6617,7 @@
         <v>46198</v>
       </c>
       <c r="J104" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6682,7 +6682,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6732,7 +6732,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6767,7 +6767,7 @@
         <v>46253</v>
       </c>
       <c r="J107" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K107" t="s">
         <v>277</v>
@@ -6782,7 +6782,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6832,7 +6832,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6852,10 +6852,10 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F109" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G109" s="3">
         <v>46106</v>
@@ -6867,7 +6867,7 @@
         <v>46253</v>
       </c>
       <c r="J109" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K109" t="s">
         <v>277</v>
@@ -6882,7 +6882,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6932,7 +6932,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -6993,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7017,7 +7017,7 @@
         <v>46190</v>
       </c>
       <c r="J112" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
@@ -7032,7 +7032,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7067,7 +7067,7 @@
         <v>46190</v>
       </c>
       <c r="J113" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
@@ -7082,7 +7082,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7117,7 +7117,7 @@
         <v>46254</v>
       </c>
       <c r="J114" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -7132,7 +7132,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7167,7 +7167,7 @@
         <v>46254</v>
       </c>
       <c r="J115" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
@@ -7182,7 +7182,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7202,10 +7202,10 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F116" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G116" s="3">
         <v>46113</v>
@@ -7232,7 +7232,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7282,7 +7282,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7332,7 +7332,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7343,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7382,7 +7382,7 @@
         <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7443,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7452,10 +7452,10 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G121" s="3">
         <v>46122</v>
@@ -7467,7 +7467,7 @@
         <v>46161</v>
       </c>
       <c r="J121" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
@@ -7482,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7493,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7532,7 +7532,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7567,7 +7567,7 @@
         <v>46168</v>
       </c>
       <c r="J123" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
@@ -7582,7 +7582,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7602,10 +7602,10 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F124" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G124" s="3">
         <v>46122</v>
@@ -7632,7 +7632,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7652,10 +7652,10 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F125" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G125" s="3">
         <v>46122</v>
@@ -7682,7 +7682,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7693,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7732,7 +7732,7 @@
         <v>7</v>
       </c>
       <c r="O126" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P126" t="s">
         <v>9</v>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7752,10 +7752,10 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F127" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G127" s="3">
         <v>46122</v>
@@ -7782,7 +7782,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7802,10 +7802,10 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G128" s="3">
         <v>46125</v>
@@ -7832,7 +7832,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7852,10 +7852,10 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F129" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G129" s="3">
         <v>46125</v>
@@ -7882,7 +7882,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7902,10 +7902,10 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F130" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G130" s="3">
         <v>46126</v>
@@ -7917,7 +7917,7 @@
         <v>46170</v>
       </c>
       <c r="J130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
@@ -7932,7 +7932,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7952,10 +7952,10 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F131" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G131" s="3">
         <v>46127</v>
@@ -7982,7 +7982,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -8002,10 +8002,10 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F132" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G132" s="3">
         <v>46132</v>
@@ -8032,7 +8032,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -8052,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F133" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G133" s="3">
         <v>46133</v>
@@ -8067,7 +8067,7 @@
         <v>46195</v>
       </c>
       <c r="J133" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
@@ -8082,7 +8082,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8102,10 +8102,10 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F134" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G134" s="3">
         <v>46133</v>
@@ -8117,7 +8117,7 @@
         <v>46195</v>
       </c>
       <c r="J134" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
@@ -8132,7 +8132,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8143,7 +8143,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8152,10 +8152,10 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F135" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G135" s="3">
         <v>46133</v>
@@ -8182,7 +8182,7 @@
         <v>7</v>
       </c>
       <c r="O135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8217,7 +8217,7 @@
         <v>46171</v>
       </c>
       <c r="J136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
@@ -8232,7 +8232,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8252,10 +8252,10 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F137" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G137" s="3">
         <v>46139</v>
@@ -8282,7 +8282,7 @@
         <v>7</v>
       </c>
       <c r="O137" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8332,7 +8332,7 @@
         <v>7</v>
       </c>
       <c r="O138" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P138" t="s">
         <v>9</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8382,7 +8382,7 @@
         <v>7</v>
       </c>
       <c r="O139" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8432,7 +8432,7 @@
         <v>7</v>
       </c>
       <c r="O140" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8440,10 +8440,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8452,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F141" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G141" s="3">
         <v>46043</v>
@@ -8470,7 +8470,7 @@
         <v>308</v>
       </c>
       <c r="K141" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L141" s="3">
         <v>46043</v>
@@ -8479,10 +8479,10 @@
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O141" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P141" t="s">
         <v>9</v>
@@ -8490,10 +8490,10 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B142" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C142" s="2">
         <v>1</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F142" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G142" s="3">
         <v>46057</v>
@@ -8520,7 +8520,7 @@
         <v>13</v>
       </c>
       <c r="K142" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L142" s="3">
         <v>46057</v>
@@ -8529,10 +8529,10 @@
         <v>6</v>
       </c>
       <c r="N142" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O142" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8540,10 +8540,10 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B143" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C143" s="2">
         <v>1</v>
@@ -8552,10 +8552,10 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G143" s="3">
         <v>46114</v>
@@ -8567,10 +8567,10 @@
         <v>46148</v>
       </c>
       <c r="J143" t="s">
-        <v>407</v>
+        <v>311</v>
       </c>
       <c r="K143" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L143" s="3">
         <v>46114</v>
@@ -8579,10 +8579,10 @@
         <v>6</v>
       </c>
       <c r="N143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P143" t="s">
         <v>9</v>
@@ -8590,7 +8590,7 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B144" t="s">
         <v>408</v>
@@ -8617,10 +8617,10 @@
         <v>46148</v>
       </c>
       <c r="J144" t="s">
-        <v>407</v>
+        <v>311</v>
       </c>
       <c r="K144" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L144" s="3">
         <v>46122</v>
@@ -8629,10 +8629,10 @@
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O144" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8640,7 +8640,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B145" t="s">
         <v>411</v>
@@ -8670,7 +8670,7 @@
         <v>414</v>
       </c>
       <c r="K145" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L145" s="3">
         <v>46135</v>
@@ -8679,10 +8679,10 @@
         <v>6</v>
       </c>
       <c r="N145" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O145" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P145" t="s">
         <v>9</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B146" t="s">
         <v>415</v>
@@ -8720,7 +8720,7 @@
         <v>308</v>
       </c>
       <c r="K146" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L146" s="3">
         <v>46140</v>
@@ -8729,10 +8729,10 @@
         <v>6</v>
       </c>
       <c r="N146" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O146" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P146" t="s">
         <v>9</v>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="453">
   <si>
     <t>ZP01</t>
   </si>
@@ -154,6 +154,9 @@
     <t>LG-1570 NEO_X=1500, Y=700, Z=650</t>
   </si>
   <si>
+    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
+  </si>
+  <si>
     <t>1100190750</t>
   </si>
   <si>
@@ -190,7 +193,7 @@
     <t>HCMC-1370_X=1300, Y=700, Z=660</t>
   </si>
   <si>
-    <t>1100169870</t>
+    <t>1100190880</t>
   </si>
   <si>
     <t>100003346</t>
@@ -205,7 +208,7 @@
     <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF PRC  CSER MANC MSCP RESA*</t>
+    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
   </si>
   <si>
     <t>1100170790</t>
@@ -268,7 +271,238 @@
     <t>4200000001</t>
   </si>
   <si>
-    <t>100003446</t>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>980000017700</t>
+  </si>
+  <si>
+    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100182240</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>980000019200</t>
+  </si>
+  <si>
+    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182450</t>
+  </si>
+  <si>
+    <t>100003460</t>
+  </si>
+  <si>
+    <t>980000019400</t>
+  </si>
+  <si>
+    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100175760</t>
+  </si>
+  <si>
+    <t>100003465</t>
+  </si>
+  <si>
+    <t>980000013700</t>
+  </si>
+  <si>
+    <t>S-Plus 8_X=800, Y=520, Z=550</t>
+  </si>
+  <si>
+    <t>1100177930</t>
+  </si>
+  <si>
+    <t>100003468</t>
+  </si>
+  <si>
+    <t>980000045000</t>
+  </si>
+  <si>
+    <t>TGV-106_X=1000, Y=600, Z=510</t>
+  </si>
+  <si>
+    <t>1100182880</t>
+  </si>
+  <si>
+    <t>100003469</t>
+  </si>
+  <si>
+    <t>1100179090</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1100182820</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>980000018002</t>
+  </si>
+  <si>
+    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100172880</t>
+  </si>
+  <si>
+    <t>100003472</t>
+  </si>
+  <si>
+    <t>980000030801</t>
+  </si>
+  <si>
+    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
+  </si>
+  <si>
+    <t>1100177910</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>1300000180</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>980000027800</t>
+  </si>
+  <si>
+    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100183180</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>1100184110</t>
+  </si>
+  <si>
+    <t>100003478</t>
+  </si>
+  <si>
+    <t>980000000800</t>
+  </si>
+  <si>
+    <t>PRO-1000_X=1000, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100180510</t>
+  </si>
+  <si>
+    <t>100003481</t>
+  </si>
+  <si>
+    <t>1100184950</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
+    <t>1100185590</t>
+  </si>
+  <si>
+    <t>100003483</t>
+  </si>
+  <si>
+    <t>1100185600</t>
+  </si>
+  <si>
+    <t>100003488</t>
+  </si>
+  <si>
+    <t>1100185870</t>
+  </si>
+  <si>
+    <t>100003496</t>
+  </si>
+  <si>
+    <t>1300000181</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
+    <t>980000048000</t>
+  </si>
+  <si>
+    <t>SMC-7_X=700, Y=400, Z=300</t>
+  </si>
+  <si>
+    <t>1100193980</t>
+  </si>
+  <si>
+    <t>100003502</t>
+  </si>
+  <si>
+    <t>1100183140</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003507</t>
+  </si>
+  <si>
+    <t>980000045400</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003509</t>
+  </si>
+  <si>
+    <t>1100188510</t>
+  </si>
+  <si>
+    <t>100003510</t>
   </si>
   <si>
     <t>980000022400</t>
@@ -277,163 +511,655 @@
     <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
-  </si>
-  <si>
-    <t>1100181710</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>980000017700</t>
-  </si>
-  <si>
-    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100182240</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>980000019200</t>
-  </si>
-  <si>
-    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182450</t>
-  </si>
-  <si>
-    <t>100003460</t>
-  </si>
-  <si>
-    <t>980000019400</t>
-  </si>
-  <si>
-    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100175760</t>
-  </si>
-  <si>
-    <t>100003465</t>
-  </si>
-  <si>
-    <t>980000013700</t>
-  </si>
-  <si>
-    <t>S-Plus 8_X=800, Y=520, Z=550</t>
-  </si>
-  <si>
-    <t>1100177930</t>
-  </si>
-  <si>
-    <t>100003468</t>
-  </si>
-  <si>
-    <t>980000045000</t>
-  </si>
-  <si>
-    <t>TGV-106_X=1000, Y=600, Z=510</t>
-  </si>
-  <si>
-    <t>1100182880</t>
-  </si>
-  <si>
-    <t>100003469</t>
-  </si>
-  <si>
-    <t>1100179090</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1100182820</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>980000018002</t>
-  </si>
-  <si>
-    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100172880</t>
-  </si>
-  <si>
-    <t>100003472</t>
-  </si>
-  <si>
-    <t>980000030801</t>
-  </si>
-  <si>
-    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
-  </si>
-  <si>
-    <t>1100177910</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>1300000180</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>980000027800</t>
-  </si>
-  <si>
-    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>1100183180</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>1100184110</t>
-  </si>
-  <si>
-    <t>100003478</t>
-  </si>
-  <si>
-    <t>980000000800</t>
-  </si>
-  <si>
-    <t>PRO-1000_X=1000, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100180510</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>1100184950</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>1100185590</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1100185600</t>
-  </si>
-  <si>
-    <t>100003484</t>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
+  </si>
+  <si>
+    <t>980000028700</t>
+  </si>
+  <si>
+    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182140</t>
+  </si>
+  <si>
+    <t>100003513</t>
+  </si>
+  <si>
+    <t>980000028600</t>
+  </si>
+  <si>
+    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182130</t>
+  </si>
+  <si>
+    <t>100003514</t>
+  </si>
+  <si>
+    <t>980000017001</t>
+  </si>
+  <si>
+    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182120</t>
+  </si>
+  <si>
+    <t>100003515</t>
+  </si>
+  <si>
+    <t>1100185540</t>
+  </si>
+  <si>
+    <t>100003516</t>
+  </si>
+  <si>
+    <t>980000017201</t>
+  </si>
+  <si>
+    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182570</t>
+  </si>
+  <si>
+    <t>100003520</t>
+  </si>
+  <si>
+    <t>1100186590</t>
+  </si>
+  <si>
+    <t>100003521</t>
+  </si>
+  <si>
+    <t>980000000100</t>
+  </si>
+  <si>
+    <t>MVP-8_X=860, Y=530, Z=630</t>
+  </si>
+  <si>
+    <t>1100180520</t>
+  </si>
+  <si>
+    <t>100003522</t>
+  </si>
+  <si>
+    <t>1100187480</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>980000044600</t>
+  </si>
+  <si>
+    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100190220</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1100190240</t>
+  </si>
+  <si>
+    <t>100003527</t>
+  </si>
+  <si>
+    <t>980000005501</t>
+  </si>
+  <si>
+    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100186230</t>
+  </si>
+  <si>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003541</t>
+  </si>
+  <si>
+    <t>1100185360</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
+  </si>
+  <si>
+    <t>980000017600</t>
+  </si>
+  <si>
+    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100186250</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>100003551</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>980000018800</t>
+  </si>
+  <si>
+    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100171080</t>
+  </si>
+  <si>
+    <t>100003558</t>
+  </si>
+  <si>
+    <t>980000018600</t>
+  </si>
+  <si>
+    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185560</t>
+  </si>
+  <si>
+    <t>100003559</t>
+  </si>
+  <si>
+    <t>1100190960</t>
+  </si>
+  <si>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>980000023300</t>
+  </si>
+  <si>
+    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
+  </si>
+  <si>
+    <t>1100189660</t>
+  </si>
+  <si>
+    <t>100003561</t>
+  </si>
+  <si>
+    <t>980000027600</t>
+  </si>
+  <si>
+    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>1100189730</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>980000037701</t>
+  </si>
+  <si>
+    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100191710</t>
+  </si>
+  <si>
+    <t>100003563</t>
+  </si>
+  <si>
+    <t>980000032501</t>
+  </si>
+  <si>
+    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100184050</t>
+  </si>
+  <si>
+    <t>100003564</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100192160</t>
+  </si>
+  <si>
+    <t>100003568</t>
+  </si>
+  <si>
+    <t>980000041900</t>
+  </si>
+  <si>
+    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
+  </si>
+  <si>
+    <t>1300000184</t>
+  </si>
+  <si>
+    <t>100003569</t>
+  </si>
+  <si>
+    <t>1100192900</t>
+  </si>
+  <si>
+    <t>100003570</t>
+  </si>
+  <si>
+    <t>100003571</t>
+  </si>
+  <si>
+    <t>100003572</t>
+  </si>
+  <si>
+    <t>1100192930</t>
+  </si>
+  <si>
+    <t>100003573</t>
+  </si>
+  <si>
+    <t>100003574</t>
+  </si>
+  <si>
+    <t>100003575</t>
+  </si>
+  <si>
+    <t>1100192830</t>
+  </si>
+  <si>
+    <t>100003576</t>
+  </si>
+  <si>
+    <t>100003577</t>
+  </si>
+  <si>
+    <t>100003578</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003579</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>100003585</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  CSER MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100178040</t>
+  </si>
+  <si>
+    <t>100003587</t>
+  </si>
+  <si>
+    <t>1100193830</t>
+  </si>
+  <si>
+    <t>100003590</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100193820</t>
+  </si>
+  <si>
+    <t>100003592</t>
+  </si>
+  <si>
+    <t>1100178390</t>
+  </si>
+  <si>
+    <t>100003593</t>
+  </si>
+  <si>
+    <t>980000022901</t>
+  </si>
+  <si>
+    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100193130</t>
+  </si>
+  <si>
+    <t>100003594</t>
+  </si>
+  <si>
+    <t>1100194400</t>
+  </si>
+  <si>
+    <t>100003595</t>
+  </si>
+  <si>
+    <t>1100193850</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>100003597</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>100003598</t>
+  </si>
+  <si>
+    <t>1100193860</t>
+  </si>
+  <si>
+    <t>100003599</t>
+  </si>
+  <si>
+    <t>100003600</t>
+  </si>
+  <si>
+    <t>980000045100</t>
+  </si>
+  <si>
+    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100191950</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>1100183290</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>1100194940</t>
+  </si>
+  <si>
+    <t>100003603</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100194930</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100194670</t>
+  </si>
+  <si>
+    <t>100003606</t>
+  </si>
+  <si>
+    <t>1100195420</t>
+  </si>
+  <si>
+    <t>100003607</t>
+  </si>
+  <si>
+    <t>1100195960</t>
+  </si>
+  <si>
+    <t>100003608</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100195080</t>
+  </si>
+  <si>
+    <t>100003609</t>
+  </si>
+  <si>
+    <t>100003610</t>
+  </si>
+  <si>
+    <t>1100187490</t>
+  </si>
+  <si>
+    <t>100003611</t>
+  </si>
+  <si>
+    <t>980000036400</t>
+  </si>
+  <si>
+    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
+  </si>
+  <si>
+    <t>1100195950</t>
+  </si>
+  <si>
+    <t>100003612</t>
+  </si>
+  <si>
+    <t>1100195920</t>
+  </si>
+  <si>
+    <t>100003613</t>
+  </si>
+  <si>
+    <t>980000043300</t>
+  </si>
+  <si>
+    <t>HSA-216, #50_X=2250, Y=1600, Z=780</t>
+  </si>
+  <si>
+    <t>1100193540</t>
+  </si>
+  <si>
+    <t>100003614</t>
+  </si>
+  <si>
+    <t>1100196310</t>
+  </si>
+  <si>
+    <t>100003615</t>
+  </si>
+  <si>
+    <t>980000008401</t>
+  </si>
+  <si>
+    <t>LG-500_X=520, Y=420, Z=450</t>
+  </si>
+  <si>
+    <t>1100195930</t>
+  </si>
+  <si>
+    <t>100003616</t>
+  </si>
+  <si>
+    <t>1100194450</t>
+  </si>
+  <si>
+    <t>100003617</t>
+  </si>
+  <si>
+    <t>1100194550</t>
+  </si>
+  <si>
+    <t>100003618</t>
+  </si>
+  <si>
+    <t>1100197010</t>
+  </si>
+  <si>
+    <t>100003619</t>
+  </si>
+  <si>
+    <t>1100197020</t>
+  </si>
+  <si>
+    <t>100003620</t>
+  </si>
+  <si>
+    <t>1100191150</t>
+  </si>
+  <si>
+    <t>100003621</t>
+  </si>
+  <si>
+    <t>1100197580</t>
+  </si>
+  <si>
+    <t>100003622</t>
+  </si>
+  <si>
+    <t>1100197240</t>
+  </si>
+  <si>
+    <t>100003623</t>
   </si>
   <si>
     <t>980000043500</t>
@@ -442,760 +1168,88 @@
     <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
   </si>
   <si>
-    <t>1100181160</t>
-  </si>
-  <si>
-    <t>100003488</t>
-  </si>
-  <si>
-    <t>1100185870</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1300000181</t>
-  </si>
-  <si>
-    <t>100003499</t>
-  </si>
-  <si>
-    <t>980000048000</t>
-  </si>
-  <si>
-    <t>SMC-7_X=700, Y=400, Z=300</t>
-  </si>
-  <si>
-    <t>1100193980</t>
-  </si>
-  <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1100183140</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>980000045400</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
-    <t>980000028700</t>
-  </si>
-  <si>
-    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182140</t>
-  </si>
-  <si>
-    <t>100003512</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100188460</t>
-  </si>
-  <si>
-    <t>100003513</t>
-  </si>
-  <si>
-    <t>980000028600</t>
-  </si>
-  <si>
-    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182130</t>
-  </si>
-  <si>
-    <t>100003514</t>
-  </si>
-  <si>
-    <t>980000017001</t>
-  </si>
-  <si>
-    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182120</t>
-  </si>
-  <si>
-    <t>100003515</t>
-  </si>
-  <si>
-    <t>1100185540</t>
-  </si>
-  <si>
-    <t>100003516</t>
-  </si>
-  <si>
-    <t>980000017201</t>
-  </si>
-  <si>
-    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182570</t>
-  </si>
-  <si>
-    <t>100003520</t>
-  </si>
-  <si>
-    <t>1100186590</t>
-  </si>
-  <si>
-    <t>100003521</t>
-  </si>
-  <si>
-    <t>980000000100</t>
-  </si>
-  <si>
-    <t>MVP-8_X=860, Y=530, Z=630</t>
-  </si>
-  <si>
-    <t>1100180520</t>
-  </si>
-  <si>
-    <t>100003522</t>
-  </si>
-  <si>
-    <t>1100187480</t>
-  </si>
-  <si>
-    <t>100003525</t>
-  </si>
-  <si>
-    <t>980000044600</t>
-  </si>
-  <si>
-    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100190220</t>
-  </si>
-  <si>
-    <t>100003526</t>
-  </si>
-  <si>
-    <t>1100190240</t>
-  </si>
-  <si>
-    <t>100003527</t>
-  </si>
-  <si>
-    <t>980000005501</t>
-  </si>
-  <si>
-    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100186230</t>
-  </si>
-  <si>
-    <t>100003528</t>
-  </si>
-  <si>
-    <t>1100190870</t>
-  </si>
-  <si>
-    <t>100003529</t>
-  </si>
-  <si>
-    <t>100003530</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190880</t>
-  </si>
-  <si>
-    <t>100003531</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>100003532</t>
-  </si>
-  <si>
-    <t>1100190890</t>
-  </si>
-  <si>
-    <t>100003533</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>1100190900</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190910</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1100190920</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1100190930</t>
-  </si>
-  <si>
-    <t>100003541</t>
-  </si>
-  <si>
-    <t>1100185360</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>980000048100</t>
-  </si>
-  <si>
-    <t>5A-350XL_X=650, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100191210</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100191250</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1100191260</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1100191270</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>100003549</t>
-  </si>
-  <si>
-    <t>980000017600</t>
-  </si>
-  <si>
-    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100186250</t>
-  </si>
-  <si>
-    <t>100003550</t>
-  </si>
-  <si>
-    <t>100003551</t>
-  </si>
-  <si>
-    <t>100003552</t>
-  </si>
-  <si>
-    <t>100003553</t>
-  </si>
-  <si>
-    <t>980000018800</t>
-  </si>
-  <si>
-    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100171080</t>
-  </si>
-  <si>
-    <t>100003558</t>
-  </si>
-  <si>
-    <t>980000018600</t>
-  </si>
-  <si>
-    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185560</t>
-  </si>
-  <si>
-    <t>100003559</t>
-  </si>
-  <si>
-    <t>1100190960</t>
-  </si>
-  <si>
-    <t>100003560</t>
-  </si>
-  <si>
-    <t>980000023300</t>
-  </si>
-  <si>
-    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
-  </si>
-  <si>
-    <t>1100189660</t>
-  </si>
-  <si>
-    <t>100003561</t>
-  </si>
-  <si>
-    <t>980000027600</t>
-  </si>
-  <si>
-    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>1100189730</t>
-  </si>
-  <si>
-    <t>100003562</t>
-  </si>
-  <si>
-    <t>980000037701</t>
-  </si>
-  <si>
-    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100191710</t>
-  </si>
-  <si>
-    <t>100003563</t>
-  </si>
-  <si>
-    <t>980000032501</t>
-  </si>
-  <si>
-    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100184050</t>
-  </si>
-  <si>
-    <t>100003564</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100192160</t>
-  </si>
-  <si>
-    <t>100003568</t>
-  </si>
-  <si>
-    <t>980000041900</t>
-  </si>
-  <si>
-    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
-  </si>
-  <si>
-    <t>1300000184</t>
-  </si>
-  <si>
-    <t>100003569</t>
-  </si>
-  <si>
-    <t>1100192900</t>
-  </si>
-  <si>
-    <t>100003570</t>
-  </si>
-  <si>
-    <t>100003571</t>
-  </si>
-  <si>
-    <t>100003572</t>
-  </si>
-  <si>
-    <t>1100192930</t>
-  </si>
-  <si>
-    <t>100003573</t>
-  </si>
-  <si>
-    <t>100003574</t>
-  </si>
-  <si>
-    <t>100003575</t>
-  </si>
-  <si>
-    <t>1100192830</t>
-  </si>
-  <si>
-    <t>100003576</t>
-  </si>
-  <si>
-    <t>100003577</t>
-  </si>
-  <si>
-    <t>100003578</t>
+    <t>1100191070</t>
+  </si>
+  <si>
+    <t>100003624</t>
+  </si>
+  <si>
+    <t>100003625</t>
+  </si>
+  <si>
+    <t>1100197570</t>
+  </si>
+  <si>
+    <t>100003626</t>
+  </si>
+  <si>
+    <t>100003627</t>
+  </si>
+  <si>
+    <t>100003628</t>
+  </si>
+  <si>
+    <t>100003629</t>
   </si>
   <si>
     <t>REL  PRC  MANC SETC</t>
   </si>
   <si>
-    <t>100003579</t>
-  </si>
-  <si>
-    <t>100003580</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003585</t>
-  </si>
-  <si>
-    <t>1100178040</t>
-  </si>
-  <si>
-    <t>100003587</t>
-  </si>
-  <si>
-    <t>1100193830</t>
-  </si>
-  <si>
-    <t>100003590</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100193820</t>
-  </si>
-  <si>
-    <t>100003592</t>
-  </si>
-  <si>
-    <t>1100178390</t>
-  </si>
-  <si>
-    <t>100003593</t>
-  </si>
-  <si>
-    <t>980000022901</t>
-  </si>
-  <si>
-    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100193130</t>
-  </si>
-  <si>
-    <t>100003594</t>
-  </si>
-  <si>
-    <t>1100194400</t>
-  </si>
-  <si>
-    <t>100003595</t>
-  </si>
-  <si>
-    <t>1100193850</t>
-  </si>
-  <si>
-    <t>100003596</t>
-  </si>
-  <si>
-    <t>100003597</t>
-  </si>
-  <si>
-    <t>100003598</t>
-  </si>
-  <si>
-    <t>1100193860</t>
-  </si>
-  <si>
-    <t>100003599</t>
-  </si>
-  <si>
-    <t>100003600</t>
-  </si>
-  <si>
-    <t>980000045100</t>
-  </si>
-  <si>
-    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100191950</t>
-  </si>
-  <si>
-    <t>100003601</t>
-  </si>
-  <si>
-    <t>1100183290</t>
-  </si>
-  <si>
-    <t>100003602</t>
-  </si>
-  <si>
-    <t>1100194940</t>
-  </si>
-  <si>
-    <t>100003603</t>
-  </si>
-  <si>
-    <t>100003604</t>
-  </si>
-  <si>
-    <t>1100194930</t>
-  </si>
-  <si>
-    <t>100003605</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100194670</t>
-  </si>
-  <si>
-    <t>100003606</t>
-  </si>
-  <si>
-    <t>1100195420</t>
-  </si>
-  <si>
-    <t>100003607</t>
-  </si>
-  <si>
-    <t>1100195960</t>
-  </si>
-  <si>
-    <t>100003608</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100195080</t>
-  </si>
-  <si>
-    <t>100003609</t>
-  </si>
-  <si>
-    <t>100003610</t>
-  </si>
-  <si>
-    <t>1100187490</t>
-  </si>
-  <si>
-    <t>100003611</t>
-  </si>
-  <si>
-    <t>980000036400</t>
-  </si>
-  <si>
-    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
-  </si>
-  <si>
-    <t>1100195950</t>
-  </si>
-  <si>
-    <t>100003612</t>
-  </si>
-  <si>
-    <t>1100195920</t>
-  </si>
-  <si>
-    <t>100003613</t>
-  </si>
-  <si>
-    <t>980000043300</t>
-  </si>
-  <si>
-    <t>HSA-216, #50_X=2250, Y=1600, Z=780</t>
-  </si>
-  <si>
-    <t>1100193540</t>
-  </si>
-  <si>
-    <t>100003614</t>
-  </si>
-  <si>
-    <t>1100196310</t>
-  </si>
-  <si>
-    <t>100003615</t>
-  </si>
-  <si>
-    <t>980000008401</t>
-  </si>
-  <si>
-    <t>LG-500_X=520, Y=420, Z=450</t>
-  </si>
-  <si>
-    <t>1100195930</t>
-  </si>
-  <si>
-    <t>100003616</t>
-  </si>
-  <si>
-    <t>1100194450</t>
-  </si>
-  <si>
-    <t>100003617</t>
-  </si>
-  <si>
-    <t>1100194550</t>
-  </si>
-  <si>
-    <t>100003618</t>
-  </si>
-  <si>
-    <t>1100197010</t>
-  </si>
-  <si>
-    <t>100003619</t>
-  </si>
-  <si>
-    <t>1100197020</t>
-  </si>
-  <si>
-    <t>100003620</t>
-  </si>
-  <si>
-    <t>1100191150</t>
-  </si>
-  <si>
-    <t>100003621</t>
-  </si>
-  <si>
-    <t>1100197580</t>
-  </si>
-  <si>
-    <t>100003622</t>
-  </si>
-  <si>
-    <t>1100197240</t>
-  </si>
-  <si>
-    <t>100003623</t>
-  </si>
-  <si>
-    <t>1100191070</t>
-  </si>
-  <si>
-    <t>100003624</t>
+    <t>100003630</t>
+  </si>
+  <si>
+    <t>100003631</t>
+  </si>
+  <si>
+    <t>CRTD MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100196080</t>
+  </si>
+  <si>
+    <t>100003632</t>
+  </si>
+  <si>
+    <t>980000018201</t>
+  </si>
+  <si>
+    <t>HSA-423,#50_X4000,Y2300,Z780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100197300</t>
+  </si>
+  <si>
+    <t>100003633</t>
+  </si>
+  <si>
+    <t>1100189770</t>
+  </si>
+  <si>
+    <t>100003634</t>
+  </si>
+  <si>
+    <t>1100197090</t>
+  </si>
+  <si>
+    <t>100003635</t>
+  </si>
+  <si>
+    <t>1100196060</t>
+  </si>
+  <si>
+    <t>100003636</t>
+  </si>
+  <si>
+    <t>980000047800</t>
+  </si>
+  <si>
+    <t>LG-2100,#40_X=2050, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>CRTD PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>1100197450</t>
   </si>
   <si>
     <t>ZP09</t>
@@ -1244,6 +1298,9 @@
   </si>
   <si>
     <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
+  </si>
+  <si>
+    <t>REL  PCNF DLV  PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>630000354</t>
@@ -1417,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1425,7 +1482,7 @@
     <col min="3" max="3" bestFit="1" width="9" customWidth="1"/>
     <col min="4" max="4" bestFit="1" width="9" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="14" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="39" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="40" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="13" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="13" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="13" customWidth="1"/>
@@ -1440,52 +1497,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1614,7 +1671,7 @@
         <v>45580</v>
       </c>
       <c r="I4" s="3">
-        <v>46132</v>
+        <v>46157</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
@@ -1764,7 +1821,7 @@
         <v>45741</v>
       </c>
       <c r="I7" s="3">
-        <v>46204</v>
+        <v>46210</v>
       </c>
       <c r="J7" t="s">
         <v>13</v>
@@ -1949,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -1967,7 +2024,7 @@
         <v>46129</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
@@ -1982,7 +2039,7 @@
         <v>7</v>
       </c>
       <c r="O11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P11" t="s">
         <v>9</v>
@@ -1993,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -2002,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3">
         <v>45813</v>
@@ -2032,7 +2089,7 @@
         <v>7</v>
       </c>
       <c r="O12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P12" t="s">
         <v>9</v>
@@ -2043,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -2052,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3">
         <v>45813</v>
@@ -2082,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="O13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P13" t="s">
         <v>9</v>
@@ -2093,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -2102,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3">
         <v>45835</v>
@@ -2114,7 +2171,7 @@
         <v>46056</v>
       </c>
       <c r="I14" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -2132,7 +2189,7 @@
         <v>7</v>
       </c>
       <c r="O14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P14" t="s">
         <v>9</v>
@@ -2143,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -2152,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3">
         <v>45835</v>
@@ -2164,7 +2221,7 @@
         <v>46055</v>
       </c>
       <c r="I15" s="3">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -2182,7 +2239,7 @@
         <v>7</v>
       </c>
       <c r="O15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P15" t="s">
         <v>9</v>
@@ -2193,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -2202,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="3">
         <v>45848</v>
@@ -2217,7 +2274,7 @@
         <v>46169</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -2232,7 +2289,7 @@
         <v>7</v>
       </c>
       <c r="O16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P16" t="s">
         <v>9</v>
@@ -2243,19 +2300,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="3">
         <v>45861</v>
@@ -2267,7 +2324,7 @@
         <v>46140</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -2282,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P17" t="s">
         <v>9</v>
@@ -2293,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -2302,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" s="3">
         <v>45901</v>
@@ -2317,7 +2374,7 @@
         <v>46183</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2332,7 +2389,7 @@
         <v>7</v>
       </c>
       <c r="O18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" t="s">
         <v>9</v>
@@ -2343,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -2352,10 +2409,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" s="3">
         <v>45943</v>
@@ -2367,7 +2424,7 @@
         <v>46135</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -2382,7 +2439,7 @@
         <v>7</v>
       </c>
       <c r="O19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" t="s">
         <v>9</v>
@@ -2393,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -2402,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" s="3">
         <v>45943</v>
@@ -2432,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="O20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P20" t="s">
         <v>9</v>
@@ -2443,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -2482,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="O21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P21" t="s">
         <v>9</v>
@@ -2493,37 +2550,37 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="H22" s="3">
-        <v>46042</v>
+        <v>46099</v>
       </c>
       <c r="I22" s="3">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="M22" t="s">
         <v>6</v>
@@ -2561,10 +2618,10 @@
         <v>45979</v>
       </c>
       <c r="H23" s="3">
-        <v>46099</v>
+        <v>46065</v>
       </c>
       <c r="I23" s="3">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="J23" t="s">
         <v>13</v>
@@ -2608,22 +2665,22 @@
         <v>96</v>
       </c>
       <c r="G24" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="H24" s="3">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="I24" s="3">
-        <v>46153</v>
+        <v>46199</v>
       </c>
       <c r="J24" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2649,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
         <v>99</v>
@@ -2658,22 +2715,22 @@
         <v>100</v>
       </c>
       <c r="G25" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H25" s="3">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="I25" s="3">
-        <v>46191</v>
+        <v>46129</v>
       </c>
       <c r="J25" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2711,10 +2768,10 @@
         <v>45993</v>
       </c>
       <c r="H26" s="3">
-        <v>46076</v>
+        <v>46041</v>
       </c>
       <c r="I26" s="3">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -2752,19 +2809,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="G27" s="3">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H27" s="3">
-        <v>46041</v>
+        <v>46125</v>
       </c>
       <c r="I27" s="3">
-        <v>46142</v>
+        <v>46226</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -2773,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2782,7 +2839,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2793,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2802,28 +2859,28 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G28" s="3">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H28" s="3">
-        <v>46125</v>
+        <v>46101</v>
       </c>
       <c r="I28" s="3">
-        <v>46216</v>
+        <v>46154</v>
       </c>
       <c r="J28" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2832,7 +2889,7 @@
         <v>7</v>
       </c>
       <c r="O28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P28" t="s">
         <v>9</v>
@@ -2843,28 +2900,28 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" t="s">
         <v>112</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" t="s">
-        <v>92</v>
       </c>
       <c r="G29" s="3">
         <v>45995</v>
       </c>
       <c r="H29" s="3">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="I29" s="3">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -2911,10 +2968,10 @@
         <v>45995</v>
       </c>
       <c r="H30" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="I30" s="3">
-        <v>46148</v>
+        <v>46202</v>
       </c>
       <c r="J30" t="s">
         <v>22</v>
@@ -2952,37 +3009,37 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H31" s="3">
+        <v>46087</v>
+      </c>
+      <c r="I31" s="3">
+        <v>46122</v>
+      </c>
+      <c r="J31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s">
+        <v>5</v>
+      </c>
+      <c r="L31" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M31" t="s">
+        <v>6</v>
+      </c>
+      <c r="N31" t="s">
+        <v>7</v>
+      </c>
+      <c r="O31" t="s">
         <v>119</v>
-      </c>
-      <c r="F31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="3">
-        <v>45995</v>
-      </c>
-      <c r="H31" s="3">
-        <v>46105</v>
-      </c>
-      <c r="I31" s="3">
-        <v>46202</v>
-      </c>
-      <c r="J31" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" t="s">
-        <v>5</v>
-      </c>
-      <c r="L31" s="3">
-        <v>45995</v>
-      </c>
-      <c r="M31" t="s">
-        <v>6</v>
-      </c>
-      <c r="N31" t="s">
-        <v>7</v>
-      </c>
-      <c r="O31" t="s">
-        <v>121</v>
       </c>
       <c r="P31" t="s">
         <v>9</v>
@@ -2993,31 +3050,31 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" t="s">
         <v>122</v>
-      </c>
-      <c r="C32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" t="s">
-        <v>81</v>
       </c>
       <c r="G32" s="3">
         <v>46000</v>
       </c>
       <c r="H32" s="3">
-        <v>46087</v>
+        <v>46050</v>
       </c>
       <c r="I32" s="3">
-        <v>46122</v>
+        <v>46148</v>
       </c>
       <c r="J32" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -3052,19 +3109,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G33" s="3">
         <v>46000</v>
       </c>
       <c r="H33" s="3">
-        <v>46050</v>
+        <v>46104</v>
       </c>
       <c r="I33" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
@@ -3082,7 +3139,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P33" t="s">
         <v>9</v>
@@ -3093,28 +3150,28 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="2">
-        <v>1</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" t="s">
-        <v>42</v>
-      </c>
       <c r="G34" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H34" s="3">
-        <v>46104</v>
+        <v>46010</v>
       </c>
       <c r="I34" s="3">
-        <v>46147</v>
+        <v>46045</v>
       </c>
       <c r="J34" t="s">
         <v>22</v>
@@ -3123,7 +3180,7 @@
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -3152,19 +3209,19 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="G35" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H35" s="3">
-        <v>46010</v>
+        <v>46041</v>
       </c>
       <c r="I35" s="3">
-        <v>46045</v>
+        <v>46155</v>
       </c>
       <c r="J35" t="s">
         <v>22</v>
@@ -3173,7 +3230,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -3182,7 +3239,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3193,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3211,10 +3268,10 @@
         <v>46007</v>
       </c>
       <c r="H36" s="3">
-        <v>46041</v>
+        <v>46090</v>
       </c>
       <c r="I36" s="3">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
@@ -3232,7 +3289,7 @@
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -3243,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3261,10 +3318,10 @@
         <v>46007</v>
       </c>
       <c r="H37" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="I37" s="3">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -3282,7 +3339,7 @@
         <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -3293,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3302,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G38" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="H38" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="I38" s="3">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="J38" t="s">
         <v>22</v>
@@ -3323,7 +3380,7 @@
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -3332,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3343,37 +3400,37 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="G39" s="3">
-        <v>46007</v>
+        <v>46027</v>
       </c>
       <c r="H39" s="3">
-        <v>46041</v>
+        <v>46126</v>
       </c>
       <c r="I39" s="3">
-        <v>46139</v>
+        <v>46188</v>
       </c>
       <c r="J39" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -3382,7 +3439,7 @@
         <v>7</v>
       </c>
       <c r="O39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3393,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -3402,19 +3459,19 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="G40" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="H40" s="3">
-        <v>46077</v>
+        <v>46031</v>
       </c>
       <c r="I40" s="3">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -3423,7 +3480,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3432,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3443,37 +3500,37 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="G41" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="H41" s="3">
-        <v>46126</v>
+        <v>46057</v>
       </c>
       <c r="I41" s="3">
-        <v>46188</v>
+        <v>46136</v>
       </c>
       <c r="J41" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3482,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3493,28 +3550,28 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
-        <v>149</v>
-      </c>
-      <c r="F42" t="s">
-        <v>150</v>
-      </c>
       <c r="G42" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="H42" s="3">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="I42" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -3523,7 +3580,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3532,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="O42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3543,28 +3600,28 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" t="s">
-        <v>116</v>
-      </c>
       <c r="G43" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="H43" s="3">
-        <v>46057</v>
+        <v>46090</v>
       </c>
       <c r="I43" s="3">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
@@ -3573,7 +3630,7 @@
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3608,10 +3665,10 @@
         <v>156</v>
       </c>
       <c r="G44" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="H44" s="3">
-        <v>46050</v>
+        <v>46129</v>
       </c>
       <c r="I44" s="3">
         <v>46167</v>
@@ -3623,7 +3680,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3652,37 +3709,37 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H45" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I45" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J45" t="s">
         <v>159</v>
       </c>
-      <c r="F45" t="s">
+      <c r="K45" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
+        <v>46044</v>
+      </c>
+      <c r="M45" t="s">
+        <v>6</v>
+      </c>
+      <c r="N45" t="s">
+        <v>7</v>
+      </c>
+      <c r="O45" t="s">
         <v>160</v>
-      </c>
-      <c r="G45" s="3">
-        <v>46041</v>
-      </c>
-      <c r="H45" s="3">
-        <v>46090</v>
-      </c>
-      <c r="I45" s="3">
-        <v>46211</v>
-      </c>
-      <c r="J45" t="s">
-        <v>22</v>
-      </c>
-      <c r="K45" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>46041</v>
-      </c>
-      <c r="M45" t="s">
-        <v>6</v>
-      </c>
-      <c r="N45" t="s">
-        <v>7</v>
-      </c>
-      <c r="O45" t="s">
-        <v>161</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3693,46 +3750,46 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H46" s="3">
+        <v>46090</v>
+      </c>
+      <c r="I46" s="3">
+        <v>46136</v>
+      </c>
+      <c r="J46" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
+        <v>46044</v>
+      </c>
+      <c r="M46" t="s">
+        <v>6</v>
+      </c>
+      <c r="N46" t="s">
+        <v>7</v>
+      </c>
+      <c r="O46" t="s">
         <v>162</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>163</v>
-      </c>
-      <c r="F46" t="s">
-        <v>164</v>
-      </c>
-      <c r="G46" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H46" s="3">
-        <v>46129</v>
-      </c>
-      <c r="I46" s="3">
-        <v>46167</v>
-      </c>
-      <c r="J46" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M46" t="s">
-        <v>6</v>
-      </c>
-      <c r="N46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O46" t="s">
-        <v>165</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3743,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3752,22 +3809,22 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="G47" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H47" s="3">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="I47" s="3">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="J47" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -3782,7 +3839,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3793,28 +3850,28 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" t="s">
         <v>169</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F48" t="s">
-        <v>92</v>
       </c>
       <c r="G48" s="3">
         <v>46044</v>
       </c>
       <c r="H48" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I48" s="3">
-        <v>46136</v>
+        <v>46156</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -3852,22 +3909,22 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="G49" s="3">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="H49" s="3">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="I49" s="3">
-        <v>46195</v>
+        <v>46153</v>
       </c>
       <c r="J49" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
@@ -3882,7 +3939,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3893,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3902,19 +3959,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G50" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H50" s="3">
-        <v>46083</v>
+        <v>46106</v>
       </c>
       <c r="I50" s="3">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -3923,7 +3980,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3932,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3943,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3952,28 +4009,28 @@
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="G51" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H51" s="3">
-        <v>46066</v>
+        <v>46086</v>
       </c>
       <c r="I51" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="J51" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -4008,22 +4065,22 @@
         <v>183</v>
       </c>
       <c r="G52" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="H52" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="I52" s="3">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="J52" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -4052,19 +4109,19 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G53" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="H53" s="3">
-        <v>46106</v>
+        <v>46083</v>
       </c>
       <c r="I53" s="3">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="J53" t="s">
         <v>22</v>
@@ -4073,7 +4130,7 @@
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -4082,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -4093,37 +4150,37 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
+        <v>187</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>188</v>
+      </c>
+      <c r="F54" t="s">
         <v>189</v>
       </c>
-      <c r="C54" s="2">
-        <v>1</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" t="s">
-        <v>92</v>
-      </c>
       <c r="G54" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="H54" s="3">
-        <v>46086</v>
+        <v>46099</v>
       </c>
       <c r="I54" s="3">
         <v>46134</v>
       </c>
       <c r="J54" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -4152,19 +4209,19 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F55" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G55" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="H55" s="3">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="I55" s="3">
-        <v>46164</v>
+        <v>46136</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -4173,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -4182,7 +4239,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4193,28 +4250,28 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" t="s">
         <v>195</v>
       </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
-        <v>192</v>
-      </c>
-      <c r="F56" t="s">
-        <v>193</v>
-      </c>
       <c r="G56" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="H56" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="I56" s="3">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="J56" t="s">
         <v>22</v>
@@ -4223,7 +4280,7 @@
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4252,19 +4309,19 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G57" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="H57" s="3">
-        <v>46099</v>
+        <v>46108</v>
       </c>
       <c r="I57" s="3">
-        <v>46134</v>
+        <v>46183</v>
       </c>
       <c r="J57" t="s">
         <v>22</v>
@@ -4273,7 +4330,7 @@
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4282,7 +4339,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4293,37 +4350,37 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>200</v>
+      </c>
+      <c r="F58" t="s">
         <v>201</v>
       </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>198</v>
-      </c>
-      <c r="F58" t="s">
-        <v>199</v>
-      </c>
       <c r="G58" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="H58" s="3">
-        <v>46083</v>
+        <v>46079</v>
       </c>
       <c r="I58" s="3">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="J58" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4352,28 +4409,28 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="F59" t="s">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="G59" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H59" s="3">
-        <v>46091</v>
+        <v>46135</v>
       </c>
       <c r="I59" s="3">
         <v>46170</v>
       </c>
       <c r="J59" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4382,7 +4439,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4393,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4402,28 +4459,28 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="G60" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H60" s="3">
         <v>46134</v>
       </c>
       <c r="I60" s="3">
-        <v>46183</v>
+        <v>46168</v>
       </c>
       <c r="J60" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M60" t="s">
         <v>6</v>
@@ -4432,7 +4489,7 @@
         <v>7</v>
       </c>
       <c r="O60" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="P60" t="s">
         <v>9</v>
@@ -4443,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4452,22 +4509,22 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="F61" t="s">
-        <v>211</v>
+        <v>59</v>
       </c>
       <c r="G61" s="3">
         <v>46064</v>
       </c>
       <c r="H61" s="3">
-        <v>46079</v>
+        <v>46308</v>
       </c>
       <c r="I61" s="3">
-        <v>46140</v>
+        <v>46344</v>
       </c>
       <c r="J61" t="s">
-        <v>22</v>
+        <v>207</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
@@ -4482,7 +4539,7 @@
         <v>7</v>
       </c>
       <c r="O61" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4493,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4502,22 +4559,22 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G62" s="3">
         <v>46064</v>
       </c>
       <c r="H62" s="3">
-        <v>46140</v>
+        <v>46308</v>
       </c>
       <c r="I62" s="3">
-        <v>46176</v>
+        <v>46344</v>
       </c>
       <c r="J62" t="s">
-        <v>13</v>
+        <v>210</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
@@ -4532,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4543,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4552,22 +4609,22 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G63" s="3">
         <v>46064</v>
       </c>
       <c r="H63" s="3">
-        <v>46140</v>
+        <v>46150</v>
       </c>
       <c r="I63" s="3">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="J63" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
@@ -4582,7 +4639,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4593,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4602,22 +4659,22 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G64" s="3">
         <v>46064</v>
       </c>
       <c r="H64" s="3">
-        <v>46246</v>
+        <v>46178</v>
       </c>
       <c r="I64" s="3">
-        <v>46281</v>
+        <v>46218</v>
       </c>
       <c r="J64" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4632,7 +4689,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4643,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4652,22 +4709,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F65" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G65" s="3">
         <v>46064</v>
       </c>
       <c r="H65" s="3">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="I65" s="3">
         <v>46281</v>
       </c>
       <c r="J65" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4693,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4702,22 +4759,22 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G66" s="3">
         <v>46064</v>
       </c>
       <c r="H66" s="3">
-        <v>46308</v>
+        <v>46303</v>
       </c>
       <c r="I66" s="3">
         <v>46344</v>
       </c>
       <c r="J66" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4732,7 +4789,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4743,37 +4800,37 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
       </c>
       <c r="D67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="G67" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H67" s="3">
-        <v>46308</v>
+        <v>46090</v>
       </c>
       <c r="I67" s="3">
-        <v>46344</v>
+        <v>46140</v>
       </c>
       <c r="J67" t="s">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M67" t="s">
         <v>6</v>
@@ -4793,37 +4850,37 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
         <v>224</v>
       </c>
-      <c r="C68" s="2">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>91</v>
-      </c>
       <c r="F68" t="s">
-        <v>92</v>
+        <v>225</v>
       </c>
       <c r="G68" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H68" s="3">
-        <v>46150</v>
+        <v>46077</v>
       </c>
       <c r="I68" s="3">
-        <v>46189</v>
+        <v>46146</v>
       </c>
       <c r="J68" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4832,7 +4889,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4843,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4852,28 +4909,28 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="F69" t="s">
-        <v>92</v>
+        <v>225</v>
       </c>
       <c r="G69" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H69" s="3">
-        <v>46178</v>
+        <v>46167</v>
       </c>
       <c r="I69" s="3">
         <v>46218</v>
       </c>
       <c r="J69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4882,7 +4939,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4893,46 +4950,46 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
+        <v>230</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>224</v>
+      </c>
+      <c r="F70" t="s">
+        <v>225</v>
+      </c>
+      <c r="G70" s="3">
+        <v>46076</v>
+      </c>
+      <c r="H70" s="3">
+        <v>46167</v>
+      </c>
+      <c r="I70" s="3">
+        <v>46218</v>
+      </c>
+      <c r="J70" t="s">
+        <v>228</v>
+      </c>
+      <c r="K70" t="s">
+        <v>5</v>
+      </c>
+      <c r="L70" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M70" t="s">
+        <v>6</v>
+      </c>
+      <c r="N70" t="s">
+        <v>7</v>
+      </c>
+      <c r="O70" t="s">
         <v>229</v>
-      </c>
-      <c r="C70" s="2">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0</v>
-      </c>
-      <c r="E70" t="s">
-        <v>91</v>
-      </c>
-      <c r="F70" t="s">
-        <v>92</v>
-      </c>
-      <c r="G70" s="3">
-        <v>46064</v>
-      </c>
-      <c r="H70" s="3">
-        <v>46244</v>
-      </c>
-      <c r="I70" s="3">
-        <v>46281</v>
-      </c>
-      <c r="J70" t="s">
-        <v>220</v>
-      </c>
-      <c r="K70" t="s">
-        <v>5</v>
-      </c>
-      <c r="L70" s="3">
-        <v>46064</v>
-      </c>
-      <c r="M70" t="s">
-        <v>6</v>
-      </c>
-      <c r="N70" t="s">
-        <v>7</v>
-      </c>
-      <c r="O70" t="s">
-        <v>230</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -4952,28 +5009,28 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="F71" t="s">
-        <v>92</v>
+        <v>225</v>
       </c>
       <c r="G71" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H71" s="3">
-        <v>46303</v>
+        <v>46217</v>
       </c>
       <c r="I71" s="3">
-        <v>46344</v>
+        <v>46267</v>
       </c>
       <c r="J71" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="K71" t="s">
         <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M71" t="s">
         <v>6</v>
@@ -5002,22 +5059,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>224</v>
       </c>
       <c r="F72" t="s">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="G72" s="3">
         <v>46076</v>
       </c>
       <c r="H72" s="3">
-        <v>46090</v>
+        <v>46217</v>
       </c>
       <c r="I72" s="3">
-        <v>46140</v>
+        <v>46267</v>
       </c>
       <c r="J72" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -5032,7 +5089,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5052,22 +5109,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F73" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G73" s="3">
         <v>46076</v>
       </c>
       <c r="H73" s="3">
-        <v>46077</v>
+        <v>46254</v>
       </c>
       <c r="I73" s="3">
-        <v>46146</v>
+        <v>46309</v>
       </c>
       <c r="J73" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -5082,7 +5139,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5093,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -5102,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F74" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G74" s="3">
         <v>46076</v>
       </c>
       <c r="H74" s="3">
-        <v>46167</v>
+        <v>46254</v>
       </c>
       <c r="I74" s="3">
-        <v>46218</v>
+        <v>46309</v>
       </c>
       <c r="J74" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -5132,7 +5189,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5143,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5152,22 +5209,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F75" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G75" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H75" s="3">
-        <v>46167</v>
+        <v>46107</v>
       </c>
       <c r="I75" s="3">
-        <v>46218</v>
+        <v>46153</v>
       </c>
       <c r="J75" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -5193,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5202,22 +5259,22 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G76" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H76" s="3">
-        <v>46217</v>
+        <v>46108</v>
       </c>
       <c r="I76" s="3">
-        <v>46267</v>
+        <v>46156</v>
       </c>
       <c r="J76" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
@@ -5232,7 +5289,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5243,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5252,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F77" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G77" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H77" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="I77" s="3">
-        <v>46267</v>
+        <v>46154</v>
       </c>
       <c r="J77" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
@@ -5282,7 +5339,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5293,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5302,22 +5359,22 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F78" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G78" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H78" s="3">
-        <v>46254</v>
+        <v>46114</v>
       </c>
       <c r="I78" s="3">
-        <v>46309</v>
+        <v>46154</v>
       </c>
       <c r="J78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -5332,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5343,37 +5400,37 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
+        <v>246</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
+        <v>247</v>
+      </c>
+      <c r="F79" t="s">
+        <v>248</v>
+      </c>
+      <c r="G79" s="3">
+        <v>46079</v>
+      </c>
+      <c r="H79" s="3">
+        <v>46163</v>
+      </c>
+      <c r="I79" s="3">
+        <v>46238</v>
+      </c>
+      <c r="J79" t="s">
         <v>249</v>
       </c>
-      <c r="C79" s="2">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
-        <v>236</v>
-      </c>
-      <c r="F79" t="s">
-        <v>237</v>
-      </c>
-      <c r="G79" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H79" s="3">
-        <v>46254</v>
-      </c>
-      <c r="I79" s="3">
-        <v>46309</v>
-      </c>
-      <c r="J79" t="s">
-        <v>246</v>
-      </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5382,7 +5439,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5393,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5402,28 +5459,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G80" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H80" s="3">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="I80" s="3">
-        <v>46154</v>
+        <v>46203</v>
       </c>
       <c r="J80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5432,7 +5489,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5443,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5452,28 +5509,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>251</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>252</v>
+        <v>165</v>
       </c>
       <c r="G81" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H81" s="3">
-        <v>46108</v>
+        <v>46128</v>
       </c>
       <c r="I81" s="3">
-        <v>46156</v>
+        <v>46217</v>
       </c>
       <c r="J81" t="s">
-        <v>22</v>
+        <v>254</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5482,7 +5539,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5493,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5502,28 +5559,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G82" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H82" s="3">
-        <v>46114</v>
+        <v>46219</v>
       </c>
       <c r="I82" s="3">
-        <v>46154</v>
+        <v>46279</v>
       </c>
       <c r="J82" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5532,7 +5589,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5543,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5552,28 +5609,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F83" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G83" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H83" s="3">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="I83" s="3">
-        <v>46154</v>
+        <v>46203</v>
       </c>
       <c r="J83" t="s">
-        <v>253</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
       <c r="L83" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5582,7 +5639,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5593,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5602,28 +5659,28 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F84" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G84" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="H84" s="3">
-        <v>46163</v>
+        <v>46210</v>
       </c>
       <c r="I84" s="3">
-        <v>46238</v>
+        <v>46324</v>
       </c>
       <c r="J84" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="K84" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
       <c r="L84" s="3">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="M84" t="s">
         <v>6</v>
@@ -5632,7 +5689,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5643,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5652,28 +5709,28 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F85" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G85" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H85" s="3">
-        <v>46128</v>
+        <v>46178</v>
       </c>
       <c r="I85" s="3">
-        <v>46196</v>
+        <v>46233</v>
       </c>
       <c r="J85" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M85" t="s">
         <v>6</v>
@@ -5682,7 +5739,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5693,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5702,28 +5759,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F86" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G86" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H86" s="3">
-        <v>46128</v>
+        <v>46212</v>
       </c>
       <c r="I86" s="3">
-        <v>46217</v>
+        <v>46234</v>
       </c>
       <c r="J86" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5732,7 +5789,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5743,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5752,28 +5809,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F87" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G87" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="H87" s="3">
-        <v>46219</v>
+        <v>46092</v>
       </c>
       <c r="I87" s="3">
-        <v>46279</v>
+        <v>46163</v>
       </c>
       <c r="J87" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5782,7 +5839,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5793,37 +5850,37 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="F88" t="s">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="G88" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H88" s="3">
-        <v>46121</v>
+        <v>46100</v>
       </c>
       <c r="I88" s="3">
-        <v>46203</v>
+        <v>46146</v>
       </c>
       <c r="J88" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K88" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="L88" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5832,7 +5889,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5843,37 +5900,37 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
       </c>
       <c r="D89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="F89" t="s">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="G89" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H89" s="3">
-        <v>46210</v>
+        <v>46106</v>
       </c>
       <c r="I89" s="3">
-        <v>46324</v>
+        <v>46146</v>
       </c>
       <c r="J89" t="s">
-        <v>246</v>
+        <v>47</v>
       </c>
       <c r="K89" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="L89" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5882,7 +5939,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5893,46 +5950,46 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
+        <v>81</v>
+      </c>
+      <c r="F90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G90" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H90" s="3">
+        <v>46101</v>
+      </c>
+      <c r="I90" s="3">
+        <v>46146</v>
+      </c>
+      <c r="J90" t="s">
+        <v>47</v>
+      </c>
+      <c r="K90" t="s">
+        <v>5</v>
+      </c>
+      <c r="L90" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M90" t="s">
+        <v>6</v>
+      </c>
+      <c r="N90" t="s">
+        <v>7</v>
+      </c>
+      <c r="O90" t="s">
         <v>284</v>
-      </c>
-      <c r="F90" t="s">
-        <v>285</v>
-      </c>
-      <c r="G90" s="3">
-        <v>46090</v>
-      </c>
-      <c r="H90" s="3">
-        <v>46178</v>
-      </c>
-      <c r="I90" s="3">
-        <v>46233</v>
-      </c>
-      <c r="J90" t="s">
-        <v>286</v>
-      </c>
-      <c r="K90" t="s">
-        <v>5</v>
-      </c>
-      <c r="L90" s="3">
-        <v>46090</v>
-      </c>
-      <c r="M90" t="s">
-        <v>6</v>
-      </c>
-      <c r="N90" t="s">
-        <v>7</v>
-      </c>
-      <c r="O90" t="s">
-        <v>287</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5943,46 +6000,46 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
+        <v>287</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H91" s="3">
+        <v>46133</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46170</v>
+      </c>
+      <c r="J91" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M91" t="s">
+        <v>6</v>
+      </c>
+      <c r="N91" t="s">
+        <v>7</v>
+      </c>
+      <c r="O91" t="s">
         <v>288</v>
-      </c>
-      <c r="C91" s="2">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
-        <v>45</v>
-      </c>
-      <c r="F91" t="s">
-        <v>46</v>
-      </c>
-      <c r="G91" s="3">
-        <v>46090</v>
-      </c>
-      <c r="H91" s="3">
-        <v>46212</v>
-      </c>
-      <c r="I91" s="3">
-        <v>46234</v>
-      </c>
-      <c r="J91" t="s">
-        <v>289</v>
-      </c>
-      <c r="K91" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
-        <v>46090</v>
-      </c>
-      <c r="M91" t="s">
-        <v>6</v>
-      </c>
-      <c r="N91" t="s">
-        <v>7</v>
-      </c>
-      <c r="O91" t="s">
-        <v>290</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -5993,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -6002,28 +6059,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="F92" t="s">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="G92" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="H92" s="3">
-        <v>46092</v>
+        <v>46133</v>
       </c>
       <c r="I92" s="3">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="J92" t="s">
-        <v>261</v>
+        <v>13</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -6032,7 +6089,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6043,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6052,22 +6109,22 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G93" s="3">
         <v>46094</v>
       </c>
       <c r="H93" s="3">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="I93" s="3">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="J93" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
@@ -6082,7 +6139,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6093,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6102,22 +6159,22 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F94" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G94" s="3">
         <v>46094</v>
       </c>
       <c r="H94" s="3">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="I94" s="3">
-        <v>46147</v>
+        <v>46170</v>
       </c>
       <c r="J94" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
@@ -6132,7 +6189,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6143,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6152,22 +6209,22 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F95" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G95" s="3">
         <v>46094</v>
       </c>
       <c r="H95" s="3">
-        <v>46101</v>
+        <v>46127</v>
       </c>
       <c r="I95" s="3">
-        <v>46142</v>
+        <v>46168</v>
       </c>
       <c r="J95" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
@@ -6182,7 +6239,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6193,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6202,19 +6259,19 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F96" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G96" s="3">
         <v>46094</v>
       </c>
       <c r="H96" s="3">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="I96" s="3">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="J96" t="s">
         <v>13</v>
@@ -6232,7 +6289,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6243,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6252,22 +6309,22 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F97" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G97" s="3">
         <v>46094</v>
       </c>
       <c r="H97" s="3">
-        <v>46133</v>
+        <v>46167</v>
       </c>
       <c r="I97" s="3">
-        <v>46162</v>
+        <v>46198</v>
       </c>
       <c r="J97" t="s">
-        <v>13</v>
+        <v>296</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
@@ -6282,7 +6339,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6293,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6302,22 +6359,22 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F98" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G98" s="3">
         <v>46094</v>
       </c>
       <c r="H98" s="3">
-        <v>46133</v>
+        <v>46167</v>
       </c>
       <c r="I98" s="3">
-        <v>46162</v>
+        <v>46198</v>
       </c>
       <c r="J98" t="s">
-        <v>13</v>
+        <v>296</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
@@ -6332,7 +6389,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6343,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6352,22 +6409,22 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F99" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G99" s="3">
         <v>46094</v>
       </c>
       <c r="H99" s="3">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="I99" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J99" t="s">
-        <v>13</v>
+        <v>296</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
@@ -6382,7 +6439,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6393,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6402,29 +6459,29 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="F100" t="s">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="G100" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H100" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I100" s="3">
+        <v>46181</v>
+      </c>
+      <c r="J100" t="s">
+        <v>302</v>
+      </c>
+      <c r="K100" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>46094</v>
       </c>
-      <c r="H100" s="3">
-        <v>46127</v>
-      </c>
-      <c r="I100" s="3">
-        <v>46171</v>
-      </c>
-      <c r="J100" t="s">
-        <v>13</v>
-      </c>
-      <c r="K100" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>46093</v>
-      </c>
       <c r="M100" t="s">
         <v>6</v>
       </c>
@@ -6432,7 +6489,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6443,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6452,28 +6509,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F101" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G101" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H101" s="3">
-        <v>46127</v>
+        <v>46224</v>
       </c>
       <c r="I101" s="3">
-        <v>46170</v>
+        <v>46246</v>
       </c>
       <c r="J101" t="s">
-        <v>13</v>
+        <v>277</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6482,7 +6539,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6493,46 +6550,46 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
+        <v>306</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
+        <v>50</v>
+      </c>
+      <c r="F102" t="s">
+        <v>51</v>
+      </c>
+      <c r="G102" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H102" s="3">
+        <v>46232</v>
+      </c>
+      <c r="I102" s="3">
+        <v>46253</v>
+      </c>
+      <c r="J102" t="s">
         <v>307</v>
       </c>
-      <c r="C102" s="2">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2">
-        <v>0</v>
-      </c>
-      <c r="E102" t="s">
-        <v>80</v>
-      </c>
-      <c r="F102" t="s">
-        <v>81</v>
-      </c>
-      <c r="G102" s="3">
-        <v>46094</v>
-      </c>
-      <c r="H102" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I102" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
+        <v>265</v>
+      </c>
+      <c r="L102" s="3">
+        <v>46106</v>
+      </c>
+      <c r="M102" t="s">
+        <v>6</v>
+      </c>
+      <c r="N102" t="s">
+        <v>7</v>
+      </c>
+      <c r="O102" t="s">
         <v>308</v>
-      </c>
-      <c r="K102" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M102" t="s">
-        <v>6</v>
-      </c>
-      <c r="N102" t="s">
-        <v>7</v>
-      </c>
-      <c r="O102" t="s">
-        <v>304</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6552,28 +6609,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="F103" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="G103" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H103" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I103" s="3">
-        <v>46198</v>
+        <v>46251</v>
       </c>
       <c r="J103" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="K103" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
       <c r="L103" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6582,7 +6639,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6593,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6602,28 +6659,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="F104" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="G104" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H104" s="3">
-        <v>46167</v>
+        <v>46227</v>
       </c>
       <c r="I104" s="3">
-        <v>46198</v>
+        <v>46253</v>
       </c>
       <c r="J104" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="K104" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
       <c r="L104" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6632,7 +6689,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6643,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6652,28 +6709,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>178</v>
+        <v>99</v>
       </c>
       <c r="F105" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="G105" s="3">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="H105" s="3">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="I105" s="3">
-        <v>46181</v>
+        <v>46160</v>
       </c>
       <c r="J105" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K105" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
       <c r="L105" s="3">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6682,7 +6739,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6693,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6702,28 +6759,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="F106" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="G106" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H106" s="3">
-        <v>46224</v>
+        <v>46171</v>
       </c>
       <c r="I106" s="3">
-        <v>46246</v>
+        <v>46190</v>
       </c>
       <c r="J106" t="s">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6732,7 +6789,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6743,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6752,28 +6809,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F107" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G107" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H107" s="3">
-        <v>46232</v>
+        <v>46171</v>
       </c>
       <c r="I107" s="3">
-        <v>46253</v>
+        <v>46190</v>
       </c>
       <c r="J107" t="s">
-        <v>317</v>
+        <v>159</v>
       </c>
       <c r="K107" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6793,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6802,28 +6859,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="F108" t="s">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="G108" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H108" s="3">
-        <v>46217</v>
+        <v>46171</v>
       </c>
       <c r="I108" s="3">
-        <v>46251</v>
+        <v>46190</v>
       </c>
       <c r="J108" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="K108" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6832,7 +6889,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6843,46 +6900,46 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
+        <v>322</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
+        <v>81</v>
+      </c>
+      <c r="F109" t="s">
+        <v>82</v>
+      </c>
+      <c r="G109" s="3">
+        <v>46113</v>
+      </c>
+      <c r="H109" s="3">
+        <v>46237</v>
+      </c>
+      <c r="I109" s="3">
+        <v>46254</v>
+      </c>
+      <c r="J109" t="s">
         <v>321</v>
       </c>
-      <c r="C109" s="2">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" t="s">
-        <v>322</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="K109" t="s">
+        <v>5</v>
+      </c>
+      <c r="L109" s="3">
+        <v>46113</v>
+      </c>
+      <c r="M109" t="s">
+        <v>6</v>
+      </c>
+      <c r="N109" t="s">
+        <v>7</v>
+      </c>
+      <c r="O109" t="s">
         <v>323</v>
-      </c>
-      <c r="G109" s="3">
-        <v>46106</v>
-      </c>
-      <c r="H109" s="3">
-        <v>46227</v>
-      </c>
-      <c r="I109" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J109" t="s">
-        <v>324</v>
-      </c>
-      <c r="K109" t="s">
-        <v>277</v>
-      </c>
-      <c r="L109" s="3">
-        <v>46106</v>
-      </c>
-      <c r="M109" t="s">
-        <v>6</v>
-      </c>
-      <c r="N109" t="s">
-        <v>7</v>
-      </c>
-      <c r="O109" t="s">
-        <v>325</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6893,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6902,28 +6959,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="F110" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G110" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H110" s="3">
-        <v>46135</v>
+        <v>46237</v>
       </c>
       <c r="I110" s="3">
-        <v>46156</v>
+        <v>46254</v>
       </c>
       <c r="J110" t="s">
-        <v>266</v>
+        <v>321</v>
       </c>
       <c r="K110" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6932,7 +6989,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6943,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6952,22 +7009,22 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="F111" t="s">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="G111" s="3">
         <v>46113</v>
       </c>
       <c r="H111" s="3">
-        <v>46171</v>
+        <v>46231</v>
       </c>
       <c r="I111" s="3">
-        <v>46190</v>
+        <v>46266</v>
       </c>
       <c r="J111" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
@@ -6982,7 +7039,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -6993,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7002,22 +7059,22 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F112" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G112" s="3">
         <v>46113</v>
       </c>
       <c r="H112" s="3">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="I112" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="J112" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
@@ -7032,7 +7089,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7052,28 +7109,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F113" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G113" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H113" s="3">
-        <v>46171</v>
+        <v>46154</v>
       </c>
       <c r="I113" s="3">
-        <v>46190</v>
+        <v>46183</v>
       </c>
       <c r="J113" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -7082,7 +7139,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7093,46 +7150,46 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
+        <v>333</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
+        <v>81</v>
+      </c>
+      <c r="F114" t="s">
+        <v>82</v>
+      </c>
+      <c r="G114" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H114" s="3">
+        <v>46154</v>
+      </c>
+      <c r="I114" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J114" t="s">
+        <v>277</v>
+      </c>
+      <c r="K114" t="s">
+        <v>5</v>
+      </c>
+      <c r="L114" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M114" t="s">
+        <v>6</v>
+      </c>
+      <c r="N114" t="s">
+        <v>7</v>
+      </c>
+      <c r="O114" t="s">
         <v>332</v>
-      </c>
-      <c r="C114" s="2">
-        <v>1</v>
-      </c>
-      <c r="D114" s="2">
-        <v>0</v>
-      </c>
-      <c r="E114" t="s">
-        <v>80</v>
-      </c>
-      <c r="F114" t="s">
-        <v>81</v>
-      </c>
-      <c r="G114" s="3">
-        <v>46113</v>
-      </c>
-      <c r="H114" s="3">
-        <v>46237</v>
-      </c>
-      <c r="I114" s="3">
-        <v>46254</v>
-      </c>
-      <c r="J114" t="s">
-        <v>324</v>
-      </c>
-      <c r="K114" t="s">
-        <v>5</v>
-      </c>
-      <c r="L114" s="3">
-        <v>46113</v>
-      </c>
-      <c r="M114" t="s">
-        <v>6</v>
-      </c>
-      <c r="N114" t="s">
-        <v>7</v>
-      </c>
-      <c r="O114" t="s">
-        <v>333</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7152,28 +7209,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F115" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G115" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H115" s="3">
-        <v>46237</v>
+        <v>46161</v>
       </c>
       <c r="I115" s="3">
-        <v>46254</v>
+        <v>46182</v>
       </c>
       <c r="J115" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -7182,7 +7239,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7193,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7202,28 +7259,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F116" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G116" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H116" s="3">
-        <v>46231</v>
+        <v>46127</v>
       </c>
       <c r="I116" s="3">
-        <v>46266</v>
+        <v>46154</v>
       </c>
       <c r="J116" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -7232,7 +7289,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7243,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7252,28 +7309,28 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F117" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G117" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H117" s="3">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="I117" s="3">
-        <v>46196</v>
+        <v>46182</v>
       </c>
       <c r="J117" t="s">
-        <v>261</v>
+        <v>159</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -7282,7 +7339,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7293,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7302,28 +7359,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F118" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="G118" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H118" s="3">
-        <v>46154</v>
+        <v>46141</v>
       </c>
       <c r="I118" s="3">
-        <v>46183</v>
+        <v>46168</v>
       </c>
       <c r="J118" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7332,7 +7389,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7343,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7352,28 +7409,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="F119" t="s">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="G119" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H119" s="3">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="I119" s="3">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="J119" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7382,7 +7439,7 @@
         <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7393,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7402,28 +7459,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>49</v>
+        <v>346</v>
       </c>
       <c r="F120" t="s">
-        <v>50</v>
+        <v>347</v>
       </c>
       <c r="G120" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H120" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="I120" s="3">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="J120" t="s">
-        <v>167</v>
+        <v>335</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7432,7 +7489,7 @@
         <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7443,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7452,28 +7509,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>347</v>
+        <v>200</v>
       </c>
       <c r="F121" t="s">
-        <v>348</v>
+        <v>201</v>
       </c>
       <c r="G121" s="3">
         <v>46122</v>
       </c>
       <c r="H121" s="3">
-        <v>46135</v>
+        <v>46156</v>
       </c>
       <c r="I121" s="3">
-        <v>46161</v>
+        <v>46188</v>
       </c>
       <c r="J121" t="s">
-        <v>349</v>
+        <v>254</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7482,7 +7539,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7493,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7502,28 +7559,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>49</v>
+        <v>353</v>
       </c>
       <c r="F122" t="s">
-        <v>50</v>
+        <v>354</v>
       </c>
       <c r="G122" s="3">
         <v>46122</v>
       </c>
       <c r="H122" s="3">
-        <v>46161</v>
+        <v>46141</v>
       </c>
       <c r="I122" s="3">
-        <v>46182</v>
+        <v>46168</v>
       </c>
       <c r="J122" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7532,7 +7589,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7543,37 +7600,37 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
+        <v>356</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
         <v>353</v>
       </c>
-      <c r="C123" s="2">
-        <v>1</v>
-      </c>
-      <c r="D123" s="2">
-        <v>0</v>
-      </c>
-      <c r="E123" t="s">
-        <v>131</v>
-      </c>
       <c r="F123" t="s">
-        <v>132</v>
+        <v>354</v>
       </c>
       <c r="G123" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H123" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="I123" s="3">
         <v>46168</v>
       </c>
       <c r="J123" t="s">
-        <v>349</v>
+        <v>254</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7582,7 +7639,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7593,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7602,28 +7659,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F124" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G124" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H124" s="3">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="I124" s="3">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="J124" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7632,7 +7689,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7643,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7652,28 +7709,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F125" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G125" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="H125" s="3">
-        <v>46167</v>
+        <v>46146</v>
       </c>
       <c r="I125" s="3">
-        <v>46189</v>
+        <v>46170</v>
       </c>
       <c r="J125" t="s">
-        <v>167</v>
+        <v>335</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7682,7 +7739,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7693,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7702,28 +7759,28 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>210</v>
+        <v>365</v>
       </c>
       <c r="F126" t="s">
-        <v>211</v>
+        <v>366</v>
       </c>
       <c r="G126" s="3">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="H126" s="3">
-        <v>46156</v>
+        <v>46127</v>
       </c>
       <c r="I126" s="3">
-        <v>46188</v>
+        <v>46146</v>
       </c>
       <c r="J126" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7732,7 +7789,7 @@
         <v>7</v>
       </c>
       <c r="O126" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P126" t="s">
         <v>9</v>
@@ -7743,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7752,28 +7809,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="F127" t="s">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="G127" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H127" s="3">
-        <v>46141</v>
+        <v>46182</v>
       </c>
       <c r="I127" s="3">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="J127" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7782,7 +7839,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7793,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7802,28 +7859,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="F128" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="G128" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H128" s="3">
-        <v>46142</v>
+        <v>46174</v>
       </c>
       <c r="I128" s="3">
-        <v>46168</v>
+        <v>46195</v>
       </c>
       <c r="J128" t="s">
-        <v>266</v>
+        <v>159</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7832,7 +7889,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7843,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7852,28 +7909,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="F129" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="G129" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H129" s="3">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="I129" s="3">
-        <v>46210</v>
+        <v>46195</v>
       </c>
       <c r="J129" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7882,7 +7939,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7893,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7902,28 +7959,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F130" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G130" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="H130" s="3">
-        <v>46146</v>
+        <v>46174</v>
       </c>
       <c r="I130" s="3">
-        <v>46170</v>
+        <v>46195</v>
       </c>
       <c r="J130" t="s">
-        <v>349</v>
+        <v>159</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7932,7 +7989,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7943,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7952,28 +8009,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>375</v>
+        <v>239</v>
       </c>
       <c r="F131" t="s">
-        <v>376</v>
+        <v>240</v>
       </c>
       <c r="G131" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="H131" s="3">
-        <v>46127</v>
+        <v>46139</v>
       </c>
       <c r="I131" s="3">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="J131" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -8002,28 +8059,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F132" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G132" s="3">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="H132" s="3">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="I132" s="3">
-        <v>46210</v>
+        <v>46198</v>
       </c>
       <c r="J132" t="s">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8052,28 +8109,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>356</v>
+        <v>200</v>
       </c>
       <c r="F133" t="s">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="G133" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H133" s="3">
-        <v>46174</v>
+        <v>46146</v>
       </c>
       <c r="I133" s="3">
-        <v>46195</v>
+        <v>46167</v>
       </c>
       <c r="J133" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8102,28 +8159,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="F134" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="G134" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H134" s="3">
-        <v>46174</v>
+        <v>46191</v>
       </c>
       <c r="I134" s="3">
-        <v>46195</v>
+        <v>46245</v>
       </c>
       <c r="J134" t="s">
-        <v>324</v>
+        <v>234</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -8132,7 +8189,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8143,37 +8200,37 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
+        <v>386</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s">
+        <v>383</v>
+      </c>
+      <c r="F135" t="s">
         <v>384</v>
       </c>
-      <c r="C135" s="2">
-        <v>1</v>
-      </c>
-      <c r="D135" s="2">
-        <v>0</v>
-      </c>
-      <c r="E135" t="s">
-        <v>356</v>
-      </c>
-      <c r="F135" t="s">
-        <v>357</v>
-      </c>
       <c r="G135" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H135" s="3">
-        <v>46174</v>
+        <v>46191</v>
       </c>
       <c r="I135" s="3">
-        <v>46195</v>
+        <v>46245</v>
       </c>
       <c r="J135" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -8193,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8202,28 +8259,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>251</v>
+        <v>353</v>
       </c>
       <c r="F136" t="s">
-        <v>252</v>
+        <v>354</v>
       </c>
       <c r="G136" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="H136" s="3">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="I136" s="3">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="J136" t="s">
-        <v>349</v>
+        <v>234</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8232,7 +8289,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8243,46 +8300,46 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
+        <v>389</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>353</v>
+      </c>
+      <c r="F137" t="s">
+        <v>354</v>
+      </c>
+      <c r="G137" s="3">
+        <v>46142</v>
+      </c>
+      <c r="H137" s="3">
+        <v>46155</v>
+      </c>
+      <c r="I137" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J137" t="s">
+        <v>234</v>
+      </c>
+      <c r="K137" t="s">
+        <v>5</v>
+      </c>
+      <c r="L137" s="3">
+        <v>46142</v>
+      </c>
+      <c r="M137" t="s">
+        <v>6</v>
+      </c>
+      <c r="N137" t="s">
+        <v>7</v>
+      </c>
+      <c r="O137" t="s">
         <v>388</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1</v>
-      </c>
-      <c r="D137" s="2">
-        <v>0</v>
-      </c>
-      <c r="E137" t="s">
-        <v>322</v>
-      </c>
-      <c r="F137" t="s">
-        <v>323</v>
-      </c>
-      <c r="G137" s="3">
-        <v>46139</v>
-      </c>
-      <c r="H137" s="3">
-        <v>46171</v>
-      </c>
-      <c r="I137" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J137" t="s">
-        <v>167</v>
-      </c>
-      <c r="K137" t="s">
-        <v>5</v>
-      </c>
-      <c r="L137" s="3">
-        <v>46139</v>
-      </c>
-      <c r="M137" t="s">
-        <v>6</v>
-      </c>
-      <c r="N137" t="s">
-        <v>7</v>
-      </c>
-      <c r="O137" t="s">
-        <v>389</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8302,29 +8359,29 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="F138" t="s">
-        <v>211</v>
+        <v>354</v>
       </c>
       <c r="G138" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H138" s="3">
+        <v>46155</v>
+      </c>
+      <c r="I138" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J138" t="s">
+        <v>234</v>
+      </c>
+      <c r="K138" t="s">
+        <v>5</v>
+      </c>
+      <c r="L138" s="3">
         <v>46142</v>
       </c>
-      <c r="I138" s="3">
-        <v>46168</v>
-      </c>
-      <c r="J138" t="s">
-        <v>167</v>
-      </c>
-      <c r="K138" t="s">
-        <v>5</v>
-      </c>
-      <c r="L138" s="3">
-        <v>46140</v>
-      </c>
       <c r="M138" t="s">
         <v>6</v>
       </c>
@@ -8332,7 +8389,7 @@
         <v>7</v>
       </c>
       <c r="O138" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="P138" t="s">
         <v>9</v>
@@ -8343,7 +8400,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8352,28 +8409,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="F139" t="s">
-        <v>142</v>
+        <v>354</v>
       </c>
       <c r="G139" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H139" s="3">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="I139" s="3">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="J139" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="K139" t="s">
         <v>5</v>
       </c>
       <c r="L139" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
@@ -8382,7 +8439,7 @@
         <v>7</v>
       </c>
       <c r="O139" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8393,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8402,28 +8459,28 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="F140" t="s">
-        <v>142</v>
+        <v>354</v>
       </c>
       <c r="G140" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H140" s="3">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="I140" s="3">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="J140" t="s">
-        <v>246</v>
+        <v>393</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
       </c>
       <c r="L140" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
@@ -8432,7 +8489,7 @@
         <v>7</v>
       </c>
       <c r="O140" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8440,10 +8497,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8452,37 +8509,37 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="F141" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="G141" s="3">
-        <v>46043</v>
+        <v>46142</v>
       </c>
       <c r="H141" s="3">
-        <v>46051</v>
+        <v>46189</v>
       </c>
       <c r="I141" s="3">
-        <v>46057</v>
+        <v>46213</v>
       </c>
       <c r="J141" t="s">
-        <v>308</v>
+        <v>393</v>
       </c>
       <c r="K141" t="s">
-        <v>399</v>
+        <v>5</v>
       </c>
       <c r="L141" s="3">
-        <v>46043</v>
+        <v>46142</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="O141" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="P141" t="s">
         <v>9</v>
@@ -8490,11 +8547,11 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
         <v>395</v>
       </c>
-      <c r="B142" t="s">
-        <v>402</v>
-      </c>
       <c r="C142" s="2">
         <v>1</v>
       </c>
@@ -8502,37 +8559,35 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>403</v>
+        <v>50</v>
       </c>
       <c r="F142" t="s">
-        <v>404</v>
-      </c>
-      <c r="G142" s="3">
-        <v>46057</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G142" s="3"/>
       <c r="H142" s="3">
-        <v>46076</v>
+        <v>46206</v>
       </c>
       <c r="I142" s="3">
-        <v>46083</v>
+        <v>46225</v>
       </c>
       <c r="J142" t="s">
-        <v>13</v>
+        <v>396</v>
       </c>
       <c r="K142" t="s">
-        <v>399</v>
+        <v>5</v>
       </c>
       <c r="L142" s="3">
-        <v>46057</v>
+        <v>46148</v>
       </c>
       <c r="M142" t="s">
         <v>6</v>
       </c>
       <c r="N142" t="s">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="O142" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8540,10 +8595,10 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C143" s="2">
         <v>1</v>
@@ -8552,34 +8607,34 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F143" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="G143" s="3">
-        <v>46114</v>
+        <v>46148</v>
       </c>
       <c r="H143" s="3">
+        <v>46175</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46241</v>
+      </c>
+      <c r="J143" t="s">
+        <v>321</v>
+      </c>
+      <c r="K143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L143" s="3">
         <v>46148</v>
       </c>
-      <c r="I143" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J143" t="s">
-        <v>311</v>
-      </c>
-      <c r="K143" t="s">
-        <v>399</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46114</v>
-      </c>
       <c r="M143" t="s">
         <v>6</v>
       </c>
       <c r="N143" t="s">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="O143" t="s">
         <v>401</v>
@@ -8590,10 +8645,10 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
@@ -8602,37 +8657,37 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>409</v>
+        <v>115</v>
       </c>
       <c r="F144" t="s">
-        <v>410</v>
+        <v>116</v>
       </c>
       <c r="G144" s="3">
-        <v>46122</v>
+        <v>46148</v>
       </c>
       <c r="H144" s="3">
-        <v>46142</v>
+        <v>46267</v>
       </c>
       <c r="I144" s="3">
+        <v>46353</v>
+      </c>
+      <c r="J144" t="s">
+        <v>321</v>
+      </c>
+      <c r="K144" t="s">
+        <v>5</v>
+      </c>
+      <c r="L144" s="3">
         <v>46148</v>
       </c>
-      <c r="J144" t="s">
-        <v>311</v>
-      </c>
-      <c r="K144" t="s">
-        <v>399</v>
-      </c>
-      <c r="L144" s="3">
-        <v>46122</v>
-      </c>
       <c r="M144" t="s">
         <v>6</v>
       </c>
       <c r="N144" t="s">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="O144" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P144" t="s">
         <v>9</v>
@@ -8640,10 +8695,10 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C145" s="2">
         <v>1</v>
@@ -8652,37 +8707,35 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>412</v>
+        <v>155</v>
       </c>
       <c r="F145" t="s">
-        <v>413</v>
-      </c>
-      <c r="G145" s="3">
-        <v>46135</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="G145" s="3"/>
       <c r="H145" s="3">
-        <v>46135</v>
+        <v>46196</v>
       </c>
       <c r="I145" s="3">
-        <v>46147</v>
+        <v>46230</v>
       </c>
       <c r="J145" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="K145" t="s">
-        <v>399</v>
+        <v>5</v>
       </c>
       <c r="L145" s="3">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="M145" t="s">
         <v>6</v>
       </c>
       <c r="N145" t="s">
-        <v>400</v>
+        <v>7</v>
       </c>
       <c r="O145" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="P145" t="s">
         <v>9</v>
@@ -8690,51 +8743,397 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="B146" t="s">
+        <v>406</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" t="s">
+        <v>45</v>
+      </c>
+      <c r="F146" t="s">
+        <v>46</v>
+      </c>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3">
+        <v>46203</v>
+      </c>
+      <c r="I146" s="3">
+        <v>46225</v>
+      </c>
+      <c r="J146" t="s">
+        <v>396</v>
+      </c>
+      <c r="K146" t="s">
+        <v>5</v>
+      </c>
+      <c r="L146" s="3">
+        <v>46148</v>
+      </c>
+      <c r="M146" t="s">
+        <v>6</v>
+      </c>
+      <c r="N146" t="s">
+        <v>7</v>
+      </c>
+      <c r="O146" t="s">
+        <v>407</v>
+      </c>
+      <c r="P146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" t="s">
+        <v>408</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>409</v>
+      </c>
+      <c r="F147" t="s">
+        <v>410</v>
+      </c>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3">
+        <v>46282</v>
+      </c>
+      <c r="I147" s="3">
+        <v>46316</v>
+      </c>
+      <c r="J147" t="s">
+        <v>411</v>
+      </c>
+      <c r="K147" t="s">
+        <v>5</v>
+      </c>
+      <c r="L147" s="3">
+        <v>46148</v>
+      </c>
+      <c r="M147" t="s">
+        <v>6</v>
+      </c>
+      <c r="N147" t="s">
+        <v>7</v>
+      </c>
+      <c r="O147" t="s">
+        <v>412</v>
+      </c>
+      <c r="P147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" t="s">
+        <v>413</v>
+      </c>
+      <c r="B148" t="s">
+        <v>414</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148" t="s">
         <v>415</v>
       </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
+      <c r="F148" t="s">
         <v>416</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G148" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H148" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I148" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J148" t="s">
+        <v>393</v>
+      </c>
+      <c r="K148" t="s">
         <v>417</v>
       </c>
-      <c r="G146" s="3">
+      <c r="L148" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M148" t="s">
+        <v>6</v>
+      </c>
+      <c r="N148" t="s">
+        <v>418</v>
+      </c>
+      <c r="O148" t="s">
+        <v>419</v>
+      </c>
+      <c r="P148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149" t="s">
+        <v>413</v>
+      </c>
+      <c r="B149" t="s">
+        <v>420</v>
+      </c>
+      <c r="C149" s="2">
+        <v>1</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0</v>
+      </c>
+      <c r="E149" t="s">
+        <v>421</v>
+      </c>
+      <c r="F149" t="s">
+        <v>422</v>
+      </c>
+      <c r="G149" s="3">
+        <v>46057</v>
+      </c>
+      <c r="H149" s="3">
+        <v>46076</v>
+      </c>
+      <c r="I149" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K149" t="s">
+        <v>417</v>
+      </c>
+      <c r="L149" s="3">
+        <v>46057</v>
+      </c>
+      <c r="M149" t="s">
+        <v>6</v>
+      </c>
+      <c r="N149" t="s">
+        <v>418</v>
+      </c>
+      <c r="O149" t="s">
+        <v>419</v>
+      </c>
+      <c r="P149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150" t="s">
+        <v>413</v>
+      </c>
+      <c r="B150" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" s="2">
+        <v>1</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" t="s">
+        <v>424</v>
+      </c>
+      <c r="F150" t="s">
+        <v>425</v>
+      </c>
+      <c r="G150" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H150" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I150" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J150" t="s">
+        <v>296</v>
+      </c>
+      <c r="K150" t="s">
+        <v>417</v>
+      </c>
+      <c r="L150" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M150" t="s">
+        <v>6</v>
+      </c>
+      <c r="N150" t="s">
+        <v>418</v>
+      </c>
+      <c r="O150" t="s">
+        <v>419</v>
+      </c>
+      <c r="P150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151" t="s">
+        <v>413</v>
+      </c>
+      <c r="B151" t="s">
+        <v>426</v>
+      </c>
+      <c r="C151" s="2">
+        <v>1</v>
+      </c>
+      <c r="D151" s="2">
+        <v>1</v>
+      </c>
+      <c r="E151" t="s">
+        <v>427</v>
+      </c>
+      <c r="F151" t="s">
+        <v>428</v>
+      </c>
+      <c r="G151" s="3">
+        <v>46122</v>
+      </c>
+      <c r="H151" s="3">
+        <v>46142</v>
+      </c>
+      <c r="I151" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J151" t="s">
+        <v>429</v>
+      </c>
+      <c r="K151" t="s">
+        <v>417</v>
+      </c>
+      <c r="L151" s="3">
+        <v>46122</v>
+      </c>
+      <c r="M151" t="s">
+        <v>6</v>
+      </c>
+      <c r="N151" t="s">
+        <v>418</v>
+      </c>
+      <c r="O151" t="s">
+        <v>419</v>
+      </c>
+      <c r="P151" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" t="s">
+        <v>413</v>
+      </c>
+      <c r="B152" t="s">
+        <v>430</v>
+      </c>
+      <c r="C152" s="2">
+        <v>1</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" t="s">
+        <v>431</v>
+      </c>
+      <c r="F152" t="s">
+        <v>432</v>
+      </c>
+      <c r="G152" s="3">
+        <v>46135</v>
+      </c>
+      <c r="H152" s="3">
+        <v>46135</v>
+      </c>
+      <c r="I152" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J152" t="s">
+        <v>433</v>
+      </c>
+      <c r="K152" t="s">
+        <v>417</v>
+      </c>
+      <c r="L152" s="3">
+        <v>46135</v>
+      </c>
+      <c r="M152" t="s">
+        <v>6</v>
+      </c>
+      <c r="N152" t="s">
+        <v>418</v>
+      </c>
+      <c r="O152" t="s">
+        <v>419</v>
+      </c>
+      <c r="P152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" t="s">
+        <v>413</v>
+      </c>
+      <c r="B153" t="s">
+        <v>434</v>
+      </c>
+      <c r="C153" s="2">
+        <v>1</v>
+      </c>
+      <c r="D153" s="2">
+        <v>0</v>
+      </c>
+      <c r="E153" t="s">
+        <v>435</v>
+      </c>
+      <c r="F153" t="s">
+        <v>436</v>
+      </c>
+      <c r="G153" s="3">
         <v>46140</v>
       </c>
-      <c r="H146" s="3">
+      <c r="H153" s="3">
         <v>46140</v>
       </c>
-      <c r="I146" s="3">
+      <c r="I153" s="3">
         <v>46147</v>
       </c>
-      <c r="J146" t="s">
-        <v>308</v>
-      </c>
-      <c r="K146" t="s">
-        <v>399</v>
-      </c>
-      <c r="L146" s="3">
+      <c r="J153" t="s">
+        <v>296</v>
+      </c>
+      <c r="K153" t="s">
+        <v>417</v>
+      </c>
+      <c r="L153" s="3">
         <v>46140</v>
       </c>
-      <c r="M146" t="s">
-        <v>6</v>
-      </c>
-      <c r="N146" t="s">
-        <v>400</v>
-      </c>
-      <c r="O146" t="s">
-        <v>401</v>
-      </c>
-      <c r="P146" t="s">
+      <c r="M153" t="s">
+        <v>6</v>
+      </c>
+      <c r="N153" t="s">
+        <v>418</v>
+      </c>
+      <c r="O153" t="s">
+        <v>419</v>
+      </c>
+      <c r="P153" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="429">
   <si>
     <t>ZP01</t>
   </si>
@@ -214,18 +214,6 @@
     <t>1100170790</t>
   </si>
   <si>
-    <t>100003370</t>
-  </si>
-  <si>
-    <t>980000029700</t>
-  </si>
-  <si>
-    <t>HSA-728EAY_X=7M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100167320</t>
-  </si>
-  <si>
     <t>100003400</t>
   </si>
   <si>
@@ -445,12 +433,6 @@
     <t>1100193980</t>
   </si>
   <si>
-    <t>100003502</t>
-  </si>
-  <si>
-    <t>1100183140</t>
-  </si>
-  <si>
     <t>100003504</t>
   </si>
   <si>
@@ -496,12 +478,6 @@
     <t>1100185550</t>
   </si>
   <si>
-    <t>100003509</t>
-  </si>
-  <si>
-    <t>1100188510</t>
-  </si>
-  <si>
     <t>100003510</t>
   </si>
   <si>
@@ -550,12 +526,6 @@
     <t>1100182120</t>
   </si>
   <si>
-    <t>100003515</t>
-  </si>
-  <si>
-    <t>1100185540</t>
-  </si>
-  <si>
     <t>100003516</t>
   </si>
   <si>
@@ -610,7 +580,430 @@
     <t>1100190240</t>
   </si>
   <si>
-    <t>100003527</t>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
+  </si>
+  <si>
+    <t>980000017600</t>
+  </si>
+  <si>
+    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100186250</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>100003551</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>980000018800</t>
+  </si>
+  <si>
+    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100171080</t>
+  </si>
+  <si>
+    <t>100003558</t>
+  </si>
+  <si>
+    <t>980000018600</t>
+  </si>
+  <si>
+    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185560</t>
+  </si>
+  <si>
+    <t>100003559</t>
+  </si>
+  <si>
+    <t>1100190960</t>
+  </si>
+  <si>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>980000023300</t>
+  </si>
+  <si>
+    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
+  </si>
+  <si>
+    <t>1100189660</t>
+  </si>
+  <si>
+    <t>100003561</t>
+  </si>
+  <si>
+    <t>980000027600</t>
+  </si>
+  <si>
+    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>1100189730</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>980000037701</t>
+  </si>
+  <si>
+    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100191710</t>
+  </si>
+  <si>
+    <t>100003563</t>
+  </si>
+  <si>
+    <t>980000032501</t>
+  </si>
+  <si>
+    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100184050</t>
+  </si>
+  <si>
+    <t>100003564</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100192160</t>
+  </si>
+  <si>
+    <t>100003568</t>
+  </si>
+  <si>
+    <t>980000041900</t>
+  </si>
+  <si>
+    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
+  </si>
+  <si>
+    <t>1300000184</t>
+  </si>
+  <si>
+    <t>100003572</t>
+  </si>
+  <si>
+    <t>1100192930</t>
+  </si>
+  <si>
+    <t>100003573</t>
+  </si>
+  <si>
+    <t>100003574</t>
+  </si>
+  <si>
+    <t>100003575</t>
+  </si>
+  <si>
+    <t>1100192830</t>
+  </si>
+  <si>
+    <t>100003576</t>
+  </si>
+  <si>
+    <t>100003577</t>
+  </si>
+  <si>
+    <t>100003578</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003579</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>100003585</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  CSER MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100178040</t>
+  </si>
+  <si>
+    <t>100003587</t>
+  </si>
+  <si>
+    <t>1100193830</t>
+  </si>
+  <si>
+    <t>100003590</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100193820</t>
+  </si>
+  <si>
+    <t>100003592</t>
+  </si>
+  <si>
+    <t>1100178390</t>
+  </si>
+  <si>
+    <t>100003593</t>
+  </si>
+  <si>
+    <t>980000022901</t>
+  </si>
+  <si>
+    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100193130</t>
+  </si>
+  <si>
+    <t>100003594</t>
+  </si>
+  <si>
+    <t>1100194400</t>
+  </si>
+  <si>
+    <t>100003595</t>
+  </si>
+  <si>
+    <t>1100193850</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>100003597</t>
+  </si>
+  <si>
+    <t>100003598</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100193860</t>
+  </si>
+  <si>
+    <t>100003599</t>
+  </si>
+  <si>
+    <t>100003600</t>
+  </si>
+  <si>
+    <t>980000045100</t>
+  </si>
+  <si>
+    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100191950</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>1100183290</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>1100194940</t>
+  </si>
+  <si>
+    <t>100003603</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100194930</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100194670</t>
+  </si>
+  <si>
+    <t>100003606</t>
+  </si>
+  <si>
+    <t>1100195420</t>
+  </si>
+  <si>
+    <t>100003607</t>
+  </si>
+  <si>
+    <t>1100195960</t>
+  </si>
+  <si>
+    <t>100003608</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100195080</t>
+  </si>
+  <si>
+    <t>100003609</t>
+  </si>
+  <si>
+    <t>100003610</t>
   </si>
   <si>
     <t>980000005501</t>
@@ -619,453 +1012,6 @@
     <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
   </si>
   <si>
-    <t>1100186230</t>
-  </si>
-  <si>
-    <t>100003528</t>
-  </si>
-  <si>
-    <t>1100190870</t>
-  </si>
-  <si>
-    <t>100003529</t>
-  </si>
-  <si>
-    <t>100003532</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>1100190890</t>
-  </si>
-  <si>
-    <t>100003533</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190900</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190910</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1100190920</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1100190930</t>
-  </si>
-  <si>
-    <t>100003541</t>
-  </si>
-  <si>
-    <t>1100185360</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>980000048100</t>
-  </si>
-  <si>
-    <t>5A-350XL_X=650, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100191210</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100191250</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1100191260</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1100191270</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>100003549</t>
-  </si>
-  <si>
-    <t>980000017600</t>
-  </si>
-  <si>
-    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100186250</t>
-  </si>
-  <si>
-    <t>100003550</t>
-  </si>
-  <si>
-    <t>100003551</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003552</t>
-  </si>
-  <si>
-    <t>100003553</t>
-  </si>
-  <si>
-    <t>980000018800</t>
-  </si>
-  <si>
-    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100171080</t>
-  </si>
-  <si>
-    <t>100003558</t>
-  </si>
-  <si>
-    <t>980000018600</t>
-  </si>
-  <si>
-    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100185560</t>
-  </si>
-  <si>
-    <t>100003559</t>
-  </si>
-  <si>
-    <t>1100190960</t>
-  </si>
-  <si>
-    <t>100003560</t>
-  </si>
-  <si>
-    <t>980000023300</t>
-  </si>
-  <si>
-    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
-  </si>
-  <si>
-    <t>1100189660</t>
-  </si>
-  <si>
-    <t>100003561</t>
-  </si>
-  <si>
-    <t>980000027600</t>
-  </si>
-  <si>
-    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>1100189730</t>
-  </si>
-  <si>
-    <t>100003562</t>
-  </si>
-  <si>
-    <t>980000037701</t>
-  </si>
-  <si>
-    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100191710</t>
-  </si>
-  <si>
-    <t>100003563</t>
-  </si>
-  <si>
-    <t>980000032501</t>
-  </si>
-  <si>
-    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100184050</t>
-  </si>
-  <si>
-    <t>100003564</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100192160</t>
-  </si>
-  <si>
-    <t>100003568</t>
-  </si>
-  <si>
-    <t>980000041900</t>
-  </si>
-  <si>
-    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
-  </si>
-  <si>
-    <t>1300000184</t>
-  </si>
-  <si>
-    <t>100003569</t>
-  </si>
-  <si>
-    <t>1100192900</t>
-  </si>
-  <si>
-    <t>100003570</t>
-  </si>
-  <si>
-    <t>100003571</t>
-  </si>
-  <si>
-    <t>100003572</t>
-  </si>
-  <si>
-    <t>1100192930</t>
-  </si>
-  <si>
-    <t>100003573</t>
-  </si>
-  <si>
-    <t>100003574</t>
-  </si>
-  <si>
-    <t>100003575</t>
-  </si>
-  <si>
-    <t>1100192830</t>
-  </si>
-  <si>
-    <t>100003576</t>
-  </si>
-  <si>
-    <t>100003577</t>
-  </si>
-  <si>
-    <t>100003578</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003579</t>
-  </si>
-  <si>
-    <t>100003580</t>
-  </si>
-  <si>
-    <t>100003585</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100178040</t>
-  </si>
-  <si>
-    <t>100003587</t>
-  </si>
-  <si>
-    <t>1100193830</t>
-  </si>
-  <si>
-    <t>100003590</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100193820</t>
-  </si>
-  <si>
-    <t>100003592</t>
-  </si>
-  <si>
-    <t>1100178390</t>
-  </si>
-  <si>
-    <t>100003593</t>
-  </si>
-  <si>
-    <t>980000022901</t>
-  </si>
-  <si>
-    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>1100193130</t>
-  </si>
-  <si>
-    <t>100003594</t>
-  </si>
-  <si>
-    <t>1100194400</t>
-  </si>
-  <si>
-    <t>100003595</t>
-  </si>
-  <si>
-    <t>1100193850</t>
-  </si>
-  <si>
-    <t>100003596</t>
-  </si>
-  <si>
-    <t>100003597</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>100003598</t>
-  </si>
-  <si>
-    <t>1100193860</t>
-  </si>
-  <si>
-    <t>100003599</t>
-  </si>
-  <si>
-    <t>100003600</t>
-  </si>
-  <si>
-    <t>980000045100</t>
-  </si>
-  <si>
-    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100191950</t>
-  </si>
-  <si>
-    <t>100003601</t>
-  </si>
-  <si>
-    <t>1100183290</t>
-  </si>
-  <si>
-    <t>100003602</t>
-  </si>
-  <si>
-    <t>1100194940</t>
-  </si>
-  <si>
-    <t>100003603</t>
-  </si>
-  <si>
-    <t>100003604</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100194930</t>
-  </si>
-  <si>
-    <t>100003605</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100194670</t>
-  </si>
-  <si>
-    <t>100003606</t>
-  </si>
-  <si>
-    <t>1100195420</t>
-  </si>
-  <si>
-    <t>100003607</t>
-  </si>
-  <si>
-    <t>1100195960</t>
-  </si>
-  <si>
-    <t>100003608</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100195080</t>
-  </si>
-  <si>
-    <t>100003609</t>
-  </si>
-  <si>
-    <t>100003610</t>
-  </si>
-  <si>
     <t>1100187490</t>
   </si>
   <si>
@@ -1192,78 +1138,72 @@
     <t>100003629</t>
   </si>
   <si>
+    <t>100003630</t>
+  </si>
+  <si>
+    <t>100003631</t>
+  </si>
+  <si>
+    <t>1100196080</t>
+  </si>
+  <si>
+    <t>100003632</t>
+  </si>
+  <si>
+    <t>980000018201</t>
+  </si>
+  <si>
+    <t>HSA-423,#50_X4000,Y2300,Z780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100197300</t>
+  </si>
+  <si>
+    <t>100003633</t>
+  </si>
+  <si>
+    <t>1100189770</t>
+  </si>
+  <si>
+    <t>100003634</t>
+  </si>
+  <si>
+    <t>1100197090</t>
+  </si>
+  <si>
+    <t>100003635</t>
+  </si>
+  <si>
+    <t>1100196060</t>
+  </si>
+  <si>
+    <t>100003636</t>
+  </si>
+  <si>
+    <t>980000047800</t>
+  </si>
+  <si>
+    <t>LG-2100,#40_X=2050, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100197450</t>
+  </si>
+  <si>
+    <t>ZP09</t>
+  </si>
+  <si>
+    <t>630000332</t>
+  </si>
+  <si>
+    <t>080100145201</t>
+  </si>
+  <si>
+    <t>D6K 主軸,010801_BT50,M65,0045</t>
+  </si>
+  <si>
     <t>REL  PRC  MANC SETC</t>
   </si>
   <si>
-    <t>100003630</t>
-  </si>
-  <si>
-    <t>100003631</t>
-  </si>
-  <si>
-    <t>CRTD MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100196080</t>
-  </si>
-  <si>
-    <t>100003632</t>
-  </si>
-  <si>
-    <t>980000018201</t>
-  </si>
-  <si>
-    <t>HSA-423,#50_X4000,Y2300,Z780/1070/1200</t>
-  </si>
-  <si>
-    <t>1100197300</t>
-  </si>
-  <si>
-    <t>100003633</t>
-  </si>
-  <si>
-    <t>1100189770</t>
-  </si>
-  <si>
-    <t>100003634</t>
-  </si>
-  <si>
-    <t>1100197090</t>
-  </si>
-  <si>
-    <t>100003635</t>
-  </si>
-  <si>
-    <t>1100196060</t>
-  </si>
-  <si>
-    <t>100003636</t>
-  </si>
-  <si>
-    <t>980000047800</t>
-  </si>
-  <si>
-    <t>LG-2100,#40_X=2050, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>CRTD PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>1100197450</t>
-  </si>
-  <si>
-    <t>ZP09</t>
-  </si>
-  <si>
-    <t>630000332</t>
-  </si>
-  <si>
-    <t>080100145201</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BT50,M65,0045</t>
-  </si>
-  <si>
     <t>PENNY</t>
   </si>
   <si>
@@ -1289,18 +1229,6 @@
   </si>
   <si>
     <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
-  </si>
-  <si>
-    <t>630000351</t>
-  </si>
-  <si>
-    <t>080100076704</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF DLV  PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>630000354</t>
@@ -1474,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1497,52 +1425,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2306,7 +2234,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
@@ -2315,22 +2243,22 @@
         <v>69</v>
       </c>
       <c r="G17" s="3">
-        <v>45861</v>
+        <v>45901</v>
       </c>
       <c r="H17" s="3">
-        <v>45946</v>
+        <v>46045</v>
       </c>
       <c r="I17" s="3">
-        <v>46140</v>
+        <v>46183</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="3">
-        <v>45861</v>
+        <v>45901</v>
       </c>
       <c r="M17" t="s">
         <v>6</v>
@@ -2339,7 +2267,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P17" t="s">
         <v>9</v>
@@ -2350,37 +2278,37 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18" s="3">
-        <v>45901</v>
+        <v>45943</v>
       </c>
       <c r="H18" s="3">
-        <v>46045</v>
+        <v>46017</v>
       </c>
       <c r="I18" s="3">
-        <v>46183</v>
+        <v>46135</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="3">
-        <v>45901</v>
+        <v>45943</v>
       </c>
       <c r="M18" t="s">
         <v>6</v>
@@ -2418,10 +2346,10 @@
         <v>45943</v>
       </c>
       <c r="H19" s="3">
-        <v>46017</v>
+        <v>46041</v>
       </c>
       <c r="I19" s="3">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -2459,19 +2387,19 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3">
-        <v>45943</v>
+        <v>45966</v>
       </c>
       <c r="H20" s="3">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="I20" s="3">
-        <v>46114</v>
+        <v>46162</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -2480,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>45943</v>
+        <v>45966</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2489,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="O20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P20" t="s">
         <v>9</v>
@@ -2500,37 +2428,37 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" t="s">
-        <v>26</v>
-      </c>
       <c r="G21" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H21" s="3">
-        <v>46051</v>
+        <v>46099</v>
       </c>
       <c r="I21" s="3">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
@@ -2568,10 +2496,10 @@
         <v>45979</v>
       </c>
       <c r="H22" s="3">
-        <v>46099</v>
+        <v>46065</v>
       </c>
       <c r="I22" s="3">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="J22" t="s">
         <v>13</v>
@@ -2615,22 +2543,22 @@
         <v>92</v>
       </c>
       <c r="G23" s="3">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="H23" s="3">
-        <v>46065</v>
+        <v>46125</v>
       </c>
       <c r="I23" s="3">
-        <v>46157</v>
+        <v>46199</v>
       </c>
       <c r="J23" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2656,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
         <v>95</v>
@@ -2665,22 +2593,22 @@
         <v>96</v>
       </c>
       <c r="G24" s="3">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H24" s="3">
-        <v>46125</v>
+        <v>46076</v>
       </c>
       <c r="I24" s="3">
-        <v>46199</v>
+        <v>46129</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2718,10 +2646,10 @@
         <v>45993</v>
       </c>
       <c r="H25" s="3">
-        <v>46076</v>
+        <v>46041</v>
       </c>
       <c r="I25" s="3">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="J25" t="s">
         <v>47</v>
@@ -2759,19 +2687,19 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="G26" s="3">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H26" s="3">
-        <v>46041</v>
+        <v>46125</v>
       </c>
       <c r="I26" s="3">
-        <v>46142</v>
+        <v>46226</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -2780,7 +2708,7 @@
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2789,7 +2717,7 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P26" t="s">
         <v>9</v>
@@ -2800,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2809,19 +2737,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G27" s="3">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H27" s="3">
-        <v>46125</v>
+        <v>46101</v>
       </c>
       <c r="I27" s="3">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -2830,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2839,7 +2767,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2850,28 +2778,28 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
         <v>108</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" t="s">
-        <v>88</v>
       </c>
       <c r="G28" s="3">
         <v>45995</v>
       </c>
       <c r="H28" s="3">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="I28" s="3">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="J28" t="s">
         <v>22</v>
@@ -2918,10 +2846,10 @@
         <v>45995</v>
       </c>
       <c r="H29" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="I29" s="3">
-        <v>46148</v>
+        <v>46202</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -2959,37 +2887,37 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H30" s="3">
+        <v>46087</v>
+      </c>
+      <c r="I30" s="3">
+        <v>46122</v>
+      </c>
+      <c r="J30" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s">
+        <v>5</v>
+      </c>
+      <c r="L30" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M30" t="s">
+        <v>6</v>
+      </c>
+      <c r="N30" t="s">
+        <v>7</v>
+      </c>
+      <c r="O30" t="s">
         <v>115</v>
-      </c>
-      <c r="F30" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="3">
-        <v>45995</v>
-      </c>
-      <c r="H30" s="3">
-        <v>46105</v>
-      </c>
-      <c r="I30" s="3">
-        <v>46202</v>
-      </c>
-      <c r="J30" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" t="s">
-        <v>5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>45995</v>
-      </c>
-      <c r="M30" t="s">
-        <v>6</v>
-      </c>
-      <c r="N30" t="s">
-        <v>7</v>
-      </c>
-      <c r="O30" t="s">
-        <v>117</v>
       </c>
       <c r="P30" t="s">
         <v>9</v>
@@ -3000,31 +2928,31 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" t="s">
         <v>118</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" t="s">
-        <v>82</v>
       </c>
       <c r="G31" s="3">
         <v>46000</v>
       </c>
       <c r="H31" s="3">
-        <v>46087</v>
+        <v>46050</v>
       </c>
       <c r="I31" s="3">
-        <v>46122</v>
+        <v>46148</v>
       </c>
       <c r="J31" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -3059,19 +2987,19 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="G32" s="3">
         <v>46000</v>
       </c>
       <c r="H32" s="3">
-        <v>46050</v>
+        <v>46104</v>
       </c>
       <c r="I32" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="J32" t="s">
         <v>22</v>
@@ -3089,7 +3017,7 @@
         <v>7</v>
       </c>
       <c r="O32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P32" t="s">
         <v>9</v>
@@ -3100,28 +3028,28 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
         <v>124</v>
       </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>41</v>
-      </c>
-      <c r="F33" t="s">
-        <v>42</v>
-      </c>
       <c r="G33" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="H33" s="3">
-        <v>46104</v>
+        <v>46010</v>
       </c>
       <c r="I33" s="3">
-        <v>46153</v>
+        <v>46045</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
@@ -3130,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -3159,19 +3087,19 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="F34" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="G34" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="H34" s="3">
-        <v>46010</v>
+        <v>46041</v>
       </c>
       <c r="I34" s="3">
-        <v>46045</v>
+        <v>46155</v>
       </c>
       <c r="J34" t="s">
         <v>22</v>
@@ -3180,7 +3108,7 @@
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -3189,7 +3117,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P34" t="s">
         <v>9</v>
@@ -3200,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -3218,10 +3146,10 @@
         <v>46007</v>
       </c>
       <c r="H35" s="3">
-        <v>46041</v>
+        <v>46090</v>
       </c>
       <c r="I35" s="3">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="J35" t="s">
         <v>22</v>
@@ -3239,7 +3167,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3250,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3268,10 +3196,10 @@
         <v>46007</v>
       </c>
       <c r="H36" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="I36" s="3">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
@@ -3289,7 +3217,7 @@
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -3300,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3309,19 +3237,19 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G37" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="H37" s="3">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="I37" s="3">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -3330,7 +3258,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3339,7 +3267,7 @@
         <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -3350,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3359,28 +3287,28 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="G38" s="3">
-        <v>46014</v>
+        <v>46027</v>
       </c>
       <c r="H38" s="3">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="I38" s="3">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="J38" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K38" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="3">
-        <v>46014</v>
+        <v>46022</v>
       </c>
       <c r="M38" t="s">
         <v>6</v>
@@ -3389,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="O38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3400,37 +3328,37 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" t="s">
-        <v>26</v>
-      </c>
       <c r="G39" s="3">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H39" s="3">
-        <v>46126</v>
+        <v>46031</v>
       </c>
       <c r="I39" s="3">
-        <v>46188</v>
+        <v>46155</v>
       </c>
       <c r="J39" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="M39" t="s">
         <v>6</v>
@@ -3465,13 +3393,13 @@
         <v>142</v>
       </c>
       <c r="G40" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="H40" s="3">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="I40" s="3">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -3480,7 +3408,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3506,31 +3434,31 @@
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="F41" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="G41" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="H41" s="3">
-        <v>46057</v>
+        <v>46090</v>
       </c>
       <c r="I41" s="3">
-        <v>46136</v>
+        <v>46211</v>
       </c>
       <c r="J41" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3539,7 +3467,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3550,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -3559,19 +3487,19 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G42" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="H42" s="3">
-        <v>46050</v>
+        <v>46129</v>
       </c>
       <c r="I42" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -3580,7 +3508,7 @@
         <v>5</v>
       </c>
       <c r="L42" s="3">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="M42" t="s">
         <v>6</v>
@@ -3589,7 +3517,7 @@
         <v>7</v>
       </c>
       <c r="O42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3600,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3609,28 +3537,28 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="F43" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="G43" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="H43" s="3">
-        <v>46090</v>
+        <v>46148</v>
       </c>
       <c r="I43" s="3">
-        <v>46211</v>
+        <v>46183</v>
       </c>
       <c r="J43" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="M43" t="s">
         <v>6</v>
@@ -3639,7 +3567,7 @@
         <v>7</v>
       </c>
       <c r="O43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P43" t="s">
         <v>9</v>
@@ -3650,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -3659,19 +3587,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G44" s="3">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="H44" s="3">
-        <v>46129</v>
+        <v>46090</v>
       </c>
       <c r="I44" s="3">
-        <v>46167</v>
+        <v>46195</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -3680,7 +3608,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3689,7 +3617,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3700,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3709,22 +3637,22 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="G45" s="3">
         <v>46044</v>
       </c>
       <c r="H45" s="3">
-        <v>46148</v>
+        <v>46083</v>
       </c>
       <c r="I45" s="3">
-        <v>46183</v>
+        <v>46156</v>
       </c>
       <c r="J45" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -3739,7 +3667,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3750,31 +3678,31 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="G46" s="3">
         <v>46044</v>
       </c>
       <c r="H46" s="3">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="I46" s="3">
-        <v>46136</v>
+        <v>46153</v>
       </c>
       <c r="J46" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -3789,7 +3717,7 @@
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3800,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3809,19 +3737,19 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F47" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G47" s="3">
         <v>46048</v>
       </c>
       <c r="H47" s="3">
-        <v>46090</v>
+        <v>46106</v>
       </c>
       <c r="I47" s="3">
-        <v>46195</v>
+        <v>46157</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -3830,7 +3758,7 @@
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3839,7 +3767,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3850,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3859,19 +3787,19 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F48" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G48" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="H48" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="I48" s="3">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -3880,7 +3808,7 @@
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3889,7 +3817,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3900,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3915,22 +3843,22 @@
         <v>173</v>
       </c>
       <c r="G49" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H49" s="3">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="I49" s="3">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="J49" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3939,7 +3867,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3950,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3959,19 +3887,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G50" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="H50" s="3">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="I50" s="3">
-        <v>46157</v>
+        <v>46134</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -3980,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3989,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -4000,37 +3928,37 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" t="s">
         <v>179</v>
       </c>
-      <c r="C51" s="2">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" t="s">
-        <v>88</v>
-      </c>
       <c r="G51" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="H51" s="3">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="I51" s="3">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="J51" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -4039,7 +3967,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -4050,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -4059,19 +3987,19 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F52" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G52" s="3">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="H52" s="3">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="I52" s="3">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -4080,7 +4008,7 @@
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -4089,7 +4017,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -4100,28 +4028,28 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F53" t="s">
         <v>185</v>
       </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>182</v>
-      </c>
-      <c r="F53" t="s">
-        <v>183</v>
-      </c>
       <c r="G53" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="H53" s="3">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="I53" s="3">
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="J53" t="s">
         <v>22</v>
@@ -4130,7 +4058,7 @@
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -4139,7 +4067,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -4150,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -4159,28 +4087,28 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="G54" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="H54" s="3">
-        <v>46099</v>
+        <v>46135</v>
       </c>
       <c r="I54" s="3">
-        <v>46134</v>
+        <v>46170</v>
       </c>
       <c r="J54" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="M54" t="s">
         <v>6</v>
@@ -4209,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="F55" t="s">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="G55" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="H55" s="3">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="I55" s="3">
-        <v>46136</v>
+        <v>46168</v>
       </c>
       <c r="J55" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="M55" t="s">
         <v>6</v>
@@ -4239,7 +4167,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4250,46 +4178,46 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" s="3">
+        <v>46064</v>
+      </c>
+      <c r="H56" s="3">
+        <v>46308</v>
+      </c>
+      <c r="I56" s="3">
+        <v>46344</v>
+      </c>
+      <c r="J56" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="K56" t="s">
+        <v>5</v>
+      </c>
+      <c r="L56" s="3">
+        <v>46064</v>
+      </c>
+      <c r="M56" t="s">
+        <v>6</v>
+      </c>
+      <c r="N56" t="s">
+        <v>7</v>
+      </c>
+      <c r="O56" t="s">
         <v>194</v>
-      </c>
-      <c r="F56" t="s">
-        <v>195</v>
-      </c>
-      <c r="G56" s="3">
-        <v>46063</v>
-      </c>
-      <c r="H56" s="3">
-        <v>46091</v>
-      </c>
-      <c r="I56" s="3">
-        <v>46170</v>
-      </c>
-      <c r="J56" t="s">
-        <v>22</v>
-      </c>
-      <c r="K56" t="s">
-        <v>5</v>
-      </c>
-      <c r="L56" s="3">
-        <v>46063</v>
-      </c>
-      <c r="M56" t="s">
-        <v>6</v>
-      </c>
-      <c r="N56" t="s">
-        <v>7</v>
-      </c>
-      <c r="O56" t="s">
-        <v>196</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4300,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4309,37 +4237,37 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
+        <v>58</v>
+      </c>
+      <c r="F57" t="s">
+        <v>59</v>
+      </c>
+      <c r="G57" s="3">
+        <v>46064</v>
+      </c>
+      <c r="H57" s="3">
+        <v>46308</v>
+      </c>
+      <c r="I57" s="3">
+        <v>46344</v>
+      </c>
+      <c r="J57" t="s">
+        <v>196</v>
+      </c>
+      <c r="K57" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
+        <v>46064</v>
+      </c>
+      <c r="M57" t="s">
+        <v>6</v>
+      </c>
+      <c r="N57" t="s">
+        <v>7</v>
+      </c>
+      <c r="O57" t="s">
         <v>194</v>
-      </c>
-      <c r="F57" t="s">
-        <v>195</v>
-      </c>
-      <c r="G57" s="3">
-        <v>46063</v>
-      </c>
-      <c r="H57" s="3">
-        <v>46108</v>
-      </c>
-      <c r="I57" s="3">
-        <v>46183</v>
-      </c>
-      <c r="J57" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
-        <v>46063</v>
-      </c>
-      <c r="M57" t="s">
-        <v>6</v>
-      </c>
-      <c r="N57" t="s">
-        <v>7</v>
-      </c>
-      <c r="O57" t="s">
-        <v>198</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4350,31 +4278,31 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="F58" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="G58" s="3">
         <v>46064</v>
       </c>
       <c r="H58" s="3">
-        <v>46079</v>
+        <v>46150</v>
       </c>
       <c r="I58" s="3">
-        <v>46140</v>
+        <v>46189</v>
       </c>
       <c r="J58" t="s">
-        <v>47</v>
+        <v>198</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
@@ -4389,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4400,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4409,22 +4337,22 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F59" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G59" s="3">
         <v>46064</v>
       </c>
       <c r="H59" s="3">
-        <v>46135</v>
+        <v>46178</v>
       </c>
       <c r="I59" s="3">
-        <v>46170</v>
+        <v>46218</v>
       </c>
       <c r="J59" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
@@ -4439,7 +4367,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4450,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4459,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G60" s="3">
         <v>46064</v>
       </c>
       <c r="H60" s="3">
-        <v>46134</v>
+        <v>46244</v>
       </c>
       <c r="I60" s="3">
-        <v>46168</v>
+        <v>46281</v>
       </c>
       <c r="J60" t="s">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
@@ -4500,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4509,22 +4437,22 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F61" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G61" s="3">
         <v>46064</v>
       </c>
       <c r="H61" s="3">
-        <v>46308</v>
+        <v>46303</v>
       </c>
       <c r="I61" s="3">
         <v>46344</v>
       </c>
       <c r="J61" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
@@ -4539,7 +4467,7 @@
         <v>7</v>
       </c>
       <c r="O61" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4550,46 +4478,46 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" t="s">
         <v>209</v>
       </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>58</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
       <c r="G62" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H62" s="3">
-        <v>46308</v>
+        <v>46077</v>
       </c>
       <c r="I62" s="3">
-        <v>46344</v>
+        <v>46153</v>
       </c>
       <c r="J62" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M62" t="s">
+        <v>6</v>
+      </c>
+      <c r="N62" t="s">
+        <v>7</v>
+      </c>
+      <c r="O62" t="s">
         <v>210</v>
-      </c>
-      <c r="K62" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>46064</v>
-      </c>
-      <c r="M62" t="s">
-        <v>6</v>
-      </c>
-      <c r="N62" t="s">
-        <v>7</v>
-      </c>
-      <c r="O62" t="s">
-        <v>208</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4609,37 +4537,37 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="G63" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H63" s="3">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="I63" s="3">
-        <v>46189</v>
+        <v>46218</v>
       </c>
       <c r="J63" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" t="s">
+        <v>5</v>
+      </c>
+      <c r="L63" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M63" t="s">
+        <v>6</v>
+      </c>
+      <c r="N63" t="s">
+        <v>7</v>
+      </c>
+      <c r="O63" t="s">
         <v>212</v>
-      </c>
-      <c r="K63" t="s">
-        <v>5</v>
-      </c>
-      <c r="L63" s="3">
-        <v>46064</v>
-      </c>
-      <c r="M63" t="s">
-        <v>6</v>
-      </c>
-      <c r="N63" t="s">
-        <v>7</v>
-      </c>
-      <c r="O63" t="s">
-        <v>213</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4650,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4659,28 +4587,28 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="G64" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H64" s="3">
-        <v>46178</v>
+        <v>46167</v>
       </c>
       <c r="I64" s="3">
         <v>46218</v>
       </c>
       <c r="J64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M64" t="s">
         <v>6</v>
@@ -4689,7 +4617,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4700,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4709,28 +4637,28 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="F65" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="G65" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H65" s="3">
-        <v>46244</v>
+        <v>46217</v>
       </c>
       <c r="I65" s="3">
-        <v>46281</v>
+        <v>46267</v>
       </c>
       <c r="J65" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M65" t="s">
         <v>6</v>
@@ -4739,7 +4667,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4750,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4759,28 +4687,28 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="F66" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="G66" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H66" s="3">
-        <v>46303</v>
+        <v>46217</v>
       </c>
       <c r="I66" s="3">
-        <v>46344</v>
+        <v>46267</v>
       </c>
       <c r="J66" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M66" t="s">
         <v>6</v>
@@ -4789,7 +4717,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4800,31 +4728,31 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
       </c>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="F67" t="s">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="G67" s="3">
         <v>46076</v>
       </c>
       <c r="H67" s="3">
-        <v>46090</v>
+        <v>46254</v>
       </c>
       <c r="I67" s="3">
-        <v>46140</v>
+        <v>46309</v>
       </c>
       <c r="J67" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
@@ -4839,7 +4767,7 @@
         <v>7</v>
       </c>
       <c r="O67" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4850,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4859,22 +4787,22 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F68" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="G68" s="3">
         <v>46076</v>
       </c>
       <c r="H68" s="3">
-        <v>46077</v>
+        <v>46254</v>
       </c>
       <c r="I68" s="3">
-        <v>46146</v>
+        <v>46309</v>
       </c>
       <c r="J68" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4889,7 +4817,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4900,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4909,22 +4837,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
+        <v>223</v>
+      </c>
+      <c r="F69" t="s">
         <v>224</v>
       </c>
-      <c r="F69" t="s">
-        <v>225</v>
-      </c>
       <c r="G69" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H69" s="3">
-        <v>46167</v>
+        <v>46107</v>
       </c>
       <c r="I69" s="3">
-        <v>46218</v>
+        <v>46153</v>
       </c>
       <c r="J69" t="s">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4939,7 +4867,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4950,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4959,22 +4887,22 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
+        <v>223</v>
+      </c>
+      <c r="F70" t="s">
         <v>224</v>
       </c>
-      <c r="F70" t="s">
-        <v>225</v>
-      </c>
       <c r="G70" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H70" s="3">
-        <v>46167</v>
+        <v>46108</v>
       </c>
       <c r="I70" s="3">
-        <v>46218</v>
+        <v>46156</v>
       </c>
       <c r="J70" t="s">
-        <v>228</v>
+        <v>22</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
@@ -4989,7 +4917,7 @@
         <v>7</v>
       </c>
       <c r="O70" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -5000,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -5009,19 +4937,19 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
+        <v>223</v>
+      </c>
+      <c r="F71" t="s">
         <v>224</v>
       </c>
-      <c r="F71" t="s">
-        <v>225</v>
-      </c>
       <c r="G71" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H71" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="I71" s="3">
-        <v>46267</v>
+        <v>46154</v>
       </c>
       <c r="J71" t="s">
         <v>228</v>
@@ -5039,7 +4967,7 @@
         <v>7</v>
       </c>
       <c r="O71" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="P71" t="s">
         <v>9</v>
@@ -5050,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -5059,22 +4987,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
+        <v>223</v>
+      </c>
+      <c r="F72" t="s">
         <v>224</v>
       </c>
-      <c r="F72" t="s">
-        <v>225</v>
-      </c>
       <c r="G72" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H72" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="I72" s="3">
-        <v>46267</v>
+        <v>46154</v>
       </c>
       <c r="J72" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
@@ -5089,7 +5017,7 @@
         <v>7</v>
       </c>
       <c r="O72" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5100,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -5109,37 +5037,37 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F73" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G73" s="3">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="H73" s="3">
-        <v>46254</v>
+        <v>46163</v>
       </c>
       <c r="I73" s="3">
-        <v>46309</v>
+        <v>46238</v>
       </c>
       <c r="J73" t="s">
+        <v>233</v>
+      </c>
+      <c r="K73" t="s">
+        <v>5</v>
+      </c>
+      <c r="L73" s="3">
+        <v>46079</v>
+      </c>
+      <c r="M73" t="s">
+        <v>6</v>
+      </c>
+      <c r="N73" t="s">
+        <v>7</v>
+      </c>
+      <c r="O73" t="s">
         <v>234</v>
-      </c>
-      <c r="K73" t="s">
-        <v>5</v>
-      </c>
-      <c r="L73" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M73" t="s">
-        <v>6</v>
-      </c>
-      <c r="N73" t="s">
-        <v>7</v>
-      </c>
-      <c r="O73" t="s">
-        <v>236</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5150,37 +5078,37 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" t="s">
         <v>237</v>
       </c>
-      <c r="C74" s="2">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
-        <v>224</v>
-      </c>
-      <c r="F74" t="s">
-        <v>225</v>
-      </c>
       <c r="G74" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H74" s="3">
-        <v>46254</v>
+        <v>46128</v>
       </c>
       <c r="I74" s="3">
-        <v>46309</v>
+        <v>46203</v>
       </c>
       <c r="J74" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
       </c>
       <c r="L74" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M74" t="s">
         <v>6</v>
@@ -5189,7 +5117,7 @@
         <v>7</v>
       </c>
       <c r="O74" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5200,37 +5128,37 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>156</v>
+      </c>
+      <c r="F75" t="s">
+        <v>157</v>
+      </c>
+      <c r="G75" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H75" s="3">
+        <v>46128</v>
+      </c>
+      <c r="I75" s="3">
+        <v>46217</v>
+      </c>
+      <c r="J75" t="s">
         <v>238</v>
       </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>239</v>
-      </c>
-      <c r="F75" t="s">
-        <v>240</v>
-      </c>
-      <c r="G75" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H75" s="3">
-        <v>46107</v>
-      </c>
-      <c r="I75" s="3">
-        <v>46153</v>
-      </c>
-      <c r="J75" t="s">
-        <v>22</v>
-      </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -5259,28 +5187,28 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F76" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G76" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H76" s="3">
-        <v>46108</v>
+        <v>46219</v>
       </c>
       <c r="I76" s="3">
-        <v>46156</v>
+        <v>46279</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M76" t="s">
         <v>6</v>
@@ -5289,7 +5217,7 @@
         <v>7</v>
       </c>
       <c r="O76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5300,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5309,28 +5237,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F77" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G77" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H77" s="3">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="I77" s="3">
-        <v>46154</v>
+        <v>46203</v>
       </c>
       <c r="J77" t="s">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="K77" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L77" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5339,7 +5267,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5350,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5359,28 +5287,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F78" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="G78" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H78" s="3">
-        <v>46114</v>
+        <v>46210</v>
       </c>
       <c r="I78" s="3">
-        <v>46154</v>
+        <v>46324</v>
       </c>
       <c r="J78" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="K78" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L78" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5389,7 +5317,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5400,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5409,28 +5337,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F79" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="G79" s="3">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="H79" s="3">
-        <v>46163</v>
+        <v>46178</v>
       </c>
       <c r="I79" s="3">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="J79" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5439,7 +5367,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5450,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5459,28 +5387,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>252</v>
+        <v>45</v>
       </c>
       <c r="F80" t="s">
-        <v>253</v>
+        <v>46</v>
       </c>
       <c r="G80" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="H80" s="3">
-        <v>46128</v>
+        <v>46212</v>
       </c>
       <c r="I80" s="3">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="J80" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5489,7 +5417,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5500,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5509,28 +5437,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="G81" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="H81" s="3">
-        <v>46128</v>
+        <v>46092</v>
       </c>
       <c r="I81" s="3">
-        <v>46217</v>
+        <v>46163</v>
       </c>
       <c r="J81" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5539,7 +5467,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5550,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5559,28 +5487,28 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="F82" t="s">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="G82" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H82" s="3">
-        <v>46219</v>
+        <v>46133</v>
       </c>
       <c r="I82" s="3">
-        <v>46279</v>
+        <v>46170</v>
       </c>
       <c r="J82" t="s">
-        <v>234</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M82" t="s">
         <v>6</v>
@@ -5589,7 +5517,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5600,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5609,28 +5537,28 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="F83" t="s">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="G83" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H83" s="3">
-        <v>46121</v>
+        <v>46133</v>
       </c>
       <c r="I83" s="3">
-        <v>46203</v>
+        <v>46170</v>
       </c>
       <c r="J83" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K83" t="s">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="L83" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M83" t="s">
         <v>6</v>
@@ -5639,7 +5567,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5650,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5659,37 +5587,37 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
+        <v>77</v>
+      </c>
+      <c r="F84" t="s">
+        <v>78</v>
+      </c>
+      <c r="G84" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H84" s="3">
+        <v>46133</v>
+      </c>
+      <c r="I84" s="3">
+        <v>46170</v>
+      </c>
+      <c r="J84" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" t="s">
+        <v>5</v>
+      </c>
+      <c r="L84" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M84" t="s">
+        <v>6</v>
+      </c>
+      <c r="N84" t="s">
+        <v>7</v>
+      </c>
+      <c r="O84" t="s">
         <v>268</v>
-      </c>
-      <c r="F84" t="s">
-        <v>269</v>
-      </c>
-      <c r="G84" s="3">
-        <v>46086</v>
-      </c>
-      <c r="H84" s="3">
-        <v>46210</v>
-      </c>
-      <c r="I84" s="3">
-        <v>46324</v>
-      </c>
-      <c r="J84" t="s">
-        <v>234</v>
-      </c>
-      <c r="K84" t="s">
-        <v>265</v>
-      </c>
-      <c r="L84" s="3">
-        <v>46086</v>
-      </c>
-      <c r="M84" t="s">
-        <v>6</v>
-      </c>
-      <c r="N84" t="s">
-        <v>7</v>
-      </c>
-      <c r="O84" t="s">
-        <v>270</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5709,37 +5637,37 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
+        <v>77</v>
+      </c>
+      <c r="F85" t="s">
+        <v>78</v>
+      </c>
+      <c r="G85" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H85" s="3">
+        <v>46127</v>
+      </c>
+      <c r="I85" s="3">
+        <v>46170</v>
+      </c>
+      <c r="J85" t="s">
+        <v>13</v>
+      </c>
+      <c r="K85" t="s">
+        <v>5</v>
+      </c>
+      <c r="L85" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M85" t="s">
+        <v>6</v>
+      </c>
+      <c r="N85" t="s">
+        <v>7</v>
+      </c>
+      <c r="O85" t="s">
         <v>272</v>
-      </c>
-      <c r="F85" t="s">
-        <v>273</v>
-      </c>
-      <c r="G85" s="3">
-        <v>46090</v>
-      </c>
-      <c r="H85" s="3">
-        <v>46178</v>
-      </c>
-      <c r="I85" s="3">
-        <v>46233</v>
-      </c>
-      <c r="J85" t="s">
-        <v>274</v>
-      </c>
-      <c r="K85" t="s">
-        <v>5</v>
-      </c>
-      <c r="L85" s="3">
-        <v>46090</v>
-      </c>
-      <c r="M85" t="s">
-        <v>6</v>
-      </c>
-      <c r="N85" t="s">
-        <v>7</v>
-      </c>
-      <c r="O85" t="s">
-        <v>275</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5750,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5759,28 +5687,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F86" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="G86" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H86" s="3">
-        <v>46212</v>
+        <v>46127</v>
       </c>
       <c r="I86" s="3">
-        <v>46234</v>
+        <v>46168</v>
       </c>
       <c r="J86" t="s">
-        <v>277</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5789,7 +5717,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5800,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5809,28 +5737,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="F87" t="s">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="G87" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="H87" s="3">
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="I87" s="3">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="J87" t="s">
-        <v>249</v>
+        <v>13</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5839,7 +5767,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5850,31 +5778,31 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G88" s="3">
         <v>46094</v>
       </c>
       <c r="H88" s="3">
-        <v>46100</v>
+        <v>46167</v>
       </c>
       <c r="I88" s="3">
-        <v>46146</v>
+        <v>46198</v>
       </c>
       <c r="J88" t="s">
-        <v>47</v>
+        <v>276</v>
       </c>
       <c r="K88" t="s">
         <v>5</v>
@@ -5889,7 +5817,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5900,31 +5828,31 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
       </c>
       <c r="D89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F89" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G89" s="3">
         <v>46094</v>
       </c>
       <c r="H89" s="3">
-        <v>46106</v>
+        <v>46167</v>
       </c>
       <c r="I89" s="3">
-        <v>46146</v>
+        <v>46198</v>
       </c>
       <c r="J89" t="s">
-        <v>47</v>
+        <v>276</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
@@ -5939,7 +5867,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5950,31 +5878,31 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G90" s="3">
         <v>46094</v>
       </c>
       <c r="H90" s="3">
-        <v>46101</v>
+        <v>46167</v>
       </c>
       <c r="I90" s="3">
-        <v>46146</v>
+        <v>46198</v>
       </c>
       <c r="J90" t="s">
-        <v>47</v>
+        <v>276</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
@@ -5989,7 +5917,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -6000,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -6009,29 +5937,29 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="F91" t="s">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="G91" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H91" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46181</v>
+      </c>
+      <c r="J91" t="s">
+        <v>282</v>
+      </c>
+      <c r="K91" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>46094</v>
       </c>
-      <c r="H91" s="3">
-        <v>46133</v>
-      </c>
-      <c r="I91" s="3">
-        <v>46170</v>
-      </c>
-      <c r="J91" t="s">
-        <v>13</v>
-      </c>
-      <c r="K91" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
-        <v>46093</v>
-      </c>
       <c r="M91" t="s">
         <v>6</v>
       </c>
@@ -6039,7 +5967,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -6050,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -6059,28 +5987,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="F92" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G92" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H92" s="3">
-        <v>46133</v>
+        <v>46224</v>
       </c>
       <c r="I92" s="3">
-        <v>46162</v>
+        <v>46246</v>
       </c>
       <c r="J92" t="s">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -6089,7 +6017,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6100,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6109,28 +6037,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F93" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G93" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H93" s="3">
-        <v>46133</v>
+        <v>46232</v>
       </c>
       <c r="I93" s="3">
-        <v>46162</v>
+        <v>46253</v>
       </c>
       <c r="J93" t="s">
-        <v>13</v>
+        <v>287</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L93" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -6150,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6159,28 +6087,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="F94" t="s">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="G94" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H94" s="3">
-        <v>46127</v>
+        <v>46217</v>
       </c>
       <c r="I94" s="3">
-        <v>46170</v>
+        <v>46251</v>
       </c>
       <c r="J94" t="s">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="K94" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L94" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -6189,7 +6117,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6200,37 +6128,37 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
+        <v>291</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" t="s">
+        <v>292</v>
+      </c>
+      <c r="F95" t="s">
         <v>293</v>
       </c>
-      <c r="C95" s="2">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0</v>
-      </c>
-      <c r="E95" t="s">
-        <v>81</v>
-      </c>
-      <c r="F95" t="s">
-        <v>82</v>
-      </c>
       <c r="G95" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H95" s="3">
-        <v>46127</v>
+        <v>46227</v>
       </c>
       <c r="I95" s="3">
-        <v>46168</v>
+        <v>46253</v>
       </c>
       <c r="J95" t="s">
-        <v>13</v>
+        <v>218</v>
       </c>
       <c r="K95" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L95" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6239,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6250,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6259,28 +6187,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F96" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G96" s="3">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="H96" s="3">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="I96" s="3">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="J96" t="s">
-        <v>13</v>
+        <v>238</v>
       </c>
       <c r="K96" t="s">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="L96" s="3">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6289,7 +6217,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6300,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6309,28 +6237,28 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F97" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G97" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="H97" s="3">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="I97" s="3">
-        <v>46198</v>
+        <v>46190</v>
       </c>
       <c r="J97" t="s">
-        <v>296</v>
+        <v>153</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M97" t="s">
         <v>6</v>
@@ -6339,7 +6267,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6350,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6359,28 +6287,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F98" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G98" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="H98" s="3">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="I98" s="3">
-        <v>46198</v>
+        <v>46190</v>
       </c>
       <c r="J98" t="s">
-        <v>296</v>
+        <v>153</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46093</v>
+        <v>46113</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6389,7 +6317,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6400,46 +6328,46 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
+        <v>300</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
+        <v>77</v>
+      </c>
+      <c r="F99" t="s">
+        <v>78</v>
+      </c>
+      <c r="G99" s="3">
+        <v>46113</v>
+      </c>
+      <c r="H99" s="3">
+        <v>46171</v>
+      </c>
+      <c r="I99" s="3">
+        <v>46190</v>
+      </c>
+      <c r="J99" t="s">
+        <v>153</v>
+      </c>
+      <c r="K99" t="s">
+        <v>5</v>
+      </c>
+      <c r="L99" s="3">
+        <v>46113</v>
+      </c>
+      <c r="M99" t="s">
+        <v>6</v>
+      </c>
+      <c r="N99" t="s">
+        <v>7</v>
+      </c>
+      <c r="O99" t="s">
         <v>298</v>
-      </c>
-      <c r="C99" s="2">
-        <v>1</v>
-      </c>
-      <c r="D99" s="2">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
-        <v>81</v>
-      </c>
-      <c r="F99" t="s">
-        <v>82</v>
-      </c>
-      <c r="G99" s="3">
-        <v>46094</v>
-      </c>
-      <c r="H99" s="3">
-        <v>46167</v>
-      </c>
-      <c r="I99" s="3">
-        <v>46198</v>
-      </c>
-      <c r="J99" t="s">
-        <v>296</v>
-      </c>
-      <c r="K99" t="s">
-        <v>5</v>
-      </c>
-      <c r="L99" s="3">
-        <v>46093</v>
-      </c>
-      <c r="M99" t="s">
-        <v>6</v>
-      </c>
-      <c r="N99" t="s">
-        <v>7</v>
-      </c>
-      <c r="O99" t="s">
-        <v>292</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6450,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6459,19 +6387,19 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="F100" t="s">
-        <v>301</v>
+        <v>78</v>
       </c>
       <c r="G100" s="3">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="H100" s="3">
-        <v>46149</v>
+        <v>46237</v>
       </c>
       <c r="I100" s="3">
-        <v>46181</v>
+        <v>46254</v>
       </c>
       <c r="J100" t="s">
         <v>302</v>
@@ -6480,7 +6408,7 @@
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6509,28 +6437,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F101" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="G101" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H101" s="3">
-        <v>46224</v>
+        <v>46237</v>
       </c>
       <c r="I101" s="3">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="J101" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6539,7 +6467,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6550,37 +6478,37 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
+        <v>305</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
         <v>306</v>
       </c>
-      <c r="C102" s="2">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2">
-        <v>0</v>
-      </c>
-      <c r="E102" t="s">
-        <v>50</v>
-      </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>307</v>
       </c>
       <c r="G102" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H102" s="3">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="I102" s="3">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="J102" t="s">
-        <v>307</v>
+        <v>153</v>
       </c>
       <c r="K102" t="s">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6609,28 +6537,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="F103" t="s">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="G103" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H103" s="3">
-        <v>46217</v>
+        <v>46170</v>
       </c>
       <c r="I103" s="3">
-        <v>46251</v>
+        <v>46196</v>
       </c>
       <c r="J103" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="K103" t="s">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6659,37 +6587,37 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
+        <v>77</v>
+      </c>
+      <c r="F104" t="s">
+        <v>78</v>
+      </c>
+      <c r="G104" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H104" s="3">
+        <v>46154</v>
+      </c>
+      <c r="I104" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J104" t="s">
+        <v>261</v>
+      </c>
+      <c r="K104" t="s">
+        <v>5</v>
+      </c>
+      <c r="L104" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M104" t="s">
+        <v>6</v>
+      </c>
+      <c r="N104" t="s">
+        <v>7</v>
+      </c>
+      <c r="O104" t="s">
         <v>312</v>
-      </c>
-      <c r="F104" t="s">
-        <v>313</v>
-      </c>
-      <c r="G104" s="3">
-        <v>46106</v>
-      </c>
-      <c r="H104" s="3">
-        <v>46227</v>
-      </c>
-      <c r="I104" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J104" t="s">
-        <v>234</v>
-      </c>
-      <c r="K104" t="s">
-        <v>265</v>
-      </c>
-      <c r="L104" s="3">
-        <v>46106</v>
-      </c>
-      <c r="M104" t="s">
-        <v>6</v>
-      </c>
-      <c r="N104" t="s">
-        <v>7</v>
-      </c>
-      <c r="O104" t="s">
-        <v>314</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6700,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6709,28 +6637,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="F105" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G105" s="3">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="H105" s="3">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="I105" s="3">
-        <v>46160</v>
+        <v>46183</v>
       </c>
       <c r="J105" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="K105" t="s">
-        <v>265</v>
+        <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46107</v>
+        <v>46114</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6739,7 +6667,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6750,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6759,28 +6687,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F106" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G106" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H106" s="3">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="I106" s="3">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="J106" t="s">
-        <v>159</v>
+        <v>315</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6789,7 +6717,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6800,37 +6728,37 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
+        <v>318</v>
+      </c>
+      <c r="F107" t="s">
         <v>319</v>
       </c>
-      <c r="C107" s="2">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2">
-        <v>0</v>
-      </c>
-      <c r="E107" t="s">
-        <v>81</v>
-      </c>
-      <c r="F107" t="s">
-        <v>82</v>
-      </c>
       <c r="G107" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H107" s="3">
-        <v>46171</v>
+        <v>46127</v>
       </c>
       <c r="I107" s="3">
-        <v>46190</v>
+        <v>46154</v>
       </c>
       <c r="J107" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6839,7 +6767,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6850,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6859,28 +6787,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F108" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G108" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H108" s="3">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="I108" s="3">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="J108" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6889,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6900,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6909,28 +6837,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F109" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="G109" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H109" s="3">
-        <v>46237</v>
+        <v>46141</v>
       </c>
       <c r="I109" s="3">
-        <v>46254</v>
+        <v>46168</v>
       </c>
       <c r="J109" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6939,7 +6867,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6950,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6959,28 +6887,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="F110" t="s">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="G110" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H110" s="3">
-        <v>46237</v>
+        <v>46167</v>
       </c>
       <c r="I110" s="3">
-        <v>46254</v>
+        <v>46189</v>
       </c>
       <c r="J110" t="s">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6989,7 +6917,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -7000,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -7015,22 +6943,22 @@
         <v>327</v>
       </c>
       <c r="G111" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H111" s="3">
-        <v>46231</v>
+        <v>46167</v>
       </c>
       <c r="I111" s="3">
-        <v>46266</v>
+        <v>46189</v>
       </c>
       <c r="J111" t="s">
-        <v>159</v>
+        <v>315</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -7050,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -7059,28 +6987,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>331</v>
       </c>
       <c r="F112" t="s">
-        <v>46</v>
+        <v>332</v>
       </c>
       <c r="G112" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H112" s="3">
-        <v>46170</v>
+        <v>46156</v>
       </c>
       <c r="I112" s="3">
-        <v>46196</v>
+        <v>46188</v>
       </c>
       <c r="J112" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -7089,7 +7017,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7100,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7109,28 +7037,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="F113" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="G113" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H113" s="3">
-        <v>46154</v>
+        <v>46141</v>
       </c>
       <c r="I113" s="3">
-        <v>46183</v>
+        <v>46168</v>
       </c>
       <c r="J113" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -7139,7 +7067,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7150,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7159,28 +7087,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="F114" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="G114" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="H114" s="3">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="I114" s="3">
-        <v>46183</v>
+        <v>46168</v>
       </c>
       <c r="J114" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -7189,7 +7117,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7200,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7209,28 +7137,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>50</v>
+        <v>341</v>
       </c>
       <c r="F115" t="s">
-        <v>51</v>
+        <v>342</v>
       </c>
       <c r="G115" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="H115" s="3">
-        <v>46161</v>
+        <v>46142</v>
       </c>
       <c r="I115" s="3">
-        <v>46182</v>
+        <v>46196</v>
       </c>
       <c r="J115" t="s">
-        <v>335</v>
+        <v>238</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -7239,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7250,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7259,28 +7187,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F116" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G116" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="H116" s="3">
-        <v>46127</v>
+        <v>46146</v>
       </c>
       <c r="I116" s="3">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="J116" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -7289,7 +7217,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7300,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7309,28 +7237,28 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>50</v>
+        <v>347</v>
       </c>
       <c r="F117" t="s">
-        <v>51</v>
+        <v>348</v>
       </c>
       <c r="G117" s="3">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="H117" s="3">
-        <v>46161</v>
+        <v>46127</v>
       </c>
       <c r="I117" s="3">
-        <v>46182</v>
+        <v>46146</v>
       </c>
       <c r="J117" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -7339,7 +7267,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7350,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7359,28 +7287,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>127</v>
+        <v>292</v>
       </c>
       <c r="F118" t="s">
-        <v>128</v>
+        <v>293</v>
       </c>
       <c r="G118" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H118" s="3">
-        <v>46141</v>
+        <v>46182</v>
       </c>
       <c r="I118" s="3">
-        <v>46168</v>
+        <v>46210</v>
       </c>
       <c r="J118" t="s">
-        <v>335</v>
+        <v>218</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7389,7 +7317,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7400,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7409,28 +7337,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="F119" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="G119" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H119" s="3">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="I119" s="3">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="J119" t="s">
-        <v>302</v>
+        <v>153</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7439,7 +7367,7 @@
         <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7450,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7459,28 +7387,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="F120" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="G120" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H120" s="3">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="I120" s="3">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="J120" t="s">
-        <v>335</v>
+        <v>153</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7489,7 +7417,7 @@
         <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7500,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7509,28 +7437,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="F121" t="s">
-        <v>201</v>
+        <v>327</v>
       </c>
       <c r="G121" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H121" s="3">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="I121" s="3">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="J121" t="s">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7539,7 +7467,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7550,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7559,28 +7487,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>353</v>
+        <v>223</v>
       </c>
       <c r="F122" t="s">
-        <v>354</v>
+        <v>224</v>
       </c>
       <c r="G122" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="H122" s="3">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="I122" s="3">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="J122" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7589,7 +7517,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7600,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7609,28 +7537,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="F123" t="s">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="G123" s="3">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="H123" s="3">
-        <v>46142</v>
+        <v>46171</v>
       </c>
       <c r="I123" s="3">
-        <v>46168</v>
+        <v>46198</v>
       </c>
       <c r="J123" t="s">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7639,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7650,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7659,28 +7587,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="F124" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="G124" s="3">
-        <v>46125</v>
+        <v>46140</v>
       </c>
       <c r="H124" s="3">
-        <v>46161</v>
+        <v>46146</v>
       </c>
       <c r="I124" s="3">
-        <v>46210</v>
+        <v>46167</v>
       </c>
       <c r="J124" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46125</v>
+        <v>46140</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7689,7 +7617,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7700,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7709,28 +7637,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="F125" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="G125" s="3">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="H125" s="3">
-        <v>46146</v>
+        <v>46191</v>
       </c>
       <c r="I125" s="3">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="J125" t="s">
-        <v>335</v>
+        <v>218</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7739,7 +7667,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7750,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7765,22 +7693,22 @@
         <v>366</v>
       </c>
       <c r="G126" s="3">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="H126" s="3">
-        <v>46127</v>
+        <v>46191</v>
       </c>
       <c r="I126" s="3">
-        <v>46146</v>
+        <v>46245</v>
       </c>
       <c r="J126" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7800,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7809,28 +7737,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="F127" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="G127" s="3">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="H127" s="3">
-        <v>46182</v>
+        <v>46155</v>
       </c>
       <c r="I127" s="3">
-        <v>46210</v>
+        <v>46178</v>
       </c>
       <c r="J127" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7839,7 +7767,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7850,46 +7778,46 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
+        <v>371</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
+        <v>335</v>
+      </c>
+      <c r="F128" t="s">
+        <v>336</v>
+      </c>
+      <c r="G128" s="3">
+        <v>46142</v>
+      </c>
+      <c r="H128" s="3">
+        <v>46155</v>
+      </c>
+      <c r="I128" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J128" t="s">
+        <v>261</v>
+      </c>
+      <c r="K128" t="s">
+        <v>5</v>
+      </c>
+      <c r="L128" s="3">
+        <v>46142</v>
+      </c>
+      <c r="M128" t="s">
+        <v>6</v>
+      </c>
+      <c r="N128" t="s">
+        <v>7</v>
+      </c>
+      <c r="O128" t="s">
         <v>370</v>
-      </c>
-      <c r="C128" s="2">
-        <v>1</v>
-      </c>
-      <c r="D128" s="2">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
-        <v>346</v>
-      </c>
-      <c r="F128" t="s">
-        <v>347</v>
-      </c>
-      <c r="G128" s="3">
-        <v>46133</v>
-      </c>
-      <c r="H128" s="3">
-        <v>46174</v>
-      </c>
-      <c r="I128" s="3">
-        <v>46195</v>
-      </c>
-      <c r="J128" t="s">
-        <v>159</v>
-      </c>
-      <c r="K128" t="s">
-        <v>5</v>
-      </c>
-      <c r="L128" s="3">
-        <v>46133</v>
-      </c>
-      <c r="M128" t="s">
-        <v>6</v>
-      </c>
-      <c r="N128" t="s">
-        <v>7</v>
-      </c>
-      <c r="O128" t="s">
-        <v>371</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7909,28 +7837,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="F129" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="G129" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="H129" s="3">
-        <v>46174</v>
+        <v>46155</v>
       </c>
       <c r="I129" s="3">
-        <v>46195</v>
+        <v>46178</v>
       </c>
       <c r="J129" t="s">
-        <v>159</v>
+        <v>261</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7939,7 +7867,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7950,7 +7878,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7959,28 +7887,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="F130" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="G130" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="H130" s="3">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="I130" s="3">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="J130" t="s">
-        <v>159</v>
+        <v>261</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7989,7 +7917,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -8000,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -8009,28 +7937,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>239</v>
+        <v>335</v>
       </c>
       <c r="F131" t="s">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="G131" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="H131" s="3">
-        <v>46139</v>
+        <v>46189</v>
       </c>
       <c r="I131" s="3">
-        <v>46171</v>
+        <v>46213</v>
       </c>
       <c r="J131" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -8039,7 +7967,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -8050,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -8059,28 +7987,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="F132" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="G132" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H132" s="3">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="I132" s="3">
-        <v>46198</v>
+        <v>46213</v>
       </c>
       <c r="J132" t="s">
-        <v>159</v>
+        <v>276</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8089,7 +8017,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8100,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -8109,28 +8037,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F133" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G133" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H133" s="3">
-        <v>46146</v>
+        <v>46206</v>
       </c>
       <c r="I133" s="3">
-        <v>46167</v>
+        <v>46225</v>
       </c>
       <c r="J133" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8139,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8150,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -8159,28 +8087,28 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F134" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G134" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H134" s="3">
-        <v>46191</v>
+        <v>46175</v>
       </c>
       <c r="I134" s="3">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="J134" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M134" t="s">
         <v>6</v>
@@ -8189,7 +8117,7 @@
         <v>7</v>
       </c>
       <c r="O134" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8200,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8209,37 +8137,37 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
+        <v>111</v>
+      </c>
+      <c r="F135" t="s">
+        <v>112</v>
+      </c>
+      <c r="G135" s="3">
+        <v>46148</v>
+      </c>
+      <c r="H135" s="3">
+        <v>46267</v>
+      </c>
+      <c r="I135" s="3">
+        <v>46353</v>
+      </c>
+      <c r="J135" t="s">
+        <v>302</v>
+      </c>
+      <c r="K135" t="s">
+        <v>5</v>
+      </c>
+      <c r="L135" s="3">
+        <v>46148</v>
+      </c>
+      <c r="M135" t="s">
+        <v>6</v>
+      </c>
+      <c r="N135" t="s">
+        <v>7</v>
+      </c>
+      <c r="O135" t="s">
         <v>383</v>
-      </c>
-      <c r="F135" t="s">
-        <v>384</v>
-      </c>
-      <c r="G135" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H135" s="3">
-        <v>46191</v>
-      </c>
-      <c r="I135" s="3">
-        <v>46245</v>
-      </c>
-      <c r="J135" t="s">
-        <v>234</v>
-      </c>
-      <c r="K135" t="s">
-        <v>5</v>
-      </c>
-      <c r="L135" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M135" t="s">
-        <v>6</v>
-      </c>
-      <c r="N135" t="s">
-        <v>7</v>
-      </c>
-      <c r="O135" t="s">
-        <v>385</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8250,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8259,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F136" t="s">
-        <v>354</v>
+        <v>150</v>
       </c>
       <c r="G136" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H136" s="3">
-        <v>46155</v>
+        <v>46196</v>
       </c>
       <c r="I136" s="3">
-        <v>46178</v>
+        <v>46230</v>
       </c>
       <c r="J136" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8289,7 +8217,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8300,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8309,28 +8237,28 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>353</v>
+        <v>45</v>
       </c>
       <c r="F137" t="s">
-        <v>354</v>
+        <v>46</v>
       </c>
       <c r="G137" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H137" s="3">
-        <v>46155</v>
+        <v>46203</v>
       </c>
       <c r="I137" s="3">
-        <v>46178</v>
+        <v>46225</v>
       </c>
       <c r="J137" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8339,7 +8267,7 @@
         <v>7</v>
       </c>
       <c r="O137" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8350,37 +8278,37 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
+        <v>388</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0</v>
+      </c>
+      <c r="E138" t="s">
+        <v>389</v>
+      </c>
+      <c r="F138" t="s">
         <v>390</v>
       </c>
-      <c r="C138" s="2">
-        <v>1</v>
-      </c>
-      <c r="D138" s="2">
-        <v>0</v>
-      </c>
-      <c r="E138" t="s">
-        <v>353</v>
-      </c>
-      <c r="F138" t="s">
-        <v>354</v>
-      </c>
       <c r="G138" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H138" s="3">
-        <v>46155</v>
+        <v>46282</v>
       </c>
       <c r="I138" s="3">
-        <v>46178</v>
+        <v>46316</v>
       </c>
       <c r="J138" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="K138" t="s">
         <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8389,7 +8317,7 @@
         <v>7</v>
       </c>
       <c r="O138" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="P138" t="s">
         <v>9</v>
@@ -8397,10 +8325,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="B139" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8409,37 +8337,37 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F139" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="G139" s="3">
-        <v>46142</v>
+        <v>46043</v>
       </c>
       <c r="H139" s="3">
-        <v>46189</v>
+        <v>46051</v>
       </c>
       <c r="I139" s="3">
-        <v>46213</v>
+        <v>46057</v>
       </c>
       <c r="J139" t="s">
-        <v>234</v>
+        <v>396</v>
       </c>
       <c r="K139" t="s">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="L139" s="3">
-        <v>46142</v>
+        <v>46043</v>
       </c>
       <c r="M139" t="s">
         <v>6</v>
       </c>
       <c r="N139" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="O139" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8447,10 +8375,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
@@ -8459,37 +8387,37 @@
         <v>0</v>
       </c>
       <c r="E140" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="F140" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="G140" s="3">
-        <v>46142</v>
+        <v>46057</v>
       </c>
       <c r="H140" s="3">
-        <v>46189</v>
+        <v>46076</v>
       </c>
       <c r="I140" s="3">
-        <v>46213</v>
+        <v>46083</v>
       </c>
       <c r="J140" t="s">
-        <v>393</v>
+        <v>13</v>
       </c>
       <c r="K140" t="s">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="L140" s="3">
-        <v>46142</v>
+        <v>46057</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
       </c>
       <c r="N140" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="O140" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8497,10 +8425,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="B141" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C141" s="2">
         <v>1</v>
@@ -8509,37 +8437,37 @@
         <v>0</v>
       </c>
       <c r="E141" t="s">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="F141" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="G141" s="3">
-        <v>46142</v>
+        <v>46114</v>
       </c>
       <c r="H141" s="3">
-        <v>46189</v>
+        <v>46148</v>
       </c>
       <c r="I141" s="3">
-        <v>46213</v>
+        <v>46148</v>
       </c>
       <c r="J141" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="K141" t="s">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="L141" s="3">
-        <v>46142</v>
+        <v>46114</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="O141" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="P141" t="s">
         <v>9</v>
@@ -8547,10 +8475,10 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="B142" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="C142" s="2">
         <v>1</v>
@@ -8559,35 +8487,37 @@
         <v>0</v>
       </c>
       <c r="E142" t="s">
-        <v>50</v>
+        <v>407</v>
       </c>
       <c r="F142" t="s">
-        <v>51</v>
-      </c>
-      <c r="G142" s="3"/>
+        <v>408</v>
+      </c>
+      <c r="G142" s="3">
+        <v>46135</v>
+      </c>
       <c r="H142" s="3">
-        <v>46206</v>
+        <v>46135</v>
       </c>
       <c r="I142" s="3">
-        <v>46225</v>
+        <v>46147</v>
       </c>
       <c r="J142" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="K142" t="s">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="L142" s="3">
-        <v>46148</v>
+        <v>46135</v>
       </c>
       <c r="M142" t="s">
         <v>6</v>
       </c>
       <c r="N142" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="O142" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P142" t="s">
         <v>9</v>
@@ -8595,545 +8525,51 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="B143" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" s="2">
+        <v>1</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" t="s">
+        <v>411</v>
+      </c>
+      <c r="F143" t="s">
+        <v>412</v>
+      </c>
+      <c r="G143" s="3">
+        <v>46140</v>
+      </c>
+      <c r="H143" s="3">
+        <v>46140</v>
+      </c>
+      <c r="I143" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J143" t="s">
+        <v>276</v>
+      </c>
+      <c r="K143" t="s">
+        <v>397</v>
+      </c>
+      <c r="L143" s="3">
+        <v>46140</v>
+      </c>
+      <c r="M143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="O143" t="s">
         <v>399</v>
       </c>
-      <c r="F143" t="s">
-        <v>400</v>
-      </c>
-      <c r="G143" s="3">
-        <v>46148</v>
-      </c>
-      <c r="H143" s="3">
-        <v>46175</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46241</v>
-      </c>
-      <c r="J143" t="s">
-        <v>321</v>
-      </c>
-      <c r="K143" t="s">
-        <v>5</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M143" t="s">
-        <v>6</v>
-      </c>
-      <c r="N143" t="s">
-        <v>7</v>
-      </c>
-      <c r="O143" t="s">
-        <v>401</v>
-      </c>
       <c r="P143" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16">
-      <c r="A144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" t="s">
-        <v>402</v>
-      </c>
-      <c r="C144" s="2">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2">
-        <v>0</v>
-      </c>
-      <c r="E144" t="s">
-        <v>115</v>
-      </c>
-      <c r="F144" t="s">
-        <v>116</v>
-      </c>
-      <c r="G144" s="3">
-        <v>46148</v>
-      </c>
-      <c r="H144" s="3">
-        <v>46267</v>
-      </c>
-      <c r="I144" s="3">
-        <v>46353</v>
-      </c>
-      <c r="J144" t="s">
-        <v>321</v>
-      </c>
-      <c r="K144" t="s">
-        <v>5</v>
-      </c>
-      <c r="L144" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M144" t="s">
-        <v>6</v>
-      </c>
-      <c r="N144" t="s">
-        <v>7</v>
-      </c>
-      <c r="O144" t="s">
-        <v>403</v>
-      </c>
-      <c r="P144" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16">
-      <c r="A145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" t="s">
-        <v>404</v>
-      </c>
-      <c r="C145" s="2">
-        <v>1</v>
-      </c>
-      <c r="D145" s="2">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
-        <v>155</v>
-      </c>
-      <c r="F145" t="s">
-        <v>156</v>
-      </c>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3">
-        <v>46196</v>
-      </c>
-      <c r="I145" s="3">
-        <v>46230</v>
-      </c>
-      <c r="J145" t="s">
-        <v>396</v>
-      </c>
-      <c r="K145" t="s">
-        <v>5</v>
-      </c>
-      <c r="L145" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M145" t="s">
-        <v>6</v>
-      </c>
-      <c r="N145" t="s">
-        <v>7</v>
-      </c>
-      <c r="O145" t="s">
-        <v>405</v>
-      </c>
-      <c r="P145" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16">
-      <c r="A146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B146" t="s">
-        <v>406</v>
-      </c>
-      <c r="C146" s="2">
-        <v>1</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>45</v>
-      </c>
-      <c r="F146" t="s">
-        <v>46</v>
-      </c>
-      <c r="G146" s="3"/>
-      <c r="H146" s="3">
-        <v>46203</v>
-      </c>
-      <c r="I146" s="3">
-        <v>46225</v>
-      </c>
-      <c r="J146" t="s">
-        <v>396</v>
-      </c>
-      <c r="K146" t="s">
-        <v>5</v>
-      </c>
-      <c r="L146" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M146" t="s">
-        <v>6</v>
-      </c>
-      <c r="N146" t="s">
-        <v>7</v>
-      </c>
-      <c r="O146" t="s">
-        <v>407</v>
-      </c>
-      <c r="P146" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16">
-      <c r="A147" t="s">
-        <v>0</v>
-      </c>
-      <c r="B147" t="s">
-        <v>408</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>409</v>
-      </c>
-      <c r="F147" t="s">
-        <v>410</v>
-      </c>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3">
-        <v>46282</v>
-      </c>
-      <c r="I147" s="3">
-        <v>46316</v>
-      </c>
-      <c r="J147" t="s">
-        <v>411</v>
-      </c>
-      <c r="K147" t="s">
-        <v>5</v>
-      </c>
-      <c r="L147" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M147" t="s">
-        <v>6</v>
-      </c>
-      <c r="N147" t="s">
-        <v>7</v>
-      </c>
-      <c r="O147" t="s">
-        <v>412</v>
-      </c>
-      <c r="P147" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16">
-      <c r="A148" t="s">
-        <v>413</v>
-      </c>
-      <c r="B148" t="s">
-        <v>414</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2">
-        <v>0</v>
-      </c>
-      <c r="E148" t="s">
-        <v>415</v>
-      </c>
-      <c r="F148" t="s">
-        <v>416</v>
-      </c>
-      <c r="G148" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H148" s="3">
-        <v>46051</v>
-      </c>
-      <c r="I148" s="3">
-        <v>46057</v>
-      </c>
-      <c r="J148" t="s">
-        <v>393</v>
-      </c>
-      <c r="K148" t="s">
-        <v>417</v>
-      </c>
-      <c r="L148" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M148" t="s">
-        <v>6</v>
-      </c>
-      <c r="N148" t="s">
-        <v>418</v>
-      </c>
-      <c r="O148" t="s">
-        <v>419</v>
-      </c>
-      <c r="P148" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16">
-      <c r="A149" t="s">
-        <v>413</v>
-      </c>
-      <c r="B149" t="s">
-        <v>420</v>
-      </c>
-      <c r="C149" s="2">
-        <v>1</v>
-      </c>
-      <c r="D149" s="2">
-        <v>0</v>
-      </c>
-      <c r="E149" t="s">
-        <v>421</v>
-      </c>
-      <c r="F149" t="s">
-        <v>422</v>
-      </c>
-      <c r="G149" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H149" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I149" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J149" t="s">
-        <v>13</v>
-      </c>
-      <c r="K149" t="s">
-        <v>417</v>
-      </c>
-      <c r="L149" s="3">
-        <v>46057</v>
-      </c>
-      <c r="M149" t="s">
-        <v>6</v>
-      </c>
-      <c r="N149" t="s">
-        <v>418</v>
-      </c>
-      <c r="O149" t="s">
-        <v>419</v>
-      </c>
-      <c r="P149" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16">
-      <c r="A150" t="s">
-        <v>413</v>
-      </c>
-      <c r="B150" t="s">
-        <v>423</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>424</v>
-      </c>
-      <c r="F150" t="s">
-        <v>425</v>
-      </c>
-      <c r="G150" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H150" s="3">
-        <v>46148</v>
-      </c>
-      <c r="I150" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J150" t="s">
-        <v>296</v>
-      </c>
-      <c r="K150" t="s">
-        <v>417</v>
-      </c>
-      <c r="L150" s="3">
-        <v>46114</v>
-      </c>
-      <c r="M150" t="s">
-        <v>6</v>
-      </c>
-      <c r="N150" t="s">
-        <v>418</v>
-      </c>
-      <c r="O150" t="s">
-        <v>419</v>
-      </c>
-      <c r="P150" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16">
-      <c r="A151" t="s">
-        <v>413</v>
-      </c>
-      <c r="B151" t="s">
-        <v>426</v>
-      </c>
-      <c r="C151" s="2">
-        <v>1</v>
-      </c>
-      <c r="D151" s="2">
-        <v>1</v>
-      </c>
-      <c r="E151" t="s">
-        <v>427</v>
-      </c>
-      <c r="F151" t="s">
-        <v>428</v>
-      </c>
-      <c r="G151" s="3">
-        <v>46122</v>
-      </c>
-      <c r="H151" s="3">
-        <v>46142</v>
-      </c>
-      <c r="I151" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J151" t="s">
-        <v>429</v>
-      </c>
-      <c r="K151" t="s">
-        <v>417</v>
-      </c>
-      <c r="L151" s="3">
-        <v>46122</v>
-      </c>
-      <c r="M151" t="s">
-        <v>6</v>
-      </c>
-      <c r="N151" t="s">
-        <v>418</v>
-      </c>
-      <c r="O151" t="s">
-        <v>419</v>
-      </c>
-      <c r="P151" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16">
-      <c r="A152" t="s">
-        <v>413</v>
-      </c>
-      <c r="B152" t="s">
-        <v>430</v>
-      </c>
-      <c r="C152" s="2">
-        <v>1</v>
-      </c>
-      <c r="D152" s="2">
-        <v>0</v>
-      </c>
-      <c r="E152" t="s">
-        <v>431</v>
-      </c>
-      <c r="F152" t="s">
-        <v>432</v>
-      </c>
-      <c r="G152" s="3">
-        <v>46135</v>
-      </c>
-      <c r="H152" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I152" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J152" t="s">
-        <v>433</v>
-      </c>
-      <c r="K152" t="s">
-        <v>417</v>
-      </c>
-      <c r="L152" s="3">
-        <v>46135</v>
-      </c>
-      <c r="M152" t="s">
-        <v>6</v>
-      </c>
-      <c r="N152" t="s">
-        <v>418</v>
-      </c>
-      <c r="O152" t="s">
-        <v>419</v>
-      </c>
-      <c r="P152" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16">
-      <c r="A153" t="s">
-        <v>413</v>
-      </c>
-      <c r="B153" t="s">
-        <v>434</v>
-      </c>
-      <c r="C153" s="2">
-        <v>1</v>
-      </c>
-      <c r="D153" s="2">
-        <v>0</v>
-      </c>
-      <c r="E153" t="s">
-        <v>435</v>
-      </c>
-      <c r="F153" t="s">
-        <v>436</v>
-      </c>
-      <c r="G153" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H153" s="3">
-        <v>46140</v>
-      </c>
-      <c r="I153" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J153" t="s">
-        <v>296</v>
-      </c>
-      <c r="K153" t="s">
-        <v>417</v>
-      </c>
-      <c r="L153" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M153" t="s">
-        <v>6</v>
-      </c>
-      <c r="N153" t="s">
-        <v>418</v>
-      </c>
-      <c r="O153" t="s">
-        <v>419</v>
-      </c>
-      <c r="P153" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/成品入庫TECO狀態.XLSX
+++ b/Newdata/成品入庫TECO狀態.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="417">
   <si>
     <t>ZP01</t>
   </si>
@@ -55,7 +55,7 @@
     <t>REL  PCNF PRC  MANC RESA RMWB SETC</t>
   </si>
   <si>
-    <t>1100134140</t>
+    <t>1100194700</t>
   </si>
   <si>
     <t>100002954</t>
@@ -145,7 +145,577 @@
     <t>1300000173</t>
   </si>
   <si>
-    <t>100003316</t>
+    <t>100003323</t>
+  </si>
+  <si>
+    <t>980000013801</t>
+  </si>
+  <si>
+    <t>S-Plus 10_X=1020, Y=520, Z=550</t>
+  </si>
+  <si>
+    <t>1100185500</t>
+  </si>
+  <si>
+    <t>100003324</t>
+  </si>
+  <si>
+    <t>980000024501</t>
+  </si>
+  <si>
+    <t>HSM-560_X=560, Y=430, Z=450</t>
+  </si>
+  <si>
+    <t>1300000185</t>
+  </si>
+  <si>
+    <t>100003345</t>
+  </si>
+  <si>
+    <t>980000016300</t>
+  </si>
+  <si>
+    <t>HCMC-1370_X=1300, Y=700, Z=660</t>
+  </si>
+  <si>
+    <t>1100190880</t>
+  </si>
+  <si>
+    <t>100003346</t>
+  </si>
+  <si>
+    <t>100003360</t>
+  </si>
+  <si>
+    <t>980000036900</t>
+  </si>
+  <si>
+    <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
+  </si>
+  <si>
+    <t>1100170790</t>
+  </si>
+  <si>
+    <t>100003400</t>
+  </si>
+  <si>
+    <t>980000036100</t>
+  </si>
+  <si>
+    <t>5BC-429_X=4M,Y=2.9M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  CSER MANC RESA RMWB*</t>
+  </si>
+  <si>
+    <t>1100172120</t>
+  </si>
+  <si>
+    <t>100003412</t>
+  </si>
+  <si>
+    <t>980000000900</t>
+  </si>
+  <si>
+    <t>MVP-10_X=1050, Y=530, Z=630</t>
+  </si>
+  <si>
+    <t>1300000176</t>
+  </si>
+  <si>
+    <t>100003438</t>
+  </si>
+  <si>
+    <t>4200000001</t>
+  </si>
+  <si>
+    <t>100003449</t>
+  </si>
+  <si>
+    <t>980000017700</t>
+  </si>
+  <si>
+    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100182240</t>
+  </si>
+  <si>
+    <t>100003451</t>
+  </si>
+  <si>
+    <t>980000019200</t>
+  </si>
+  <si>
+    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182450</t>
+  </si>
+  <si>
+    <t>100003460</t>
+  </si>
+  <si>
+    <t>980000019400</t>
+  </si>
+  <si>
+    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100175760</t>
+  </si>
+  <si>
+    <t>100003469</t>
+  </si>
+  <si>
+    <t>1100179090</t>
+  </si>
+  <si>
+    <t>100003470</t>
+  </si>
+  <si>
+    <t>1100182820</t>
+  </si>
+  <si>
+    <t>100003471</t>
+  </si>
+  <si>
+    <t>980000018002</t>
+  </si>
+  <si>
+    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100172880</t>
+  </si>
+  <si>
+    <t>100003472</t>
+  </si>
+  <si>
+    <t>980000030801</t>
+  </si>
+  <si>
+    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
+  </si>
+  <si>
+    <t>1100177910</t>
+  </si>
+  <si>
+    <t>100003473</t>
+  </si>
+  <si>
+    <t>1300000180</t>
+  </si>
+  <si>
+    <t>100003474</t>
+  </si>
+  <si>
+    <t>980000027800</t>
+  </si>
+  <si>
+    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100183180</t>
+  </si>
+  <si>
+    <t>100003475</t>
+  </si>
+  <si>
+    <t>1100184110</t>
+  </si>
+  <si>
+    <t>100003478</t>
+  </si>
+  <si>
+    <t>980000000800</t>
+  </si>
+  <si>
+    <t>PRO-1000_X=1000, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100180510</t>
+  </si>
+  <si>
+    <t>100003481</t>
+  </si>
+  <si>
+    <t>1100184950</t>
+  </si>
+  <si>
+    <t>100003482</t>
+  </si>
+  <si>
+    <t>1100185590</t>
+  </si>
+  <si>
+    <t>100003483</t>
+  </si>
+  <si>
+    <t>1100185600</t>
+  </si>
+  <si>
+    <t>100003488</t>
+  </si>
+  <si>
+    <t>1100185870</t>
+  </si>
+  <si>
+    <t>100003496</t>
+  </si>
+  <si>
+    <t>1300000181</t>
+  </si>
+  <si>
+    <t>100003499</t>
+  </si>
+  <si>
+    <t>980000048000</t>
+  </si>
+  <si>
+    <t>SMC-7_X=700, Y=400, Z=300</t>
+  </si>
+  <si>
+    <t>1100193980</t>
+  </si>
+  <si>
+    <t>100003504</t>
+  </si>
+  <si>
+    <t>980000034600</t>
+  </si>
+  <si>
+    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100178530</t>
+  </si>
+  <si>
+    <t>100003505</t>
+  </si>
+  <si>
+    <t>980000013400</t>
+  </si>
+  <si>
+    <t>VW-7340_X=7050, Y=3400, Z=700</t>
+  </si>
+  <si>
+    <t>1100188040</t>
+  </si>
+  <si>
+    <t>100003507</t>
+  </si>
+  <si>
+    <t>980000045400</t>
+  </si>
+  <si>
+    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
+  </si>
+  <si>
+    <t>1100188370</t>
+  </si>
+  <si>
+    <t>100003508</t>
+  </si>
+  <si>
+    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100185550</t>
+  </si>
+  <si>
+    <t>100003510</t>
+  </si>
+  <si>
+    <t>980000022400</t>
+  </si>
+  <si>
+    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100185810</t>
+  </si>
+  <si>
+    <t>100003511</t>
+  </si>
+  <si>
+    <t>980000028700</t>
+  </si>
+  <si>
+    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182140</t>
+  </si>
+  <si>
+    <t>100003513</t>
+  </si>
+  <si>
+    <t>980000028600</t>
+  </si>
+  <si>
+    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
+  </si>
+  <si>
+    <t>1100182130</t>
+  </si>
+  <si>
+    <t>100003514</t>
+  </si>
+  <si>
+    <t>980000017001</t>
+  </si>
+  <si>
+    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182120</t>
+  </si>
+  <si>
+    <t>100003516</t>
+  </si>
+  <si>
+    <t>980000017201</t>
+  </si>
+  <si>
+    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
+  </si>
+  <si>
+    <t>1100182570</t>
+  </si>
+  <si>
+    <t>100003520</t>
+  </si>
+  <si>
+    <t>1100186590</t>
+  </si>
+  <si>
+    <t>100003525</t>
+  </si>
+  <si>
+    <t>980000044600</t>
+  </si>
+  <si>
+    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100190220</t>
+  </si>
+  <si>
+    <t>100003526</t>
+  </si>
+  <si>
+    <t>1100190240</t>
+  </si>
+  <si>
+    <t>100003528</t>
+  </si>
+  <si>
+    <t>1100190870</t>
+  </si>
+  <si>
+    <t>100003529</t>
+  </si>
+  <si>
+    <t>100003532</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM SETC</t>
+  </si>
+  <si>
+    <t>1100190890</t>
+  </si>
+  <si>
+    <t>100003533</t>
+  </si>
+  <si>
+    <t>REL  PRC  MACM RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003534</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MACM RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190900</t>
+  </si>
+  <si>
+    <t>100003535</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100190910</t>
+  </si>
+  <si>
+    <t>100003536</t>
+  </si>
+  <si>
+    <t>1100190920</t>
+  </si>
+  <si>
+    <t>100003537</t>
+  </si>
+  <si>
+    <t>1100190930</t>
+  </si>
+  <si>
+    <t>100003542</t>
+  </si>
+  <si>
+    <t>980000048100</t>
+  </si>
+  <si>
+    <t>5A-350XL_X=650, Y=610, Z=510</t>
+  </si>
+  <si>
+    <t>1100191210</t>
+  </si>
+  <si>
+    <t>100003543</t>
+  </si>
+  <si>
+    <t>1100191250</t>
+  </si>
+  <si>
+    <t>100003544</t>
+  </si>
+  <si>
+    <t>100003545</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100191260</t>
+  </si>
+  <si>
+    <t>100003546</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  MANC SETC</t>
+  </si>
+  <si>
+    <t>100003547</t>
+  </si>
+  <si>
+    <t>1100191270</t>
+  </si>
+  <si>
+    <t>100003548</t>
+  </si>
+  <si>
+    <t>100003549</t>
+  </si>
+  <si>
+    <t>980000017600</t>
+  </si>
+  <si>
+    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
+  </si>
+  <si>
+    <t>1100186250</t>
+  </si>
+  <si>
+    <t>100003550</t>
+  </si>
+  <si>
+    <t>100003551</t>
+  </si>
+  <si>
+    <t>100003552</t>
+  </si>
+  <si>
+    <t>100003553</t>
+  </si>
+  <si>
+    <t>980000018800</t>
+  </si>
+  <si>
+    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100171080</t>
+  </si>
+  <si>
+    <t>100003558</t>
+  </si>
+  <si>
+    <t>980000018600</t>
+  </si>
+  <si>
+    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
+  </si>
+  <si>
+    <t>1100185560</t>
+  </si>
+  <si>
+    <t>100003559</t>
+  </si>
+  <si>
+    <t>1100190960</t>
+  </si>
+  <si>
+    <t>100003560</t>
+  </si>
+  <si>
+    <t>980000023300</t>
+  </si>
+  <si>
+    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
+  </si>
+  <si>
+    <t>1100189660</t>
+  </si>
+  <si>
+    <t>100003561</t>
+  </si>
+  <si>
+    <t>980000027600</t>
+  </si>
+  <si>
+    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>1100189730</t>
+  </si>
+  <si>
+    <t>100003562</t>
+  </si>
+  <si>
+    <t>980000037701</t>
+  </si>
+  <si>
+    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100191710</t>
+  </si>
+  <si>
+    <t>100003563</t>
+  </si>
+  <si>
+    <t>980000032501</t>
+  </si>
+  <si>
+    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>REL  PCNF PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100184050</t>
+  </si>
+  <si>
+    <t>100003564</t>
   </si>
   <si>
     <t>980000046000</t>
@@ -154,148 +724,106 @@
     <t>LG-1570 NEO_X=1500, Y=700, Z=650</t>
   </si>
   <si>
-    <t>REL  MSPT PCNF DLV  PRC  MANC RESA RMWB*</t>
-  </si>
-  <si>
-    <t>1100190750</t>
-  </si>
-  <si>
-    <t>100003323</t>
-  </si>
-  <si>
-    <t>980000013801</t>
-  </si>
-  <si>
-    <t>S-Plus 10_X=1020, Y=520, Z=550</t>
-  </si>
-  <si>
-    <t>1100185500</t>
-  </si>
-  <si>
-    <t>100003324</t>
-  </si>
-  <si>
-    <t>980000024501</t>
-  </si>
-  <si>
-    <t>HSM-560_X=560, Y=430, Z=450</t>
-  </si>
-  <si>
-    <t>1300000185</t>
-  </si>
-  <si>
-    <t>100003345</t>
-  </si>
-  <si>
-    <t>980000016300</t>
-  </si>
-  <si>
-    <t>HCMC-1370_X=1300, Y=700, Z=660</t>
-  </si>
-  <si>
-    <t>1100190880</t>
-  </si>
-  <si>
-    <t>100003346</t>
-  </si>
-  <si>
-    <t>100003360</t>
-  </si>
-  <si>
-    <t>980000036900</t>
-  </si>
-  <si>
-    <t>5BC-638_X=6M,Y=3.8M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  MANC MSCP RESA RMWB*</t>
-  </si>
-  <si>
-    <t>1100170790</t>
-  </si>
-  <si>
-    <t>100003400</t>
-  </si>
-  <si>
-    <t>980000036100</t>
-  </si>
-  <si>
-    <t>5BC-429_X=4M,Y=2.9M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  CSER MANC RESA RMWB*</t>
-  </si>
-  <si>
-    <t>1100172120</t>
-  </si>
-  <si>
-    <t>100003410</t>
-  </si>
-  <si>
-    <t>980000022800</t>
-  </si>
-  <si>
-    <t>HSA-428EAY_X=4M, Y=3.6M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100177770</t>
-  </si>
-  <si>
-    <t>100003412</t>
-  </si>
-  <si>
-    <t>980000000900</t>
-  </si>
-  <si>
-    <t>MVP-10_X=1050, Y=530, Z=630</t>
-  </si>
-  <si>
-    <t>1300000176</t>
-  </si>
-  <si>
-    <t>100003438</t>
-  </si>
-  <si>
-    <t>4200000001</t>
-  </si>
-  <si>
-    <t>100003449</t>
-  </si>
-  <si>
-    <t>980000017700</t>
-  </si>
-  <si>
-    <t>HCMC-2082_X=2060, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100182240</t>
-  </si>
-  <si>
-    <t>100003451</t>
-  </si>
-  <si>
-    <t>980000019200</t>
-  </si>
-  <si>
-    <t>SW-423_X=4000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182450</t>
-  </si>
-  <si>
-    <t>100003460</t>
-  </si>
-  <si>
-    <t>980000019400</t>
-  </si>
-  <si>
-    <t>SW-623_X=6000, Y=2300, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100175760</t>
-  </si>
-  <si>
-    <t>100003465</t>
+    <t>1100192160</t>
+  </si>
+  <si>
+    <t>100003568</t>
+  </si>
+  <si>
+    <t>980000041900</t>
+  </si>
+  <si>
+    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1300000184</t>
+  </si>
+  <si>
+    <t>100003572</t>
+  </si>
+  <si>
+    <t>1100192930</t>
+  </si>
+  <si>
+    <t>100003573</t>
+  </si>
+  <si>
+    <t>100003574</t>
+  </si>
+  <si>
+    <t>100003575</t>
+  </si>
+  <si>
+    <t>1100192830</t>
+  </si>
+  <si>
+    <t>100003576</t>
+  </si>
+  <si>
+    <t>100003577</t>
+  </si>
+  <si>
+    <t>100003578</t>
+  </si>
+  <si>
+    <t>REL  PRC  MANC RMWB SETC</t>
+  </si>
+  <si>
+    <t>100003579</t>
+  </si>
+  <si>
+    <t>100003580</t>
+  </si>
+  <si>
+    <t>100003585</t>
+  </si>
+  <si>
+    <t>980000036300</t>
+  </si>
+  <si>
+    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
+  </si>
+  <si>
+    <t>1100178040</t>
+  </si>
+  <si>
+    <t>100003587</t>
+  </si>
+  <si>
+    <t>1100193830</t>
+  </si>
+  <si>
+    <t>100003590</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  CSER MANC SETC</t>
+  </si>
+  <si>
+    <t>1100193820</t>
+  </si>
+  <si>
+    <t>100003592</t>
+  </si>
+  <si>
+    <t>1100178390</t>
+  </si>
+  <si>
+    <t>100003593</t>
+  </si>
+  <si>
+    <t>980000022901</t>
+  </si>
+  <si>
+    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
+  </si>
+  <si>
+    <t>1100193130</t>
+  </si>
+  <si>
+    <t>100003594</t>
   </si>
   <si>
     <t>980000013700</t>
@@ -304,822 +832,222 @@
     <t>S-Plus 8_X=800, Y=520, Z=550</t>
   </si>
   <si>
-    <t>1100177930</t>
-  </si>
-  <si>
-    <t>100003468</t>
-  </si>
-  <si>
-    <t>980000045000</t>
-  </si>
-  <si>
-    <t>TGV-106_X=1000, Y=600, Z=510</t>
-  </si>
-  <si>
-    <t>1100182880</t>
-  </si>
-  <si>
-    <t>100003469</t>
-  </si>
-  <si>
-    <t>1100179090</t>
-  </si>
-  <si>
-    <t>100003470</t>
-  </si>
-  <si>
-    <t>1100182820</t>
-  </si>
-  <si>
-    <t>100003471</t>
-  </si>
-  <si>
-    <t>980000018002</t>
-  </si>
-  <si>
-    <t>HCMC-2110_X=2100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100172880</t>
-  </si>
-  <si>
-    <t>100003472</t>
-  </si>
-  <si>
-    <t>980000030801</t>
-  </si>
-  <si>
-    <t>PBM-135C_X=3/4, Y=2/2.5, Z=1.5/2 M</t>
-  </si>
-  <si>
-    <t>1100177910</t>
-  </si>
-  <si>
-    <t>100003473</t>
-  </si>
-  <si>
-    <t>1300000180</t>
-  </si>
-  <si>
-    <t>100003474</t>
-  </si>
-  <si>
-    <t>980000027800</t>
-  </si>
-  <si>
-    <t>MVP-16, #50_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>1100183180</t>
-  </si>
-  <si>
-    <t>100003475</t>
-  </si>
-  <si>
-    <t>1100184110</t>
-  </si>
-  <si>
-    <t>100003478</t>
-  </si>
-  <si>
-    <t>980000000800</t>
-  </si>
-  <si>
-    <t>PRO-1000_X=1000, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>1100180510</t>
-  </si>
-  <si>
-    <t>100003481</t>
-  </si>
-  <si>
-    <t>1100184950</t>
-  </si>
-  <si>
-    <t>100003482</t>
-  </si>
-  <si>
-    <t>1100185590</t>
-  </si>
-  <si>
-    <t>100003483</t>
-  </si>
-  <si>
-    <t>1100185600</t>
-  </si>
-  <si>
-    <t>100003488</t>
-  </si>
-  <si>
-    <t>1100185870</t>
-  </si>
-  <si>
-    <t>100003496</t>
-  </si>
-  <si>
-    <t>1300000181</t>
-  </si>
-  <si>
-    <t>100003499</t>
-  </si>
-  <si>
-    <t>980000048000</t>
-  </si>
-  <si>
-    <t>SMC-7_X=700, Y=400, Z=300</t>
-  </si>
-  <si>
-    <t>1100193980</t>
-  </si>
-  <si>
-    <t>100003504</t>
-  </si>
-  <si>
-    <t>980000034600</t>
-  </si>
-  <si>
-    <t>HSA-832EAY_X=8M,Y=4M ,Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100178530</t>
-  </si>
-  <si>
-    <t>100003505</t>
-  </si>
-  <si>
-    <t>980000013400</t>
-  </si>
-  <si>
-    <t>VW-7340_X=7050, Y=3400, Z=700</t>
-  </si>
-  <si>
-    <t>1100188040</t>
-  </si>
-  <si>
-    <t>100003507</t>
-  </si>
-  <si>
-    <t>980000045400</t>
-  </si>
-  <si>
-    <t>HCMC-1365, #40_X=1300, Y=650, Z=630</t>
-  </si>
-  <si>
-    <t>1100188370</t>
-  </si>
-  <si>
-    <t>100003508</t>
+    <t>1100194400</t>
+  </si>
+  <si>
+    <t>100003595</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  RESA RMWB SETC</t>
+  </si>
+  <si>
+    <t>1100193850</t>
+  </si>
+  <si>
+    <t>100003596</t>
+  </si>
+  <si>
+    <t>100003597</t>
   </si>
   <si>
     <t>REL  MSPT PRC  RMWB SETC</t>
   </si>
   <si>
-    <t>1100185550</t>
-  </si>
-  <si>
-    <t>100003510</t>
-  </si>
-  <si>
-    <t>980000022400</t>
-  </si>
-  <si>
-    <t>HSA-427EAY_X=4M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100185810</t>
-  </si>
-  <si>
-    <t>100003511</t>
-  </si>
-  <si>
-    <t>980000028700</t>
-  </si>
-  <si>
-    <t>SW-316_X=3100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182140</t>
-  </si>
-  <si>
-    <t>100003513</t>
-  </si>
-  <si>
-    <t>980000028600</t>
-  </si>
-  <si>
-    <t>SW-216_X=2100, Y=1600, Z=780/1070</t>
-  </si>
-  <si>
-    <t>1100182130</t>
-  </si>
-  <si>
-    <t>100003514</t>
-  </si>
-  <si>
-    <t>980000017001</t>
-  </si>
-  <si>
-    <t>HSA-3212_X=3250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182120</t>
-  </si>
-  <si>
-    <t>100003516</t>
-  </si>
-  <si>
-    <t>980000017201</t>
-  </si>
-  <si>
-    <t>HSA-2212_X=2250, Y=1200, Z=780</t>
-  </si>
-  <si>
-    <t>1100182570</t>
-  </si>
-  <si>
-    <t>100003520</t>
-  </si>
-  <si>
-    <t>1100186590</t>
-  </si>
-  <si>
-    <t>100003521</t>
-  </si>
-  <si>
-    <t>980000000100</t>
-  </si>
-  <si>
-    <t>MVP-8_X=860, Y=530, Z=630</t>
-  </si>
-  <si>
-    <t>1100180520</t>
-  </si>
-  <si>
-    <t>100003522</t>
-  </si>
-  <si>
-    <t>1100187480</t>
-  </si>
-  <si>
-    <t>100003525</t>
-  </si>
-  <si>
-    <t>980000044600</t>
-  </si>
-  <si>
-    <t>5A-40R/5X_X=410, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100190220</t>
-  </si>
-  <si>
-    <t>100003526</t>
-  </si>
-  <si>
-    <t>1100190240</t>
-  </si>
-  <si>
-    <t>100003528</t>
-  </si>
-  <si>
-    <t>1100190870</t>
-  </si>
-  <si>
-    <t>100003529</t>
-  </si>
-  <si>
-    <t>100003532</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM SETC</t>
-  </si>
-  <si>
-    <t>1100190890</t>
-  </si>
-  <si>
-    <t>100003533</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003534</t>
-  </si>
-  <si>
-    <t>REL  PRC  MACM RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190900</t>
-  </si>
-  <si>
-    <t>100003535</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100190910</t>
-  </si>
-  <si>
-    <t>100003536</t>
-  </si>
-  <si>
-    <t>1100190920</t>
-  </si>
-  <si>
-    <t>100003537</t>
-  </si>
-  <si>
-    <t>1100190930</t>
-  </si>
-  <si>
-    <t>100003542</t>
-  </si>
-  <si>
-    <t>980000048100</t>
-  </si>
-  <si>
-    <t>5A-350XL_X=650, Y=610, Z=510</t>
-  </si>
-  <si>
-    <t>1100191210</t>
-  </si>
-  <si>
-    <t>100003543</t>
-  </si>
-  <si>
-    <t>1100191250</t>
-  </si>
-  <si>
-    <t>100003544</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003545</t>
-  </si>
-  <si>
-    <t>1100191260</t>
-  </si>
-  <si>
-    <t>100003546</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  MANC SETC</t>
-  </si>
-  <si>
-    <t>100003547</t>
-  </si>
-  <si>
-    <t>1100191270</t>
-  </si>
-  <si>
-    <t>100003548</t>
-  </si>
-  <si>
-    <t>100003549</t>
-  </si>
-  <si>
-    <t>980000017600</t>
-  </si>
-  <si>
-    <t>HCMC-1682_X=1600, Y=820, Z=660/820</t>
-  </si>
-  <si>
-    <t>1100186250</t>
-  </si>
-  <si>
-    <t>100003550</t>
-  </si>
-  <si>
-    <t>100003551</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RESA RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003552</t>
-  </si>
-  <si>
-    <t>100003553</t>
-  </si>
-  <si>
-    <t>980000018800</t>
-  </si>
-  <si>
-    <t>HSA-627_X=6000,Y=2700,Z=780/1070/1200</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100171080</t>
-  </si>
-  <si>
-    <t>100003558</t>
-  </si>
-  <si>
-    <t>980000018600</t>
-  </si>
-  <si>
-    <t>HSA-427_X=4000,Y=2700,Z=780/1070/1200</t>
+    <t>100003598</t>
+  </si>
+  <si>
+    <t>REL  MSPT PRC  SETC</t>
+  </si>
+  <si>
+    <t>1100193860</t>
+  </si>
+  <si>
+    <t>100003599</t>
+  </si>
+  <si>
+    <t>100003600</t>
+  </si>
+  <si>
+    <t>980000045100</t>
+  </si>
+  <si>
+    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
+  </si>
+  <si>
+    <t>1100191950</t>
+  </si>
+  <si>
+    <t>100003601</t>
+  </si>
+  <si>
+    <t>1100183290</t>
+  </si>
+  <si>
+    <t>100003602</t>
+  </si>
+  <si>
+    <t>1100194940</t>
+  </si>
+  <si>
+    <t>100003603</t>
+  </si>
+  <si>
+    <t>100003604</t>
+  </si>
+  <si>
+    <t>1100194930</t>
+  </si>
+  <si>
+    <t>100003605</t>
+  </si>
+  <si>
+    <t>980000013300</t>
+  </si>
+  <si>
+    <t>LG-1370_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100194670</t>
+  </si>
+  <si>
+    <t>100003606</t>
+  </si>
+  <si>
+    <t>1100195420</t>
+  </si>
+  <si>
+    <t>100003607</t>
+  </si>
+  <si>
+    <t>1100195960</t>
+  </si>
+  <si>
+    <t>100003608</t>
+  </si>
+  <si>
+    <t>980000001101</t>
+  </si>
+  <si>
+    <t>LG-1000_X=1000, Y=510, Z=630</t>
+  </si>
+  <si>
+    <t>1100195080</t>
+  </si>
+  <si>
+    <t>100003609</t>
+  </si>
+  <si>
+    <t>100003610</t>
+  </si>
+  <si>
+    <t>980000005501</t>
+  </si>
+  <si>
+    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
+  </si>
+  <si>
+    <t>1100187490</t>
+  </si>
+  <si>
+    <t>100003611</t>
+  </si>
+  <si>
+    <t>980000036400</t>
+  </si>
+  <si>
+    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
+  </si>
+  <si>
+    <t>1100195950</t>
+  </si>
+  <si>
+    <t>100003612</t>
+  </si>
+  <si>
+    <t>1100195920</t>
+  </si>
+  <si>
+    <t>100003613</t>
+  </si>
+  <si>
+    <t>980000043300</t>
+  </si>
+  <si>
+    <t>HSA-216, #50_X=2250, Y=1600, Z=780</t>
+  </si>
+  <si>
+    <t>1100193540</t>
+  </si>
+  <si>
+    <t>100003614</t>
+  </si>
+  <si>
+    <t>1100196310</t>
+  </si>
+  <si>
+    <t>100003616</t>
+  </si>
+  <si>
+    <t>1100194450</t>
+  </si>
+  <si>
+    <t>100003617</t>
+  </si>
+  <si>
+    <t>1100194550</t>
+  </si>
+  <si>
+    <t>100003618</t>
+  </si>
+  <si>
+    <t>1100197010</t>
+  </si>
+  <si>
+    <t>100003619</t>
+  </si>
+  <si>
+    <t>1100197020</t>
+  </si>
+  <si>
+    <t>100003620</t>
+  </si>
+  <si>
+    <t>1100191150</t>
+  </si>
+  <si>
+    <t>100003621</t>
+  </si>
+  <si>
+    <t>1100197580</t>
+  </si>
+  <si>
+    <t>100003622</t>
+  </si>
+  <si>
+    <t>1100197240</t>
+  </si>
+  <si>
+    <t>100003623</t>
+  </si>
+  <si>
+    <t>980000043500</t>
+  </si>
+  <si>
+    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
   </si>
   <si>
     <t>REL  MSPT PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>1100185560</t>
-  </si>
-  <si>
-    <t>100003559</t>
-  </si>
-  <si>
-    <t>1100190960</t>
-  </si>
-  <si>
-    <t>100003560</t>
-  </si>
-  <si>
-    <t>980000023300</t>
-  </si>
-  <si>
-    <t>HMC-10_X=1300, Y=1000, Z=1150</t>
-  </si>
-  <si>
-    <t>1100189660</t>
-  </si>
-  <si>
-    <t>100003561</t>
-  </si>
-  <si>
-    <t>980000027600</t>
-  </si>
-  <si>
-    <t>HSA-327EAY_X=3M, Y=3.5M, Z=1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>LUMI</t>
-  </si>
-  <si>
-    <t>1100189730</t>
-  </si>
-  <si>
-    <t>100003562</t>
-  </si>
-  <si>
-    <t>980000037701</t>
-  </si>
-  <si>
-    <t>HSA-546AAC_X=5M,Y=4.6M,Z=1.0/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>1100191710</t>
-  </si>
-  <si>
-    <t>100003563</t>
-  </si>
-  <si>
-    <t>980000032501</t>
-  </si>
-  <si>
-    <t>HSA-420,#50_X4M,Y2M ,Z0.78/1/1.2/1.4M</t>
-  </si>
-  <si>
-    <t>REL  PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100184050</t>
-  </si>
-  <si>
-    <t>100003564</t>
+    <t>1100191070</t>
+  </si>
+  <si>
+    <t>100003624</t>
   </si>
   <si>
     <t>REL  MSPT PRC  MANC RMWB SETC</t>
   </si>
   <si>
-    <t>1100192160</t>
-  </si>
-  <si>
-    <t>100003568</t>
-  </si>
-  <si>
-    <t>980000041900</t>
-  </si>
-  <si>
-    <t>5A-95Q/5X_X=950, Y=850, Z=650</t>
-  </si>
-  <si>
-    <t>1300000184</t>
-  </si>
-  <si>
-    <t>100003572</t>
-  </si>
-  <si>
-    <t>1100192930</t>
-  </si>
-  <si>
-    <t>100003573</t>
-  </si>
-  <si>
-    <t>100003574</t>
-  </si>
-  <si>
-    <t>100003575</t>
-  </si>
-  <si>
-    <t>1100192830</t>
-  </si>
-  <si>
-    <t>100003576</t>
-  </si>
-  <si>
-    <t>100003577</t>
-  </si>
-  <si>
-    <t>100003578</t>
-  </si>
-  <si>
-    <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>100003579</t>
-  </si>
-  <si>
-    <t>100003580</t>
-  </si>
-  <si>
-    <t>100003585</t>
-  </si>
-  <si>
-    <t>980000036300</t>
-  </si>
-  <si>
-    <t>HCMC-1100, #50_X=1100, Y=600, Z=630</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  CSER MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100178040</t>
-  </si>
-  <si>
-    <t>100003587</t>
-  </si>
-  <si>
-    <t>1100193830</t>
-  </si>
-  <si>
-    <t>100003590</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  CSER MANC SETC</t>
-  </si>
-  <si>
-    <t>1100193820</t>
-  </si>
-  <si>
-    <t>100003592</t>
-  </si>
-  <si>
-    <t>1100178390</t>
-  </si>
-  <si>
-    <t>100003593</t>
-  </si>
-  <si>
-    <t>980000022901</t>
-  </si>
-  <si>
-    <t>MVP-16, #40_X=1600, Y=820, Z=700</t>
-  </si>
-  <si>
-    <t>1100193130</t>
-  </si>
-  <si>
-    <t>100003594</t>
-  </si>
-  <si>
-    <t>1100194400</t>
-  </si>
-  <si>
-    <t>100003595</t>
-  </si>
-  <si>
-    <t>1100193850</t>
-  </si>
-  <si>
-    <t>100003596</t>
-  </si>
-  <si>
-    <t>100003597</t>
-  </si>
-  <si>
-    <t>100003598</t>
-  </si>
-  <si>
-    <t>REL  MSPT PRC  SETC</t>
-  </si>
-  <si>
-    <t>1100193860</t>
-  </si>
-  <si>
-    <t>100003599</t>
-  </si>
-  <si>
-    <t>100003600</t>
-  </si>
-  <si>
-    <t>980000045100</t>
-  </si>
-  <si>
-    <t>HCMC-3110_X=3100, Y=1020, Z=820</t>
-  </si>
-  <si>
-    <t>1100191950</t>
-  </si>
-  <si>
-    <t>100003601</t>
-  </si>
-  <si>
-    <t>1100183290</t>
-  </si>
-  <si>
-    <t>100003602</t>
-  </si>
-  <si>
-    <t>1100194940</t>
-  </si>
-  <si>
-    <t>100003603</t>
-  </si>
-  <si>
-    <t>100003604</t>
-  </si>
-  <si>
-    <t>REL  MSPT PCNF PRC  RMWB SETC</t>
-  </si>
-  <si>
-    <t>1100194930</t>
-  </si>
-  <si>
-    <t>100003605</t>
-  </si>
-  <si>
-    <t>980000013300</t>
-  </si>
-  <si>
-    <t>LG-1370_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100194670</t>
-  </si>
-  <si>
-    <t>100003606</t>
-  </si>
-  <si>
-    <t>1100195420</t>
-  </si>
-  <si>
-    <t>100003607</t>
-  </si>
-  <si>
-    <t>1100195960</t>
-  </si>
-  <si>
-    <t>100003608</t>
-  </si>
-  <si>
-    <t>980000001101</t>
-  </si>
-  <si>
-    <t>LG-1000_X=1000, Y=510, Z=630</t>
-  </si>
-  <si>
-    <t>1100195080</t>
-  </si>
-  <si>
-    <t>100003609</t>
-  </si>
-  <si>
-    <t>100003610</t>
-  </si>
-  <si>
-    <t>980000005501</t>
-  </si>
-  <si>
-    <t>MVP-13, #40_X=1300, Y=700, Z=650</t>
-  </si>
-  <si>
-    <t>1100187490</t>
-  </si>
-  <si>
-    <t>100003611</t>
-  </si>
-  <si>
-    <t>980000036400</t>
-  </si>
-  <si>
-    <t>MVP-11, #40_X=1100 , Y=600 , Z=630</t>
-  </si>
-  <si>
-    <t>1100195950</t>
-  </si>
-  <si>
-    <t>100003612</t>
-  </si>
-  <si>
-    <t>1100195920</t>
-  </si>
-  <si>
-    <t>100003613</t>
-  </si>
-  <si>
-    <t>980000043300</t>
-  </si>
-  <si>
-    <t>HSA-216, #50_X=2250, Y=1600, Z=780</t>
-  </si>
-  <si>
-    <t>1100193540</t>
-  </si>
-  <si>
-    <t>100003614</t>
-  </si>
-  <si>
-    <t>1100196310</t>
-  </si>
-  <si>
-    <t>100003615</t>
-  </si>
-  <si>
-    <t>980000008401</t>
-  </si>
-  <si>
-    <t>LG-500_X=520, Y=420, Z=450</t>
-  </si>
-  <si>
-    <t>1100195930</t>
-  </si>
-  <si>
-    <t>100003616</t>
-  </si>
-  <si>
-    <t>1100194450</t>
-  </si>
-  <si>
-    <t>100003617</t>
-  </si>
-  <si>
-    <t>1100194550</t>
-  </si>
-  <si>
-    <t>100003618</t>
-  </si>
-  <si>
-    <t>1100197010</t>
-  </si>
-  <si>
-    <t>100003619</t>
-  </si>
-  <si>
-    <t>1100197020</t>
-  </si>
-  <si>
-    <t>100003620</t>
-  </si>
-  <si>
-    <t>1100191150</t>
-  </si>
-  <si>
-    <t>100003621</t>
-  </si>
-  <si>
-    <t>1100197580</t>
-  </si>
-  <si>
-    <t>100003622</t>
-  </si>
-  <si>
-    <t>1100197240</t>
-  </si>
-  <si>
-    <t>100003623</t>
-  </si>
-  <si>
-    <t>980000043500</t>
-  </si>
-  <si>
-    <t>HSA-316, #50_X=3250, Y=1600, Z=780</t>
-  </si>
-  <si>
-    <t>1100191070</t>
-  </si>
-  <si>
-    <t>100003624</t>
-  </si>
-  <si>
     <t>100003625</t>
   </si>
   <si>
@@ -1135,6 +1063,9 @@
     <t>100003628</t>
   </si>
   <si>
+    <t>1100199350</t>
+  </si>
+  <si>
     <t>100003629</t>
   </si>
   <si>
@@ -1189,6 +1120,60 @@
     <t>1100197450</t>
   </si>
   <si>
+    <t>100003638</t>
+  </si>
+  <si>
+    <t>980000033000</t>
+  </si>
+  <si>
+    <t>HSA-320EAY_X=3M,Y=2.8M ,Z=1.0/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100181490</t>
+  </si>
+  <si>
+    <t>100003639</t>
+  </si>
+  <si>
+    <t>1100192880</t>
+  </si>
+  <si>
+    <t>100003640</t>
+  </si>
+  <si>
+    <t>980000022200</t>
+  </si>
+  <si>
+    <t>HSA-423EA_X=4M, Y=2.3M, Z=1/1.2/1.4M</t>
+  </si>
+  <si>
+    <t>1100197430</t>
+  </si>
+  <si>
+    <t>100003641</t>
+  </si>
+  <si>
+    <t>1100199120</t>
+  </si>
+  <si>
+    <t>100003642</t>
+  </si>
+  <si>
+    <t>1100195840</t>
+  </si>
+  <si>
+    <t>100003643</t>
+  </si>
+  <si>
+    <t>1100195850</t>
+  </si>
+  <si>
+    <t>100003644</t>
+  </si>
+  <si>
+    <t>1100199540</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -1213,15 +1198,6 @@
     <t/>
   </si>
   <si>
-    <t>630000340</t>
-  </si>
-  <si>
-    <t>080100018301</t>
-  </si>
-  <si>
-    <t>D6K 主軸,010801_BBT50,M50E,C045</t>
-  </si>
-  <si>
     <t>630000349</t>
   </si>
   <si>
@@ -1229,18 +1205,6 @@
   </si>
   <si>
     <t>LG1370NEO機頭P12K,021964_#40,8YU-91,CI</t>
-  </si>
-  <si>
-    <t>630000354</t>
-  </si>
-  <si>
-    <t>080200017902</t>
-  </si>
-  <si>
-    <t>EA機頭G8K,011262_Z1200,55A22,C</t>
-  </si>
-  <si>
-    <t>REL  PCNF PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>630000355</t>
@@ -1402,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P143"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -1425,52 +1389,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="O1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="P1" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1799,7 +1763,7 @@
         <v>45799</v>
       </c>
       <c r="I8" s="3">
-        <v>46121</v>
+        <v>46160</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -1934,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -1943,31 +1907,31 @@
         <v>46</v>
       </c>
       <c r="G11" s="3">
-        <v>45810</v>
+        <v>45813</v>
       </c>
       <c r="H11" s="3">
-        <v>45853</v>
+        <v>45814</v>
       </c>
       <c r="I11" s="3">
-        <v>46129</v>
+        <v>46140</v>
       </c>
       <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="3">
+        <v>45812</v>
+      </c>
+      <c r="M11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" t="s">
         <v>47</v>
-      </c>
-      <c r="K11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11" s="3">
-        <v>45806</v>
-      </c>
-      <c r="M11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N11" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" t="s">
-        <v>48</v>
       </c>
       <c r="P11" t="s">
         <v>9</v>
@@ -1978,28 +1942,28 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>50</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
       </c>
       <c r="G12" s="3">
         <v>45813</v>
       </c>
       <c r="H12" s="3">
-        <v>45814</v>
+        <v>45827</v>
       </c>
       <c r="I12" s="3">
-        <v>46140</v>
+        <v>46231</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -2017,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="O12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P12" t="s">
         <v>9</v>
@@ -2028,28 +1992,28 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>54</v>
       </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
       <c r="G13" s="3">
-        <v>45813</v>
+        <v>45835</v>
       </c>
       <c r="H13" s="3">
-        <v>45827</v>
+        <v>46056</v>
       </c>
       <c r="I13" s="3">
-        <v>46231</v>
+        <v>46150</v>
       </c>
       <c r="J13" t="s">
         <v>22</v>
@@ -2058,7 +2022,7 @@
         <v>5</v>
       </c>
       <c r="L13" s="3">
-        <v>45812</v>
+        <v>45835</v>
       </c>
       <c r="M13" t="s">
         <v>6</v>
@@ -2067,7 +2031,7 @@
         <v>7</v>
       </c>
       <c r="O13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P13" t="s">
         <v>9</v>
@@ -2078,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -2087,16 +2051,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G14" s="3">
         <v>45835</v>
       </c>
       <c r="H14" s="3">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I14" s="3">
         <v>46150</v>
@@ -2117,7 +2081,7 @@
         <v>7</v>
       </c>
       <c r="O14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="P14" t="s">
         <v>9</v>
@@ -2128,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -2143,22 +2107,22 @@
         <v>59</v>
       </c>
       <c r="G15" s="3">
-        <v>45835</v>
+        <v>45848</v>
       </c>
       <c r="H15" s="3">
-        <v>46055</v>
+        <v>46001</v>
       </c>
       <c r="I15" s="3">
-        <v>46150</v>
+        <v>46169</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" s="3">
-        <v>45835</v>
+        <v>45848</v>
       </c>
       <c r="M15" t="s">
         <v>6</v>
@@ -2167,7 +2131,7 @@
         <v>7</v>
       </c>
       <c r="O15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P15" t="s">
         <v>9</v>
@@ -2193,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="G16" s="3">
-        <v>45848</v>
+        <v>45901</v>
       </c>
       <c r="H16" s="3">
-        <v>46001</v>
+        <v>46045</v>
       </c>
       <c r="I16" s="3">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="J16" t="s">
         <v>65</v>
@@ -2208,7 +2172,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="3">
-        <v>45848</v>
+        <v>45901</v>
       </c>
       <c r="M16" t="s">
         <v>6</v>
@@ -2243,31 +2207,31 @@
         <v>69</v>
       </c>
       <c r="G17" s="3">
-        <v>45901</v>
+        <v>45943</v>
       </c>
       <c r="H17" s="3">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="I17" s="3">
-        <v>46183</v>
+        <v>46114</v>
       </c>
       <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
+        <v>45943</v>
+      </c>
+      <c r="M17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" t="s">
         <v>70</v>
-      </c>
-      <c r="K17" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
-        <v>45901</v>
-      </c>
-      <c r="M17" t="s">
-        <v>6</v>
-      </c>
-      <c r="N17" t="s">
-        <v>7</v>
-      </c>
-      <c r="O17" t="s">
-        <v>71</v>
       </c>
       <c r="P17" t="s">
         <v>9</v>
@@ -2278,46 +2242,46 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="3">
+        <v>45966</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I18" s="3">
+        <v>46162</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
+        <v>45966</v>
+      </c>
+      <c r="M18" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18" t="s">
         <v>72</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46017</v>
-      </c>
-      <c r="I18" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K18" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
-        <v>45943</v>
-      </c>
-      <c r="M18" t="s">
-        <v>6</v>
-      </c>
-      <c r="N18" t="s">
-        <v>7</v>
-      </c>
-      <c r="O18" t="s">
-        <v>75</v>
       </c>
       <c r="P18" t="s">
         <v>9</v>
@@ -2328,46 +2292,46 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="3">
+        <v>45979</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46099</v>
+      </c>
+      <c r="I19" s="3">
+        <v>46155</v>
+      </c>
+      <c r="J19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s">
+        <v>5</v>
+      </c>
+      <c r="L19" s="3">
+        <v>45979</v>
+      </c>
+      <c r="M19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" t="s">
+        <v>7</v>
+      </c>
+      <c r="O19" t="s">
         <v>76</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="3">
-        <v>45943</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46041</v>
-      </c>
-      <c r="I19" s="3">
-        <v>46114</v>
-      </c>
-      <c r="J19" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" t="s">
-        <v>5</v>
-      </c>
-      <c r="L19" s="3">
-        <v>45943</v>
-      </c>
-      <c r="M19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N19" t="s">
-        <v>7</v>
-      </c>
-      <c r="O19" t="s">
-        <v>79</v>
       </c>
       <c r="P19" t="s">
         <v>9</v>
@@ -2378,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -2387,28 +2351,28 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G20" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="H20" s="3">
-        <v>46051</v>
+        <v>46065</v>
       </c>
       <c r="I20" s="3">
         <v>46162</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="M20" t="s">
         <v>6</v>
@@ -2417,7 +2381,7 @@
         <v>7</v>
       </c>
       <c r="O20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P20" t="s">
         <v>9</v>
@@ -2428,46 +2392,46 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>83</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" s="3">
+        <v>45987</v>
+      </c>
+      <c r="H21" s="3">
+        <v>46125</v>
+      </c>
+      <c r="I21" s="3">
+        <v>46202</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
+        <v>45986</v>
+      </c>
+      <c r="M21" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O21" t="s">
         <v>84</v>
-      </c>
-      <c r="G21" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46099</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46155</v>
-      </c>
-      <c r="J21" t="s">
-        <v>13</v>
-      </c>
-      <c r="K21" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
-        <v>45979</v>
-      </c>
-      <c r="M21" t="s">
-        <v>6</v>
-      </c>
-      <c r="N21" t="s">
-        <v>7</v>
-      </c>
-      <c r="O21" t="s">
-        <v>85</v>
       </c>
       <c r="P21" t="s">
         <v>9</v>
@@ -2478,46 +2442,46 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="3">
+        <v>45994</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46125</v>
+      </c>
+      <c r="I22" s="3">
+        <v>46226</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
+        <v>45994</v>
+      </c>
+      <c r="M22" t="s">
+        <v>6</v>
+      </c>
+      <c r="N22" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" t="s">
         <v>86</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="3">
-        <v>45979</v>
-      </c>
-      <c r="H22" s="3">
-        <v>46065</v>
-      </c>
-      <c r="I22" s="3">
-        <v>46157</v>
-      </c>
-      <c r="J22" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
-        <v>45979</v>
-      </c>
-      <c r="M22" t="s">
-        <v>6</v>
-      </c>
-      <c r="N22" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22" t="s">
-        <v>89</v>
       </c>
       <c r="P22" t="s">
         <v>9</v>
@@ -2528,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -2537,19 +2501,19 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G23" s="3">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="H23" s="3">
-        <v>46125</v>
+        <v>46101</v>
       </c>
       <c r="I23" s="3">
-        <v>46199</v>
+        <v>46154</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -2558,7 +2522,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="3">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="M23" t="s">
         <v>6</v>
@@ -2567,7 +2531,7 @@
         <v>7</v>
       </c>
       <c r="O23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="P23" t="s">
         <v>9</v>
@@ -2578,37 +2542,37 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G24" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H24" s="3">
-        <v>46076</v>
+        <v>46094</v>
       </c>
       <c r="I24" s="3">
-        <v>46129</v>
+        <v>46148</v>
       </c>
       <c r="J24" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="M24" t="s">
         <v>6</v>
@@ -2617,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="O24" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P24" t="s">
         <v>9</v>
@@ -2628,37 +2592,37 @@
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G25" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="H25" s="3">
-        <v>46041</v>
+        <v>46105</v>
       </c>
       <c r="I25" s="3">
-        <v>46142</v>
+        <v>46202</v>
       </c>
       <c r="J25" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="M25" t="s">
         <v>6</v>
@@ -2667,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P25" t="s">
         <v>9</v>
@@ -2678,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -2693,22 +2657,22 @@
         <v>69</v>
       </c>
       <c r="G26" s="3">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="H26" s="3">
-        <v>46125</v>
+        <v>46087</v>
       </c>
       <c r="I26" s="3">
-        <v>46226</v>
+        <v>46122</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="M26" t="s">
         <v>6</v>
@@ -2717,7 +2681,7 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="P26" t="s">
         <v>9</v>
@@ -2728,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -2737,19 +2701,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="G27" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H27" s="3">
-        <v>46101</v>
+        <v>46050</v>
       </c>
       <c r="I27" s="3">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -2758,7 +2722,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M27" t="s">
         <v>6</v>
@@ -2767,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P27" t="s">
         <v>9</v>
@@ -2778,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -2787,19 +2751,19 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="G28" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="H28" s="3">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="I28" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="J28" t="s">
         <v>22</v>
@@ -2808,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="L28" s="3">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="M28" t="s">
         <v>6</v>
@@ -2817,7 +2781,7 @@
         <v>7</v>
       </c>
       <c r="O28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P28" t="s">
         <v>9</v>
@@ -2828,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2837,19 +2801,19 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G29" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="H29" s="3">
-        <v>46105</v>
+        <v>46010</v>
       </c>
       <c r="I29" s="3">
-        <v>46202</v>
+        <v>46045</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -2858,7 +2822,7 @@
         <v>5</v>
       </c>
       <c r="L29" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="M29" t="s">
         <v>6</v>
@@ -2867,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="O29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="P29" t="s">
         <v>9</v>
@@ -2878,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
@@ -2887,28 +2851,28 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G30" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H30" s="3">
-        <v>46087</v>
+        <v>46041</v>
       </c>
       <c r="I30" s="3">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="J30" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M30" t="s">
         <v>6</v>
@@ -2917,7 +2881,7 @@
         <v>7</v>
       </c>
       <c r="O30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="P30" t="s">
         <v>9</v>
@@ -2928,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -2937,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="G31" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H31" s="3">
-        <v>46050</v>
+        <v>46090</v>
       </c>
       <c r="I31" s="3">
-        <v>46148</v>
+        <v>46171</v>
       </c>
       <c r="J31" t="s">
         <v>22</v>
@@ -2958,7 +2922,7 @@
         <v>5</v>
       </c>
       <c r="L31" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
@@ -2967,7 +2931,7 @@
         <v>7</v>
       </c>
       <c r="O31" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="P31" t="s">
         <v>9</v>
@@ -2978,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C32" s="2">
         <v>1</v>
@@ -2987,19 +2951,19 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G32" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="H32" s="3">
-        <v>46104</v>
+        <v>46093</v>
       </c>
       <c r="I32" s="3">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="J32" t="s">
         <v>22</v>
@@ -3008,7 +2972,7 @@
         <v>5</v>
       </c>
       <c r="L32" s="3">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="M32" t="s">
         <v>6</v>
@@ -3017,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="O32" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="P32" t="s">
         <v>9</v>
@@ -3028,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -3037,19 +3001,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="G33" s="3">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="H33" s="3">
-        <v>46010</v>
+        <v>46077</v>
       </c>
       <c r="I33" s="3">
-        <v>46045</v>
+        <v>46156</v>
       </c>
       <c r="J33" t="s">
         <v>22</v>
@@ -3058,7 +3022,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="3">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="M33" t="s">
         <v>6</v>
@@ -3067,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="P33" t="s">
         <v>9</v>
@@ -3078,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -3087,28 +3051,28 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G34" s="3">
-        <v>46007</v>
+        <v>46027</v>
       </c>
       <c r="H34" s="3">
-        <v>46041</v>
+        <v>46126</v>
       </c>
       <c r="I34" s="3">
-        <v>46155</v>
+        <v>46188</v>
       </c>
       <c r="J34" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" s="3">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="M34" t="s">
         <v>6</v>
@@ -3117,7 +3081,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P34" t="s">
         <v>9</v>
@@ -3128,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C35" s="2">
         <v>1</v>
@@ -3137,19 +3101,19 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="G35" s="3">
-        <v>46007</v>
+        <v>46028</v>
       </c>
       <c r="H35" s="3">
-        <v>46090</v>
+        <v>46031</v>
       </c>
       <c r="I35" s="3">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="J35" t="s">
         <v>22</v>
@@ -3158,7 +3122,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="3">
-        <v>46007</v>
+        <v>46028</v>
       </c>
       <c r="M35" t="s">
         <v>6</v>
@@ -3167,7 +3131,7 @@
         <v>7</v>
       </c>
       <c r="O35" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="P35" t="s">
         <v>9</v>
@@ -3178,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3187,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="G36" s="3">
-        <v>46007</v>
+        <v>46031</v>
       </c>
       <c r="H36" s="3">
-        <v>46093</v>
+        <v>46050</v>
       </c>
       <c r="I36" s="3">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="J36" t="s">
         <v>22</v>
@@ -3208,7 +3172,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="3">
-        <v>46007</v>
+        <v>46031</v>
       </c>
       <c r="M36" t="s">
         <v>6</v>
@@ -3217,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -3228,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -3237,19 +3201,19 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="G37" s="3">
-        <v>46014</v>
+        <v>46041</v>
       </c>
       <c r="H37" s="3">
-        <v>46077</v>
+        <v>46090</v>
       </c>
       <c r="I37" s="3">
-        <v>46153</v>
+        <v>46211</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -3258,7 +3222,7 @@
         <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>46014</v>
+        <v>46041</v>
       </c>
       <c r="M37" t="s">
         <v>6</v>
@@ -3267,7 +3231,7 @@
         <v>7</v>
       </c>
       <c r="O37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -3278,46 +3242,46 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H38" s="3">
+        <v>46129</v>
+      </c>
+      <c r="I38" s="3">
+        <v>46167</v>
+      </c>
+      <c r="J38" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M38" t="s">
+        <v>6</v>
+      </c>
+      <c r="N38" t="s">
+        <v>7</v>
+      </c>
+      <c r="O38" t="s">
         <v>134</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="3">
-        <v>46027</v>
-      </c>
-      <c r="H38" s="3">
-        <v>46126</v>
-      </c>
-      <c r="I38" s="3">
-        <v>46188</v>
-      </c>
-      <c r="J38" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" t="s">
-        <v>5</v>
-      </c>
-      <c r="L38" s="3">
-        <v>46022</v>
-      </c>
-      <c r="M38" t="s">
-        <v>6</v>
-      </c>
-      <c r="N38" t="s">
-        <v>7</v>
-      </c>
-      <c r="O38" t="s">
-        <v>135</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -3328,46 +3292,46 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H39" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I39" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J39" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="K39" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="3">
+        <v>46044</v>
+      </c>
+      <c r="M39" t="s">
+        <v>6</v>
+      </c>
+      <c r="N39" t="s">
+        <v>7</v>
+      </c>
+      <c r="O39" t="s">
         <v>137</v>
-      </c>
-      <c r="F39" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39" s="3">
-        <v>46028</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46031</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46155</v>
-      </c>
-      <c r="J39" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" s="3">
-        <v>46028</v>
-      </c>
-      <c r="M39" t="s">
-        <v>6</v>
-      </c>
-      <c r="N39" t="s">
-        <v>7</v>
-      </c>
-      <c r="O39" t="s">
-        <v>139</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -3378,28 +3342,28 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" t="s">
         <v>140</v>
       </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>141</v>
-      </c>
-      <c r="F40" t="s">
-        <v>142</v>
-      </c>
       <c r="G40" s="3">
-        <v>46031</v>
+        <v>46048</v>
       </c>
       <c r="H40" s="3">
-        <v>46050</v>
+        <v>46090</v>
       </c>
       <c r="I40" s="3">
-        <v>46161</v>
+        <v>46195</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -3408,7 +3372,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>46031</v>
+        <v>46044</v>
       </c>
       <c r="M40" t="s">
         <v>6</v>
@@ -3417,7 +3381,7 @@
         <v>7</v>
       </c>
       <c r="O40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -3428,28 +3392,28 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" t="s">
-        <v>146</v>
-      </c>
       <c r="G41" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="H41" s="3">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="I41" s="3">
-        <v>46211</v>
+        <v>46156</v>
       </c>
       <c r="J41" t="s">
         <v>22</v>
@@ -3458,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="M41" t="s">
         <v>6</v>
@@ -3467,7 +3431,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -3478,46 +3442,46 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="G42" s="3">
+        <v>46044</v>
+      </c>
+      <c r="H42" s="3">
+        <v>46087</v>
+      </c>
+      <c r="I42" s="3">
+        <v>46153</v>
+      </c>
+      <c r="J42" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="3">
+        <v>46044</v>
+      </c>
+      <c r="M42" t="s">
+        <v>6</v>
+      </c>
+      <c r="N42" t="s">
+        <v>7</v>
+      </c>
+      <c r="O42" t="s">
         <v>149</v>
-      </c>
-      <c r="F42" t="s">
-        <v>150</v>
-      </c>
-      <c r="G42" s="3">
-        <v>46043</v>
-      </c>
-      <c r="H42" s="3">
-        <v>46129</v>
-      </c>
-      <c r="I42" s="3">
-        <v>46167</v>
-      </c>
-      <c r="J42" t="s">
-        <v>22</v>
-      </c>
-      <c r="K42" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3">
-        <v>46043</v>
-      </c>
-      <c r="M42" t="s">
-        <v>6</v>
-      </c>
-      <c r="N42" t="s">
-        <v>7</v>
-      </c>
-      <c r="O42" t="s">
-        <v>151</v>
       </c>
       <c r="P42" t="s">
         <v>9</v>
@@ -3528,46 +3492,46 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" t="s">
         <v>152</v>
       </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F43" t="s">
-        <v>84</v>
-      </c>
       <c r="G43" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H43" s="3">
-        <v>46148</v>
+        <v>46106</v>
       </c>
       <c r="I43" s="3">
-        <v>46183</v>
+        <v>46163</v>
       </c>
       <c r="J43" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
+        <v>46048</v>
+      </c>
+      <c r="M43" t="s">
+        <v>6</v>
+      </c>
+      <c r="N43" t="s">
+        <v>7</v>
+      </c>
+      <c r="O43" t="s">
         <v>153</v>
-      </c>
-      <c r="K43" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>46044</v>
-      </c>
-      <c r="M43" t="s">
-        <v>6</v>
-      </c>
-      <c r="N43" t="s">
-        <v>7</v>
-      </c>
-      <c r="O43" t="s">
-        <v>154</v>
       </c>
       <c r="P43" t="s">
         <v>9</v>
@@ -3578,28 +3542,28 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
         <v>155</v>
       </c>
-      <c r="C44" s="2">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>156</v>
       </c>
-      <c r="F44" t="s">
-        <v>157</v>
-      </c>
       <c r="G44" s="3">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="H44" s="3">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="I44" s="3">
-        <v>46195</v>
+        <v>46156</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -3608,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="M44" t="s">
         <v>6</v>
@@ -3617,7 +3581,7 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P44" t="s">
         <v>9</v>
@@ -3628,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -3637,19 +3601,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F45" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G45" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="H45" s="3">
         <v>46083</v>
       </c>
       <c r="I45" s="3">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -3658,7 +3622,7 @@
         <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M45" t="s">
         <v>6</v>
@@ -3667,7 +3631,7 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P45" t="s">
         <v>9</v>
@@ -3678,46 +3642,46 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" s="3">
+        <v>46063</v>
+      </c>
+      <c r="H46" s="3">
+        <v>46091</v>
+      </c>
+      <c r="I46" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J46" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
+        <v>46063</v>
+      </c>
+      <c r="M46" t="s">
+        <v>6</v>
+      </c>
+      <c r="N46" t="s">
+        <v>7</v>
+      </c>
+      <c r="O46" t="s">
         <v>163</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>164</v>
-      </c>
-      <c r="F46" t="s">
-        <v>165</v>
-      </c>
-      <c r="G46" s="3">
-        <v>46044</v>
-      </c>
-      <c r="H46" s="3">
-        <v>46087</v>
-      </c>
-      <c r="I46" s="3">
-        <v>46153</v>
-      </c>
-      <c r="J46" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>46044</v>
-      </c>
-      <c r="M46" t="s">
-        <v>6</v>
-      </c>
-      <c r="N46" t="s">
-        <v>7</v>
-      </c>
-      <c r="O46" t="s">
-        <v>166</v>
       </c>
       <c r="P46" t="s">
         <v>9</v>
@@ -3728,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -3737,19 +3701,19 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F47" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G47" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="H47" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="I47" s="3">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -3758,7 +3722,7 @@
         <v>5</v>
       </c>
       <c r="L47" s="3">
-        <v>46048</v>
+        <v>46063</v>
       </c>
       <c r="M47" t="s">
         <v>6</v>
@@ -3767,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="P47" t="s">
         <v>9</v>
@@ -3778,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -3787,28 +3751,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="G48" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="H48" s="3">
-        <v>46086</v>
+        <v>46135</v>
       </c>
       <c r="I48" s="3">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="J48" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="M48" t="s">
         <v>6</v>
@@ -3817,7 +3781,7 @@
         <v>7</v>
       </c>
       <c r="O48" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="P48" t="s">
         <v>9</v>
@@ -3828,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -3837,28 +3801,28 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="G49" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="H49" s="3">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="I49" s="3">
-        <v>46149</v>
+        <v>46168</v>
       </c>
       <c r="J49" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K49" t="s">
         <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="M49" t="s">
         <v>6</v>
@@ -3867,7 +3831,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="P49" t="s">
         <v>9</v>
@@ -3878,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -3887,28 +3851,28 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="G50" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="H50" s="3">
-        <v>46099</v>
+        <v>46308</v>
       </c>
       <c r="I50" s="3">
-        <v>46134</v>
+        <v>46344</v>
       </c>
       <c r="J50" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="M50" t="s">
         <v>6</v>
@@ -3917,7 +3881,7 @@
         <v>7</v>
       </c>
       <c r="O50" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="P50" t="s">
         <v>9</v>
@@ -3928,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -3937,28 +3901,28 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="G51" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="H51" s="3">
-        <v>46083</v>
+        <v>46308</v>
       </c>
       <c r="I51" s="3">
-        <v>46136</v>
+        <v>46344</v>
       </c>
       <c r="J51" t="s">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="M51" t="s">
         <v>6</v>
@@ -3967,7 +3931,7 @@
         <v>7</v>
       </c>
       <c r="O51" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="P51" t="s">
         <v>9</v>
@@ -3978,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -3987,28 +3951,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="F52" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G52" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H52" s="3">
-        <v>46091</v>
+        <v>46150</v>
       </c>
       <c r="I52" s="3">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="J52" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M52" t="s">
         <v>6</v>
@@ -4017,7 +3981,7 @@
         <v>7</v>
       </c>
       <c r="O52" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
         <v>9</v>
@@ -4028,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -4037,28 +4001,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="F53" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G53" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H53" s="3">
-        <v>46108</v>
+        <v>46178</v>
       </c>
       <c r="I53" s="3">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="J53" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="M53" t="s">
         <v>6</v>
@@ -4067,7 +4031,7 @@
         <v>7</v>
       </c>
       <c r="O53" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="P53" t="s">
         <v>9</v>
@@ -4078,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -4087,22 +4051,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F54" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G54" s="3">
         <v>46064</v>
       </c>
       <c r="H54" s="3">
-        <v>46135</v>
+        <v>46244</v>
       </c>
       <c r="I54" s="3">
-        <v>46170</v>
+        <v>46281</v>
       </c>
       <c r="J54" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -4117,7 +4081,7 @@
         <v>7</v>
       </c>
       <c r="O54" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="P54" t="s">
         <v>9</v>
@@ -4128,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -4137,22 +4101,22 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F55" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G55" s="3">
         <v>46064</v>
       </c>
       <c r="H55" s="3">
-        <v>46134</v>
+        <v>46303</v>
       </c>
       <c r="I55" s="3">
-        <v>46168</v>
+        <v>46344</v>
       </c>
       <c r="J55" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
@@ -4167,7 +4131,7 @@
         <v>7</v>
       </c>
       <c r="O55" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="P55" t="s">
         <v>9</v>
@@ -4178,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -4187,28 +4151,28 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="G56" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H56" s="3">
-        <v>46308</v>
+        <v>46077</v>
       </c>
       <c r="I56" s="3">
-        <v>46344</v>
+        <v>46160</v>
       </c>
       <c r="J56" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M56" t="s">
         <v>6</v>
@@ -4217,7 +4181,7 @@
         <v>7</v>
       </c>
       <c r="O56" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="P56" t="s">
         <v>9</v>
@@ -4228,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -4237,28 +4201,28 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="G57" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H57" s="3">
-        <v>46308</v>
+        <v>46167</v>
       </c>
       <c r="I57" s="3">
-        <v>46344</v>
+        <v>46218</v>
       </c>
       <c r="J57" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M57" t="s">
         <v>6</v>
@@ -4267,7 +4231,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P57" t="s">
         <v>9</v>
@@ -4278,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
@@ -4287,28 +4251,28 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="F58" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="G58" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H58" s="3">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="I58" s="3">
-        <v>46189</v>
+        <v>46218</v>
       </c>
       <c r="J58" t="s">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M58" t="s">
         <v>6</v>
@@ -4317,7 +4281,7 @@
         <v>7</v>
       </c>
       <c r="O58" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="P58" t="s">
         <v>9</v>
@@ -4328,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
@@ -4337,28 +4301,28 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="F59" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="G59" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H59" s="3">
-        <v>46178</v>
+        <v>46217</v>
       </c>
       <c r="I59" s="3">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="J59" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M59" t="s">
         <v>6</v>
@@ -4367,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="P59" t="s">
         <v>9</v>
@@ -4378,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
@@ -4387,37 +4351,37 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="G60" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H60" s="3">
-        <v>46244</v>
+        <v>46217</v>
       </c>
       <c r="I60" s="3">
-        <v>46281</v>
+        <v>46267</v>
       </c>
       <c r="J60" t="s">
+        <v>195</v>
+      </c>
+      <c r="K60" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
+        <v>46076</v>
+      </c>
+      <c r="M60" t="s">
+        <v>6</v>
+      </c>
+      <c r="N60" t="s">
+        <v>7</v>
+      </c>
+      <c r="O60" t="s">
         <v>193</v>
-      </c>
-      <c r="K60" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
-        <v>46064</v>
-      </c>
-      <c r="M60" t="s">
-        <v>6</v>
-      </c>
-      <c r="N60" t="s">
-        <v>7</v>
-      </c>
-      <c r="O60" t="s">
-        <v>204</v>
       </c>
       <c r="P60" t="s">
         <v>9</v>
@@ -4428,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
@@ -4437,28 +4401,28 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="F61" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="G61" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="H61" s="3">
-        <v>46303</v>
+        <v>46254</v>
       </c>
       <c r="I61" s="3">
-        <v>46344</v>
+        <v>46309</v>
       </c>
       <c r="J61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="M61" t="s">
         <v>6</v>
@@ -4467,7 +4431,7 @@
         <v>7</v>
       </c>
       <c r="O61" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="P61" t="s">
         <v>9</v>
@@ -4478,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
@@ -4487,22 +4451,22 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F62" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="G62" s="3">
         <v>46076</v>
       </c>
       <c r="H62" s="3">
-        <v>46077</v>
+        <v>46254</v>
       </c>
       <c r="I62" s="3">
-        <v>46153</v>
+        <v>46309</v>
       </c>
       <c r="J62" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="K62" t="s">
         <v>5</v>
@@ -4517,7 +4481,7 @@
         <v>7</v>
       </c>
       <c r="O62" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="P62" t="s">
         <v>9</v>
@@ -4528,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -4537,19 +4501,19 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F63" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G63" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H63" s="3">
-        <v>46167</v>
+        <v>46107</v>
       </c>
       <c r="I63" s="3">
-        <v>46218</v>
+        <v>46153</v>
       </c>
       <c r="J63" t="s">
         <v>22</v>
@@ -4567,7 +4531,7 @@
         <v>7</v>
       </c>
       <c r="O63" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="P63" t="s">
         <v>9</v>
@@ -4578,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C64" s="2">
         <v>1</v>
@@ -4587,22 +4551,22 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F64" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G64" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H64" s="3">
-        <v>46167</v>
+        <v>46108</v>
       </c>
       <c r="I64" s="3">
-        <v>46218</v>
+        <v>46156</v>
       </c>
       <c r="J64" t="s">
-        <v>214</v>
+        <v>22</v>
       </c>
       <c r="K64" t="s">
         <v>5</v>
@@ -4617,7 +4581,7 @@
         <v>7</v>
       </c>
       <c r="O64" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="P64" t="s">
         <v>9</v>
@@ -4628,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C65" s="2">
         <v>1</v>
@@ -4637,22 +4601,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F65" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G65" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H65" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="I65" s="3">
-        <v>46267</v>
+        <v>46154</v>
       </c>
       <c r="J65" t="s">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4667,7 +4631,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="P65" t="s">
         <v>9</v>
@@ -4678,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -4687,22 +4651,22 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F66" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G66" s="3">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="H66" s="3">
-        <v>46217</v>
+        <v>46114</v>
       </c>
       <c r="I66" s="3">
-        <v>46267</v>
+        <v>46154</v>
       </c>
       <c r="J66" t="s">
-        <v>218</v>
+        <v>136</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
@@ -4717,7 +4681,7 @@
         <v>7</v>
       </c>
       <c r="O66" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="P66" t="s">
         <v>9</v>
@@ -4728,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
@@ -4737,37 +4701,37 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
+        <v>207</v>
+      </c>
+      <c r="F67" t="s">
         <v>208</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" s="3">
+        <v>46079</v>
+      </c>
+      <c r="H67" s="3">
+        <v>46163</v>
+      </c>
+      <c r="I67" s="3">
+        <v>46238</v>
+      </c>
+      <c r="J67" t="s">
+        <v>65</v>
+      </c>
+      <c r="K67" t="s">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3">
+        <v>46079</v>
+      </c>
+      <c r="M67" t="s">
+        <v>6</v>
+      </c>
+      <c r="N67" t="s">
+        <v>7</v>
+      </c>
+      <c r="O67" t="s">
         <v>209</v>
-      </c>
-      <c r="G67" s="3">
-        <v>46076</v>
-      </c>
-      <c r="H67" s="3">
-        <v>46254</v>
-      </c>
-      <c r="I67" s="3">
-        <v>46309</v>
-      </c>
-      <c r="J67" t="s">
-        <v>218</v>
-      </c>
-      <c r="K67" t="s">
-        <v>5</v>
-      </c>
-      <c r="L67" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M67" t="s">
-        <v>6</v>
-      </c>
-      <c r="N67" t="s">
-        <v>7</v>
-      </c>
-      <c r="O67" t="s">
-        <v>220</v>
       </c>
       <c r="P67" t="s">
         <v>9</v>
@@ -4778,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -4787,28 +4751,28 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F68" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G68" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="H68" s="3">
-        <v>46254</v>
+        <v>46128</v>
       </c>
       <c r="I68" s="3">
-        <v>46309</v>
+        <v>46203</v>
       </c>
       <c r="J68" t="s">
-        <v>218</v>
+        <v>22</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M68" t="s">
         <v>6</v>
@@ -4817,7 +4781,7 @@
         <v>7</v>
       </c>
       <c r="O68" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="P68" t="s">
         <v>9</v>
@@ -4828,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -4837,19 +4801,19 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="F69" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
       <c r="G69" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H69" s="3">
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="I69" s="3">
-        <v>46153</v>
+        <v>46232</v>
       </c>
       <c r="J69" t="s">
         <v>22</v>
@@ -4858,7 +4822,7 @@
         <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M69" t="s">
         <v>6</v>
@@ -4867,7 +4831,7 @@
         <v>7</v>
       </c>
       <c r="O69" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="P69" t="s">
         <v>9</v>
@@ -4878,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -4887,28 +4851,28 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F70" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G70" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="H70" s="3">
-        <v>46108</v>
+        <v>46219</v>
       </c>
       <c r="I70" s="3">
-        <v>46156</v>
+        <v>46279</v>
       </c>
       <c r="J70" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="K70" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="3">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="M70" t="s">
         <v>6</v>
@@ -4917,7 +4881,7 @@
         <v>7</v>
       </c>
       <c r="O70" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="P70" t="s">
         <v>9</v>
@@ -4928,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -4937,37 +4901,37 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
+        <v>221</v>
+      </c>
+      <c r="F71" t="s">
+        <v>222</v>
+      </c>
+      <c r="G71" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H71" s="3">
+        <v>46121</v>
+      </c>
+      <c r="I71" s="3">
+        <v>46203</v>
+      </c>
+      <c r="J71" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" t="s">
         <v>223</v>
       </c>
-      <c r="F71" t="s">
+      <c r="L71" s="3">
+        <v>46086</v>
+      </c>
+      <c r="M71" t="s">
+        <v>6</v>
+      </c>
+      <c r="N71" t="s">
+        <v>7</v>
+      </c>
+      <c r="O71" t="s">
         <v>224</v>
-      </c>
-      <c r="G71" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H71" s="3">
-        <v>46114</v>
-      </c>
-      <c r="I71" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J71" t="s">
-        <v>228</v>
-      </c>
-      <c r="K71" t="s">
-        <v>5</v>
-      </c>
-      <c r="L71" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M71" t="s">
-        <v>6</v>
-      </c>
-      <c r="N71" t="s">
-        <v>7</v>
-      </c>
-      <c r="O71" t="s">
-        <v>225</v>
       </c>
       <c r="P71" t="s">
         <v>9</v>
@@ -4978,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -4987,37 +4951,37 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
+        <v>226</v>
+      </c>
+      <c r="F72" t="s">
+        <v>227</v>
+      </c>
+      <c r="G72" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H72" s="3">
+        <v>46210</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46324</v>
+      </c>
+      <c r="J72" t="s">
+        <v>195</v>
+      </c>
+      <c r="K72" t="s">
         <v>223</v>
       </c>
-      <c r="F72" t="s">
-        <v>224</v>
-      </c>
-      <c r="G72" s="3">
-        <v>46083</v>
-      </c>
-      <c r="H72" s="3">
-        <v>46114</v>
-      </c>
-      <c r="I72" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="L72" s="3">
+        <v>46086</v>
+      </c>
+      <c r="M72" t="s">
+        <v>6</v>
+      </c>
+      <c r="N72" t="s">
+        <v>7</v>
+      </c>
+      <c r="O72" t="s">
         <v>228</v>
-      </c>
-      <c r="K72" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
-        <v>46076</v>
-      </c>
-      <c r="M72" t="s">
-        <v>6</v>
-      </c>
-      <c r="N72" t="s">
-        <v>7</v>
-      </c>
-      <c r="O72" t="s">
-        <v>225</v>
       </c>
       <c r="P72" t="s">
         <v>9</v>
@@ -5028,46 +4992,46 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
+        <v>229</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
         <v>230</v>
       </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>231</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" s="3">
+        <v>46090</v>
+      </c>
+      <c r="H73" s="3">
+        <v>46178</v>
+      </c>
+      <c r="I73" s="3">
+        <v>46233</v>
+      </c>
+      <c r="J73" t="s">
         <v>232</v>
       </c>
-      <c r="G73" s="3">
-        <v>46079</v>
-      </c>
-      <c r="H73" s="3">
-        <v>46163</v>
-      </c>
-      <c r="I73" s="3">
-        <v>46238</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
+        <v>5</v>
+      </c>
+      <c r="L73" s="3">
+        <v>46090</v>
+      </c>
+      <c r="M73" t="s">
+        <v>6</v>
+      </c>
+      <c r="N73" t="s">
+        <v>7</v>
+      </c>
+      <c r="O73" t="s">
         <v>233</v>
-      </c>
-      <c r="K73" t="s">
-        <v>5</v>
-      </c>
-      <c r="L73" s="3">
-        <v>46079</v>
-      </c>
-      <c r="M73" t="s">
-        <v>6</v>
-      </c>
-      <c r="N73" t="s">
-        <v>7</v>
-      </c>
-      <c r="O73" t="s">
-        <v>234</v>
       </c>
       <c r="P73" t="s">
         <v>9</v>
@@ -5078,46 +5042,46 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
         <v>235</v>
       </c>
-      <c r="C74" s="2">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>236</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" s="3">
+        <v>46090</v>
+      </c>
+      <c r="H74" s="3">
+        <v>46212</v>
+      </c>
+      <c r="I74" s="3">
+        <v>46234</v>
+      </c>
+      <c r="J74" t="s">
+        <v>192</v>
+      </c>
+      <c r="K74" t="s">
+        <v>5</v>
+      </c>
+      <c r="L74" s="3">
+        <v>46090</v>
+      </c>
+      <c r="M74" t="s">
+        <v>6</v>
+      </c>
+      <c r="N74" t="s">
+        <v>7</v>
+      </c>
+      <c r="O74" t="s">
         <v>237</v>
-      </c>
-      <c r="G74" s="3">
-        <v>46086</v>
-      </c>
-      <c r="H74" s="3">
-        <v>46128</v>
-      </c>
-      <c r="I74" s="3">
-        <v>46203</v>
-      </c>
-      <c r="J74" t="s">
-        <v>238</v>
-      </c>
-      <c r="K74" t="s">
-        <v>5</v>
-      </c>
-      <c r="L74" s="3">
-        <v>46086</v>
-      </c>
-      <c r="M74" t="s">
-        <v>6</v>
-      </c>
-      <c r="N74" t="s">
-        <v>7</v>
-      </c>
-      <c r="O74" t="s">
-        <v>239</v>
       </c>
       <c r="P74" t="s">
         <v>9</v>
@@ -5128,37 +5092,37 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>239</v>
+      </c>
+      <c r="F75" t="s">
         <v>240</v>
       </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>156</v>
-      </c>
-      <c r="F75" t="s">
-        <v>157</v>
-      </c>
       <c r="G75" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="H75" s="3">
-        <v>46128</v>
+        <v>46092</v>
       </c>
       <c r="I75" s="3">
-        <v>46217</v>
+        <v>46163</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="M75" t="s">
         <v>6</v>
@@ -5167,7 +5131,7 @@
         <v>7</v>
       </c>
       <c r="O75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P75" t="s">
         <v>9</v>
@@ -5178,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5187,37 +5151,37 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>243</v>
+        <v>68</v>
       </c>
       <c r="F76" t="s">
+        <v>69</v>
+      </c>
+      <c r="G76" s="3">
+        <v>46094</v>
+      </c>
+      <c r="H76" s="3">
+        <v>46133</v>
+      </c>
+      <c r="I76" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J76" t="s">
+        <v>13</v>
+      </c>
+      <c r="K76" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
+        <v>46093</v>
+      </c>
+      <c r="M76" t="s">
+        <v>6</v>
+      </c>
+      <c r="N76" t="s">
+        <v>7</v>
+      </c>
+      <c r="O76" t="s">
         <v>244</v>
-      </c>
-      <c r="G76" s="3">
-        <v>46086</v>
-      </c>
-      <c r="H76" s="3">
-        <v>46219</v>
-      </c>
-      <c r="I76" s="3">
-        <v>46279</v>
-      </c>
-      <c r="J76" t="s">
-        <v>218</v>
-      </c>
-      <c r="K76" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3">
-        <v>46086</v>
-      </c>
-      <c r="M76" t="s">
-        <v>6</v>
-      </c>
-      <c r="N76" t="s">
-        <v>7</v>
-      </c>
-      <c r="O76" t="s">
-        <v>245</v>
       </c>
       <c r="P76" t="s">
         <v>9</v>
@@ -5228,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5237,28 +5201,28 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>247</v>
+        <v>68</v>
       </c>
       <c r="F77" t="s">
-        <v>248</v>
+        <v>69</v>
       </c>
       <c r="G77" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H77" s="3">
-        <v>46121</v>
+        <v>46133</v>
       </c>
       <c r="I77" s="3">
-        <v>46203</v>
+        <v>46164</v>
       </c>
       <c r="J77" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L77" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M77" t="s">
         <v>6</v>
@@ -5267,7 +5231,7 @@
         <v>7</v>
       </c>
       <c r="O77" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P77" t="s">
         <v>9</v>
@@ -5278,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5287,28 +5251,28 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="F78" t="s">
-        <v>253</v>
+        <v>69</v>
       </c>
       <c r="G78" s="3">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="H78" s="3">
-        <v>46210</v>
+        <v>46133</v>
       </c>
       <c r="I78" s="3">
-        <v>46324</v>
+        <v>46169</v>
       </c>
       <c r="J78" t="s">
-        <v>218</v>
+        <v>13</v>
       </c>
       <c r="K78" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L78" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="M78" t="s">
         <v>6</v>
@@ -5317,7 +5281,7 @@
         <v>7</v>
       </c>
       <c r="O78" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P78" t="s">
         <v>9</v>
@@ -5328,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5337,28 +5301,28 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="F79" t="s">
-        <v>257</v>
+        <v>69</v>
       </c>
       <c r="G79" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H79" s="3">
+        <v>46127</v>
+      </c>
+      <c r="I79" s="3">
         <v>46178</v>
       </c>
-      <c r="I79" s="3">
-        <v>46233</v>
-      </c>
       <c r="J79" t="s">
-        <v>258</v>
+        <v>13</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M79" t="s">
         <v>6</v>
@@ -5367,7 +5331,7 @@
         <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="P79" t="s">
         <v>9</v>
@@ -5378,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5387,28 +5351,28 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G80" s="3">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="H80" s="3">
-        <v>46212</v>
+        <v>46127</v>
       </c>
       <c r="I80" s="3">
-        <v>46234</v>
+        <v>46176</v>
       </c>
       <c r="J80" t="s">
-        <v>261</v>
+        <v>13</v>
       </c>
       <c r="K80" t="s">
         <v>5</v>
       </c>
       <c r="L80" s="3">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="M80" t="s">
         <v>6</v>
@@ -5417,7 +5381,7 @@
         <v>7</v>
       </c>
       <c r="O80" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="P80" t="s">
         <v>9</v>
@@ -5428,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5437,28 +5401,28 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>264</v>
+        <v>68</v>
       </c>
       <c r="F81" t="s">
-        <v>265</v>
+        <v>69</v>
       </c>
       <c r="G81" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="H81" s="3">
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="I81" s="3">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="J81" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" s="3">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="M81" t="s">
         <v>6</v>
@@ -5467,7 +5431,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="P81" t="s">
         <v>9</v>
@@ -5478,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5487,22 +5451,22 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F82" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G82" s="3">
         <v>46094</v>
       </c>
       <c r="H82" s="3">
-        <v>46133</v>
+        <v>46164</v>
       </c>
       <c r="I82" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J82" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -5517,7 +5481,7 @@
         <v>7</v>
       </c>
       <c r="O82" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="P82" t="s">
         <v>9</v>
@@ -5528,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -5537,22 +5501,22 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F83" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G83" s="3">
         <v>46094</v>
       </c>
       <c r="H83" s="3">
-        <v>46133</v>
+        <v>46164</v>
       </c>
       <c r="I83" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J83" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
@@ -5567,7 +5531,7 @@
         <v>7</v>
       </c>
       <c r="O83" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="P83" t="s">
         <v>9</v>
@@ -5578,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -5587,19 +5551,19 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F84" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G84" s="3">
         <v>46094</v>
       </c>
       <c r="H84" s="3">
-        <v>46133</v>
+        <v>46164</v>
       </c>
       <c r="I84" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J84" t="s">
         <v>13</v>
@@ -5617,7 +5581,7 @@
         <v>7</v>
       </c>
       <c r="O84" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="P84" t="s">
         <v>9</v>
@@ -5628,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -5637,29 +5601,29 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="F85" t="s">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="G85" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H85" s="3">
+        <v>46146</v>
+      </c>
+      <c r="I85" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J85" t="s">
+        <v>22</v>
+      </c>
+      <c r="K85" t="s">
+        <v>5</v>
+      </c>
+      <c r="L85" s="3">
         <v>46094</v>
       </c>
-      <c r="H85" s="3">
-        <v>46127</v>
-      </c>
-      <c r="I85" s="3">
-        <v>46170</v>
-      </c>
-      <c r="J85" t="s">
-        <v>13</v>
-      </c>
-      <c r="K85" t="s">
-        <v>5</v>
-      </c>
-      <c r="L85" s="3">
-        <v>46093</v>
-      </c>
       <c r="M85" t="s">
         <v>6</v>
       </c>
@@ -5667,7 +5631,7 @@
         <v>7</v>
       </c>
       <c r="O85" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P85" t="s">
         <v>9</v>
@@ -5678,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -5687,28 +5651,28 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F86" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G86" s="3">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="H86" s="3">
-        <v>46127</v>
+        <v>46224</v>
       </c>
       <c r="I86" s="3">
-        <v>46168</v>
+        <v>46246</v>
       </c>
       <c r="J86" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" s="3">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="M86" t="s">
         <v>6</v>
@@ -5717,7 +5681,7 @@
         <v>7</v>
       </c>
       <c r="O86" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P86" t="s">
         <v>9</v>
@@ -5728,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -5737,28 +5701,28 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="F87" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G87" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H87" s="3">
-        <v>46127</v>
+        <v>46232</v>
       </c>
       <c r="I87" s="3">
-        <v>46170</v>
+        <v>46253</v>
       </c>
       <c r="J87" t="s">
-        <v>13</v>
+        <v>262</v>
       </c>
       <c r="K87" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="L87" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M87" t="s">
         <v>6</v>
@@ -5767,7 +5731,7 @@
         <v>7</v>
       </c>
       <c r="O87" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="P87" t="s">
         <v>9</v>
@@ -5778,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -5787,28 +5751,28 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="F88" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="G88" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H88" s="3">
-        <v>46167</v>
+        <v>46217</v>
       </c>
       <c r="I88" s="3">
-        <v>46198</v>
+        <v>46251</v>
       </c>
       <c r="J88" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="K88" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="L88" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M88" t="s">
         <v>6</v>
@@ -5817,7 +5781,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P88" t="s">
         <v>9</v>
@@ -5828,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -5837,28 +5801,28 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="F89" t="s">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="G89" s="3">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="H89" s="3">
-        <v>46167</v>
+        <v>46227</v>
       </c>
       <c r="I89" s="3">
-        <v>46198</v>
+        <v>46253</v>
       </c>
       <c r="J89" t="s">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="K89" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="L89" s="3">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="M89" t="s">
         <v>6</v>
@@ -5867,7 +5831,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P89" t="s">
         <v>9</v>
@@ -5878,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
@@ -5887,28 +5851,28 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="G90" s="3">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="H90" s="3">
-        <v>46167</v>
+        <v>46135</v>
       </c>
       <c r="I90" s="3">
-        <v>46198</v>
+        <v>46162</v>
       </c>
       <c r="J90" t="s">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="K90" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="L90" s="3">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="M90" t="s">
         <v>6</v>
@@ -5917,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="O90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P90" t="s">
         <v>9</v>
@@ -5928,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C91" s="2">
         <v>1</v>
@@ -5937,28 +5901,28 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>280</v>
+        <v>68</v>
       </c>
       <c r="F91" t="s">
-        <v>281</v>
+        <v>69</v>
       </c>
       <c r="G91" s="3">
-        <v>46097</v>
+        <v>46113</v>
       </c>
       <c r="H91" s="3">
-        <v>46149</v>
+        <v>46171</v>
       </c>
       <c r="I91" s="3">
-        <v>46181</v>
+        <v>46190</v>
       </c>
       <c r="J91" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="M91" t="s">
         <v>6</v>
@@ -5967,7 +5931,7 @@
         <v>7</v>
       </c>
       <c r="O91" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="P91" t="s">
         <v>9</v>
@@ -5978,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -5987,28 +5951,28 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F92" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G92" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="H92" s="3">
-        <v>46224</v>
+        <v>46171</v>
       </c>
       <c r="I92" s="3">
-        <v>46246</v>
+        <v>46190</v>
       </c>
       <c r="J92" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" s="3">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="M92" t="s">
         <v>6</v>
@@ -6017,7 +5981,7 @@
         <v>7</v>
       </c>
       <c r="O92" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P92" t="s">
         <v>9</v>
@@ -6028,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C93" s="2">
         <v>1</v>
@@ -6037,28 +6001,28 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F93" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="G93" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H93" s="3">
-        <v>46232</v>
+        <v>46171</v>
       </c>
       <c r="I93" s="3">
-        <v>46253</v>
+        <v>46190</v>
       </c>
       <c r="J93" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K93" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L93" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M93" t="s">
         <v>6</v>
@@ -6067,7 +6031,7 @@
         <v>7</v>
       </c>
       <c r="O93" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="P93" t="s">
         <v>9</v>
@@ -6078,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
@@ -6087,28 +6051,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="F94" t="s">
-        <v>224</v>
+        <v>69</v>
       </c>
       <c r="G94" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H94" s="3">
-        <v>46217</v>
+        <v>46237</v>
       </c>
       <c r="I94" s="3">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="J94" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K94" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L94" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M94" t="s">
         <v>6</v>
@@ -6117,7 +6081,7 @@
         <v>7</v>
       </c>
       <c r="O94" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="P94" t="s">
         <v>9</v>
@@ -6128,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
@@ -6137,28 +6101,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>68</v>
       </c>
       <c r="F95" t="s">
-        <v>293</v>
+        <v>69</v>
       </c>
       <c r="G95" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="H95" s="3">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="I95" s="3">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J95" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="K95" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L95" s="3">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="M95" t="s">
         <v>6</v>
@@ -6167,7 +6131,7 @@
         <v>7</v>
       </c>
       <c r="O95" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="P95" t="s">
         <v>9</v>
@@ -6178,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -6187,28 +6151,28 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="F96" t="s">
-        <v>96</v>
+        <v>286</v>
       </c>
       <c r="G96" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="H96" s="3">
-        <v>46135</v>
+        <v>46231</v>
       </c>
       <c r="I96" s="3">
-        <v>46162</v>
+        <v>46266</v>
       </c>
       <c r="J96" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K96" t="s">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="L96" s="3">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="M96" t="s">
         <v>6</v>
@@ -6217,7 +6181,7 @@
         <v>7</v>
       </c>
       <c r="O96" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="P96" t="s">
         <v>9</v>
@@ -6228,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -6237,22 +6201,22 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="F97" t="s">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="G97" s="3">
         <v>46113</v>
       </c>
       <c r="H97" s="3">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="I97" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="J97" t="s">
-        <v>153</v>
+        <v>241</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
@@ -6267,7 +6231,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="P97" t="s">
         <v>9</v>
@@ -6278,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -6287,28 +6251,28 @@
         <v>0</v>
       </c>
       <c r="E98" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G98" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H98" s="3">
-        <v>46171</v>
+        <v>46154</v>
       </c>
       <c r="I98" s="3">
-        <v>46190</v>
+        <v>46183</v>
       </c>
       <c r="J98" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M98" t="s">
         <v>6</v>
@@ -6317,7 +6281,7 @@
         <v>7</v>
       </c>
       <c r="O98" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P98" t="s">
         <v>9</v>
@@ -6328,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -6337,28 +6301,28 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F99" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G99" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H99" s="3">
-        <v>46171</v>
+        <v>46154</v>
       </c>
       <c r="I99" s="3">
-        <v>46190</v>
+        <v>46183</v>
       </c>
       <c r="J99" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M99" t="s">
         <v>6</v>
@@ -6367,7 +6331,7 @@
         <v>7</v>
       </c>
       <c r="O99" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P99" t="s">
         <v>9</v>
@@ -6378,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -6387,28 +6351,28 @@
         <v>0</v>
       </c>
       <c r="E100" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="F100" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G100" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H100" s="3">
-        <v>46237</v>
+        <v>46147</v>
       </c>
       <c r="I100" s="3">
-        <v>46254</v>
+        <v>46171</v>
       </c>
       <c r="J100" t="s">
-        <v>302</v>
+        <v>22</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" s="3">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="M100" t="s">
         <v>6</v>
@@ -6417,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="O100" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="P100" t="s">
         <v>9</v>
@@ -6428,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -6437,28 +6401,28 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="F101" t="s">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="G101" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H101" s="3">
-        <v>46237</v>
+        <v>46127</v>
       </c>
       <c r="I101" s="3">
-        <v>46254</v>
+        <v>46154</v>
       </c>
       <c r="J101" t="s">
-        <v>302</v>
+        <v>22</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="M101" t="s">
         <v>6</v>
@@ -6467,7 +6431,7 @@
         <v>7</v>
       </c>
       <c r="O101" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="P101" t="s">
         <v>9</v>
@@ -6478,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -6487,28 +6451,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>306</v>
+        <v>45</v>
       </c>
       <c r="F102" t="s">
-        <v>307</v>
+        <v>46</v>
       </c>
       <c r="G102" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H102" s="3">
-        <v>46231</v>
+        <v>46161</v>
       </c>
       <c r="I102" s="3">
-        <v>46266</v>
+        <v>46182</v>
       </c>
       <c r="J102" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" s="3">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M102" t="s">
         <v>6</v>
@@ -6517,7 +6481,7 @@
         <v>7</v>
       </c>
       <c r="O102" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P102" t="s">
         <v>9</v>
@@ -6528,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -6537,28 +6501,28 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="F103" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="G103" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="H103" s="3">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="I103" s="3">
-        <v>46196</v>
+        <v>46168</v>
       </c>
       <c r="J103" t="s">
-        <v>233</v>
+        <v>136</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="3">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="M103" t="s">
         <v>6</v>
@@ -6567,7 +6531,7 @@
         <v>7</v>
       </c>
       <c r="O103" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="P103" t="s">
         <v>9</v>
@@ -6578,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -6587,28 +6551,28 @@
         <v>0</v>
       </c>
       <c r="E104" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="F104" t="s">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="G104" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H104" s="3">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="I104" s="3">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="J104" t="s">
-        <v>261</v>
+        <v>65</v>
       </c>
       <c r="K104" t="s">
         <v>5</v>
       </c>
       <c r="L104" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M104" t="s">
         <v>6</v>
@@ -6617,7 +6581,7 @@
         <v>7</v>
       </c>
       <c r="O104" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P104" t="s">
         <v>9</v>
@@ -6628,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -6637,28 +6601,28 @@
         <v>0</v>
       </c>
       <c r="E105" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="F105" t="s">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="G105" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H105" s="3">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="I105" s="3">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="J105" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="K105" t="s">
         <v>5</v>
       </c>
       <c r="L105" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M105" t="s">
         <v>6</v>
@@ -6667,7 +6631,7 @@
         <v>7</v>
       </c>
       <c r="O105" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P105" t="s">
         <v>9</v>
@@ -6678,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -6687,28 +6651,28 @@
         <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>50</v>
+        <v>309</v>
       </c>
       <c r="F106" t="s">
-        <v>51</v>
+        <v>310</v>
       </c>
       <c r="G106" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H106" s="3">
-        <v>46161</v>
+        <v>46148</v>
       </c>
       <c r="I106" s="3">
         <v>46182</v>
       </c>
       <c r="J106" t="s">
-        <v>315</v>
+        <v>22</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" s="3">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="M106" t="s">
         <v>6</v>
@@ -6717,7 +6681,7 @@
         <v>7</v>
       </c>
       <c r="O106" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P106" t="s">
         <v>9</v>
@@ -6728,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -6737,28 +6701,28 @@
         <v>0</v>
       </c>
       <c r="E107" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F107" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G107" s="3">
         <v>46122</v>
       </c>
       <c r="H107" s="3">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="I107" s="3">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="J107" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" s="3">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="M107" t="s">
         <v>6</v>
@@ -6767,7 +6731,7 @@
         <v>7</v>
       </c>
       <c r="O107" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="P107" t="s">
         <v>9</v>
@@ -6778,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -6787,28 +6751,28 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>50</v>
+        <v>313</v>
       </c>
       <c r="F108" t="s">
-        <v>51</v>
+        <v>314</v>
       </c>
       <c r="G108" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H108" s="3">
-        <v>46161</v>
+        <v>46142</v>
       </c>
       <c r="I108" s="3">
-        <v>46182</v>
+        <v>46168</v>
       </c>
       <c r="J108" t="s">
-        <v>315</v>
+        <v>22</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" s="3">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="M108" t="s">
         <v>6</v>
@@ -6817,7 +6781,7 @@
         <v>7</v>
       </c>
       <c r="O108" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="P108" t="s">
         <v>9</v>
@@ -6828,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -6837,28 +6801,28 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>123</v>
+        <v>319</v>
       </c>
       <c r="F109" t="s">
-        <v>124</v>
+        <v>320</v>
       </c>
       <c r="G109" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="H109" s="3">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="I109" s="3">
-        <v>46168</v>
+        <v>46196</v>
       </c>
       <c r="J109" t="s">
-        <v>315</v>
+        <v>22</v>
       </c>
       <c r="K109" t="s">
         <v>5</v>
       </c>
       <c r="L109" s="3">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="M109" t="s">
         <v>6</v>
@@ -6867,7 +6831,7 @@
         <v>7</v>
       </c>
       <c r="O109" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P109" t="s">
         <v>9</v>
@@ -6878,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -6887,28 +6851,28 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="F110" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="G110" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="H110" s="3">
-        <v>46167</v>
+        <v>46146</v>
       </c>
       <c r="I110" s="3">
-        <v>46189</v>
+        <v>46170</v>
       </c>
       <c r="J110" t="s">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="M110" t="s">
         <v>6</v>
@@ -6917,7 +6881,7 @@
         <v>7</v>
       </c>
       <c r="O110" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="P110" t="s">
         <v>9</v>
@@ -6928,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -6937,28 +6901,28 @@
         <v>0</v>
       </c>
       <c r="E111" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="F111" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="G111" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="H111" s="3">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="I111" s="3">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="J111" t="s">
-        <v>315</v>
+        <v>195</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="M111" t="s">
         <v>6</v>
@@ -6967,7 +6931,7 @@
         <v>7</v>
       </c>
       <c r="O111" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P111" t="s">
         <v>9</v>
@@ -6978,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -6987,28 +6951,28 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
       <c r="F112" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="G112" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H112" s="3">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="I112" s="3">
-        <v>46188</v>
+        <v>46171</v>
       </c>
       <c r="J112" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="K112" t="s">
         <v>5</v>
       </c>
       <c r="L112" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M112" t="s">
         <v>6</v>
@@ -7017,7 +6981,7 @@
         <v>7</v>
       </c>
       <c r="O112" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="P112" t="s">
         <v>9</v>
@@ -7028,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -7037,28 +7001,28 @@
         <v>0</v>
       </c>
       <c r="E113" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="F113" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="G113" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="H113" s="3">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="I113" s="3">
-        <v>46168</v>
+        <v>46195</v>
       </c>
       <c r="J113" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="3">
-        <v>46122</v>
+        <v>46133</v>
       </c>
       <c r="M113" t="s">
         <v>6</v>
@@ -7067,7 +7031,7 @@
         <v>7</v>
       </c>
       <c r="O113" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="P113" t="s">
         <v>9</v>
@@ -7078,7 +7042,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
@@ -7087,28 +7051,28 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="F114" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="G114" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="H114" s="3">
-        <v>46142</v>
+        <v>46174</v>
       </c>
       <c r="I114" s="3">
-        <v>46168</v>
+        <v>46195</v>
       </c>
       <c r="J114" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="M114" t="s">
         <v>6</v>
@@ -7117,7 +7081,7 @@
         <v>7</v>
       </c>
       <c r="O114" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="P114" t="s">
         <v>9</v>
@@ -7128,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C115" s="2">
         <v>1</v>
@@ -7137,28 +7101,28 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>341</v>
+        <v>200</v>
       </c>
       <c r="F115" t="s">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="G115" s="3">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="H115" s="3">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="I115" s="3">
-        <v>46196</v>
+        <v>46171</v>
       </c>
       <c r="J115" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" s="3">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="M115" t="s">
         <v>6</v>
@@ -7167,7 +7131,7 @@
         <v>7</v>
       </c>
       <c r="O115" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="P115" t="s">
         <v>9</v>
@@ -7178,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
@@ -7187,28 +7151,28 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="F116" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="G116" s="3">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="H116" s="3">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="I116" s="3">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="J116" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="K116" t="s">
         <v>5</v>
       </c>
       <c r="L116" s="3">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="M116" t="s">
         <v>6</v>
@@ -7217,7 +7181,7 @@
         <v>7</v>
       </c>
       <c r="O116" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="P116" t="s">
         <v>9</v>
@@ -7228,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -7237,28 +7201,28 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="F117" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="G117" s="3">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="H117" s="3">
-        <v>46127</v>
+        <v>46146</v>
       </c>
       <c r="I117" s="3">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="J117" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="K117" t="s">
         <v>5</v>
       </c>
       <c r="L117" s="3">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="M117" t="s">
         <v>6</v>
@@ -7267,7 +7231,7 @@
         <v>7</v>
       </c>
       <c r="O117" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="P117" t="s">
         <v>9</v>
@@ -7278,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
@@ -7287,28 +7251,28 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="F118" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="G118" s="3">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="H118" s="3">
-        <v>46182</v>
+        <v>46191</v>
       </c>
       <c r="I118" s="3">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="J118" t="s">
-        <v>218</v>
+        <v>341</v>
       </c>
       <c r="K118" t="s">
         <v>5</v>
       </c>
       <c r="L118" s="3">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="M118" t="s">
         <v>6</v>
@@ -7317,7 +7281,7 @@
         <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="P118" t="s">
         <v>9</v>
@@ -7328,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -7337,28 +7301,28 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="F119" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="G119" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="H119" s="3">
-        <v>46174</v>
+        <v>46191</v>
       </c>
       <c r="I119" s="3">
-        <v>46195</v>
+        <v>46245</v>
       </c>
       <c r="J119" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="K119" t="s">
         <v>5</v>
       </c>
       <c r="L119" s="3">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="M119" t="s">
         <v>6</v>
@@ -7367,7 +7331,7 @@
         <v>7</v>
       </c>
       <c r="O119" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="P119" t="s">
         <v>9</v>
@@ -7378,7 +7342,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -7387,28 +7351,28 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="F120" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="G120" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="H120" s="3">
-        <v>46174</v>
+        <v>46155</v>
       </c>
       <c r="I120" s="3">
-        <v>46195</v>
+        <v>46178</v>
       </c>
       <c r="J120" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="M120" t="s">
         <v>6</v>
@@ -7417,7 +7381,7 @@
         <v>7</v>
       </c>
       <c r="O120" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="P120" t="s">
         <v>9</v>
@@ -7428,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -7437,28 +7401,28 @@
         <v>0</v>
       </c>
       <c r="E121" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="F121" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="G121" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="H121" s="3">
-        <v>46174</v>
+        <v>46155</v>
       </c>
       <c r="I121" s="3">
-        <v>46195</v>
+        <v>46178</v>
       </c>
       <c r="J121" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" s="3">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="M121" t="s">
         <v>6</v>
@@ -7467,7 +7431,7 @@
         <v>7</v>
       </c>
       <c r="O121" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="P121" t="s">
         <v>9</v>
@@ -7478,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -7487,28 +7451,28 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="F122" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="G122" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="H122" s="3">
-        <v>46139</v>
+        <v>46155</v>
       </c>
       <c r="I122" s="3">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="J122" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="K122" t="s">
         <v>5</v>
       </c>
       <c r="L122" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="M122" t="s">
         <v>6</v>
@@ -7517,7 +7481,7 @@
         <v>7</v>
       </c>
       <c r="O122" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="P122" t="s">
         <v>9</v>
@@ -7528,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
@@ -7537,28 +7501,28 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="F123" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="G123" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="H123" s="3">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="I123" s="3">
-        <v>46198</v>
+        <v>46213</v>
       </c>
       <c r="J123" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="M123" t="s">
         <v>6</v>
@@ -7567,7 +7531,7 @@
         <v>7</v>
       </c>
       <c r="O123" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="P123" t="s">
         <v>9</v>
@@ -7578,7 +7542,7 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
@@ -7587,28 +7551,28 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="F124" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G124" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H124" s="3">
-        <v>46146</v>
+        <v>46189</v>
       </c>
       <c r="I124" s="3">
-        <v>46167</v>
+        <v>46213</v>
       </c>
       <c r="J124" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="K124" t="s">
         <v>5</v>
       </c>
       <c r="L124" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M124" t="s">
         <v>6</v>
@@ -7617,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="O124" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="P124" t="s">
         <v>9</v>
@@ -7628,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -7637,28 +7601,28 @@
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="F125" t="s">
-        <v>366</v>
+        <v>314</v>
       </c>
       <c r="G125" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="H125" s="3">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="I125" s="3">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="J125" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="K125" t="s">
         <v>5</v>
       </c>
       <c r="L125" s="3">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="M125" t="s">
         <v>6</v>
@@ -7667,7 +7631,7 @@
         <v>7</v>
       </c>
       <c r="O125" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="P125" t="s">
         <v>9</v>
@@ -7678,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -7687,28 +7651,28 @@
         <v>0</v>
       </c>
       <c r="E126" t="s">
-        <v>365</v>
+        <v>45</v>
       </c>
       <c r="F126" t="s">
-        <v>366</v>
+        <v>46</v>
       </c>
       <c r="G126" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="H126" s="3">
-        <v>46191</v>
+        <v>46206</v>
       </c>
       <c r="I126" s="3">
-        <v>46245</v>
+        <v>46225</v>
       </c>
       <c r="J126" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="K126" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="M126" t="s">
         <v>6</v>
@@ -7717,7 +7681,7 @@
         <v>7</v>
       </c>
       <c r="O126" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="P126" t="s">
         <v>9</v>
@@ -7728,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -7737,28 +7701,28 @@
         <v>0</v>
       </c>
       <c r="E127" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="F127" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="G127" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H127" s="3">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="I127" s="3">
-        <v>46178</v>
+        <v>46241</v>
       </c>
       <c r="J127" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="K127" t="s">
         <v>5</v>
       </c>
       <c r="L127" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M127" t="s">
         <v>6</v>
@@ -7767,7 +7731,7 @@
         <v>7</v>
       </c>
       <c r="O127" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="P127" t="s">
         <v>9</v>
@@ -7778,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C128" s="2">
         <v>1</v>
@@ -7787,28 +7751,28 @@
         <v>0</v>
       </c>
       <c r="E128" t="s">
-        <v>335</v>
+        <v>94</v>
       </c>
       <c r="F128" t="s">
-        <v>336</v>
+        <v>95</v>
       </c>
       <c r="G128" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H128" s="3">
-        <v>46155</v>
+        <v>46267</v>
       </c>
       <c r="I128" s="3">
-        <v>46178</v>
+        <v>46353</v>
       </c>
       <c r="J128" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K128" t="s">
         <v>5</v>
       </c>
       <c r="L128" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M128" t="s">
         <v>6</v>
@@ -7817,7 +7781,7 @@
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="P128" t="s">
         <v>9</v>
@@ -7828,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
@@ -7837,28 +7801,28 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>335</v>
+        <v>132</v>
       </c>
       <c r="F129" t="s">
-        <v>336</v>
+        <v>133</v>
       </c>
       <c r="G129" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H129" s="3">
-        <v>46155</v>
+        <v>46196</v>
       </c>
       <c r="I129" s="3">
-        <v>46178</v>
+        <v>46230</v>
       </c>
       <c r="J129" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="K129" t="s">
         <v>5</v>
       </c>
       <c r="L129" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M129" t="s">
         <v>6</v>
@@ -7867,7 +7831,7 @@
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="P129" t="s">
         <v>9</v>
@@ -7878,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -7887,28 +7851,28 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>335</v>
+        <v>235</v>
       </c>
       <c r="F130" t="s">
-        <v>336</v>
+        <v>236</v>
       </c>
       <c r="G130" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="H130" s="3">
-        <v>46189</v>
+        <v>46203</v>
       </c>
       <c r="I130" s="3">
-        <v>46213</v>
+        <v>46225</v>
       </c>
       <c r="J130" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M130" t="s">
         <v>6</v>
@@ -7917,7 +7881,7 @@
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="P130" t="s">
         <v>9</v>
@@ -7928,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -7937,28 +7901,28 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="F131" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="G131" s="3">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="H131" s="3">
-        <v>46189</v>
+        <v>46283</v>
       </c>
       <c r="I131" s="3">
-        <v>46213</v>
+        <v>46316</v>
       </c>
       <c r="J131" t="s">
-        <v>276</v>
+        <v>170</v>
       </c>
       <c r="K131" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="3">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="M131" t="s">
         <v>6</v>
@@ -7967,7 +7931,7 @@
         <v>7</v>
       </c>
       <c r="O131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P131" t="s">
         <v>9</v>
@@ -7978,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -7987,28 +7951,28 @@
         <v>0</v>
       </c>
       <c r="E132" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="F132" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="G132" s="3">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="H132" s="3">
-        <v>46189</v>
+        <v>46205</v>
       </c>
       <c r="I132" s="3">
-        <v>46213</v>
+        <v>46287</v>
       </c>
       <c r="J132" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" s="3">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="M132" t="s">
         <v>6</v>
@@ -8017,7 +7981,7 @@
         <v>7</v>
       </c>
       <c r="O132" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P132" t="s">
         <v>9</v>
@@ -8028,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -8037,28 +8001,28 @@
         <v>0</v>
       </c>
       <c r="E133" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="F133" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="G133" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="H133" s="3">
-        <v>46206</v>
+        <v>46161</v>
       </c>
       <c r="I133" s="3">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="J133" t="s">
-        <v>302</v>
+        <v>173</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" s="3">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="M133" t="s">
         <v>6</v>
@@ -8067,7 +8031,7 @@
         <v>7</v>
       </c>
       <c r="O133" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P133" t="s">
         <v>9</v>
@@ -8078,46 +8042,46 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
+        <v>375</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
+      <c r="D134" s="2">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s">
+        <v>376</v>
+      </c>
+      <c r="F134" t="s">
+        <v>377</v>
+      </c>
+      <c r="G134" s="3">
+        <v>46154</v>
+      </c>
+      <c r="H134" s="3">
+        <v>46206</v>
+      </c>
+      <c r="I134" s="3">
+        <v>46297</v>
+      </c>
+      <c r="J134" t="s">
+        <v>281</v>
+      </c>
+      <c r="K134" t="s">
+        <v>5</v>
+      </c>
+      <c r="L134" s="3">
+        <v>46154</v>
+      </c>
+      <c r="M134" t="s">
+        <v>6</v>
+      </c>
+      <c r="N134" t="s">
+        <v>7</v>
+      </c>
+      <c r="O134" t="s">
         <v>378</v>
-      </c>
-      <c r="C134" s="2">
-        <v>1</v>
-      </c>
-      <c r="D134" s="2">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
-        <v>379</v>
-      </c>
-      <c r="F134" t="s">
-        <v>380</v>
-      </c>
-      <c r="G134" s="3">
-        <v>46148</v>
-      </c>
-      <c r="H134" s="3">
-        <v>46175</v>
-      </c>
-      <c r="I134" s="3">
-        <v>46241</v>
-      </c>
-      <c r="J134" t="s">
-        <v>302</v>
-      </c>
-      <c r="K134" t="s">
-        <v>5</v>
-      </c>
-      <c r="L134" s="3">
-        <v>46148</v>
-      </c>
-      <c r="M134" t="s">
-        <v>6</v>
-      </c>
-      <c r="N134" t="s">
-        <v>7</v>
-      </c>
-      <c r="O134" t="s">
-        <v>381</v>
       </c>
       <c r="P134" t="s">
         <v>9</v>
@@ -8128,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
@@ -8137,28 +8101,28 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="F135" t="s">
-        <v>112</v>
+        <v>310</v>
       </c>
       <c r="G135" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="H135" s="3">
-        <v>46267</v>
+        <v>46213</v>
       </c>
       <c r="I135" s="3">
-        <v>46353</v>
+        <v>46238</v>
       </c>
       <c r="J135" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="K135" t="s">
         <v>5</v>
       </c>
       <c r="L135" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="M135" t="s">
         <v>6</v>
@@ -8167,7 +8131,7 @@
         <v>7</v>
       </c>
       <c r="O135" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="P135" t="s">
         <v>9</v>
@@ -8178,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -8187,28 +8151,28 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="F136" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="G136" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="H136" s="3">
-        <v>46196</v>
+        <v>46339</v>
       </c>
       <c r="I136" s="3">
-        <v>46230</v>
+        <v>46358</v>
       </c>
       <c r="J136" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="K136" t="s">
         <v>5</v>
       </c>
       <c r="L136" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="M136" t="s">
         <v>6</v>
@@ -8217,7 +8181,7 @@
         <v>7</v>
       </c>
       <c r="O136" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P136" t="s">
         <v>9</v>
@@ -8228,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
@@ -8243,22 +8207,22 @@
         <v>46</v>
       </c>
       <c r="G137" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="H137" s="3">
-        <v>46203</v>
+        <v>46339</v>
       </c>
       <c r="I137" s="3">
-        <v>46225</v>
+        <v>46358</v>
       </c>
       <c r="J137" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
       </c>
       <c r="L137" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="M137" t="s">
         <v>6</v>
@@ -8267,7 +8231,7 @@
         <v>7</v>
       </c>
       <c r="O137" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="P137" t="s">
         <v>9</v>
@@ -8278,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
@@ -8287,28 +8251,28 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>389</v>
+        <v>313</v>
       </c>
       <c r="F138" t="s">
-        <v>390</v>
+        <v>314</v>
       </c>
       <c r="G138" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="H138" s="3">
-        <v>46282</v>
+        <v>46171</v>
       </c>
       <c r="I138" s="3">
-        <v>46316</v>
+        <v>46198</v>
       </c>
       <c r="J138" t="s">
-        <v>193</v>
+        <v>279</v>
       </c>
       <c r="K138" t="s">
         <v>5</v>
       </c>
       <c r="L138" s="3">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="M138" t="s">
         <v>6</v>
@@ -8317,7 +8281,7 @@
         <v>7</v>
       </c>
       <c r="O138" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="P138" t="s">
         <v>9</v>
@@ -8325,10 +8289,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B139" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
@@ -8337,10 +8301,10 @@
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F139" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G139" s="3">
         <v>46043</v>
@@ -8352,10 +8316,10 @@
         <v>46057</v>
       </c>
       <c r="J139" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="K139" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="L139" s="3">
         <v>46043</v>
@@ -8364,10 +8328,10 @@
         <v>6</v>
       </c>
       <c r="N139" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O139" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="P139" t="s">
         <v>9</v>
@@ -8375,49 +8339,49 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
+        <v>387</v>
+      </c>
+      <c r="B140" t="s">
+        <v>395</v>
+      </c>
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0</v>
+      </c>
+      <c r="E140" t="s">
+        <v>396</v>
+      </c>
+      <c r="F140" t="s">
+        <v>397</v>
+      </c>
+      <c r="G140" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H140" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I140" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J140" t="s">
+        <v>178</v>
+      </c>
+      <c r="K140" t="s">
         <v>392</v>
       </c>
-      <c r="B140" t="s">
-        <v>400</v>
-      </c>
-      <c r="C140" s="2">
-        <v>1</v>
-      </c>
-      <c r="D140" s="2">
-        <v>0</v>
-      </c>
-      <c r="E140" t="s">
-        <v>401</v>
-      </c>
-      <c r="F140" t="s">
-        <v>402</v>
-      </c>
-      <c r="G140" s="3">
-        <v>46057</v>
-      </c>
-      <c r="H140" s="3">
-        <v>46076</v>
-      </c>
-      <c r="I140" s="3">
-        <v>46083</v>
-      </c>
-      <c r="J140" t="s">
-        <v>13</v>
-      </c>
-      <c r="K140" t="s">
-        <v>397</v>
-      </c>
       <c r="L140" s="3">
-        <v>46057</v>
+        <v>46114</v>
       </c>
       <c r="M140" t="s">
         <v>6</v>
       </c>
       <c r="N140" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O140" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="P140" t="s">
         <v>9</v>
@@ -8425,151 +8389,51 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
+        <v>387</v>
+      </c>
+      <c r="B141" t="s">
+        <v>398</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s">
+        <v>399</v>
+      </c>
+      <c r="F141" t="s">
+        <v>400</v>
+      </c>
+      <c r="G141" s="3">
+        <v>46140</v>
+      </c>
+      <c r="H141" s="3">
+        <v>46140</v>
+      </c>
+      <c r="I141" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J141" t="s">
+        <v>178</v>
+      </c>
+      <c r="K141" t="s">
         <v>392</v>
       </c>
-      <c r="B141" t="s">
-        <v>403</v>
-      </c>
-      <c r="C141" s="2">
-        <v>1</v>
-      </c>
-      <c r="D141" s="2">
-        <v>0</v>
-      </c>
-      <c r="E141" t="s">
-        <v>404</v>
-      </c>
-      <c r="F141" t="s">
-        <v>405</v>
-      </c>
-      <c r="G141" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H141" s="3">
-        <v>46148</v>
-      </c>
-      <c r="I141" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J141" t="s">
-        <v>276</v>
-      </c>
-      <c r="K141" t="s">
-        <v>397</v>
-      </c>
       <c r="L141" s="3">
-        <v>46114</v>
+        <v>46140</v>
       </c>
       <c r="M141" t="s">
         <v>6</v>
       </c>
       <c r="N141" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O141" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="P141" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
-      <c r="A142" t="s">
-        <v>392</v>
-      </c>
-      <c r="B142" t="s">
-        <v>406</v>
-      </c>
-      <c r="C142" s="2">
-        <v>1</v>
-      </c>
-      <c r="D142" s="2">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
-        <v>407</v>
-      </c>
-      <c r="F142" t="s">
-        <v>408</v>
-      </c>
-      <c r="G142" s="3">
-        <v>46135</v>
-      </c>
-      <c r="H142" s="3">
-        <v>46135</v>
-      </c>
-      <c r="I142" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J142" t="s">
-        <v>409</v>
-      </c>
-      <c r="K142" t="s">
-        <v>397</v>
-      </c>
-      <c r="L142" s="3">
-        <v>46135</v>
-      </c>
-      <c r="M142" t="s">
-        <v>6</v>
-      </c>
-      <c r="N142" t="s">
-        <v>398</v>
-      </c>
-      <c r="O142" t="s">
-        <v>399</v>
-      </c>
-      <c r="P142" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
-      <c r="A143" t="s">
-        <v>392</v>
-      </c>
-      <c r="B143" t="s">
-        <v>410</v>
-      </c>
-      <c r="C143" s="2">
-        <v>1</v>
-      </c>
-      <c r="D143" s="2">
-        <v>0</v>
-      </c>
-      <c r="E143" t="s">
-        <v>411</v>
-      </c>
-      <c r="F143" t="s">
-        <v>412</v>
-      </c>
-      <c r="G143" s="3">
-        <v>46140</v>
-      </c>
-      <c r="H143" s="3">
-        <v>46140</v>
-      </c>
-      <c r="I143" s="3">
-        <v>46147</v>
-      </c>
-      <c r="J143" t="s">
-        <v>276</v>
-      </c>
-      <c r="K143" t="s">
-        <v>397</v>
-      </c>
-      <c r="L143" s="3">
-        <v>46140</v>
-      </c>
-      <c r="M143" t="s">
-        <v>6</v>
-      </c>
-      <c r="N143" t="s">
-        <v>398</v>
-      </c>
-      <c r="O143" t="s">
-        <v>399</v>
-      </c>
-      <c r="P143" t="s">
         <v>9</v>
       </c>
     </row>
